--- a/research/traditional_assets/database/data/netherlands/netherlands_transportation.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_transportation.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="enxtam_pnl" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,46 +590,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0274</v>
+        <v>0.0278</v>
+      </c>
+      <c r="E2">
+        <v>-0.2</v>
       </c>
       <c r="F2">
-        <v>0.279</v>
+        <v>-0.0239</v>
       </c>
       <c r="G2">
-        <v>-0.400047838306524</v>
+        <v>0.04108210832262031</v>
       </c>
       <c r="H2">
-        <v>-0.400047838306524</v>
+        <v>0.04108210832262031</v>
       </c>
       <c r="I2">
-        <v>-0.4126651916522155</v>
+        <v>0.01436476440668493</v>
       </c>
       <c r="J2">
-        <v>-0.4126651916522155</v>
+        <v>0.007182382203342463</v>
       </c>
       <c r="K2">
-        <v>-1028.8</v>
+        <v>21.2</v>
       </c>
       <c r="L2">
-        <v>-0.3076003109489924</v>
+        <v>0.005924766642445923</v>
       </c>
       <c r="M2">
-        <v>30.7</v>
+        <v>24.6</v>
       </c>
       <c r="N2">
-        <v>0.03977199119056873</v>
+        <v>0.04541258999446188</v>
       </c>
       <c r="O2">
-        <v>-0.02984059097978227</v>
+        <v>1.160377358490566</v>
       </c>
       <c r="P2">
-        <v>30.7</v>
+        <v>24.6</v>
       </c>
       <c r="Q2">
-        <v>0.03977199119056873</v>
+        <v>0.04541258999446188</v>
       </c>
       <c r="R2">
-        <v>-0.02984059097978227</v>
+        <v>1.160377358490566</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,70 +641,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>443.5</v>
+        <v>781.5</v>
       </c>
       <c r="V2">
-        <v>0.5745562896748284</v>
+        <v>1.442680450433819</v>
       </c>
       <c r="W2">
-        <v>-8.006225680933852</v>
+        <v>0.1267942583732057</v>
       </c>
       <c r="X2">
-        <v>0.1164195850200985</v>
+        <v>0.1500943537698408</v>
       </c>
       <c r="Y2">
-        <v>-8.122645265953951</v>
+        <v>-0.02330009539663502</v>
       </c>
       <c r="Z2">
-        <v>7.164952870608398</v>
+        <v>5.910472414932276</v>
       </c>
       <c r="AA2">
-        <v>-2.956726649528707</v>
+        <v>0.04245127188635613</v>
       </c>
       <c r="AB2">
-        <v>0.07133141363988574</v>
+        <v>0.07259139955865312</v>
       </c>
       <c r="AC2">
-        <v>-3.028058063168592</v>
+        <v>-0.030140127672297</v>
       </c>
       <c r="AD2">
-        <v>1100.8</v>
+        <v>1413.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1100.8</v>
+        <v>1413.4</v>
       </c>
       <c r="AG2">
-        <v>657.3</v>
+        <v>631.9000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.587814385646393</v>
+        <v>0.7229297734131247</v>
       </c>
       <c r="AI2">
-        <v>0.8667034091803795</v>
+        <v>0.8921853301350839</v>
       </c>
       <c r="AJ2">
-        <v>0.4599076406381192</v>
+        <v>0.5384287661895024</v>
       </c>
       <c r="AK2">
-        <v>0.7951850955722236</v>
+        <v>0.7872181387816122</v>
       </c>
       <c r="AL2">
-        <v>14.8</v>
+        <v>27.9</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-1.100000000000001</v>
       </c>
       <c r="AN2">
-        <v>-0.8387686680889972</v>
+        <v>11.71973466003317</v>
       </c>
       <c r="AO2">
-        <v>-93.25675675675676</v>
+        <v>1.842293906810036</v>
       </c>
       <c r="AP2">
-        <v>-0.5008381590978359</v>
+        <v>5.239635157545607</v>
+      </c>
+      <c r="AQ2">
+        <v>-46.72727272727266</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +727,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0274</v>
+        <v>0.0278</v>
+      </c>
+      <c r="E3">
+        <v>-0.2</v>
       </c>
       <c r="F3">
-        <v>0.279</v>
+        <v>-0.0239</v>
       </c>
       <c r="G3">
-        <v>-0.400047838306524</v>
+        <v>0.04108210832262031</v>
       </c>
       <c r="H3">
-        <v>-0.400047838306524</v>
+        <v>0.04108210832262031</v>
       </c>
       <c r="I3">
-        <v>-0.4126651916522155</v>
+        <v>0.01436476440668493</v>
       </c>
       <c r="J3">
-        <v>-0.4126651916522155</v>
+        <v>0.007182382203342463</v>
       </c>
       <c r="K3">
-        <v>-1028.8</v>
+        <v>21.2</v>
       </c>
       <c r="L3">
-        <v>-0.3076003109489924</v>
+        <v>0.005924766642445923</v>
       </c>
       <c r="M3">
-        <v>30.7</v>
+        <v>24.6</v>
       </c>
       <c r="N3">
-        <v>0.03977199119056873</v>
+        <v>0.04541258999446188</v>
       </c>
       <c r="O3">
-        <v>-0.02984059097978227</v>
+        <v>1.160377358490566</v>
       </c>
       <c r="P3">
-        <v>30.7</v>
+        <v>24.6</v>
       </c>
       <c r="Q3">
-        <v>0.03977199119056873</v>
+        <v>0.04541258999446188</v>
       </c>
       <c r="R3">
-        <v>-0.02984059097978227</v>
+        <v>1.160377358490566</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,70 +778,8834 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>443.5</v>
+        <v>781.5</v>
       </c>
       <c r="V3">
-        <v>0.5745562896748284</v>
+        <v>1.442680450433819</v>
       </c>
       <c r="W3">
-        <v>-8.006225680933852</v>
+        <v>0.1267942583732057</v>
       </c>
       <c r="X3">
-        <v>0.1164195850200985</v>
+        <v>0.1500943537698408</v>
       </c>
       <c r="Y3">
-        <v>-8.122645265953951</v>
+        <v>-0.02330009539663502</v>
       </c>
       <c r="Z3">
-        <v>7.164952870608398</v>
+        <v>5.910472414932276</v>
       </c>
       <c r="AA3">
-        <v>-2.956726649528707</v>
+        <v>0.04245127188635613</v>
       </c>
       <c r="AB3">
-        <v>0.07133141363988574</v>
+        <v>0.07259139955865312</v>
       </c>
       <c r="AC3">
-        <v>-3.028058063168592</v>
+        <v>-0.030140127672297</v>
       </c>
       <c r="AD3">
-        <v>1100.8</v>
+        <v>1413.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1100.8</v>
+        <v>1413.4</v>
       </c>
       <c r="AG3">
-        <v>657.3</v>
+        <v>631.9000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.587814385646393</v>
+        <v>0.7229297734131247</v>
       </c>
       <c r="AI3">
-        <v>0.8667034091803795</v>
+        <v>0.8921853301350839</v>
       </c>
       <c r="AJ3">
-        <v>0.4599076406381192</v>
+        <v>0.5384287661895024</v>
       </c>
       <c r="AK3">
-        <v>0.7951850955722236</v>
+        <v>0.7872181387816122</v>
       </c>
       <c r="AL3">
-        <v>14.8</v>
+        <v>27.9</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-1.100000000000001</v>
       </c>
       <c r="AN3">
-        <v>-0.8387686680889972</v>
+        <v>11.71973466003317</v>
       </c>
       <c r="AO3">
-        <v>-93.25675675675676</v>
+        <v>1.842293906810036</v>
       </c>
       <c r="AP3">
-        <v>-0.5008381590978359</v>
+        <v>5.239635157545607</v>
+      </c>
+      <c r="AQ3">
+        <v>-46.72727272727266</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PostNL N.V. (ENXTAM:PNL)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ENXTAM:PNL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>-3.12186379928315</v>
+      </c>
+      <c r="F2">
+        <v>-9.75937460762216</v>
+      </c>
+      <c r="G2">
+        <v>11.7197346600332</v>
+      </c>
+      <c r="H2">
+        <v>0.162114427860697</v>
+      </c>
+      <c r="I2">
+        <v>0.722929773413125</v>
+      </c>
+      <c r="J2">
+        <v>0.01</v>
+      </c>
+      <c r="K2">
+        <v>541.7</v>
+      </c>
+      <c r="L2">
+        <v>1728.06946826041</v>
+      </c>
+      <c r="M2">
+        <v>1173.6</v>
+      </c>
+      <c r="N2">
+        <v>966.120468260414</v>
+      </c>
+      <c r="O2">
+        <v>1413.4</v>
+      </c>
+      <c r="P2">
+        <v>19.551</v>
+      </c>
+      <c r="Q2">
+        <v>0.0725913995586531</v>
+      </c>
+      <c r="R2">
+        <v>0.0904058086578748</v>
+      </c>
+      <c r="S2">
+        <v>0.0428876</v>
+      </c>
+      <c r="T2">
+        <v>0.86470440386681</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.150094353769841</v>
+      </c>
+      <c r="X2">
+        <v>0.0825846107264714</v>
+      </c>
+      <c r="Y2">
+        <v>2.4070970386428</v>
+      </c>
+      <c r="Z2">
+        <v>0.848982944395233</v>
+      </c>
+      <c r="AA2">
+        <v>1413.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.0578</v>
+      </c>
+      <c r="AC2">
+        <v>-3.121863799283154</v>
+      </c>
+      <c r="AD2">
+        <v>1413.4</v>
+      </c>
+      <c r="AE2">
+        <v>27.9</v>
+      </c>
+      <c r="AF2">
+        <v>207.7</v>
+      </c>
+      <c r="AG2">
+        <v>120.6</v>
+      </c>
+      <c r="AH2">
+        <v>6.938893903907228E-18</v>
+      </c>
+      <c r="AI2">
+        <v>0.0458</v>
+      </c>
+      <c r="AJ2">
+        <v>541.7</v>
+      </c>
+      <c r="AK2">
+        <v>0.043327855959079</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.258</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>44.69999999999997</v>
+      </c>
+      <c r="AR2">
+        <v>27.9</v>
+      </c>
+      <c r="AS2">
+        <v>1413.4</v>
+      </c>
+      <c r="AT2">
+        <v>781.5</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-1413.4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>781.5</v>
+      </c>
+      <c r="H2">
+        <v>541.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>160.8</v>
+      </c>
+      <c r="K2">
+        <v>207.7</v>
+      </c>
+      <c r="L2">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="O2">
+        <v>-12.1002</v>
+      </c>
+      <c r="P2">
+        <v>-34.7998</v>
+      </c>
+      <c r="Q2">
+        <v>172.9002</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0.05170000000000001</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09040580865787483</v>
+      </c>
+      <c r="C3">
+        <v>1728.069468260414</v>
+      </c>
+      <c r="D3">
+        <v>966.1204682604141</v>
+      </c>
+      <c r="E3">
+        <v>-1393.849</v>
+      </c>
+      <c r="F3">
+        <v>19.551</v>
+      </c>
+      <c r="G3">
+        <v>781.5</v>
+      </c>
+      <c r="H3">
+        <v>541.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>160.8</v>
+      </c>
+      <c r="K3">
+        <v>207.7</v>
+      </c>
+      <c r="L3">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M3">
+        <v>4.805635800000001</v>
+      </c>
+      <c r="N3">
+        <v>-51.70563580000001</v>
+      </c>
+      <c r="O3">
+        <v>-13.3400540364</v>
+      </c>
+      <c r="P3">
+        <v>-38.36558176360001</v>
+      </c>
+      <c r="Q3">
+        <v>169.3344182364</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08258461072647144</v>
+      </c>
+      <c r="T3">
+        <v>0.8489829443952331</v>
+      </c>
+      <c r="U3">
+        <v>0.2458</v>
+      </c>
+      <c r="V3">
+        <v>-2.517918648766517</v>
+      </c>
+      <c r="W3">
+        <v>0.8647044038668099</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>-9.759374607622158</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09240580865787482</v>
+      </c>
+      <c r="C4">
+        <v>1689.716226787631</v>
+      </c>
+      <c r="D4">
+        <v>947.3182267876309</v>
+      </c>
+      <c r="E4">
+        <v>-1374.298</v>
+      </c>
+      <c r="F4">
+        <v>39.102</v>
+      </c>
+      <c r="G4">
+        <v>781.5</v>
+      </c>
+      <c r="H4">
+        <v>541.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>160.8</v>
+      </c>
+      <c r="K4">
+        <v>207.7</v>
+      </c>
+      <c r="L4">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M4">
+        <v>9.611271600000002</v>
+      </c>
+      <c r="N4">
+        <v>-56.51127160000001</v>
+      </c>
+      <c r="O4">
+        <v>-14.5799080728</v>
+      </c>
+      <c r="P4">
+        <v>-41.93136352720001</v>
+      </c>
+      <c r="Q4">
+        <v>165.7686364728</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08295996389714971</v>
+      </c>
+      <c r="T4">
+        <v>0.8576460356645723</v>
+      </c>
+      <c r="U4">
+        <v>0.2458</v>
+      </c>
+      <c r="V4">
+        <v>-1.258959324383258</v>
+      </c>
+      <c r="W4">
+        <v>0.555252201933405</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>-4.879687303811079</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09440580865787482</v>
+      </c>
+      <c r="C5">
+        <v>1652.080857450208</v>
+      </c>
+      <c r="D5">
+        <v>929.2338574502085</v>
+      </c>
+      <c r="E5">
+        <v>-1354.747</v>
+      </c>
+      <c r="F5">
+        <v>58.653</v>
+      </c>
+      <c r="G5">
+        <v>781.5</v>
+      </c>
+      <c r="H5">
+        <v>541.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>160.8</v>
+      </c>
+      <c r="K5">
+        <v>207.7</v>
+      </c>
+      <c r="L5">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M5">
+        <v>14.4169074</v>
+      </c>
+      <c r="N5">
+        <v>-61.31690740000001</v>
+      </c>
+      <c r="O5">
+        <v>-15.8197621092</v>
+      </c>
+      <c r="P5">
+        <v>-45.49714529080001</v>
+      </c>
+      <c r="Q5">
+        <v>162.2028547092</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08334305630846055</v>
+      </c>
+      <c r="T5">
+        <v>0.8664877473724546</v>
+      </c>
+      <c r="U5">
+        <v>0.2458</v>
+      </c>
+      <c r="V5">
+        <v>-0.8393062162555057</v>
+      </c>
+      <c r="W5">
+        <v>0.4521014679556033</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>-3.253124869207387</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09640580865787482</v>
+      </c>
+      <c r="C6">
+        <v>1615.12301770644</v>
+      </c>
+      <c r="D6">
+        <v>911.8270177064396</v>
+      </c>
+      <c r="E6">
+        <v>-1335.196</v>
+      </c>
+      <c r="F6">
+        <v>78.20400000000001</v>
+      </c>
+      <c r="G6">
+        <v>781.5</v>
+      </c>
+      <c r="H6">
+        <v>541.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>160.8</v>
+      </c>
+      <c r="K6">
+        <v>207.7</v>
+      </c>
+      <c r="L6">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M6">
+        <v>19.2225432</v>
+      </c>
+      <c r="N6">
+        <v>-66.12254320000001</v>
+      </c>
+      <c r="O6">
+        <v>-17.0596161456</v>
+      </c>
+      <c r="P6">
+        <v>-49.06292705440001</v>
+      </c>
+      <c r="Q6">
+        <v>158.6370729456</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08373412981167368</v>
+      </c>
+      <c r="T6">
+        <v>0.8755136614075842</v>
+      </c>
+      <c r="U6">
+        <v>0.2458</v>
+      </c>
+      <c r="V6">
+        <v>-0.6294796621916292</v>
+      </c>
+      <c r="W6">
+        <v>0.4005261009667025</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>-2.43984365190554</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09840580865787485</v>
+      </c>
+      <c r="C7">
+        <v>1578.805332291052</v>
+      </c>
+      <c r="D7">
+        <v>895.0603322910517</v>
+      </c>
+      <c r="E7">
+        <v>-1315.645</v>
+      </c>
+      <c r="F7">
+        <v>97.75500000000001</v>
+      </c>
+      <c r="G7">
+        <v>781.5</v>
+      </c>
+      <c r="H7">
+        <v>541.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>160.8</v>
+      </c>
+      <c r="K7">
+        <v>207.7</v>
+      </c>
+      <c r="L7">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M7">
+        <v>24.02817900000001</v>
+      </c>
+      <c r="N7">
+        <v>-70.92817900000001</v>
+      </c>
+      <c r="O7">
+        <v>-18.299470182</v>
+      </c>
+      <c r="P7">
+        <v>-52.62870881800001</v>
+      </c>
+      <c r="Q7">
+        <v>155.071291182</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08413343644127025</v>
+      </c>
+      <c r="T7">
+        <v>0.8847295946855589</v>
+      </c>
+      <c r="U7">
+        <v>0.2458</v>
+      </c>
+      <c r="V7">
+        <v>-0.5035837297533033</v>
+      </c>
+      <c r="W7">
+        <v>0.369580880773362</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>-1.951874921524432</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1004058086578748</v>
+      </c>
+      <c r="C8">
+        <v>1543.093125329532</v>
+      </c>
+      <c r="D8">
+        <v>878.8991253295316</v>
+      </c>
+      <c r="E8">
+        <v>-1296.094</v>
+      </c>
+      <c r="F8">
+        <v>117.306</v>
+      </c>
+      <c r="G8">
+        <v>781.5</v>
+      </c>
+      <c r="H8">
+        <v>541.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>160.8</v>
+      </c>
+      <c r="K8">
+        <v>207.7</v>
+      </c>
+      <c r="L8">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M8">
+        <v>28.8338148</v>
+      </c>
+      <c r="N8">
+        <v>-75.7338148</v>
+      </c>
+      <c r="O8">
+        <v>-19.5393242184</v>
+      </c>
+      <c r="P8">
+        <v>-56.19449058160001</v>
+      </c>
+      <c r="Q8">
+        <v>151.5055094184</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.0845412389566029</v>
+      </c>
+      <c r="T8">
+        <v>0.8941416116502988</v>
+      </c>
+      <c r="U8">
+        <v>0.2458</v>
+      </c>
+      <c r="V8">
+        <v>-0.4196531081277529</v>
+      </c>
+      <c r="W8">
+        <v>0.3489507339778017</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>-1.626562434603693</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1024058086578748</v>
+      </c>
+      <c r="C9">
+        <v>1507.954180959384</v>
+      </c>
+      <c r="D9">
+        <v>863.3111809593836</v>
+      </c>
+      <c r="E9">
+        <v>-1276.543</v>
+      </c>
+      <c r="F9">
+        <v>136.857</v>
+      </c>
+      <c r="G9">
+        <v>781.5</v>
+      </c>
+      <c r="H9">
+        <v>541.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>160.8</v>
+      </c>
+      <c r="K9">
+        <v>207.7</v>
+      </c>
+      <c r="L9">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M9">
+        <v>33.63945060000001</v>
+      </c>
+      <c r="N9">
+        <v>-80.53945060000001</v>
+      </c>
+      <c r="O9">
+        <v>-20.7791782548</v>
+      </c>
+      <c r="P9">
+        <v>-59.76027234520001</v>
+      </c>
+      <c r="Q9">
+        <v>147.9397276548</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08495781141850185</v>
+      </c>
+      <c r="T9">
+        <v>0.9037560375820224</v>
+      </c>
+      <c r="U9">
+        <v>0.2458</v>
+      </c>
+      <c r="V9">
+        <v>-0.3597026641095024</v>
+      </c>
+      <c r="W9">
+        <v>0.3342149148381157</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>-1.394196372517451</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1044058086578748</v>
+      </c>
+      <c r="C10">
+        <v>1473.358528980859</v>
+      </c>
+      <c r="D10">
+        <v>848.2665289808591</v>
+      </c>
+      <c r="E10">
+        <v>-1256.992</v>
+      </c>
+      <c r="F10">
+        <v>156.408</v>
+      </c>
+      <c r="G10">
+        <v>781.5</v>
+      </c>
+      <c r="H10">
+        <v>541.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>160.8</v>
+      </c>
+      <c r="K10">
+        <v>207.7</v>
+      </c>
+      <c r="L10">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M10">
+        <v>38.44508640000001</v>
+      </c>
+      <c r="N10">
+        <v>-85.34508640000001</v>
+      </c>
+      <c r="O10">
+        <v>-22.01903229120001</v>
+      </c>
+      <c r="P10">
+        <v>-63.32605410880001</v>
+      </c>
+      <c r="Q10">
+        <v>144.3739458912</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08538343980348558</v>
+      </c>
+      <c r="T10">
+        <v>0.9135794727731313</v>
+      </c>
+      <c r="U10">
+        <v>0.2458</v>
+      </c>
+      <c r="V10">
+        <v>-0.3147398310958146</v>
+      </c>
+      <c r="W10">
+        <v>0.3231630504833513</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>-1.21992182595277</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1064058086578748</v>
+      </c>
+      <c r="C11">
+        <v>1439.278252536184</v>
+      </c>
+      <c r="D11">
+        <v>833.737252536184</v>
+      </c>
+      <c r="E11">
+        <v>-1237.441</v>
+      </c>
+      <c r="F11">
+        <v>175.959</v>
+      </c>
+      <c r="G11">
+        <v>781.5</v>
+      </c>
+      <c r="H11">
+        <v>541.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>160.8</v>
+      </c>
+      <c r="K11">
+        <v>207.7</v>
+      </c>
+      <c r="L11">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M11">
+        <v>43.25072220000001</v>
+      </c>
+      <c r="N11">
+        <v>-90.15072220000002</v>
+      </c>
+      <c r="O11">
+        <v>-23.25888632760001</v>
+      </c>
+      <c r="P11">
+        <v>-66.89183587240001</v>
+      </c>
+      <c r="Q11">
+        <v>140.8081641276</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08581842265846892</v>
+      </c>
+      <c r="T11">
+        <v>0.9236188076387701</v>
+      </c>
+      <c r="U11">
+        <v>0.2458</v>
+      </c>
+      <c r="V11">
+        <v>-0.2797687387518352</v>
+      </c>
+      <c r="W11">
+        <v>0.3145671559852011</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>-1.084374956402462</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1084058086578748</v>
+      </c>
+      <c r="C12">
+        <v>1405.687315220601</v>
+      </c>
+      <c r="D12">
+        <v>819.6973152206012</v>
+      </c>
+      <c r="E12">
+        <v>-1217.89</v>
+      </c>
+      <c r="F12">
+        <v>195.51</v>
+      </c>
+      <c r="G12">
+        <v>781.5</v>
+      </c>
+      <c r="H12">
+        <v>541.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>160.8</v>
+      </c>
+      <c r="K12">
+        <v>207.7</v>
+      </c>
+      <c r="L12">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M12">
+        <v>48.05635800000001</v>
+      </c>
+      <c r="N12">
+        <v>-94.95635800000002</v>
+      </c>
+      <c r="O12">
+        <v>-24.49874036400001</v>
+      </c>
+      <c r="P12">
+        <v>-70.45761763600001</v>
+      </c>
+      <c r="Q12">
+        <v>137.242382364</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08626307179911859</v>
+      </c>
+      <c r="T12">
+        <v>0.9338812388347566</v>
+      </c>
+      <c r="U12">
+        <v>0.2458</v>
+      </c>
+      <c r="V12">
+        <v>-0.2517918648766517</v>
+      </c>
+      <c r="W12">
+        <v>0.307690440386681</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>-0.975937460762216</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1104058086578748</v>
+      </c>
+      <c r="C13">
+        <v>1372.561405372577</v>
+      </c>
+      <c r="D13">
+        <v>806.1224053725774</v>
+      </c>
+      <c r="E13">
+        <v>-1198.339</v>
+      </c>
+      <c r="F13">
+        <v>215.061</v>
+      </c>
+      <c r="G13">
+        <v>781.5</v>
+      </c>
+      <c r="H13">
+        <v>541.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>160.8</v>
+      </c>
+      <c r="K13">
+        <v>207.7</v>
+      </c>
+      <c r="L13">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M13">
+        <v>52.86199380000001</v>
+      </c>
+      <c r="N13">
+        <v>-99.76199380000001</v>
+      </c>
+      <c r="O13">
+        <v>-25.7385944004</v>
+      </c>
+      <c r="P13">
+        <v>-74.02339939960001</v>
+      </c>
+      <c r="Q13">
+        <v>133.6766006004</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08671771305528846</v>
+      </c>
+      <c r="T13">
+        <v>0.9443742864621133</v>
+      </c>
+      <c r="U13">
+        <v>0.2458</v>
+      </c>
+      <c r="V13">
+        <v>-0.2289016953424106</v>
+      </c>
+      <c r="W13">
+        <v>0.3020640367151645</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>-0.8872158734201963</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1124058086578748</v>
+      </c>
+      <c r="C14">
+        <v>1339.877795584097</v>
+      </c>
+      <c r="D14">
+        <v>792.9897955840972</v>
+      </c>
+      <c r="E14">
+        <v>-1178.788</v>
+      </c>
+      <c r="F14">
+        <v>234.612</v>
+      </c>
+      <c r="G14">
+        <v>781.5</v>
+      </c>
+      <c r="H14">
+        <v>541.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>160.8</v>
+      </c>
+      <c r="K14">
+        <v>207.7</v>
+      </c>
+      <c r="L14">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M14">
+        <v>57.66762960000001</v>
+      </c>
+      <c r="N14">
+        <v>-104.5676296</v>
+      </c>
+      <c r="O14">
+        <v>-26.9784484368</v>
+      </c>
+      <c r="P14">
+        <v>-77.58918116320001</v>
+      </c>
+      <c r="Q14">
+        <v>130.1108188368</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08718268706728038</v>
+      </c>
+      <c r="T14">
+        <v>0.9551058124446374</v>
+      </c>
+      <c r="U14">
+        <v>0.2458</v>
+      </c>
+      <c r="V14">
+        <v>-0.2098265540638764</v>
+      </c>
+      <c r="W14">
+        <v>0.2973753669889008</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>-0.8132812173018464</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1144058086578748</v>
+      </c>
+      <c r="C15">
+        <v>1307.61521572321</v>
+      </c>
+      <c r="D15">
+        <v>780.2782157232094</v>
+      </c>
+      <c r="E15">
+        <v>-1159.237</v>
+      </c>
+      <c r="F15">
+        <v>254.163</v>
+      </c>
+      <c r="G15">
+        <v>781.5</v>
+      </c>
+      <c r="H15">
+        <v>541.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>160.8</v>
+      </c>
+      <c r="K15">
+        <v>207.7</v>
+      </c>
+      <c r="L15">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M15">
+        <v>62.47326540000002</v>
+      </c>
+      <c r="N15">
+        <v>-109.3732654</v>
+      </c>
+      <c r="O15">
+        <v>-28.2183024732</v>
+      </c>
+      <c r="P15">
+        <v>-81.15496292680001</v>
+      </c>
+      <c r="Q15">
+        <v>126.5450370732</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08765835013701923</v>
+      </c>
+      <c r="T15">
+        <v>0.966084040173886</v>
+      </c>
+      <c r="U15">
+        <v>0.2458</v>
+      </c>
+      <c r="V15">
+        <v>-0.1936860499051166</v>
+      </c>
+      <c r="W15">
+        <v>0.2934080310666777</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>-0.750721123663243</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1164058086578748</v>
+      </c>
+      <c r="C16">
+        <v>1275.75373797654</v>
+      </c>
+      <c r="D16">
+        <v>767.9677379765399</v>
+      </c>
+      <c r="E16">
+        <v>-1139.686</v>
+      </c>
+      <c r="F16">
+        <v>273.7140000000001</v>
+      </c>
+      <c r="G16">
+        <v>781.5</v>
+      </c>
+      <c r="H16">
+        <v>541.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>160.8</v>
+      </c>
+      <c r="K16">
+        <v>207.7</v>
+      </c>
+      <c r="L16">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M16">
+        <v>67.27890120000002</v>
+      </c>
+      <c r="N16">
+        <v>-114.1789012</v>
+      </c>
+      <c r="O16">
+        <v>-29.45815650960001</v>
+      </c>
+      <c r="P16">
+        <v>-84.72074469040001</v>
+      </c>
+      <c r="Q16">
+        <v>122.9792553096</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08814507513861247</v>
+      </c>
+      <c r="T16">
+        <v>0.9773175755247453</v>
+      </c>
+      <c r="U16">
+        <v>0.2458</v>
+      </c>
+      <c r="V16">
+        <v>-0.1798513320547512</v>
+      </c>
+      <c r="W16">
+        <v>0.2900074574190579</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>-0.6970981862587255</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1184058086578748</v>
+      </c>
+      <c r="C17">
+        <v>1244.274672604914</v>
+      </c>
+      <c r="D17">
+        <v>756.0396726049139</v>
+      </c>
+      <c r="E17">
+        <v>-1120.135</v>
+      </c>
+      <c r="F17">
+        <v>293.265</v>
+      </c>
+      <c r="G17">
+        <v>781.5</v>
+      </c>
+      <c r="H17">
+        <v>541.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>160.8</v>
+      </c>
+      <c r="K17">
+        <v>207.7</v>
+      </c>
+      <c r="L17">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M17">
+        <v>72.084537</v>
+      </c>
+      <c r="N17">
+        <v>-118.984537</v>
+      </c>
+      <c r="O17">
+        <v>-30.698010546</v>
+      </c>
+      <c r="P17">
+        <v>-88.286526454</v>
+      </c>
+      <c r="Q17">
+        <v>119.413473546</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08864325249318439</v>
+      </c>
+      <c r="T17">
+        <v>0.9888154293544481</v>
+      </c>
+      <c r="U17">
+        <v>0.2458</v>
+      </c>
+      <c r="V17">
+        <v>-0.1678612432511012</v>
+      </c>
+      <c r="W17">
+        <v>0.2870602935911207</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>-0.6506249738414773</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1204058086578748</v>
+      </c>
+      <c r="C18">
+        <v>1213.160473265132</v>
+      </c>
+      <c r="D18">
+        <v>744.4764732651321</v>
+      </c>
+      <c r="E18">
+        <v>-1100.584</v>
+      </c>
+      <c r="F18">
+        <v>312.816</v>
+      </c>
+      <c r="G18">
+        <v>781.5</v>
+      </c>
+      <c r="H18">
+        <v>541.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>160.8</v>
+      </c>
+      <c r="K18">
+        <v>207.7</v>
+      </c>
+      <c r="L18">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M18">
+        <v>76.89017280000002</v>
+      </c>
+      <c r="N18">
+        <v>-123.7901728</v>
+      </c>
+      <c r="O18">
+        <v>-31.93786458240001</v>
+      </c>
+      <c r="P18">
+        <v>-91.85230821760001</v>
+      </c>
+      <c r="Q18">
+        <v>115.8476917824</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.08915329121334134</v>
+      </c>
+      <c r="T18">
+        <v>1.000587041608668</v>
+      </c>
+      <c r="U18">
+        <v>0.2458</v>
+      </c>
+      <c r="V18">
+        <v>-0.1573699155479073</v>
+      </c>
+      <c r="W18">
+        <v>0.2844815252416756</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>-0.6099609129763848</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1224058086578748</v>
+      </c>
+      <c r="C19">
+        <v>1182.394650889164</v>
+      </c>
+      <c r="D19">
+        <v>733.2616508891643</v>
+      </c>
+      <c r="E19">
+        <v>-1081.033</v>
+      </c>
+      <c r="F19">
+        <v>332.3670000000001</v>
+      </c>
+      <c r="G19">
+        <v>781.5</v>
+      </c>
+      <c r="H19">
+        <v>541.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>160.8</v>
+      </c>
+      <c r="K19">
+        <v>207.7</v>
+      </c>
+      <c r="L19">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M19">
+        <v>81.69580860000002</v>
+      </c>
+      <c r="N19">
+        <v>-128.5958086</v>
+      </c>
+      <c r="O19">
+        <v>-33.17771861880001</v>
+      </c>
+      <c r="P19">
+        <v>-95.41808998120001</v>
+      </c>
+      <c r="Q19">
+        <v>112.2819100188</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.08967562002314064</v>
+      </c>
+      <c r="T19">
+        <v>1.012642307170218</v>
+      </c>
+      <c r="U19">
+        <v>0.2458</v>
+      </c>
+      <c r="V19">
+        <v>-0.148112861692148</v>
+      </c>
+      <c r="W19">
+        <v>0.28220614140393</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>-0.5740808592718916</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1244058086578748</v>
+      </c>
+      <c r="C20">
+        <v>1151.961695231789</v>
+      </c>
+      <c r="D20">
+        <v>722.3796952317891</v>
+      </c>
+      <c r="E20">
+        <v>-1061.482</v>
+      </c>
+      <c r="F20">
+        <v>351.918</v>
+      </c>
+      <c r="G20">
+        <v>781.5</v>
+      </c>
+      <c r="H20">
+        <v>541.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>160.8</v>
+      </c>
+      <c r="K20">
+        <v>207.7</v>
+      </c>
+      <c r="L20">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M20">
+        <v>86.50144440000001</v>
+      </c>
+      <c r="N20">
+        <v>-133.4014444</v>
+      </c>
+      <c r="O20">
+        <v>-34.4175726552</v>
+      </c>
+      <c r="P20">
+        <v>-98.9838717448</v>
+      </c>
+      <c r="Q20">
+        <v>108.7161282552</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09021068856000822</v>
+      </c>
+      <c r="T20">
+        <v>1.024991603599123</v>
+      </c>
+      <c r="U20">
+        <v>0.2458</v>
+      </c>
+      <c r="V20">
+        <v>-0.1398843693759176</v>
+      </c>
+      <c r="W20">
+        <v>0.2801835779926006</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>-0.5421874782012308</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1264058086578748</v>
+      </c>
+      <c r="C21">
+        <v>1121.847003301703</v>
+      </c>
+      <c r="D21">
+        <v>711.8160033017033</v>
+      </c>
+      <c r="E21">
+        <v>-1041.931</v>
+      </c>
+      <c r="F21">
+        <v>371.4690000000001</v>
+      </c>
+      <c r="G21">
+        <v>781.5</v>
+      </c>
+      <c r="H21">
+        <v>541.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>160.8</v>
+      </c>
+      <c r="K21">
+        <v>207.7</v>
+      </c>
+      <c r="L21">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M21">
+        <v>91.30708020000002</v>
+      </c>
+      <c r="N21">
+        <v>-138.2070802</v>
+      </c>
+      <c r="O21">
+        <v>-35.6574266916</v>
+      </c>
+      <c r="P21">
+        <v>-102.5496535084</v>
+      </c>
+      <c r="Q21">
+        <v>105.1503464916</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09075896866568732</v>
+      </c>
+      <c r="T21">
+        <v>1.037645820927507</v>
+      </c>
+      <c r="U21">
+        <v>0.2458</v>
+      </c>
+      <c r="V21">
+        <v>-0.1325220341456061</v>
+      </c>
+      <c r="W21">
+        <v>0.27837391599299</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>-0.5136512951380081</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1284058086578748</v>
+      </c>
+      <c r="C22">
+        <v>1092.036813981638</v>
+      </c>
+      <c r="D22">
+        <v>701.5568139816376</v>
+      </c>
+      <c r="E22">
+        <v>-1022.38</v>
+      </c>
+      <c r="F22">
+        <v>391.02</v>
+      </c>
+      <c r="G22">
+        <v>781.5</v>
+      </c>
+      <c r="H22">
+        <v>541.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>160.8</v>
+      </c>
+      <c r="K22">
+        <v>207.7</v>
+      </c>
+      <c r="L22">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M22">
+        <v>96.11271600000002</v>
+      </c>
+      <c r="N22">
+        <v>-143.012716</v>
+      </c>
+      <c r="O22">
+        <v>-36.89728072800001</v>
+      </c>
+      <c r="P22">
+        <v>-106.115435272</v>
+      </c>
+      <c r="Q22">
+        <v>101.584564728</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09132095577400841</v>
+      </c>
+      <c r="T22">
+        <v>1.050616393689101</v>
+      </c>
+      <c r="U22">
+        <v>0.2458</v>
+      </c>
+      <c r="V22">
+        <v>-0.1258959324383258</v>
+      </c>
+      <c r="W22">
+        <v>0.2767452201933405</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>-0.4879687303811078</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1304058086578748</v>
+      </c>
+      <c r="C23">
+        <v>1062.518148221945</v>
+      </c>
+      <c r="D23">
+        <v>691.5891482219444</v>
+      </c>
+      <c r="E23">
+        <v>-1002.829</v>
+      </c>
+      <c r="F23">
+        <v>410.571</v>
+      </c>
+      <c r="G23">
+        <v>781.5</v>
+      </c>
+      <c r="H23">
+        <v>541.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>160.8</v>
+      </c>
+      <c r="K23">
+        <v>207.7</v>
+      </c>
+      <c r="L23">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M23">
+        <v>100.9183518</v>
+      </c>
+      <c r="N23">
+        <v>-147.8183518</v>
+      </c>
+      <c r="O23">
+        <v>-38.1371347644</v>
+      </c>
+      <c r="P23">
+        <v>-109.6812170356</v>
+      </c>
+      <c r="Q23">
+        <v>98.01878296439997</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09189717040405915</v>
+      </c>
+      <c r="T23">
+        <v>1.063915335381368</v>
+      </c>
+      <c r="U23">
+        <v>0.2458</v>
+      </c>
+      <c r="V23">
+        <v>-0.1199008880365008</v>
+      </c>
+      <c r="W23">
+        <v>0.275271638279372</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>-0.4647321241724838</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1324058086578749</v>
+      </c>
+      <c r="C24">
+        <v>1033.278754261116</v>
+      </c>
+      <c r="D24">
+        <v>681.9007542611162</v>
+      </c>
+      <c r="E24">
+        <v>-983.278</v>
+      </c>
+      <c r="F24">
+        <v>430.122</v>
+      </c>
+      <c r="G24">
+        <v>781.5</v>
+      </c>
+      <c r="H24">
+        <v>541.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>160.8</v>
+      </c>
+      <c r="K24">
+        <v>207.7</v>
+      </c>
+      <c r="L24">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M24">
+        <v>105.7239876</v>
+      </c>
+      <c r="N24">
+        <v>-152.6239876</v>
+      </c>
+      <c r="O24">
+        <v>-39.37698880080001</v>
+      </c>
+      <c r="P24">
+        <v>-113.2469987992</v>
+      </c>
+      <c r="Q24">
+        <v>94.45300120079997</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09248815976821376</v>
+      </c>
+      <c r="T24">
+        <v>1.077555275578565</v>
+      </c>
+      <c r="U24">
+        <v>0.2458</v>
+      </c>
+      <c r="V24">
+        <v>-0.1144508476712053</v>
+      </c>
+      <c r="W24">
+        <v>0.2739320183575823</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>-0.443607936710098</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1344058086578748</v>
+      </c>
+      <c r="C25">
+        <v>1004.307057387088</v>
+      </c>
+      <c r="D25">
+        <v>672.4800573870878</v>
+      </c>
+      <c r="E25">
+        <v>-963.7270000000001</v>
+      </c>
+      <c r="F25">
+        <v>449.6730000000001</v>
+      </c>
+      <c r="G25">
+        <v>781.5</v>
+      </c>
+      <c r="H25">
+        <v>541.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>160.8</v>
+      </c>
+      <c r="K25">
+        <v>207.7</v>
+      </c>
+      <c r="L25">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M25">
+        <v>110.5296234</v>
+      </c>
+      <c r="N25">
+        <v>-157.4296234</v>
+      </c>
+      <c r="O25">
+        <v>-40.61684283720001</v>
+      </c>
+      <c r="P25">
+        <v>-116.8127805628</v>
+      </c>
+      <c r="Q25">
+        <v>90.88721943719997</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09309449950546328</v>
+      </c>
+      <c r="T25">
+        <v>1.091549499936729</v>
+      </c>
+      <c r="U25">
+        <v>0.2458</v>
+      </c>
+      <c r="V25">
+        <v>-0.1094747238594138</v>
+      </c>
+      <c r="W25">
+        <v>0.2727088871246439</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>-0.424320635114007</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1364058086578748</v>
+      </c>
+      <c r="C26">
+        <v>975.5921138061815</v>
+      </c>
+      <c r="D26">
+        <v>663.3161138061813</v>
+      </c>
+      <c r="E26">
+        <v>-944.1760000000002</v>
+      </c>
+      <c r="F26">
+        <v>469.224</v>
+      </c>
+      <c r="G26">
+        <v>781.5</v>
+      </c>
+      <c r="H26">
+        <v>541.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>160.8</v>
+      </c>
+      <c r="K26">
+        <v>207.7</v>
+      </c>
+      <c r="L26">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M26">
+        <v>115.3352592</v>
+      </c>
+      <c r="N26">
+        <v>-162.2352592</v>
+      </c>
+      <c r="O26">
+        <v>-41.85669687360001</v>
+      </c>
+      <c r="P26">
+        <v>-120.3785623264</v>
+      </c>
+      <c r="Q26">
+        <v>87.32143767359997</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09371679555158779</v>
+      </c>
+      <c r="T26">
+        <v>1.105911993356949</v>
+      </c>
+      <c r="U26">
+        <v>0.2458</v>
+      </c>
+      <c r="V26">
+        <v>-0.1049132770319382</v>
+      </c>
+      <c r="W26">
+        <v>0.2715876834944504</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>-0.4066406086509233</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1384058086578748</v>
+      </c>
+      <c r="C27">
+        <v>947.1235682331344</v>
+      </c>
+      <c r="D27">
+        <v>654.3985682331345</v>
+      </c>
+      <c r="E27">
+        <v>-924.625</v>
+      </c>
+      <c r="F27">
+        <v>488.775</v>
+      </c>
+      <c r="G27">
+        <v>781.5</v>
+      </c>
+      <c r="H27">
+        <v>541.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>160.8</v>
+      </c>
+      <c r="K27">
+        <v>207.7</v>
+      </c>
+      <c r="L27">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M27">
+        <v>120.140895</v>
+      </c>
+      <c r="N27">
+        <v>-167.040895</v>
+      </c>
+      <c r="O27">
+        <v>-43.09655091000001</v>
+      </c>
+      <c r="P27">
+        <v>-123.94434409</v>
+      </c>
+      <c r="Q27">
+        <v>83.75565590999997</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.0943556861589423</v>
+      </c>
+      <c r="T27">
+        <v>1.120657486601708</v>
+      </c>
+      <c r="U27">
+        <v>0.2458</v>
+      </c>
+      <c r="V27">
+        <v>-0.1007167459506607</v>
+      </c>
+      <c r="W27">
+        <v>0.2705561761546724</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>-0.3903749843048865</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1404058086578748</v>
+      </c>
+      <c r="C28">
+        <v>918.8916148566782</v>
+      </c>
+      <c r="D28">
+        <v>645.7176148566782</v>
+      </c>
+      <c r="E28">
+        <v>-905.0740000000001</v>
+      </c>
+      <c r="F28">
+        <v>508.3260000000001</v>
+      </c>
+      <c r="G28">
+        <v>781.5</v>
+      </c>
+      <c r="H28">
+        <v>541.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>160.8</v>
+      </c>
+      <c r="K28">
+        <v>207.7</v>
+      </c>
+      <c r="L28">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M28">
+        <v>124.9465308</v>
+      </c>
+      <c r="N28">
+        <v>-171.8465308</v>
+      </c>
+      <c r="O28">
+        <v>-44.33640494640001</v>
+      </c>
+      <c r="P28">
+        <v>-127.5101258536</v>
+      </c>
+      <c r="Q28">
+        <v>80.18987414639996</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09501184408000909</v>
+      </c>
+      <c r="T28">
+        <v>1.13580150669092</v>
+      </c>
+      <c r="U28">
+        <v>0.2458</v>
+      </c>
+      <c r="V28">
+        <v>-0.09684302495255832</v>
+      </c>
+      <c r="W28">
+        <v>0.2696040155333388</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>-0.3753605618316214</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1424058086578748</v>
+      </c>
+      <c r="C29">
+        <v>890.8869613713158</v>
+      </c>
+      <c r="D29">
+        <v>637.263961371316</v>
+      </c>
+      <c r="E29">
+        <v>-885.523</v>
+      </c>
+      <c r="F29">
+        <v>527.8770000000001</v>
+      </c>
+      <c r="G29">
+        <v>781.5</v>
+      </c>
+      <c r="H29">
+        <v>541.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>160.8</v>
+      </c>
+      <c r="K29">
+        <v>207.7</v>
+      </c>
+      <c r="L29">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M29">
+        <v>129.7521666</v>
+      </c>
+      <c r="N29">
+        <v>-176.6521666</v>
+      </c>
+      <c r="O29">
+        <v>-45.57625898280001</v>
+      </c>
+      <c r="P29">
+        <v>-131.0759076172</v>
+      </c>
+      <c r="Q29">
+        <v>76.62409238279997</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09568597893042019</v>
+      </c>
+      <c r="T29">
+        <v>1.151360431440111</v>
+      </c>
+      <c r="U29">
+        <v>0.2458</v>
+      </c>
+      <c r="V29">
+        <v>-0.09325624625061173</v>
+      </c>
+      <c r="W29">
+        <v>0.2687223853284004</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>-0.3614583188008207</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1444058086578748</v>
+      </c>
+      <c r="C30">
+        <v>863.1007957979393</v>
+      </c>
+      <c r="D30">
+        <v>629.0287957979394</v>
+      </c>
+      <c r="E30">
+        <v>-865.972</v>
+      </c>
+      <c r="F30">
+        <v>547.4280000000001</v>
+      </c>
+      <c r="G30">
+        <v>781.5</v>
+      </c>
+      <c r="H30">
+        <v>541.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>160.8</v>
+      </c>
+      <c r="K30">
+        <v>207.7</v>
+      </c>
+      <c r="L30">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M30">
+        <v>134.5578024</v>
+      </c>
+      <c r="N30">
+        <v>-181.4578024</v>
+      </c>
+      <c r="O30">
+        <v>-46.81611301920002</v>
+      </c>
+      <c r="P30">
+        <v>-134.6416893808</v>
+      </c>
+      <c r="Q30">
+        <v>73.05831061919997</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09637883974889823</v>
+      </c>
+      <c r="T30">
+        <v>1.167351548543446</v>
+      </c>
+      <c r="U30">
+        <v>0.2458</v>
+      </c>
+      <c r="V30">
+        <v>-0.0899256660273756</v>
+      </c>
+      <c r="W30">
+        <v>0.2679037287095289</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>-0.3485490931293627</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1464058086578748</v>
+      </c>
+      <c r="C31">
+        <v>835.524755844227</v>
+      </c>
+      <c r="D31">
+        <v>621.003755844227</v>
+      </c>
+      <c r="E31">
+        <v>-846.421</v>
+      </c>
+      <c r="F31">
+        <v>566.979</v>
+      </c>
+      <c r="G31">
+        <v>781.5</v>
+      </c>
+      <c r="H31">
+        <v>541.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>160.8</v>
+      </c>
+      <c r="K31">
+        <v>207.7</v>
+      </c>
+      <c r="L31">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M31">
+        <v>139.3634382</v>
+      </c>
+      <c r="N31">
+        <v>-186.2634382</v>
+      </c>
+      <c r="O31">
+        <v>-48.05596705560001</v>
+      </c>
+      <c r="P31">
+        <v>-138.2074711444</v>
+      </c>
+      <c r="Q31">
+        <v>69.49252885559997</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09709121777353061</v>
+      </c>
+      <c r="T31">
+        <v>1.183793119649691</v>
+      </c>
+      <c r="U31">
+        <v>0.2458</v>
+      </c>
+      <c r="V31">
+        <v>-0.08682478099194886</v>
+      </c>
+      <c r="W31">
+        <v>0.2671415311678211</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>-0.3365301588835228</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1484058086578748</v>
+      </c>
+      <c r="C32">
+        <v>808.1509005808641</v>
+      </c>
+      <c r="D32">
+        <v>613.180900580864</v>
+      </c>
+      <c r="E32">
+        <v>-826.8700000000001</v>
+      </c>
+      <c r="F32">
+        <v>586.53</v>
+      </c>
+      <c r="G32">
+        <v>781.5</v>
+      </c>
+      <c r="H32">
+        <v>541.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>160.8</v>
+      </c>
+      <c r="K32">
+        <v>207.7</v>
+      </c>
+      <c r="L32">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M32">
+        <v>144.169074</v>
+      </c>
+      <c r="N32">
+        <v>-191.069074</v>
+      </c>
+      <c r="O32">
+        <v>-49.295821092</v>
+      </c>
+      <c r="P32">
+        <v>-141.773252908</v>
+      </c>
+      <c r="Q32">
+        <v>65.926747092</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.09782394945600961</v>
+      </c>
+      <c r="T32">
+        <v>1.200704449930401</v>
+      </c>
+      <c r="U32">
+        <v>0.2458</v>
+      </c>
+      <c r="V32">
+        <v>-0.08393062162555058</v>
+      </c>
+      <c r="W32">
+        <v>0.2664301467955604</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>-0.3253124869207387</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1504058086578748</v>
+      </c>
+      <c r="C33">
+        <v>780.9716842319186</v>
+      </c>
+      <c r="D33">
+        <v>605.5526842319188</v>
+      </c>
+      <c r="E33">
+        <v>-807.3190000000001</v>
+      </c>
+      <c r="F33">
+        <v>606.081</v>
+      </c>
+      <c r="G33">
+        <v>781.5</v>
+      </c>
+      <c r="H33">
+        <v>541.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>160.8</v>
+      </c>
+      <c r="K33">
+        <v>207.7</v>
+      </c>
+      <c r="L33">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M33">
+        <v>148.9747098</v>
+      </c>
+      <c r="N33">
+        <v>-195.8747098</v>
+      </c>
+      <c r="O33">
+        <v>-50.53567512840001</v>
+      </c>
+      <c r="P33">
+        <v>-145.3390346716</v>
+      </c>
+      <c r="Q33">
+        <v>62.36096532839997</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.09857791973798077</v>
+      </c>
+      <c r="T33">
+        <v>1.218105963697509</v>
+      </c>
+      <c r="U33">
+        <v>0.2458</v>
+      </c>
+      <c r="V33">
+        <v>-0.08122318221827474</v>
+      </c>
+      <c r="W33">
+        <v>0.2657646581892519</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>-0.3148185357297471</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1524058086578748</v>
+      </c>
+      <c r="C34">
+        <v>753.9799318975297</v>
+      </c>
+      <c r="D34">
+        <v>598.1119318975296</v>
+      </c>
+      <c r="E34">
+        <v>-787.768</v>
+      </c>
+      <c r="F34">
+        <v>625.6320000000001</v>
+      </c>
+      <c r="G34">
+        <v>781.5</v>
+      </c>
+      <c r="H34">
+        <v>541.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>160.8</v>
+      </c>
+      <c r="K34">
+        <v>207.7</v>
+      </c>
+      <c r="L34">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M34">
+        <v>153.7803456</v>
+      </c>
+      <c r="N34">
+        <v>-200.6803456</v>
+      </c>
+      <c r="O34">
+        <v>-51.77552916480001</v>
+      </c>
+      <c r="P34">
+        <v>-148.9048164352</v>
+      </c>
+      <c r="Q34">
+        <v>58.79518356479997</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.09935406561648048</v>
+      </c>
+      <c r="T34">
+        <v>1.23601928669306</v>
+      </c>
+      <c r="U34">
+        <v>0.2458</v>
+      </c>
+      <c r="V34">
+        <v>-0.07868495777395365</v>
+      </c>
+      <c r="W34">
+        <v>0.2651407626208379</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>-0.3049804564881924</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1544058086578748</v>
+      </c>
+      <c r="C35">
+        <v>727.1688170447154</v>
+      </c>
+      <c r="D35">
+        <v>590.8518170447156</v>
+      </c>
+      <c r="E35">
+        <v>-768.217</v>
+      </c>
+      <c r="F35">
+        <v>645.1830000000001</v>
+      </c>
+      <c r="G35">
+        <v>781.5</v>
+      </c>
+      <c r="H35">
+        <v>541.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>160.8</v>
+      </c>
+      <c r="K35">
+        <v>207.7</v>
+      </c>
+      <c r="L35">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M35">
+        <v>158.5859814</v>
+      </c>
+      <c r="N35">
+        <v>-205.4859814</v>
+      </c>
+      <c r="O35">
+        <v>-53.01538320120001</v>
+      </c>
+      <c r="P35">
+        <v>-152.4705981988</v>
+      </c>
+      <c r="Q35">
+        <v>55.22940180119997</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1001533800286668</v>
+      </c>
+      <c r="T35">
+        <v>1.254467335748181</v>
+      </c>
+      <c r="U35">
+        <v>0.2458</v>
+      </c>
+      <c r="V35">
+        <v>-0.07630056511413687</v>
+      </c>
+      <c r="W35">
+        <v>0.2645546789050549</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>-0.2957386244733988</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1564058086578748</v>
+      </c>
+      <c r="C36">
+        <v>700.5318406178794</v>
+      </c>
+      <c r="D36">
+        <v>583.7658406178796</v>
+      </c>
+      <c r="E36">
+        <v>-748.6659999999999</v>
+      </c>
+      <c r="F36">
+        <v>664.7340000000002</v>
+      </c>
+      <c r="G36">
+        <v>781.5</v>
+      </c>
+      <c r="H36">
+        <v>541.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>160.8</v>
+      </c>
+      <c r="K36">
+        <v>207.7</v>
+      </c>
+      <c r="L36">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M36">
+        <v>163.3916172</v>
+      </c>
+      <c r="N36">
+        <v>-210.2916172</v>
+      </c>
+      <c r="O36">
+        <v>-54.25523723760001</v>
+      </c>
+      <c r="P36">
+        <v>-156.0363799624</v>
+      </c>
+      <c r="Q36">
+        <v>51.66362003759997</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1009769160897072</v>
+      </c>
+      <c r="T36">
+        <v>1.27347441659285</v>
+      </c>
+      <c r="U36">
+        <v>0.2458</v>
+      </c>
+      <c r="V36">
+        <v>-0.07405643084607402</v>
+      </c>
+      <c r="W36">
+        <v>0.264003070701965</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>-0.2870404296359459</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1584058086578748</v>
+      </c>
+      <c r="C37">
+        <v>674.06281163464</v>
+      </c>
+      <c r="D37">
+        <v>576.84781163464</v>
+      </c>
+      <c r="E37">
+        <v>-729.115</v>
+      </c>
+      <c r="F37">
+        <v>684.2850000000001</v>
+      </c>
+      <c r="G37">
+        <v>781.5</v>
+      </c>
+      <c r="H37">
+        <v>541.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>160.8</v>
+      </c>
+      <c r="K37">
+        <v>207.7</v>
+      </c>
+      <c r="L37">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M37">
+        <v>168.197253</v>
+      </c>
+      <c r="N37">
+        <v>-215.0972530000001</v>
+      </c>
+      <c r="O37">
+        <v>-55.49509127400002</v>
+      </c>
+      <c r="P37">
+        <v>-159.602161726</v>
+      </c>
+      <c r="Q37">
+        <v>48.09783827399997</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1018257917218565</v>
+      </c>
+      <c r="T37">
+        <v>1.293066330694278</v>
+      </c>
+      <c r="U37">
+        <v>0.2458</v>
+      </c>
+      <c r="V37">
+        <v>-0.07194053282190048</v>
+      </c>
+      <c r="W37">
+        <v>0.2634829829676232</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>-0.2788392745034902</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1604058086578748</v>
+      </c>
+      <c r="C38">
+        <v>647.7558291452222</v>
+      </c>
+      <c r="D38">
+        <v>570.0918291452221</v>
+      </c>
+      <c r="E38">
+        <v>-709.5640000000001</v>
+      </c>
+      <c r="F38">
+        <v>703.836</v>
+      </c>
+      <c r="G38">
+        <v>781.5</v>
+      </c>
+      <c r="H38">
+        <v>541.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>160.8</v>
+      </c>
+      <c r="K38">
+        <v>207.7</v>
+      </c>
+      <c r="L38">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M38">
+        <v>173.0028888</v>
+      </c>
+      <c r="N38">
+        <v>-219.9028888</v>
+      </c>
+      <c r="O38">
+        <v>-56.73494531040001</v>
+      </c>
+      <c r="P38">
+        <v>-163.1679434896</v>
+      </c>
+      <c r="Q38">
+        <v>44.53205651039997</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1027011947175105</v>
+      </c>
+      <c r="T38">
+        <v>1.313270492111376</v>
+      </c>
+      <c r="U38">
+        <v>0.2458</v>
+      </c>
+      <c r="V38">
+        <v>-0.06994218468795881</v>
+      </c>
+      <c r="W38">
+        <v>0.2629917889963003</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>-0.2710937391006156</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1624058086578748</v>
+      </c>
+      <c r="C39">
+        <v>621.6052654449105</v>
+      </c>
+      <c r="D39">
+        <v>563.4922654449106</v>
+      </c>
+      <c r="E39">
+        <v>-690.013</v>
+      </c>
+      <c r="F39">
+        <v>723.3870000000001</v>
+      </c>
+      <c r="G39">
+        <v>781.5</v>
+      </c>
+      <c r="H39">
+        <v>541.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>160.8</v>
+      </c>
+      <c r="K39">
+        <v>207.7</v>
+      </c>
+      <c r="L39">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M39">
+        <v>177.8085246</v>
+      </c>
+      <c r="N39">
+        <v>-224.7085246</v>
+      </c>
+      <c r="O39">
+        <v>-57.97479934680001</v>
+      </c>
+      <c r="P39">
+        <v>-166.7337252532</v>
+      </c>
+      <c r="Q39">
+        <v>40.96627474679997</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1036043882844551</v>
+      </c>
+      <c r="T39">
+        <v>1.334116055478224</v>
+      </c>
+      <c r="U39">
+        <v>0.2458</v>
+      </c>
+      <c r="V39">
+        <v>-0.06805185537206802</v>
+      </c>
+      <c r="W39">
+        <v>0.2625271460504543</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>-0.2637668812870855</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1644058086578748</v>
+      </c>
+      <c r="C40">
+        <v>595.6057504391858</v>
+      </c>
+      <c r="D40">
+        <v>557.0437504391859</v>
+      </c>
+      <c r="E40">
+        <v>-670.462</v>
+      </c>
+      <c r="F40">
+        <v>742.9380000000001</v>
+      </c>
+      <c r="G40">
+        <v>781.5</v>
+      </c>
+      <c r="H40">
+        <v>541.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>160.8</v>
+      </c>
+      <c r="K40">
+        <v>207.7</v>
+      </c>
+      <c r="L40">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M40">
+        <v>182.6141604</v>
+      </c>
+      <c r="N40">
+        <v>-229.5141604</v>
+      </c>
+      <c r="O40">
+        <v>-59.21465338320001</v>
+      </c>
+      <c r="P40">
+        <v>-170.2995070168</v>
+      </c>
+      <c r="Q40">
+        <v>37.40049298319997</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1045367171277528</v>
+      </c>
+      <c r="T40">
+        <v>1.355634056373034</v>
+      </c>
+      <c r="U40">
+        <v>0.2458</v>
+      </c>
+      <c r="V40">
+        <v>-0.06626101707280307</v>
+      </c>
+      <c r="W40">
+        <v>0.262086957996495</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>-0.2568256475690043</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1664058086578749</v>
+      </c>
+      <c r="C41">
+        <v>569.7521570702538</v>
+      </c>
+      <c r="D41">
+        <v>550.7411570702537</v>
+      </c>
+      <c r="E41">
+        <v>-650.9110000000001</v>
+      </c>
+      <c r="F41">
+        <v>762.489</v>
+      </c>
+      <c r="G41">
+        <v>781.5</v>
+      </c>
+      <c r="H41">
+        <v>541.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>160.8</v>
+      </c>
+      <c r="K41">
+        <v>207.7</v>
+      </c>
+      <c r="L41">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M41">
+        <v>187.4197962</v>
+      </c>
+      <c r="N41">
+        <v>-234.3197962</v>
+      </c>
+      <c r="O41">
+        <v>-60.45450741960001</v>
+      </c>
+      <c r="P41">
+        <v>-173.8652887804</v>
+      </c>
+      <c r="Q41">
+        <v>33.83471121959997</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1054996141298471</v>
+      </c>
+      <c r="T41">
+        <v>1.377857565493903</v>
+      </c>
+      <c r="U41">
+        <v>0.2458</v>
+      </c>
+      <c r="V41">
+        <v>-0.0645620166350389</v>
+      </c>
+      <c r="W41">
+        <v>0.2616693436888926</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>-0.2502403745544144</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1684058086578749</v>
+      </c>
+      <c r="C42">
+        <v>544.0395877218401</v>
+      </c>
+      <c r="D42">
+        <v>544.5795877218401</v>
+      </c>
+      <c r="E42">
+        <v>-631.36</v>
+      </c>
+      <c r="F42">
+        <v>782.0400000000001</v>
+      </c>
+      <c r="G42">
+        <v>781.5</v>
+      </c>
+      <c r="H42">
+        <v>541.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>160.8</v>
+      </c>
+      <c r="K42">
+        <v>207.7</v>
+      </c>
+      <c r="L42">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M42">
+        <v>192.225432</v>
+      </c>
+      <c r="N42">
+        <v>-239.125432</v>
+      </c>
+      <c r="O42">
+        <v>-61.69436145600002</v>
+      </c>
+      <c r="P42">
+        <v>-177.431070544</v>
+      </c>
+      <c r="Q42">
+        <v>30.26892945599997</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1064946076986779</v>
+      </c>
+      <c r="T42">
+        <v>1.400821858252135</v>
+      </c>
+      <c r="U42">
+        <v>0.2458</v>
+      </c>
+      <c r="V42">
+        <v>-0.06294796621916292</v>
+      </c>
+      <c r="W42">
+        <v>0.2612726100966703</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>-0.243984365190554</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1704058086578749</v>
+      </c>
+      <c r="C43">
+        <v>518.4633615264918</v>
+      </c>
+      <c r="D43">
+        <v>538.5543615264918</v>
+      </c>
+      <c r="E43">
+        <v>-611.809</v>
+      </c>
+      <c r="F43">
+        <v>801.5910000000001</v>
+      </c>
+      <c r="G43">
+        <v>781.5</v>
+      </c>
+      <c r="H43">
+        <v>541.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>160.8</v>
+      </c>
+      <c r="K43">
+        <v>207.7</v>
+      </c>
+      <c r="L43">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M43">
+        <v>197.0310678</v>
+      </c>
+      <c r="N43">
+        <v>-243.9310678000001</v>
+      </c>
+      <c r="O43">
+        <v>-62.93421549240001</v>
+      </c>
+      <c r="P43">
+        <v>-180.9968523076</v>
+      </c>
+      <c r="Q43">
+        <v>26.70314769239997</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1075233298630623</v>
+      </c>
+      <c r="T43">
+        <v>1.424564601612341</v>
+      </c>
+      <c r="U43">
+        <v>0.2458</v>
+      </c>
+      <c r="V43">
+        <v>-0.06141264996991504</v>
+      </c>
+      <c r="W43">
+        <v>0.2608952293626051</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>-0.2380335270151746</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1724058086578748</v>
+      </c>
+      <c r="C44">
+        <v>493.0190025062482</v>
+      </c>
+      <c r="D44">
+        <v>532.6610025062483</v>
+      </c>
+      <c r="E44">
+        <v>-592.258</v>
+      </c>
+      <c r="F44">
+        <v>821.1420000000001</v>
+      </c>
+      <c r="G44">
+        <v>781.5</v>
+      </c>
+      <c r="H44">
+        <v>541.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>160.8</v>
+      </c>
+      <c r="K44">
+        <v>207.7</v>
+      </c>
+      <c r="L44">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M44">
+        <v>201.8367036</v>
+      </c>
+      <c r="N44">
+        <v>-248.7367036</v>
+      </c>
+      <c r="O44">
+        <v>-64.1740695288</v>
+      </c>
+      <c r="P44">
+        <v>-184.5626340712</v>
+      </c>
+      <c r="Q44">
+        <v>23.13736592879997</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1085875252055288</v>
+      </c>
+      <c r="T44">
+        <v>1.449126060260829</v>
+      </c>
+      <c r="U44">
+        <v>0.2458</v>
+      </c>
+      <c r="V44">
+        <v>-0.05995044401825041</v>
+      </c>
+      <c r="W44">
+        <v>0.2605358191396859</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>-0.2323660620862418</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1744058086578748</v>
+      </c>
+      <c r="C45">
+        <v>467.7022284835376</v>
+      </c>
+      <c r="D45">
+        <v>526.8952284835378</v>
+      </c>
+      <c r="E45">
+        <v>-572.707</v>
+      </c>
+      <c r="F45">
+        <v>840.6930000000001</v>
+      </c>
+      <c r="G45">
+        <v>781.5</v>
+      </c>
+      <c r="H45">
+        <v>541.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>160.8</v>
+      </c>
+      <c r="K45">
+        <v>207.7</v>
+      </c>
+      <c r="L45">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M45">
+        <v>206.6423394</v>
+      </c>
+      <c r="N45">
+        <v>-253.5423394</v>
+      </c>
+      <c r="O45">
+        <v>-65.41392356520001</v>
+      </c>
+      <c r="P45">
+        <v>-188.1284158348</v>
+      </c>
+      <c r="Q45">
+        <v>19.57158416519997</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1096890607354504</v>
+      </c>
+      <c r="T45">
+        <v>1.474549324475931</v>
+      </c>
+      <c r="U45">
+        <v>0.2458</v>
+      </c>
+      <c r="V45">
+        <v>-0.05855624764573296</v>
+      </c>
+      <c r="W45">
+        <v>0.2601931256713211</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>-0.2269622001772595</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1764058086578749</v>
+      </c>
+      <c r="C46">
+        <v>442.5089407045658</v>
+      </c>
+      <c r="D46">
+        <v>521.252940704566</v>
+      </c>
+      <c r="E46">
+        <v>-553.1560000000001</v>
+      </c>
+      <c r="F46">
+        <v>860.244</v>
+      </c>
+      <c r="G46">
+        <v>781.5</v>
+      </c>
+      <c r="H46">
+        <v>541.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>160.8</v>
+      </c>
+      <c r="K46">
+        <v>207.7</v>
+      </c>
+      <c r="L46">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M46">
+        <v>211.4479752</v>
+      </c>
+      <c r="N46">
+        <v>-258.3479752000001</v>
+      </c>
+      <c r="O46">
+        <v>-66.65377760160001</v>
+      </c>
+      <c r="P46">
+        <v>-191.6941975984001</v>
+      </c>
+      <c r="Q46">
+        <v>16.00580240159994</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.110829936820012</v>
+      </c>
+      <c r="T46">
+        <v>1.500880562413002</v>
+      </c>
+      <c r="U46">
+        <v>0.2458</v>
+      </c>
+      <c r="V46">
+        <v>-0.05722542383560266</v>
+      </c>
+      <c r="W46">
+        <v>0.2598660091787912</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>-0.2218039683550492</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1784058086578749</v>
+      </c>
+      <c r="C47">
+        <v>417.4352141223494</v>
+      </c>
+      <c r="D47">
+        <v>515.7302141223496</v>
+      </c>
+      <c r="E47">
+        <v>-533.605</v>
+      </c>
+      <c r="F47">
+        <v>879.7950000000001</v>
+      </c>
+      <c r="G47">
+        <v>781.5</v>
+      </c>
+      <c r="H47">
+        <v>541.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>160.8</v>
+      </c>
+      <c r="K47">
+        <v>207.7</v>
+      </c>
+      <c r="L47">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M47">
+        <v>216.253611</v>
+      </c>
+      <c r="N47">
+        <v>-263.1536110000001</v>
+      </c>
+      <c r="O47">
+        <v>-67.89363163800002</v>
+      </c>
+      <c r="P47">
+        <v>-195.2599793620001</v>
+      </c>
+      <c r="Q47">
+        <v>12.44002063799994</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1120122993076486</v>
+      </c>
+      <c r="T47">
+        <v>1.52816929991142</v>
+      </c>
+      <c r="U47">
+        <v>0.2458</v>
+      </c>
+      <c r="V47">
+        <v>-0.05595374775036704</v>
+      </c>
+      <c r="W47">
+        <v>0.2595534311970403</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>-0.2168749912804926</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1804058086578748</v>
+      </c>
+      <c r="C48">
+        <v>392.4772882909882</v>
+      </c>
+      <c r="D48">
+        <v>510.3232882909882</v>
+      </c>
+      <c r="E48">
+        <v>-514.054</v>
+      </c>
+      <c r="F48">
+        <v>899.3460000000001</v>
+      </c>
+      <c r="G48">
+        <v>781.5</v>
+      </c>
+      <c r="H48">
+        <v>541.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>160.8</v>
+      </c>
+      <c r="K48">
+        <v>207.7</v>
+      </c>
+      <c r="L48">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M48">
+        <v>221.0592468</v>
+      </c>
+      <c r="N48">
+        <v>-267.9592468000001</v>
+      </c>
+      <c r="O48">
+        <v>-69.13348567440002</v>
+      </c>
+      <c r="P48">
+        <v>-198.8257611256001</v>
+      </c>
+      <c r="Q48">
+        <v>8.874238874399936</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.113238452998531</v>
+      </c>
+      <c r="T48">
+        <v>1.556468731391261</v>
+      </c>
+      <c r="U48">
+        <v>0.2458</v>
+      </c>
+      <c r="V48">
+        <v>-0.05473736192970689</v>
+      </c>
+      <c r="W48">
+        <v>0.259254443562322</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>-0.2121603175570035</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1824058086578749</v>
+      </c>
+      <c r="C49">
+        <v>367.6315588267803</v>
+      </c>
+      <c r="D49">
+        <v>505.0285588267804</v>
+      </c>
+      <c r="E49">
+        <v>-494.5029999999999</v>
+      </c>
+      <c r="F49">
+        <v>918.8970000000002</v>
+      </c>
+      <c r="G49">
+        <v>781.5</v>
+      </c>
+      <c r="H49">
+        <v>541.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>160.8</v>
+      </c>
+      <c r="K49">
+        <v>207.7</v>
+      </c>
+      <c r="L49">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M49">
+        <v>225.8648826</v>
+      </c>
+      <c r="N49">
+        <v>-272.7648826000001</v>
+      </c>
+      <c r="O49">
+        <v>-70.37333971080002</v>
+      </c>
+      <c r="P49">
+        <v>-202.3915428892001</v>
+      </c>
+      <c r="Q49">
+        <v>5.308457110799935</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1145108766400127</v>
+      </c>
+      <c r="T49">
+        <v>1.585836065945813</v>
+      </c>
+      <c r="U49">
+        <v>0.2458</v>
+      </c>
+      <c r="V49">
+        <v>-0.05357273720779823</v>
+      </c>
+      <c r="W49">
+        <v>0.2589681788056769</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>-0.2076462682472802</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1844058086578748</v>
+      </c>
+      <c r="C50">
+        <v>342.8945693954412</v>
+      </c>
+      <c r="D50">
+        <v>499.8425693954412</v>
+      </c>
+      <c r="E50">
+        <v>-474.9520000000001</v>
+      </c>
+      <c r="F50">
+        <v>938.448</v>
+      </c>
+      <c r="G50">
+        <v>781.5</v>
+      </c>
+      <c r="H50">
+        <v>541.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>160.8</v>
+      </c>
+      <c r="K50">
+        <v>207.7</v>
+      </c>
+      <c r="L50">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M50">
+        <v>230.6705184</v>
+      </c>
+      <c r="N50">
+        <v>-277.5705184</v>
+      </c>
+      <c r="O50">
+        <v>-71.61319374720001</v>
+      </c>
+      <c r="P50">
+        <v>-205.9573246528</v>
+      </c>
+      <c r="Q50">
+        <v>1.742675347199963</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1158322396523206</v>
+      </c>
+      <c r="T50">
+        <v>1.616332913367848</v>
+      </c>
+      <c r="U50">
+        <v>0.2458</v>
+      </c>
+      <c r="V50">
+        <v>-0.05245663851596911</v>
+      </c>
+      <c r="W50">
+        <v>0.2586938417472252</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>-0.2033203043254617</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1864058086578748</v>
+      </c>
+      <c r="C51">
+        <v>318.2630041879847</v>
+      </c>
+      <c r="D51">
+        <v>494.7620041879848</v>
+      </c>
+      <c r="E51">
+        <v>-455.4010000000001</v>
+      </c>
+      <c r="F51">
+        <v>957.999</v>
+      </c>
+      <c r="G51">
+        <v>781.5</v>
+      </c>
+      <c r="H51">
+        <v>541.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>160.8</v>
+      </c>
+      <c r="K51">
+        <v>207.7</v>
+      </c>
+      <c r="L51">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M51">
+        <v>235.4761542</v>
+      </c>
+      <c r="N51">
+        <v>-282.3761542</v>
+      </c>
+      <c r="O51">
+        <v>-72.8530477836</v>
+      </c>
+      <c r="P51">
+        <v>-209.5231064164</v>
+      </c>
+      <c r="Q51">
+        <v>-1.823106416400037</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.117205420821974</v>
+      </c>
+      <c r="T51">
+        <v>1.648025715590747</v>
+      </c>
+      <c r="U51">
+        <v>0.2458</v>
+      </c>
+      <c r="V51">
+        <v>-0.05138609487278607</v>
+      </c>
+      <c r="W51">
+        <v>0.2584307021197308</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>-0.199170910359636</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1884058086578748</v>
+      </c>
+      <c r="C52">
+        <v>293.7336808508579</v>
+      </c>
+      <c r="D52">
+        <v>489.783680850858</v>
+      </c>
+      <c r="E52">
+        <v>-435.85</v>
+      </c>
+      <c r="F52">
+        <v>977.5500000000001</v>
+      </c>
+      <c r="G52">
+        <v>781.5</v>
+      </c>
+      <c r="H52">
+        <v>541.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>160.8</v>
+      </c>
+      <c r="K52">
+        <v>207.7</v>
+      </c>
+      <c r="L52">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M52">
+        <v>240.28179</v>
+      </c>
+      <c r="N52">
+        <v>-287.18179</v>
+      </c>
+      <c r="O52">
+        <v>-74.09290182000001</v>
+      </c>
+      <c r="P52">
+        <v>-213.08888818</v>
+      </c>
+      <c r="Q52">
+        <v>-5.388888180000038</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1186335292384134</v>
+      </c>
+      <c r="T52">
+        <v>1.680986229902562</v>
+      </c>
+      <c r="U52">
+        <v>0.2458</v>
+      </c>
+      <c r="V52">
+        <v>-0.05035837297533034</v>
+      </c>
+      <c r="W52">
+        <v>0.2581780880773362</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>-0.1951874921524432</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1904058086578749</v>
+      </c>
+      <c r="C53">
+        <v>269.3035438386437</v>
+      </c>
+      <c r="D53">
+        <v>484.9045438386439</v>
+      </c>
+      <c r="E53">
+        <v>-416.299</v>
+      </c>
+      <c r="F53">
+        <v>997.1010000000001</v>
+      </c>
+      <c r="G53">
+        <v>781.5</v>
+      </c>
+      <c r="H53">
+        <v>541.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>160.8</v>
+      </c>
+      <c r="K53">
+        <v>207.7</v>
+      </c>
+      <c r="L53">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M53">
+        <v>245.0874258</v>
+      </c>
+      <c r="N53">
+        <v>-291.9874258</v>
+      </c>
+      <c r="O53">
+        <v>-75.33275585640001</v>
+      </c>
+      <c r="P53">
+        <v>-216.6546699436</v>
+      </c>
+      <c r="Q53">
+        <v>-8.954669943600038</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1201199277942995</v>
+      </c>
+      <c r="T53">
+        <v>1.715292071329145</v>
+      </c>
+      <c r="U53">
+        <v>0.2458</v>
+      </c>
+      <c r="V53">
+        <v>-0.04937095389738269</v>
+      </c>
+      <c r="W53">
+        <v>0.2579353804679767</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>-0.1913602864239639</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1924058086578748</v>
+      </c>
+      <c r="C54">
+        <v>244.9696581601639</v>
+      </c>
+      <c r="D54">
+        <v>480.1216581601641</v>
+      </c>
+      <c r="E54">
+        <v>-396.7479999999999</v>
+      </c>
+      <c r="F54">
+        <v>1016.652</v>
+      </c>
+      <c r="G54">
+        <v>781.5</v>
+      </c>
+      <c r="H54">
+        <v>541.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>160.8</v>
+      </c>
+      <c r="K54">
+        <v>207.7</v>
+      </c>
+      <c r="L54">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M54">
+        <v>249.8930616000001</v>
+      </c>
+      <c r="N54">
+        <v>-296.7930616000001</v>
+      </c>
+      <c r="O54">
+        <v>-76.57260989280003</v>
+      </c>
+      <c r="P54">
+        <v>-220.2204517072001</v>
+      </c>
+      <c r="Q54">
+        <v>-12.5204517072001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1216682596233473</v>
+      </c>
+      <c r="T54">
+        <v>1.751027322815169</v>
+      </c>
+      <c r="U54">
+        <v>0.2458</v>
+      </c>
+      <c r="V54">
+        <v>-0.04842151247627916</v>
+      </c>
+      <c r="W54">
+        <v>0.2577020077666695</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>-0.1876802809158109</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1944058086578748</v>
+      </c>
+      <c r="C55">
+        <v>220.7292034910768</v>
+      </c>
+      <c r="D55">
+        <v>475.4322034910771</v>
+      </c>
+      <c r="E55">
+        <v>-377.1969999999999</v>
+      </c>
+      <c r="F55">
+        <v>1036.203</v>
+      </c>
+      <c r="G55">
+        <v>781.5</v>
+      </c>
+      <c r="H55">
+        <v>541.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>160.8</v>
+      </c>
+      <c r="K55">
+        <v>207.7</v>
+      </c>
+      <c r="L55">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M55">
+        <v>254.6986974000001</v>
+      </c>
+      <c r="N55">
+        <v>-301.5986974000001</v>
+      </c>
+      <c r="O55">
+        <v>-77.81246392920004</v>
+      </c>
+      <c r="P55">
+        <v>-223.7862334708001</v>
+      </c>
+      <c r="Q55">
+        <v>-16.0862334708001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1232824779132058</v>
+      </c>
+      <c r="T55">
+        <v>1.788283223300598</v>
+      </c>
+      <c r="U55">
+        <v>0.2458</v>
+      </c>
+      <c r="V55">
+        <v>-0.0475078990333305</v>
+      </c>
+      <c r="W55">
+        <v>0.2574774415823926</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>-0.1841391435400408</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1964058086578748</v>
+      </c>
+      <c r="C56">
+        <v>196.5794686281638</v>
+      </c>
+      <c r="D56">
+        <v>470.8334686281639</v>
+      </c>
+      <c r="E56">
+        <v>-357.646</v>
+      </c>
+      <c r="F56">
+        <v>1055.754</v>
+      </c>
+      <c r="G56">
+        <v>781.5</v>
+      </c>
+      <c r="H56">
+        <v>541.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>160.8</v>
+      </c>
+      <c r="K56">
+        <v>207.7</v>
+      </c>
+      <c r="L56">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M56">
+        <v>259.5043332000001</v>
+      </c>
+      <c r="N56">
+        <v>-306.4043332000001</v>
+      </c>
+      <c r="O56">
+        <v>-79.05231796560003</v>
+      </c>
+      <c r="P56">
+        <v>-227.3520152344001</v>
+      </c>
+      <c r="Q56">
+        <v>-19.6520152344001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1249668796069711</v>
+      </c>
+      <c r="T56">
+        <v>1.827158945546263</v>
+      </c>
+      <c r="U56">
+        <v>0.2458</v>
+      </c>
+      <c r="V56">
+        <v>-0.04662812312530586</v>
+      </c>
+      <c r="W56">
+        <v>0.2572611926642002</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>-0.1807291594004103</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1984058086578749</v>
+      </c>
+      <c r="C57">
+        <v>172.5178462623821</v>
+      </c>
+      <c r="D57">
+        <v>466.3228462623823</v>
+      </c>
+      <c r="E57">
+        <v>-338.095</v>
+      </c>
+      <c r="F57">
+        <v>1075.305</v>
+      </c>
+      <c r="G57">
+        <v>781.5</v>
+      </c>
+      <c r="H57">
+        <v>541.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>160.8</v>
+      </c>
+      <c r="K57">
+        <v>207.7</v>
+      </c>
+      <c r="L57">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M57">
+        <v>264.309969</v>
+      </c>
+      <c r="N57">
+        <v>-311.209969</v>
+      </c>
+      <c r="O57">
+        <v>-80.292172002</v>
+      </c>
+      <c r="P57">
+        <v>-230.917796998</v>
+      </c>
+      <c r="Q57">
+        <v>-23.21779699800001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1267261435982372</v>
+      </c>
+      <c r="T57">
+        <v>1.867762477669513</v>
+      </c>
+      <c r="U57">
+        <v>0.2458</v>
+      </c>
+      <c r="V57">
+        <v>-0.04578033906848213</v>
+      </c>
+      <c r="W57">
+        <v>0.2570528073430329</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>-0.1774431746840393</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2004058086578749</v>
+      </c>
+      <c r="C58">
+        <v>148.5418280495169</v>
+      </c>
+      <c r="D58">
+        <v>461.897828049517</v>
+      </c>
+      <c r="E58">
+        <v>-318.5439999999999</v>
+      </c>
+      <c r="F58">
+        <v>1094.856</v>
+      </c>
+      <c r="G58">
+        <v>781.5</v>
+      </c>
+      <c r="H58">
+        <v>541.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>160.8</v>
+      </c>
+      <c r="K58">
+        <v>207.7</v>
+      </c>
+      <c r="L58">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M58">
+        <v>269.1156048000001</v>
+      </c>
+      <c r="N58">
+        <v>-316.0156048000001</v>
+      </c>
+      <c r="O58">
+        <v>-81.53202603840003</v>
+      </c>
+      <c r="P58">
+        <v>-234.4835787616001</v>
+      </c>
+      <c r="Q58">
+        <v>-26.7835787616001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1285653741345608</v>
+      </c>
+      <c r="T58">
+        <v>1.910211624889275</v>
+      </c>
+      <c r="U58">
+        <v>0.2458</v>
+      </c>
+      <c r="V58">
+        <v>-0.0449628330136878</v>
+      </c>
+      <c r="W58">
+        <v>0.2568518643547645</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>-0.1742745465646816</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2024058086578748</v>
+      </c>
+      <c r="C59">
+        <v>124.6489999588462</v>
+      </c>
+      <c r="D59">
+        <v>457.5559999588462</v>
+      </c>
+      <c r="E59">
+        <v>-298.9929999999999</v>
+      </c>
+      <c r="F59">
+        <v>1114.407</v>
+      </c>
+      <c r="G59">
+        <v>781.5</v>
+      </c>
+      <c r="H59">
+        <v>541.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>160.8</v>
+      </c>
+      <c r="K59">
+        <v>207.7</v>
+      </c>
+      <c r="L59">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M59">
+        <v>273.9212406</v>
+      </c>
+      <c r="N59">
+        <v>-320.8212406</v>
+      </c>
+      <c r="O59">
+        <v>-82.77188007480001</v>
+      </c>
+      <c r="P59">
+        <v>-238.0493605252</v>
+      </c>
+      <c r="Q59">
+        <v>-30.34936052520001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.130490150277225</v>
+      </c>
+      <c r="T59">
+        <v>1.954635151049491</v>
+      </c>
+      <c r="U59">
+        <v>0.2458</v>
+      </c>
+      <c r="V59">
+        <v>-0.04417401138186872</v>
+      </c>
+      <c r="W59">
+        <v>0.2566579719976633</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>-0.171217098379336</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2044058086578748</v>
+      </c>
+      <c r="C60">
+        <v>100.8370378816971</v>
+      </c>
+      <c r="D60">
+        <v>453.2950378816971</v>
+      </c>
+      <c r="E60">
+        <v>-279.442</v>
+      </c>
+      <c r="F60">
+        <v>1133.958</v>
+      </c>
+      <c r="G60">
+        <v>781.5</v>
+      </c>
+      <c r="H60">
+        <v>541.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>160.8</v>
+      </c>
+      <c r="K60">
+        <v>207.7</v>
+      </c>
+      <c r="L60">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M60">
+        <v>278.7268764</v>
+      </c>
+      <c r="N60">
+        <v>-325.6268764</v>
+      </c>
+      <c r="O60">
+        <v>-84.0117341112</v>
+      </c>
+      <c r="P60">
+        <v>-241.6151422888</v>
+      </c>
+      <c r="Q60">
+        <v>-33.91514228880004</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1325065824266827</v>
+      </c>
+      <c r="T60">
+        <v>2.001174083217335</v>
+      </c>
+      <c r="U60">
+        <v>0.2458</v>
+      </c>
+      <c r="V60">
+        <v>-0.04341239049597443</v>
+      </c>
+      <c r="W60">
+        <v>0.2564707655839105</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>-0.1682650794417613</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2064058086578748</v>
+      </c>
+      <c r="C61">
+        <v>77.10370348311085</v>
+      </c>
+      <c r="D61">
+        <v>449.1127034831109</v>
+      </c>
+      <c r="E61">
+        <v>-259.8910000000001</v>
+      </c>
+      <c r="F61">
+        <v>1153.509</v>
+      </c>
+      <c r="G61">
+        <v>781.5</v>
+      </c>
+      <c r="H61">
+        <v>541.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>160.8</v>
+      </c>
+      <c r="K61">
+        <v>207.7</v>
+      </c>
+      <c r="L61">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M61">
+        <v>283.5325122</v>
+      </c>
+      <c r="N61">
+        <v>-330.4325122</v>
+      </c>
+      <c r="O61">
+        <v>-85.2515881476</v>
+      </c>
+      <c r="P61">
+        <v>-245.1809240524</v>
+      </c>
+      <c r="Q61">
+        <v>-37.48092405240004</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1346213771200164</v>
+      </c>
+      <c r="T61">
+        <v>2.049983207198246</v>
+      </c>
+      <c r="U61">
+        <v>0.2458</v>
+      </c>
+      <c r="V61">
+        <v>-0.0426765872672291</v>
+      </c>
+      <c r="W61">
+        <v>0.2562899051502849</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>-0.1654131289427483</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2084058086578748</v>
+      </c>
+      <c r="C62">
+        <v>53.44684028105371</v>
+      </c>
+      <c r="D62">
+        <v>445.0068402810536</v>
+      </c>
+      <c r="E62">
+        <v>-240.3400000000001</v>
+      </c>
+      <c r="F62">
+        <v>1173.06</v>
+      </c>
+      <c r="G62">
+        <v>781.5</v>
+      </c>
+      <c r="H62">
+        <v>541.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>160.8</v>
+      </c>
+      <c r="K62">
+        <v>207.7</v>
+      </c>
+      <c r="L62">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M62">
+        <v>288.338148</v>
+      </c>
+      <c r="N62">
+        <v>-335.238148</v>
+      </c>
+      <c r="O62">
+        <v>-86.49144218400001</v>
+      </c>
+      <c r="P62">
+        <v>-248.746705816</v>
+      </c>
+      <c r="Q62">
+        <v>-41.04670581600004</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1368419115480168</v>
+      </c>
+      <c r="T62">
+        <v>2.101232787378202</v>
+      </c>
+      <c r="U62">
+        <v>0.2458</v>
+      </c>
+      <c r="V62">
+        <v>-0.04196531081277529</v>
+      </c>
+      <c r="W62">
+        <v>0.2561150733977802</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>-0.1626562434603693</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2104058086578748</v>
+      </c>
+      <c r="C63">
+        <v>29.86436993874736</v>
+      </c>
+      <c r="D63">
+        <v>440.9753699387474</v>
+      </c>
+      <c r="E63">
+        <v>-220.789</v>
+      </c>
+      <c r="F63">
+        <v>1192.611</v>
+      </c>
+      <c r="G63">
+        <v>781.5</v>
+      </c>
+      <c r="H63">
+        <v>541.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>160.8</v>
+      </c>
+      <c r="K63">
+        <v>207.7</v>
+      </c>
+      <c r="L63">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M63">
+        <v>293.1437838000001</v>
+      </c>
+      <c r="N63">
+        <v>-340.0437838</v>
+      </c>
+      <c r="O63">
+        <v>-87.73129622040001</v>
+      </c>
+      <c r="P63">
+        <v>-252.3124875796</v>
+      </c>
+      <c r="Q63">
+        <v>-44.61248757960004</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1391763195364275</v>
+      </c>
+      <c r="T63">
+        <v>2.155110551157131</v>
+      </c>
+      <c r="U63">
+        <v>0.2458</v>
+      </c>
+      <c r="V63">
+        <v>-0.04127735489781175</v>
+      </c>
+      <c r="W63">
+        <v>0.2559459738338822</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>-0.1599897476659369</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2124058086578748</v>
+      </c>
+      <c r="C64">
+        <v>6.354288756726191</v>
+      </c>
+      <c r="D64">
+        <v>437.0162887567263</v>
+      </c>
+      <c r="E64">
+        <v>-201.2380000000001</v>
+      </c>
+      <c r="F64">
+        <v>1212.162</v>
+      </c>
+      <c r="G64">
+        <v>781.5</v>
+      </c>
+      <c r="H64">
+        <v>541.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>160.8</v>
+      </c>
+      <c r="K64">
+        <v>207.7</v>
+      </c>
+      <c r="L64">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M64">
+        <v>297.9494196000001</v>
+      </c>
+      <c r="N64">
+        <v>-344.8494196</v>
+      </c>
+      <c r="O64">
+        <v>-88.97115025680002</v>
+      </c>
+      <c r="P64">
+        <v>-255.8782693432</v>
+      </c>
+      <c r="Q64">
+        <v>-48.17826934320004</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1416335911031756</v>
+      </c>
+      <c r="T64">
+        <v>2.211823986713897</v>
+      </c>
+      <c r="U64">
+        <v>0.2458</v>
+      </c>
+      <c r="V64">
+        <v>-0.04061159110913737</v>
+      </c>
+      <c r="W64">
+        <v>0.255782329094626</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>-0.1574092678648735</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2144058086578749</v>
+      </c>
+      <c r="C65">
+        <v>-17.08533564782442</v>
+      </c>
+      <c r="D65">
+        <v>433.1276643521757</v>
+      </c>
+      <c r="E65">
+        <v>-181.6869999999999</v>
+      </c>
+      <c r="F65">
+        <v>1231.713</v>
+      </c>
+      <c r="G65">
+        <v>781.5</v>
+      </c>
+      <c r="H65">
+        <v>541.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>160.8</v>
+      </c>
+      <c r="K65">
+        <v>207.7</v>
+      </c>
+      <c r="L65">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M65">
+        <v>302.7550554000001</v>
+      </c>
+      <c r="N65">
+        <v>-349.6550554</v>
+      </c>
+      <c r="O65">
+        <v>-90.21100429320001</v>
+      </c>
+      <c r="P65">
+        <v>-259.4440511068</v>
+      </c>
+      <c r="Q65">
+        <v>-51.74405110680004</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1442236881600182</v>
+      </c>
+      <c r="T65">
+        <v>2.27160301338184</v>
+      </c>
+      <c r="U65">
+        <v>0.2458</v>
+      </c>
+      <c r="V65">
+        <v>-0.0399669626788336</v>
+      </c>
+      <c r="W65">
+        <v>0.2556238794264574</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>-0.1549107080574945</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2164058086578748</v>
+      </c>
+      <c r="C66">
+        <v>-40.45636748600373</v>
+      </c>
+      <c r="D66">
+        <v>429.3076325139963</v>
+      </c>
+      <c r="E66">
+        <v>-162.136</v>
+      </c>
+      <c r="F66">
+        <v>1251.264</v>
+      </c>
+      <c r="G66">
+        <v>781.5</v>
+      </c>
+      <c r="H66">
+        <v>541.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>160.8</v>
+      </c>
+      <c r="K66">
+        <v>207.7</v>
+      </c>
+      <c r="L66">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M66">
+        <v>307.5606912000001</v>
+      </c>
+      <c r="N66">
+        <v>-354.4606912</v>
+      </c>
+      <c r="O66">
+        <v>-91.45085832960001</v>
+      </c>
+      <c r="P66">
+        <v>-263.0098328704</v>
+      </c>
+      <c r="Q66">
+        <v>-55.30983287040004</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1469576794977965</v>
+      </c>
+      <c r="T66">
+        <v>2.334703097086891</v>
+      </c>
+      <c r="U66">
+        <v>0.2458</v>
+      </c>
+      <c r="V66">
+        <v>-0.03934247888697683</v>
+      </c>
+      <c r="W66">
+        <v>0.2554703813104189</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>-0.1524902282440961</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2184058086578748</v>
+      </c>
+      <c r="C67">
+        <v>-63.76060577716635</v>
+      </c>
+      <c r="D67">
+        <v>425.5543942228337</v>
+      </c>
+      <c r="E67">
+        <v>-142.585</v>
+      </c>
+      <c r="F67">
+        <v>1270.815</v>
+      </c>
+      <c r="G67">
+        <v>781.5</v>
+      </c>
+      <c r="H67">
+        <v>541.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>160.8</v>
+      </c>
+      <c r="K67">
+        <v>207.7</v>
+      </c>
+      <c r="L67">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M67">
+        <v>312.366327</v>
+      </c>
+      <c r="N67">
+        <v>-359.266327</v>
+      </c>
+      <c r="O67">
+        <v>-92.69071236600001</v>
+      </c>
+      <c r="P67">
+        <v>-266.575614634</v>
+      </c>
+      <c r="Q67">
+        <v>-58.87561463400004</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1498478989120192</v>
+      </c>
+      <c r="T67">
+        <v>2.401408899860803</v>
+      </c>
+      <c r="U67">
+        <v>0.2458</v>
+      </c>
+      <c r="V67">
+        <v>-0.03873720998102334</v>
+      </c>
+      <c r="W67">
+        <v>0.2553216062133356</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>-0.1501442247326488</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2204058086578748</v>
+      </c>
+      <c r="C68">
+        <v>-86.99978717392992</v>
+      </c>
+      <c r="D68">
+        <v>421.8662128260704</v>
+      </c>
+      <c r="E68">
+        <v>-123.0339999999999</v>
+      </c>
+      <c r="F68">
+        <v>1290.366</v>
+      </c>
+      <c r="G68">
+        <v>781.5</v>
+      </c>
+      <c r="H68">
+        <v>541.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>160.8</v>
+      </c>
+      <c r="K68">
+        <v>207.7</v>
+      </c>
+      <c r="L68">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M68">
+        <v>317.1719628000001</v>
+      </c>
+      <c r="N68">
+        <v>-364.0719628000001</v>
+      </c>
+      <c r="O68">
+        <v>-93.93056640240002</v>
+      </c>
+      <c r="P68">
+        <v>-270.1413963976</v>
+      </c>
+      <c r="Q68">
+        <v>-62.44139639760004</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.152908131232961</v>
+      </c>
+      <c r="T68">
+        <v>2.47203857338612</v>
+      </c>
+      <c r="U68">
+        <v>0.2458</v>
+      </c>
+      <c r="V68">
+        <v>-0.03815028255706843</v>
+      </c>
+      <c r="W68">
+        <v>0.2551773394525275</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>-0.1478693122366992</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2224058086578748</v>
+      </c>
+      <c r="C69">
+        <v>-110.1755886415431</v>
+      </c>
+      <c r="D69">
+        <v>418.2414113584571</v>
+      </c>
+      <c r="E69">
+        <v>-103.4829999999999</v>
+      </c>
+      <c r="F69">
+        <v>1309.917</v>
+      </c>
+      <c r="G69">
+        <v>781.5</v>
+      </c>
+      <c r="H69">
+        <v>541.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>160.8</v>
+      </c>
+      <c r="K69">
+        <v>207.7</v>
+      </c>
+      <c r="L69">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M69">
+        <v>321.9775986000001</v>
+      </c>
+      <c r="N69">
+        <v>-368.8775986000001</v>
+      </c>
+      <c r="O69">
+        <v>-95.17042043880002</v>
+      </c>
+      <c r="P69">
+        <v>-273.7071781612</v>
+      </c>
+      <c r="Q69">
+        <v>-66.00717816120004</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1561538321794143</v>
+      </c>
+      <c r="T69">
+        <v>2.5469488331857</v>
+      </c>
+      <c r="U69">
+        <v>0.2458</v>
+      </c>
+      <c r="V69">
+        <v>-0.03758087535472413</v>
+      </c>
+      <c r="W69">
+        <v>0.2550373791621912</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>-0.14566230757645</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2244058086578749</v>
+      </c>
+      <c r="C70">
+        <v>-133.2896300003026</v>
+      </c>
+      <c r="D70">
+        <v>414.6783699996978</v>
+      </c>
+      <c r="E70">
+        <v>-83.93199999999979</v>
+      </c>
+      <c r="F70">
+        <v>1329.468</v>
+      </c>
+      <c r="G70">
+        <v>781.5</v>
+      </c>
+      <c r="H70">
+        <v>541.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>160.8</v>
+      </c>
+      <c r="K70">
+        <v>207.7</v>
+      </c>
+      <c r="L70">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M70">
+        <v>326.7832344000001</v>
+      </c>
+      <c r="N70">
+        <v>-373.6832344000001</v>
+      </c>
+      <c r="O70">
+        <v>-96.41027447520001</v>
+      </c>
+      <c r="P70">
+        <v>-277.2729599248</v>
+      </c>
+      <c r="Q70">
+        <v>-69.57295992480005</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1596023894350211</v>
+      </c>
+      <c r="T70">
+        <v>2.626540984222753</v>
+      </c>
+      <c r="U70">
+        <v>0.2458</v>
+      </c>
+      <c r="V70">
+        <v>-0.03702821542303701</v>
+      </c>
+      <c r="W70">
+        <v>0.2549015353509825</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>-0.1435202148179728</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2264058086578749</v>
+      </c>
+      <c r="C71">
+        <v>-156.3434763391065</v>
+      </c>
+      <c r="D71">
+        <v>411.1755236608938</v>
+      </c>
+      <c r="E71">
+        <v>-64.38099999999986</v>
+      </c>
+      <c r="F71">
+        <v>1349.019</v>
+      </c>
+      <c r="G71">
+        <v>781.5</v>
+      </c>
+      <c r="H71">
+        <v>541.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>160.8</v>
+      </c>
+      <c r="K71">
+        <v>207.7</v>
+      </c>
+      <c r="L71">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M71">
+        <v>331.5888702000001</v>
+      </c>
+      <c r="N71">
+        <v>-378.4888702000001</v>
+      </c>
+      <c r="O71">
+        <v>-97.65012851160002</v>
+      </c>
+      <c r="P71">
+        <v>-280.8387416884</v>
+      </c>
+      <c r="Q71">
+        <v>-73.13874168840005</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1632734342555056</v>
+      </c>
+      <c r="T71">
+        <v>2.711268112746068</v>
+      </c>
+      <c r="U71">
+        <v>0.2458</v>
+      </c>
+      <c r="V71">
+        <v>-0.03649157461980459</v>
+      </c>
+      <c r="W71">
+        <v>0.254769629041548</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>-0.1414402117046689</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2284058086578749</v>
+      </c>
+      <c r="C72">
+        <v>-179.3386403077138</v>
+      </c>
+      <c r="D72">
+        <v>407.7313596922864</v>
+      </c>
+      <c r="E72">
+        <v>-44.82999999999993</v>
+      </c>
+      <c r="F72">
+        <v>1368.57</v>
+      </c>
+      <c r="G72">
+        <v>781.5</v>
+      </c>
+      <c r="H72">
+        <v>541.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>160.8</v>
+      </c>
+      <c r="K72">
+        <v>207.7</v>
+      </c>
+      <c r="L72">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M72">
+        <v>336.3945060000001</v>
+      </c>
+      <c r="N72">
+        <v>-383.2945060000001</v>
+      </c>
+      <c r="O72">
+        <v>-98.88998254800002</v>
+      </c>
+      <c r="P72">
+        <v>-284.404523452</v>
+      </c>
+      <c r="Q72">
+        <v>-76.70452345200005</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1671892153973558</v>
+      </c>
+      <c r="T72">
+        <v>2.80164371650427</v>
+      </c>
+      <c r="U72">
+        <v>0.2458</v>
+      </c>
+      <c r="V72">
+        <v>-0.03597026641095024</v>
+      </c>
+      <c r="W72">
+        <v>0.2546414914838116</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>-0.1394196372517451</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2304058086578748</v>
+      </c>
+      <c r="C73">
+        <v>-202.2765842947495</v>
+      </c>
+      <c r="D73">
+        <v>404.3444157052507</v>
+      </c>
+      <c r="E73">
+        <v>-25.279</v>
+      </c>
+      <c r="F73">
+        <v>1388.121</v>
+      </c>
+      <c r="G73">
+        <v>781.5</v>
+      </c>
+      <c r="H73">
+        <v>541.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>160.8</v>
+      </c>
+      <c r="K73">
+        <v>207.7</v>
+      </c>
+      <c r="L73">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M73">
+        <v>341.2001418</v>
+      </c>
+      <c r="N73">
+        <v>-388.1001418000001</v>
+      </c>
+      <c r="O73">
+        <v>-100.1298365844</v>
+      </c>
+      <c r="P73">
+        <v>-287.9703052156</v>
+      </c>
+      <c r="Q73">
+        <v>-80.27030521560005</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1713750504110577</v>
+      </c>
+      <c r="T73">
+        <v>2.898252120521658</v>
+      </c>
+      <c r="U73">
+        <v>0.2458</v>
+      </c>
+      <c r="V73">
+        <v>-0.03546364294037348</v>
+      </c>
+      <c r="W73">
+        <v>0.2545169634347438</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>-0.1374559803890445</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2324058086578748</v>
+      </c>
+      <c r="C74">
+        <v>-225.1587224980551</v>
+      </c>
+      <c r="D74">
+        <v>401.0132775019449</v>
+      </c>
+      <c r="E74">
+        <v>-5.728000000000065</v>
+      </c>
+      <c r="F74">
+        <v>1407.672</v>
+      </c>
+      <c r="G74">
+        <v>781.5</v>
+      </c>
+      <c r="H74">
+        <v>541.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>160.8</v>
+      </c>
+      <c r="K74">
+        <v>207.7</v>
+      </c>
+      <c r="L74">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M74">
+        <v>346.0057776</v>
+      </c>
+      <c r="N74">
+        <v>-392.9057776000001</v>
+      </c>
+      <c r="O74">
+        <v>-101.3696906208</v>
+      </c>
+      <c r="P74">
+        <v>-291.5360869792</v>
+      </c>
+      <c r="Q74">
+        <v>-83.83608697920005</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.175859873640024</v>
+      </c>
+      <c r="T74">
+        <v>3.001761124826003</v>
+      </c>
+      <c r="U74">
+        <v>0.2458</v>
+      </c>
+      <c r="V74">
+        <v>-0.0349710923439794</v>
+      </c>
+      <c r="W74">
+        <v>0.2543958944981501</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>-0.1355468695503079</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2344058086578749</v>
+      </c>
+      <c r="C75">
+        <v>-247.9864228935348</v>
+      </c>
+      <c r="D75">
+        <v>397.7365771064652</v>
+      </c>
+      <c r="E75">
+        <v>13.82299999999987</v>
+      </c>
+      <c r="F75">
+        <v>1427.223</v>
+      </c>
+      <c r="G75">
+        <v>781.5</v>
+      </c>
+      <c r="H75">
+        <v>541.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>160.8</v>
+      </c>
+      <c r="K75">
+        <v>207.7</v>
+      </c>
+      <c r="L75">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M75">
+        <v>350.8114134</v>
+      </c>
+      <c r="N75">
+        <v>-397.7114134</v>
+      </c>
+      <c r="O75">
+        <v>-102.6095446572</v>
+      </c>
+      <c r="P75">
+        <v>-295.1018687428</v>
+      </c>
+      <c r="Q75">
+        <v>-87.40186874279999</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.180676905997062</v>
+      </c>
+      <c r="T75">
+        <v>3.112937462782522</v>
+      </c>
+      <c r="U75">
+        <v>0.2458</v>
+      </c>
+      <c r="V75">
+        <v>-0.03449203628447284</v>
+      </c>
+      <c r="W75">
+        <v>0.2542781425187235</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>-0.1336900631181117</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2364058086578749</v>
+      </c>
+      <c r="C76">
+        <v>-270.7610091082595</v>
+      </c>
+      <c r="D76">
+        <v>394.5129908917405</v>
+      </c>
+      <c r="E76">
+        <v>33.37400000000002</v>
+      </c>
+      <c r="F76">
+        <v>1446.774</v>
+      </c>
+      <c r="G76">
+        <v>781.5</v>
+      </c>
+      <c r="H76">
+        <v>541.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>160.8</v>
+      </c>
+      <c r="K76">
+        <v>207.7</v>
+      </c>
+      <c r="L76">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M76">
+        <v>355.6170492000001</v>
+      </c>
+      <c r="N76">
+        <v>-402.5170492000001</v>
+      </c>
+      <c r="O76">
+        <v>-103.8493986936</v>
+      </c>
+      <c r="P76">
+        <v>-298.6676505064</v>
+      </c>
+      <c r="Q76">
+        <v>-90.96765050640005</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1858644793046413</v>
+      </c>
+      <c r="T76">
+        <v>3.232665826735695</v>
+      </c>
+      <c r="U76">
+        <v>0.2458</v>
+      </c>
+      <c r="V76">
+        <v>-0.03402592768603401</v>
+      </c>
+      <c r="W76">
+        <v>0.2541635730252272</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>-0.1318834406435427</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2384058086578748</v>
+      </c>
+      <c r="C77">
+        <v>-293.4837622032164</v>
+      </c>
+      <c r="D77">
+        <v>391.3412377967836</v>
+      </c>
+      <c r="E77">
+        <v>52.92499999999995</v>
+      </c>
+      <c r="F77">
+        <v>1466.325</v>
+      </c>
+      <c r="G77">
+        <v>781.5</v>
+      </c>
+      <c r="H77">
+        <v>541.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>160.8</v>
+      </c>
+      <c r="K77">
+        <v>207.7</v>
+      </c>
+      <c r="L77">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M77">
+        <v>360.4226850000001</v>
+      </c>
+      <c r="N77">
+        <v>-407.3226850000001</v>
+      </c>
+      <c r="O77">
+        <v>-105.08925273</v>
+      </c>
+      <c r="P77">
+        <v>-302.2334322700001</v>
+      </c>
+      <c r="Q77">
+        <v>-94.53343227000011</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1914670584768269</v>
+      </c>
+      <c r="T77">
+        <v>3.361972459805123</v>
+      </c>
+      <c r="U77">
+        <v>0.2458</v>
+      </c>
+      <c r="V77">
+        <v>-0.03357224865022022</v>
+      </c>
+      <c r="W77">
+        <v>0.2540520587182241</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>-0.1301249947682954</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2404058086578749</v>
+      </c>
+      <c r="C78">
+        <v>-316.1559223707482</v>
+      </c>
+      <c r="D78">
+        <v>388.220077629252</v>
+      </c>
+      <c r="E78">
+        <v>72.47600000000011</v>
+      </c>
+      <c r="F78">
+        <v>1485.876</v>
+      </c>
+      <c r="G78">
+        <v>781.5</v>
+      </c>
+      <c r="H78">
+        <v>541.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>160.8</v>
+      </c>
+      <c r="K78">
+        <v>207.7</v>
+      </c>
+      <c r="L78">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M78">
+        <v>365.2283208000001</v>
+      </c>
+      <c r="N78">
+        <v>-412.1283208000001</v>
+      </c>
+      <c r="O78">
+        <v>-106.3291067664</v>
+      </c>
+      <c r="P78">
+        <v>-305.7992140336</v>
+      </c>
+      <c r="Q78">
+        <v>-98.09921403360005</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.1975365192466947</v>
+      </c>
+      <c r="T78">
+        <v>3.502054645630337</v>
+      </c>
+      <c r="U78">
+        <v>0.2458</v>
+      </c>
+      <c r="V78">
+        <v>-0.03313050853640154</v>
+      </c>
+      <c r="W78">
+        <v>0.2539434789982475</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>-0.1284128237845021</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2424058086578749</v>
+      </c>
+      <c r="C79">
+        <v>-338.7786905514051</v>
+      </c>
+      <c r="D79">
+        <v>385.1483094485951</v>
+      </c>
+      <c r="E79">
+        <v>92.02700000000004</v>
+      </c>
+      <c r="F79">
+        <v>1505.427</v>
+      </c>
+      <c r="G79">
+        <v>781.5</v>
+      </c>
+      <c r="H79">
+        <v>541.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>160.8</v>
+      </c>
+      <c r="K79">
+        <v>207.7</v>
+      </c>
+      <c r="L79">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M79">
+        <v>370.0339566000001</v>
+      </c>
+      <c r="N79">
+        <v>-416.9339566000001</v>
+      </c>
+      <c r="O79">
+        <v>-107.5689608028</v>
+      </c>
+      <c r="P79">
+        <v>-309.3649957972001</v>
+      </c>
+      <c r="Q79">
+        <v>-101.6649957972001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2041337592139423</v>
+      </c>
+      <c r="T79">
+        <v>3.654317891092526</v>
+      </c>
+      <c r="U79">
+        <v>0.2458</v>
+      </c>
+      <c r="V79">
+        <v>-0.03270024219177294</v>
+      </c>
+      <c r="W79">
+        <v>0.2538377195307378</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>-0.1267451247743139</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2444058086578748</v>
+      </c>
+      <c r="C80">
+        <v>-361.3532299746435</v>
+      </c>
+      <c r="D80">
+        <v>382.1247700253567</v>
+      </c>
+      <c r="E80">
+        <v>111.578</v>
+      </c>
+      <c r="F80">
+        <v>1524.978</v>
+      </c>
+      <c r="G80">
+        <v>781.5</v>
+      </c>
+      <c r="H80">
+        <v>541.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>160.8</v>
+      </c>
+      <c r="K80">
+        <v>207.7</v>
+      </c>
+      <c r="L80">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M80">
+        <v>374.8395924000001</v>
+      </c>
+      <c r="N80">
+        <v>-421.7395924000001</v>
+      </c>
+      <c r="O80">
+        <v>-108.8088148392</v>
+      </c>
+      <c r="P80">
+        <v>-312.9307775608001</v>
+      </c>
+      <c r="Q80">
+        <v>-105.2307775608001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2113307482691215</v>
+      </c>
+      <c r="T80">
+        <v>3.82042324977855</v>
+      </c>
+      <c r="U80">
+        <v>0.2458</v>
+      </c>
+      <c r="V80">
+        <v>-0.03228100831751945</v>
+      </c>
+      <c r="W80">
+        <v>0.2537346718444463</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>-0.1251201872772072</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2464058086578749</v>
+      </c>
+      <c r="C81">
+        <v>-383.8806676275169</v>
+      </c>
+      <c r="D81">
+        <v>379.1483323724834</v>
+      </c>
+      <c r="E81">
+        <v>131.1290000000001</v>
+      </c>
+      <c r="F81">
+        <v>1544.529</v>
+      </c>
+      <c r="G81">
+        <v>781.5</v>
+      </c>
+      <c r="H81">
+        <v>541.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>160.8</v>
+      </c>
+      <c r="K81">
+        <v>207.7</v>
+      </c>
+      <c r="L81">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M81">
+        <v>379.6452282000001</v>
+      </c>
+      <c r="N81">
+        <v>-426.5452282000001</v>
+      </c>
+      <c r="O81">
+        <v>-110.0486688756</v>
+      </c>
+      <c r="P81">
+        <v>-316.4965593244001</v>
+      </c>
+      <c r="Q81">
+        <v>-108.7965593244001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2192131648533654</v>
+      </c>
+      <c r="T81">
+        <v>4.002348166434672</v>
+      </c>
+      <c r="U81">
+        <v>0.2458</v>
+      </c>
+      <c r="V81">
+        <v>-0.03187238795906983</v>
+      </c>
+      <c r="W81">
+        <v>0.2536342329603394</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>-0.1235363874382553</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2484058086578748</v>
+      </c>
+      <c r="C82">
+        <v>-406.3620956552588</v>
+      </c>
+      <c r="D82">
+        <v>376.2179043447414</v>
+      </c>
+      <c r="E82">
+        <v>150.6800000000001</v>
+      </c>
+      <c r="F82">
+        <v>1564.08</v>
+      </c>
+      <c r="G82">
+        <v>781.5</v>
+      </c>
+      <c r="H82">
+        <v>541.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>160.8</v>
+      </c>
+      <c r="K82">
+        <v>207.7</v>
+      </c>
+      <c r="L82">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M82">
+        <v>384.4508640000001</v>
+      </c>
+      <c r="N82">
+        <v>-431.3508640000001</v>
+      </c>
+      <c r="O82">
+        <v>-111.288522912</v>
+      </c>
+      <c r="P82">
+        <v>-320.0623410880001</v>
+      </c>
+      <c r="Q82">
+        <v>-112.3623410880001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2278838230960337</v>
+      </c>
+      <c r="T82">
+        <v>4.202465574756405</v>
+      </c>
+      <c r="U82">
+        <v>0.2458</v>
+      </c>
+      <c r="V82">
+        <v>-0.03147398310958146</v>
+      </c>
+      <c r="W82">
+        <v>0.2535363050483351</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>-0.121992182595277</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2504058086578748</v>
+      </c>
+      <c r="C83">
+        <v>-428.7985726974148</v>
+      </c>
+      <c r="D83">
+        <v>373.3324273025856</v>
+      </c>
+      <c r="E83">
+        <v>170.2310000000002</v>
+      </c>
+      <c r="F83">
+        <v>1583.631</v>
+      </c>
+      <c r="G83">
+        <v>781.5</v>
+      </c>
+      <c r="H83">
+        <v>541.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>160.8</v>
+      </c>
+      <c r="K83">
+        <v>207.7</v>
+      </c>
+      <c r="L83">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M83">
+        <v>389.2564998000001</v>
+      </c>
+      <c r="N83">
+        <v>-436.1564998000001</v>
+      </c>
+      <c r="O83">
+        <v>-112.5283769484</v>
+      </c>
+      <c r="P83">
+        <v>-323.6281228516001</v>
+      </c>
+      <c r="Q83">
+        <v>-115.9281228516001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2374671822063512</v>
+      </c>
+      <c r="T83">
+        <v>4.423647973427795</v>
+      </c>
+      <c r="U83">
+        <v>0.2458</v>
+      </c>
+      <c r="V83">
+        <v>-0.03108541541687058</v>
+      </c>
+      <c r="W83">
+        <v>0.2534407951094668</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>-0.1204861062669402</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2524058086578748</v>
+      </c>
+      <c r="C84">
+        <v>-451.1911251629531</v>
+      </c>
+      <c r="D84">
+        <v>370.4908748370471</v>
+      </c>
+      <c r="E84">
+        <v>189.7820000000002</v>
+      </c>
+      <c r="F84">
+        <v>1603.182</v>
+      </c>
+      <c r="G84">
+        <v>781.5</v>
+      </c>
+      <c r="H84">
+        <v>541.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>160.8</v>
+      </c>
+      <c r="K84">
+        <v>207.7</v>
+      </c>
+      <c r="L84">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M84">
+        <v>394.0621356000001</v>
+      </c>
+      <c r="N84">
+        <v>-440.9621356000001</v>
+      </c>
+      <c r="O84">
+        <v>-113.7682309848</v>
+      </c>
+      <c r="P84">
+        <v>-327.1939046152001</v>
+      </c>
+      <c r="Q84">
+        <v>-119.4939046152001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.248115358995593</v>
+      </c>
+      <c r="T84">
+        <v>4.669406194173784</v>
+      </c>
+      <c r="U84">
+        <v>0.2458</v>
+      </c>
+      <c r="V84">
+        <v>-0.03070632498495752</v>
+      </c>
+      <c r="W84">
+        <v>0.2533476146813026</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>-0.1190167635075874</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2544058086578748</v>
+      </c>
+      <c r="C85">
+        <v>-473.5407484475877</v>
+      </c>
+      <c r="D85">
+        <v>367.6922515524126</v>
+      </c>
+      <c r="E85">
+        <v>209.3330000000001</v>
+      </c>
+      <c r="F85">
+        <v>1622.733</v>
+      </c>
+      <c r="G85">
+        <v>781.5</v>
+      </c>
+      <c r="H85">
+        <v>541.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>160.8</v>
+      </c>
+      <c r="K85">
+        <v>207.7</v>
+      </c>
+      <c r="L85">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M85">
+        <v>398.8677714000001</v>
+      </c>
+      <c r="N85">
+        <v>-445.7677714000001</v>
+      </c>
+      <c r="O85">
+        <v>-115.0080850212</v>
+      </c>
+      <c r="P85">
+        <v>-330.7596863788001</v>
+      </c>
+      <c r="Q85">
+        <v>-123.0596863788001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.260016262465922</v>
+      </c>
+      <c r="T85">
+        <v>4.944077146772242</v>
+      </c>
+      <c r="U85">
+        <v>0.2458</v>
+      </c>
+      <c r="V85">
+        <v>-0.03033636926224719</v>
+      </c>
+      <c r="W85">
+        <v>0.2532566795646604</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>-0.1175828265978573</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2564058086578748</v>
+      </c>
+      <c r="C86">
+        <v>-495.8484080963378</v>
+      </c>
+      <c r="D86">
+        <v>364.9355919036623</v>
+      </c>
+      <c r="E86">
+        <v>228.884</v>
+      </c>
+      <c r="F86">
+        <v>1642.284</v>
+      </c>
+      <c r="G86">
+        <v>781.5</v>
+      </c>
+      <c r="H86">
+        <v>541.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>160.8</v>
+      </c>
+      <c r="K86">
+        <v>207.7</v>
+      </c>
+      <c r="L86">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M86">
+        <v>403.6734072</v>
+      </c>
+      <c r="N86">
+        <v>-450.5734072</v>
+      </c>
+      <c r="O86">
+        <v>-116.2479390576</v>
+      </c>
+      <c r="P86">
+        <v>-334.3254681424</v>
+      </c>
+      <c r="Q86">
+        <v>-126.6254681424001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.273404778870042</v>
+      </c>
+      <c r="T86">
+        <v>5.253081968445504</v>
+      </c>
+      <c r="U86">
+        <v>0.2458</v>
+      </c>
+      <c r="V86">
+        <v>-0.0299752220091252</v>
+      </c>
+      <c r="W86">
+        <v>0.253167909569843</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>-0.1161830310431209</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2584058086578748</v>
+      </c>
+      <c r="C87">
+        <v>-518.1150409141849</v>
+      </c>
+      <c r="D87">
+        <v>362.2199590858152</v>
+      </c>
+      <c r="E87">
+        <v>248.4349999999999</v>
+      </c>
+      <c r="F87">
+        <v>1661.835</v>
+      </c>
+      <c r="G87">
+        <v>781.5</v>
+      </c>
+      <c r="H87">
+        <v>541.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>160.8</v>
+      </c>
+      <c r="K87">
+        <v>207.7</v>
+      </c>
+      <c r="L87">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M87">
+        <v>408.479043</v>
+      </c>
+      <c r="N87">
+        <v>-455.379043</v>
+      </c>
+      <c r="O87">
+        <v>-117.487793094</v>
+      </c>
+      <c r="P87">
+        <v>-337.891249906</v>
+      </c>
+      <c r="Q87">
+        <v>-130.191249906</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.2885784307947115</v>
+      </c>
+      <c r="T87">
+        <v>5.603287433008539</v>
+      </c>
+      <c r="U87">
+        <v>0.2458</v>
+      </c>
+      <c r="V87">
+        <v>-0.02962257233842961</v>
+      </c>
+      <c r="W87">
+        <v>0.253081228280786</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>-0.1148161718543783</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2604058086578749</v>
+      </c>
+      <c r="C88">
+        <v>-540.3415560275043</v>
+      </c>
+      <c r="D88">
+        <v>359.5444439724959</v>
+      </c>
+      <c r="E88">
+        <v>267.9860000000001</v>
+      </c>
+      <c r="F88">
+        <v>1681.386</v>
+      </c>
+      <c r="G88">
+        <v>781.5</v>
+      </c>
+      <c r="H88">
+        <v>541.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>160.8</v>
+      </c>
+      <c r="K88">
+        <v>207.7</v>
+      </c>
+      <c r="L88">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M88">
+        <v>413.2846788000001</v>
+      </c>
+      <c r="N88">
+        <v>-460.1846788</v>
+      </c>
+      <c r="O88">
+        <v>-118.7276471304</v>
+      </c>
+      <c r="P88">
+        <v>-341.4570316696</v>
+      </c>
+      <c r="Q88">
+        <v>-133.7570316696001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3059197472800481</v>
+      </c>
+      <c r="T88">
+        <v>6.003522249652007</v>
+      </c>
+      <c r="U88">
+        <v>0.2458</v>
+      </c>
+      <c r="V88">
+        <v>-0.02927812382286648</v>
+      </c>
+      <c r="W88">
+        <v>0.2529965628356606</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>-0.1134811000886298</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2624058086578749</v>
+      </c>
+      <c r="C89">
+        <v>-562.5288358988007</v>
+      </c>
+      <c r="D89">
+        <v>356.9081641011995</v>
+      </c>
+      <c r="E89">
+        <v>287.537</v>
+      </c>
+      <c r="F89">
+        <v>1700.937</v>
+      </c>
+      <c r="G89">
+        <v>781.5</v>
+      </c>
+      <c r="H89">
+        <v>541.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>160.8</v>
+      </c>
+      <c r="K89">
+        <v>207.7</v>
+      </c>
+      <c r="L89">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M89">
+        <v>418.0903146000001</v>
+      </c>
+      <c r="N89">
+        <v>-464.9903146</v>
+      </c>
+      <c r="O89">
+        <v>-119.9675011668</v>
+      </c>
+      <c r="P89">
+        <v>-345.0228134332</v>
+      </c>
+      <c r="Q89">
+        <v>-137.3228134332001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3259289586092825</v>
+      </c>
+      <c r="T89">
+        <v>6.465331653471391</v>
+      </c>
+      <c r="U89">
+        <v>0.2458</v>
+      </c>
+      <c r="V89">
+        <v>-0.02894159366398296</v>
+      </c>
+      <c r="W89">
+        <v>0.2529138437226071</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>-0.1121767196278409</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2644058086578748</v>
+      </c>
+      <c r="C90">
+        <v>-584.6777372971287</v>
+      </c>
+      <c r="D90">
+        <v>354.3102627028713</v>
+      </c>
+      <c r="E90">
+        <v>307.088</v>
+      </c>
+      <c r="F90">
+        <v>1720.488</v>
+      </c>
+      <c r="G90">
+        <v>781.5</v>
+      </c>
+      <c r="H90">
+        <v>541.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>160.8</v>
+      </c>
+      <c r="K90">
+        <v>207.7</v>
+      </c>
+      <c r="L90">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M90">
+        <v>422.8959504000001</v>
+      </c>
+      <c r="N90">
+        <v>-469.7959504</v>
+      </c>
+      <c r="O90">
+        <v>-121.2073552032</v>
+      </c>
+      <c r="P90">
+        <v>-348.5885951968</v>
+      </c>
+      <c r="Q90">
+        <v>-140.8885951968001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3492730384933894</v>
+      </c>
+      <c r="T90">
+        <v>7.004109291260674</v>
+      </c>
+      <c r="U90">
+        <v>0.2458</v>
+      </c>
+      <c r="V90">
+        <v>-0.02861271191780133</v>
+      </c>
+      <c r="W90">
+        <v>0.2528330045893956</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>-0.1109019841775245</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2664058086578749</v>
+      </c>
+      <c r="C91">
+        <v>-606.7890922264371</v>
+      </c>
+      <c r="D91">
+        <v>351.7499077735631</v>
+      </c>
+      <c r="E91">
+        <v>326.6390000000001</v>
+      </c>
+      <c r="F91">
+        <v>1740.039</v>
+      </c>
+      <c r="G91">
+        <v>781.5</v>
+      </c>
+      <c r="H91">
+        <v>541.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>160.8</v>
+      </c>
+      <c r="K91">
+        <v>207.7</v>
+      </c>
+      <c r="L91">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M91">
+        <v>427.7015862000001</v>
+      </c>
+      <c r="N91">
+        <v>-474.6015862</v>
+      </c>
+      <c r="O91">
+        <v>-122.4472092396</v>
+      </c>
+      <c r="P91">
+        <v>-352.1543769604</v>
+      </c>
+      <c r="Q91">
+        <v>-144.4543769604001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.3768614965382431</v>
+      </c>
+      <c r="T91">
+        <v>7.6408464995571</v>
+      </c>
+      <c r="U91">
+        <v>0.2458</v>
+      </c>
+      <c r="V91">
+        <v>-0.02829122077265749</v>
+      </c>
+      <c r="W91">
+        <v>0.2527539820659193</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>-0.1096558944676647</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2684058086578748</v>
+      </c>
+      <c r="C92">
+        <v>-628.8637088139476</v>
+      </c>
+      <c r="D92">
+        <v>349.2262911860526</v>
+      </c>
+      <c r="E92">
+        <v>346.1900000000001</v>
+      </c>
+      <c r="F92">
+        <v>1759.59</v>
+      </c>
+      <c r="G92">
+        <v>781.5</v>
+      </c>
+      <c r="H92">
+        <v>541.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>160.8</v>
+      </c>
+      <c r="K92">
+        <v>207.7</v>
+      </c>
+      <c r="L92">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M92">
+        <v>432.5072220000001</v>
+      </c>
+      <c r="N92">
+        <v>-479.407222</v>
+      </c>
+      <c r="O92">
+        <v>-123.687063276</v>
+      </c>
+      <c r="P92">
+        <v>-355.720158724</v>
+      </c>
+      <c r="Q92">
+        <v>-148.0201587240001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4099676461920674</v>
+      </c>
+      <c r="T92">
+        <v>8.404931149512811</v>
+      </c>
+      <c r="U92">
+        <v>0.2458</v>
+      </c>
+      <c r="V92">
+        <v>-0.02797687387518352</v>
+      </c>
+      <c r="W92">
+        <v>0.2526767155985201</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>-0.1084374956402461</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2704058086578748</v>
+      </c>
+      <c r="C93">
+        <v>-650.9023721605704</v>
+      </c>
+      <c r="D93">
+        <v>346.7386278394298</v>
+      </c>
+      <c r="E93">
+        <v>365.741</v>
+      </c>
+      <c r="F93">
+        <v>1779.141</v>
+      </c>
+      <c r="G93">
+        <v>781.5</v>
+      </c>
+      <c r="H93">
+        <v>541.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>160.8</v>
+      </c>
+      <c r="K93">
+        <v>207.7</v>
+      </c>
+      <c r="L93">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M93">
+        <v>437.3128578000001</v>
+      </c>
+      <c r="N93">
+        <v>-484.2128578000001</v>
+      </c>
+      <c r="O93">
+        <v>-124.9269173124</v>
+      </c>
+      <c r="P93">
+        <v>-359.2859404876</v>
+      </c>
+      <c r="Q93">
+        <v>-151.5859404876001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.450430717991186</v>
+      </c>
+      <c r="T93">
+        <v>9.338812388347568</v>
+      </c>
+      <c r="U93">
+        <v>0.2458</v>
+      </c>
+      <c r="V93">
+        <v>-0.02766943570073096</v>
+      </c>
+      <c r="W93">
+        <v>0.2526011472952397</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>-0.1072458748090346</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2724058086578749</v>
+      </c>
+      <c r="C94">
+        <v>-672.9058451552246</v>
+      </c>
+      <c r="D94">
+        <v>344.2861548447756</v>
+      </c>
+      <c r="E94">
+        <v>385.2920000000001</v>
+      </c>
+      <c r="F94">
+        <v>1798.692</v>
+      </c>
+      <c r="G94">
+        <v>781.5</v>
+      </c>
+      <c r="H94">
+        <v>541.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>160.8</v>
+      </c>
+      <c r="K94">
+        <v>207.7</v>
+      </c>
+      <c r="L94">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M94">
+        <v>442.1184936000001</v>
+      </c>
+      <c r="N94">
+        <v>-489.0184936000001</v>
+      </c>
+      <c r="O94">
+        <v>-126.1667713488</v>
+      </c>
+      <c r="P94">
+        <v>-362.8517222512</v>
+      </c>
+      <c r="Q94">
+        <v>-155.1517222512001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5010095577400844</v>
+      </c>
+      <c r="T94">
+        <v>10.50616393689102</v>
+      </c>
+      <c r="U94">
+        <v>0.2458</v>
+      </c>
+      <c r="V94">
+        <v>-0.02736868096485344</v>
+      </c>
+      <c r="W94">
+        <v>0.252527221781161</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>-0.1060801587785016</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2744058086578748</v>
+      </c>
+      <c r="C95">
+        <v>-694.8748692548459</v>
+      </c>
+      <c r="D95">
+        <v>341.8681307451542</v>
+      </c>
+      <c r="E95">
+        <v>404.8430000000001</v>
+      </c>
+      <c r="F95">
+        <v>1818.243</v>
+      </c>
+      <c r="G95">
+        <v>781.5</v>
+      </c>
+      <c r="H95">
+        <v>541.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>160.8</v>
+      </c>
+      <c r="K95">
+        <v>207.7</v>
+      </c>
+      <c r="L95">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M95">
+        <v>446.9241294000001</v>
+      </c>
+      <c r="N95">
+        <v>-493.8241294000001</v>
+      </c>
+      <c r="O95">
+        <v>-127.4066253852</v>
+      </c>
+      <c r="P95">
+        <v>-366.4175040148</v>
+      </c>
+      <c r="Q95">
+        <v>-158.7175040148001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.5660394945600964</v>
+      </c>
+      <c r="T95">
+        <v>12.00704449930402</v>
+      </c>
+      <c r="U95">
+        <v>0.2458</v>
+      </c>
+      <c r="V95">
+        <v>-0.02707439407275825</v>
+      </c>
+      <c r="W95">
+        <v>0.252454886063084</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>-0.1049395119099157</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2764058086578748</v>
+      </c>
+      <c r="C96">
+        <v>-716.8101652317541</v>
+      </c>
+      <c r="D96">
+        <v>339.4838347682461</v>
+      </c>
+      <c r="E96">
+        <v>424.3940000000002</v>
+      </c>
+      <c r="F96">
+        <v>1837.794</v>
+      </c>
+      <c r="G96">
+        <v>781.5</v>
+      </c>
+      <c r="H96">
+        <v>541.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>160.8</v>
+      </c>
+      <c r="K96">
+        <v>207.7</v>
+      </c>
+      <c r="L96">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M96">
+        <v>451.7297652000001</v>
+      </c>
+      <c r="N96">
+        <v>-498.6297652000001</v>
+      </c>
+      <c r="O96">
+        <v>-128.6464794216</v>
+      </c>
+      <c r="P96">
+        <v>-369.9832857784</v>
+      </c>
+      <c r="Q96">
+        <v>-162.2832857784001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.6527460769867793</v>
+      </c>
+      <c r="T96">
+        <v>14.00821858252136</v>
+      </c>
+      <c r="U96">
+        <v>0.2458</v>
+      </c>
+      <c r="V96">
+        <v>-0.02678636860389912</v>
+      </c>
+      <c r="W96">
+        <v>0.2523840894028384</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>-0.10382313412364</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2784058086578748</v>
+      </c>
+      <c r="C97">
+        <v>-738.7124338899609</v>
+      </c>
+      <c r="D97">
+        <v>337.1325661100394</v>
+      </c>
+      <c r="E97">
+        <v>443.9450000000002</v>
+      </c>
+      <c r="F97">
+        <v>1857.345</v>
+      </c>
+      <c r="G97">
+        <v>781.5</v>
+      </c>
+      <c r="H97">
+        <v>541.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>160.8</v>
+      </c>
+      <c r="K97">
+        <v>207.7</v>
+      </c>
+      <c r="L97">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M97">
+        <v>456.5354010000001</v>
+      </c>
+      <c r="N97">
+        <v>-503.4354010000001</v>
+      </c>
+      <c r="O97">
+        <v>-129.886333458</v>
+      </c>
+      <c r="P97">
+        <v>-373.549067542</v>
+      </c>
+      <c r="Q97">
+        <v>-165.8490675420001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.7741352923841355</v>
+      </c>
+      <c r="T97">
+        <v>16.80986229902564</v>
+      </c>
+      <c r="U97">
+        <v>0.2458</v>
+      </c>
+      <c r="V97">
+        <v>-0.02650440682912123</v>
+      </c>
+      <c r="W97">
+        <v>0.252314783198598</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>-0.1027302590276016</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2804058086578749</v>
+      </c>
+      <c r="C98">
+        <v>-760.5823567519187</v>
+      </c>
+      <c r="D98">
+        <v>334.8136432480813</v>
+      </c>
+      <c r="E98">
+        <v>463.4959999999999</v>
+      </c>
+      <c r="F98">
+        <v>1876.896</v>
+      </c>
+      <c r="G98">
+        <v>781.5</v>
+      </c>
+      <c r="H98">
+        <v>541.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>160.8</v>
+      </c>
+      <c r="K98">
+        <v>207.7</v>
+      </c>
+      <c r="L98">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M98">
+        <v>461.3410368</v>
+      </c>
+      <c r="N98">
+        <v>-508.2410368000001</v>
+      </c>
+      <c r="O98">
+        <v>-131.1261874944</v>
+      </c>
+      <c r="P98">
+        <v>-377.1148493056</v>
+      </c>
+      <c r="Q98">
+        <v>-169.4148493056001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>0.9562191154801675</v>
+      </c>
+      <c r="T98">
+        <v>21.01232787378201</v>
+      </c>
+      <c r="U98">
+        <v>0.2458</v>
+      </c>
+      <c r="V98">
+        <v>-0.02622831925798455</v>
+      </c>
+      <c r="W98">
+        <v>0.2522469208736127</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>-0.1016601521627309</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2824058086578748</v>
+      </c>
+      <c r="C99">
+        <v>-782.4205967171188</v>
+      </c>
+      <c r="D99">
+        <v>332.5264032828813</v>
+      </c>
+      <c r="E99">
+        <v>483.047</v>
+      </c>
+      <c r="F99">
+        <v>1896.447</v>
+      </c>
+      <c r="G99">
+        <v>781.5</v>
+      </c>
+      <c r="H99">
+        <v>541.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>160.8</v>
+      </c>
+      <c r="K99">
+        <v>207.7</v>
+      </c>
+      <c r="L99">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M99">
+        <v>466.1466726</v>
+      </c>
+      <c r="N99">
+        <v>-513.0466726000001</v>
+      </c>
+      <c r="O99">
+        <v>-132.3660415308</v>
+      </c>
+      <c r="P99">
+        <v>-380.6806310692</v>
+      </c>
+      <c r="Q99">
+        <v>-172.9806310692001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.259692153973557</v>
+      </c>
+      <c r="T99">
+        <v>28.01643716504267</v>
+      </c>
+      <c r="U99">
+        <v>0.2458</v>
+      </c>
+      <c r="V99">
+        <v>-0.02595792421408781</v>
+      </c>
+      <c r="W99">
+        <v>0.2521804577718228</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>-0.1006121093569294</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2844058086578748</v>
+      </c>
+      <c r="C100">
+        <v>-804.2277986938773</v>
+      </c>
+      <c r="D100">
+        <v>330.2702013061228</v>
+      </c>
+      <c r="E100">
+        <v>502.598</v>
+      </c>
+      <c r="F100">
+        <v>1915.998</v>
+      </c>
+      <c r="G100">
+        <v>781.5</v>
+      </c>
+      <c r="H100">
+        <v>541.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>160.8</v>
+      </c>
+      <c r="K100">
+        <v>207.7</v>
+      </c>
+      <c r="L100">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M100">
+        <v>470.9523084</v>
+      </c>
+      <c r="N100">
+        <v>-517.8523084000001</v>
+      </c>
+      <c r="O100">
+        <v>-133.6058955672</v>
+      </c>
+      <c r="P100">
+        <v>-384.2464128328</v>
+      </c>
+      <c r="Q100">
+        <v>-176.5464128328001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.866638230960335</v>
+      </c>
+      <c r="T100">
+        <v>42.024655747564</v>
+      </c>
+      <c r="U100">
+        <v>0.2458</v>
+      </c>
+      <c r="V100">
+        <v>-0.02569304743639303</v>
+      </c>
+      <c r="W100">
+        <v>0.2521153510598654</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>-0.09958545517981809</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2864058086578748</v>
+      </c>
+      <c r="C101">
+        <v>-826.0045902055761</v>
+      </c>
+      <c r="D101">
+        <v>328.0444097944241</v>
+      </c>
+      <c r="E101">
+        <v>522.1490000000001</v>
+      </c>
+      <c r="F101">
+        <v>1935.549</v>
+      </c>
+      <c r="G101">
+        <v>781.5</v>
+      </c>
+      <c r="H101">
+        <v>541.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>160.8</v>
+      </c>
+      <c r="K101">
+        <v>207.7</v>
+      </c>
+      <c r="L101">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="M101">
+        <v>475.7579442000001</v>
+      </c>
+      <c r="N101">
+        <v>-522.6579442000001</v>
+      </c>
+      <c r="O101">
+        <v>-134.8457496036</v>
+      </c>
+      <c r="P101">
+        <v>-387.8121945964001</v>
+      </c>
+      <c r="Q101">
+        <v>-180.1121945964001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>3.68747646192067</v>
+      </c>
+      <c r="T101">
+        <v>84.04931149512802</v>
+      </c>
+      <c r="U101">
+        <v>0.2458</v>
+      </c>
+      <c r="V101">
+        <v>-0.02543352170471229</v>
+      </c>
+      <c r="W101">
+        <v>0.2520515596350183</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>-0.09857954149113279</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/netherlands/netherlands_transportation.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_transportation.xlsx
@@ -650,10 +650,10 @@
         <v>0.1267942583732057</v>
       </c>
       <c r="X2">
-        <v>0.1500943537698408</v>
+        <v>0.1500273017732331</v>
       </c>
       <c r="Y2">
-        <v>-0.02330009539663502</v>
+        <v>-0.02323304340002741</v>
       </c>
       <c r="Z2">
         <v>5.910472414932276</v>
@@ -662,10 +662,10 @@
         <v>0.04245127188635613</v>
       </c>
       <c r="AB2">
-        <v>0.07259139955865312</v>
+        <v>0.07257282144675996</v>
       </c>
       <c r="AC2">
-        <v>-0.030140127672297</v>
+        <v>-0.03012154956040383</v>
       </c>
       <c r="AD2">
         <v>1413.4</v>
@@ -787,10 +787,10 @@
         <v>0.1267942583732057</v>
       </c>
       <c r="X3">
-        <v>0.1500943537698408</v>
+        <v>0.1500273017732331</v>
       </c>
       <c r="Y3">
-        <v>-0.02330009539663502</v>
+        <v>-0.02323304340002741</v>
       </c>
       <c r="Z3">
         <v>5.910472414932276</v>
@@ -799,10 +799,10 @@
         <v>0.04245127188635613</v>
       </c>
       <c r="AB3">
-        <v>0.07259139955865312</v>
+        <v>0.07257282144675996</v>
       </c>
       <c r="AC3">
-        <v>-0.030140127672297</v>
+        <v>-0.03012154956040383</v>
       </c>
       <c r="AD3">
         <v>1413.4</v>
@@ -1139,7 +1139,7 @@
         <v>-3.12186379928315</v>
       </c>
       <c r="F2">
-        <v>-9.75937460762216</v>
+        <v>-10.1732581787681</v>
       </c>
       <c r="G2">
         <v>11.7197346600332</v>
@@ -1157,13 +1157,13 @@
         <v>541.7</v>
       </c>
       <c r="L2">
-        <v>1728.06946826041</v>
+        <v>1728.70862578247</v>
       </c>
       <c r="M2">
         <v>1173.6</v>
       </c>
       <c r="N2">
-        <v>966.120468260414</v>
+        <v>966.759625782469</v>
       </c>
       <c r="O2">
         <v>1413.4</v>
@@ -1172,16 +1172,16 @@
         <v>19.551</v>
       </c>
       <c r="Q2">
-        <v>0.0725913995586531</v>
+        <v>0.07257282144676</v>
       </c>
       <c r="R2">
-        <v>0.0904058086578748</v>
+        <v>0.0903203029819159</v>
       </c>
       <c r="S2">
         <v>0.0428876</v>
       </c>
       <c r="T2">
-        <v>0.86470440386681</v>
+        <v>0.85470440386681</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.150094353769841</v>
+        <v>0.150027301773233</v>
       </c>
       <c r="X2">
-        <v>0.0825846107264714</v>
+        <v>0.082599251457826</v>
       </c>
       <c r="Y2">
         <v>2.4070970386428</v>
       </c>
       <c r="Z2">
-        <v>0.848982944395233</v>
+        <v>0.849867239210763</v>
       </c>
       <c r="AA2">
         <v>1413.4</v>
@@ -1236,7 +1236,7 @@
         <v>541.7</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -1495,13 +1495,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.09040580865787483</v>
+        <v>0.09032030298191587</v>
       </c>
       <c r="C3">
-        <v>1728.069468260414</v>
+        <v>1728.708625782469</v>
       </c>
       <c r="D3">
-        <v>966.1204682604141</v>
+        <v>966.7596257824689</v>
       </c>
       <c r="E3">
         <v>-1393.849</v>
@@ -1528,37 +1528,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M3">
-        <v>4.805635800000001</v>
+        <v>4.6101258</v>
       </c>
       <c r="N3">
-        <v>-51.70563580000001</v>
+        <v>-51.5101258</v>
       </c>
       <c r="O3">
-        <v>-13.3400540364</v>
+        <v>-13.2896124564</v>
       </c>
       <c r="P3">
-        <v>-38.36558176360001</v>
+        <v>-38.2205133436</v>
       </c>
       <c r="Q3">
-        <v>169.3344182364</v>
+        <v>169.4794866564</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08258461072647144</v>
+        <v>0.08259925145782604</v>
       </c>
       <c r="T3">
-        <v>0.8489829443952331</v>
+        <v>0.8498672392107632</v>
       </c>
       <c r="U3">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V3">
-        <v>-2.517918648766517</v>
+        <v>-2.624700610122179</v>
       </c>
       <c r="W3">
-        <v>0.8647044038668099</v>
+        <v>0.8547044038668099</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>-9.759374607622158</v>
+        <v>-10.17325817876814</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1577,13 +1577,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.09240580865787482</v>
+        <v>0.09222030298191589</v>
       </c>
       <c r="C4">
-        <v>1689.716226787631</v>
+        <v>1691.254348029332</v>
       </c>
       <c r="D4">
-        <v>947.3182267876309</v>
+        <v>948.8563480293321</v>
       </c>
       <c r="E4">
         <v>-1374.298</v>
@@ -1610,37 +1610,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M4">
-        <v>9.611271600000002</v>
+        <v>9.220251600000001</v>
       </c>
       <c r="N4">
-        <v>-56.51127160000001</v>
+        <v>-56.1202516</v>
       </c>
       <c r="O4">
-        <v>-14.5799080728</v>
+        <v>-14.4790249128</v>
       </c>
       <c r="P4">
-        <v>-41.93136352720001</v>
+        <v>-41.6412266872</v>
       </c>
       <c r="Q4">
-        <v>165.7686364728</v>
+        <v>166.0587733128</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08295996389714971</v>
+        <v>0.08297475402372223</v>
       </c>
       <c r="T4">
-        <v>0.8576460356645723</v>
+        <v>0.8585393538965874</v>
       </c>
       <c r="U4">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V4">
-        <v>-1.258959324383258</v>
+        <v>-1.31235030506109</v>
       </c>
       <c r="W4">
-        <v>0.555252201933405</v>
+        <v>0.545252201933405</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>-4.879687303811079</v>
+        <v>-5.086629089384068</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1659,13 +1659,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.09440580865787482</v>
+        <v>0.09412030298191587</v>
       </c>
       <c r="C5">
-        <v>1652.080857450208</v>
+        <v>1654.451110044537</v>
       </c>
       <c r="D5">
-        <v>929.2338574502085</v>
+        <v>931.6041100445368</v>
       </c>
       <c r="E5">
         <v>-1354.747</v>
@@ -1692,37 +1692,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M5">
-        <v>14.4169074</v>
+        <v>13.8303774</v>
       </c>
       <c r="N5">
-        <v>-61.31690740000001</v>
+        <v>-60.73037740000001</v>
       </c>
       <c r="O5">
-        <v>-15.8197621092</v>
+        <v>-15.6684373692</v>
       </c>
       <c r="P5">
-        <v>-45.49714529080001</v>
+        <v>-45.0619400308</v>
       </c>
       <c r="Q5">
-        <v>162.2028547092</v>
+        <v>162.6380599692</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08334305630846055</v>
+        <v>0.08335799891056472</v>
       </c>
       <c r="T5">
-        <v>0.8664877473724546</v>
+        <v>0.8673902750707789</v>
       </c>
       <c r="U5">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>-0.8393062162555057</v>
+        <v>-0.8749002033740598</v>
       </c>
       <c r="W5">
-        <v>0.4521014679556033</v>
+        <v>0.4421014679556033</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>-3.253124869207387</v>
+        <v>-3.391086059589379</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1741,13 +1741,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.09640580865787482</v>
+        <v>0.09602030298191588</v>
       </c>
       <c r="C6">
-        <v>1615.12301770644</v>
+        <v>1618.26403409327</v>
       </c>
       <c r="D6">
-        <v>911.8270177064396</v>
+        <v>914.96803409327</v>
       </c>
       <c r="E6">
         <v>-1335.196</v>
@@ -1774,37 +1774,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M6">
-        <v>19.2225432</v>
+        <v>18.4405032</v>
       </c>
       <c r="N6">
-        <v>-66.12254320000001</v>
+        <v>-65.3405032</v>
       </c>
       <c r="O6">
-        <v>-17.0596161456</v>
+        <v>-16.8578498256</v>
       </c>
       <c r="P6">
-        <v>-49.06292705440001</v>
+        <v>-48.4826533744</v>
       </c>
       <c r="Q6">
-        <v>158.6370729456</v>
+        <v>159.2173466256</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08373412981167368</v>
+        <v>0.08374922806588311</v>
       </c>
       <c r="T6">
-        <v>0.8755136614075842</v>
+        <v>0.8764255904360997</v>
       </c>
       <c r="U6">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>-0.6294796621916292</v>
+        <v>-0.6561751525305448</v>
       </c>
       <c r="W6">
-        <v>0.4005261009667025</v>
+        <v>0.3905261009667025</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>-2.43984365190554</v>
+        <v>-2.543314544692034</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1823,13 +1823,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.09840580865787485</v>
+        <v>0.09792030298191587</v>
       </c>
       <c r="C7">
-        <v>1578.805332291052</v>
+        <v>1582.660690042726</v>
       </c>
       <c r="D7">
-        <v>895.0603322910517</v>
+        <v>898.9156900427258</v>
       </c>
       <c r="E7">
         <v>-1315.645</v>
@@ -1856,37 +1856,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M7">
-        <v>24.02817900000001</v>
+        <v>23.050629</v>
       </c>
       <c r="N7">
-        <v>-70.92817900000001</v>
+        <v>-69.95062900000001</v>
       </c>
       <c r="O7">
-        <v>-18.299470182</v>
+        <v>-18.047262282</v>
       </c>
       <c r="P7">
-        <v>-52.62870881800001</v>
+        <v>-51.903366718</v>
       </c>
       <c r="Q7">
-        <v>155.071291182</v>
+        <v>155.796633282</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08413343644127025</v>
+        <v>0.08414869362447135</v>
       </c>
       <c r="T7">
-        <v>0.8847295946855589</v>
+        <v>0.8856511229670058</v>
       </c>
       <c r="U7">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>-0.5035837297533033</v>
+        <v>-0.5249401220244359</v>
       </c>
       <c r="W7">
-        <v>0.369580880773362</v>
+        <v>0.359580880773362</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>-1.951874921524432</v>
+        <v>-2.034651635753627</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1905,13 +1905,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1004058086578748</v>
+        <v>0.09982030298191587</v>
       </c>
       <c r="C8">
-        <v>1543.093125329532</v>
+        <v>1547.6108843584</v>
       </c>
       <c r="D8">
-        <v>878.8991253295316</v>
+        <v>883.4168843584001</v>
       </c>
       <c r="E8">
         <v>-1296.094</v>
@@ -1938,37 +1938,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M8">
-        <v>28.8338148</v>
+        <v>27.6607548</v>
       </c>
       <c r="N8">
-        <v>-75.7338148</v>
+        <v>-74.56075480000001</v>
       </c>
       <c r="O8">
-        <v>-19.5393242184</v>
+        <v>-19.2366747384</v>
       </c>
       <c r="P8">
-        <v>-56.19449058160001</v>
+        <v>-55.32408006160001</v>
       </c>
       <c r="Q8">
-        <v>151.5055094184</v>
+        <v>152.3759199384</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.0845412389566029</v>
+        <v>0.0845566584502636</v>
       </c>
       <c r="T8">
-        <v>0.8941416116502988</v>
+        <v>0.8950729434241016</v>
       </c>
       <c r="U8">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>-0.4196531081277529</v>
+        <v>-0.4374501016870299</v>
       </c>
       <c r="W8">
-        <v>0.3489507339778017</v>
+        <v>0.3389507339778017</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>-1.626562434603693</v>
+        <v>-1.69554302979469</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1987,13 +1987,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1024058086578748</v>
+        <v>0.1017203029819159</v>
       </c>
       <c r="C9">
-        <v>1507.954180959384</v>
+        <v>1513.086470558746</v>
       </c>
       <c r="D9">
-        <v>863.3111809593836</v>
+        <v>868.4434705587457</v>
       </c>
       <c r="E9">
         <v>-1276.543</v>
@@ -2020,37 +2020,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M9">
-        <v>33.63945060000001</v>
+        <v>32.27088060000001</v>
       </c>
       <c r="N9">
-        <v>-80.53945060000001</v>
+        <v>-79.1708806</v>
       </c>
       <c r="O9">
-        <v>-20.7791782548</v>
+        <v>-20.4260871948</v>
       </c>
       <c r="P9">
-        <v>-59.76027234520001</v>
+        <v>-58.7447934052</v>
       </c>
       <c r="Q9">
-        <v>147.9397276548</v>
+        <v>148.9552065948</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08495781141850185</v>
+        <v>0.08497339671316967</v>
       </c>
       <c r="T9">
-        <v>0.9037560375820224</v>
+        <v>0.9046973836759739</v>
       </c>
       <c r="U9">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>-0.3597026641095024</v>
+        <v>-0.3749572300174542</v>
       </c>
       <c r="W9">
-        <v>0.3342149148381157</v>
+        <v>0.3242149148381157</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>-1.394196372517451</v>
+        <v>-1.453322596966876</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2069,13 +2069,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1044058086578748</v>
+        <v>0.1036203029819159</v>
       </c>
       <c r="C10">
-        <v>1473.358528980859</v>
+        <v>1479.061178624667</v>
       </c>
       <c r="D10">
-        <v>848.2665289808591</v>
+        <v>853.9691786246669</v>
       </c>
       <c r="E10">
         <v>-1256.992</v>
@@ -2102,37 +2102,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M10">
-        <v>38.44508640000001</v>
+        <v>36.8810064</v>
       </c>
       <c r="N10">
-        <v>-85.34508640000001</v>
+        <v>-83.78100640000001</v>
       </c>
       <c r="O10">
-        <v>-22.01903229120001</v>
+        <v>-21.6154996512</v>
       </c>
       <c r="P10">
-        <v>-63.32605410880001</v>
+        <v>-62.16550674880001</v>
       </c>
       <c r="Q10">
-        <v>144.3739458912</v>
+        <v>145.5344932512</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08538343980348558</v>
+        <v>0.0853991945035302</v>
       </c>
       <c r="T10">
-        <v>0.9135794727731313</v>
+        <v>0.914531050889843</v>
       </c>
       <c r="U10">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>-0.3147398310958146</v>
+        <v>-0.3280875762652724</v>
       </c>
       <c r="W10">
-        <v>0.3231630504833513</v>
+        <v>0.3131630504833512</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>-1.21992182595277</v>
+        <v>-1.271657272346017</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2151,13 +2151,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1064058086578748</v>
+        <v>0.1055203029819159</v>
       </c>
       <c r="C11">
-        <v>1439.278252536184</v>
+        <v>1445.510461188673</v>
       </c>
       <c r="D11">
-        <v>833.737252536184</v>
+        <v>839.9694611886736</v>
       </c>
       <c r="E11">
         <v>-1237.441</v>
@@ -2184,37 +2184,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M11">
-        <v>43.25072220000001</v>
+        <v>41.4911322</v>
       </c>
       <c r="N11">
-        <v>-90.15072220000002</v>
+        <v>-88.39113220000002</v>
       </c>
       <c r="O11">
-        <v>-23.25888632760001</v>
+        <v>-22.8049121076</v>
       </c>
       <c r="P11">
-        <v>-66.89183587240001</v>
+        <v>-65.58622009240001</v>
       </c>
       <c r="Q11">
-        <v>140.8081641276</v>
+        <v>142.1137799076</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08581842265846892</v>
+        <v>0.08583435048708549</v>
       </c>
       <c r="T11">
-        <v>0.9236188076387701</v>
+        <v>0.9245808426578633</v>
       </c>
       <c r="U11">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>-0.2797687387518352</v>
+        <v>-0.2916334011246866</v>
       </c>
       <c r="W11">
-        <v>0.3145671559852011</v>
+        <v>0.3045671559852011</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>-1.084374956402462</v>
+        <v>-1.130362019863127</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2233,13 +2233,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1084058086578748</v>
+        <v>0.1074203029819159</v>
       </c>
       <c r="C12">
-        <v>1405.687315220601</v>
+        <v>1412.411354609192</v>
       </c>
       <c r="D12">
-        <v>819.6973152206012</v>
+        <v>826.4213546091918</v>
       </c>
       <c r="E12">
         <v>-1217.89</v>
@@ -2266,37 +2266,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M12">
-        <v>48.05635800000001</v>
+        <v>46.10125800000001</v>
       </c>
       <c r="N12">
-        <v>-94.95635800000002</v>
+        <v>-93.00125800000001</v>
       </c>
       <c r="O12">
-        <v>-24.49874036400001</v>
+        <v>-23.994324564</v>
       </c>
       <c r="P12">
-        <v>-70.45761763600001</v>
+        <v>-69.006933436</v>
       </c>
       <c r="Q12">
-        <v>137.242382364</v>
+        <v>138.693066564</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08626307179911859</v>
+        <v>0.08627917660360865</v>
       </c>
       <c r="T12">
-        <v>0.9338812388347566</v>
+        <v>0.9348539631318395</v>
       </c>
       <c r="U12">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>-0.2517918648766517</v>
+        <v>-0.2624700610122179</v>
       </c>
       <c r="W12">
-        <v>0.307690440386681</v>
+        <v>0.297690440386681</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>-0.975937460762216</v>
+        <v>-1.017325817876813</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1104058086578748</v>
+        <v>0.1093203029819159</v>
       </c>
       <c r="C13">
-        <v>1372.561405372577</v>
+        <v>1379.742353276094</v>
       </c>
       <c r="D13">
-        <v>806.1224053725774</v>
+        <v>813.3033532760941</v>
       </c>
       <c r="E13">
         <v>-1198.339</v>
@@ -2348,37 +2348,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M13">
-        <v>52.86199380000001</v>
+        <v>50.71138380000001</v>
       </c>
       <c r="N13">
-        <v>-99.76199380000001</v>
+        <v>-97.61138380000001</v>
       </c>
       <c r="O13">
-        <v>-25.7385944004</v>
+        <v>-25.1837370204</v>
       </c>
       <c r="P13">
-        <v>-74.02339939960001</v>
+        <v>-72.42764677960001</v>
       </c>
       <c r="Q13">
-        <v>133.6766006004</v>
+        <v>135.2723532204</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08671771305528846</v>
+        <v>0.08673399881263796</v>
       </c>
       <c r="T13">
-        <v>0.9443742864621133</v>
+        <v>0.9453579402456804</v>
       </c>
       <c r="U13">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>-0.2289016953424106</v>
+        <v>-0.2386091463747436</v>
       </c>
       <c r="W13">
-        <v>0.3020640367151645</v>
+        <v>0.2920640367151645</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>-0.8872158734201963</v>
+        <v>-0.9248416526152852</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2397,13 +2397,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1124058086578748</v>
+        <v>0.1112203029819159</v>
       </c>
       <c r="C14">
-        <v>1339.877795584097</v>
+        <v>1347.483295700265</v>
       </c>
       <c r="D14">
-        <v>792.9897955840972</v>
+        <v>800.5952957002654</v>
       </c>
       <c r="E14">
         <v>-1178.788</v>
@@ -2430,37 +2430,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M14">
-        <v>57.66762960000001</v>
+        <v>55.3215096</v>
       </c>
       <c r="N14">
-        <v>-104.5676296</v>
+        <v>-102.2215096</v>
       </c>
       <c r="O14">
-        <v>-26.9784484368</v>
+        <v>-26.3731494768</v>
       </c>
       <c r="P14">
-        <v>-77.58918116320001</v>
+        <v>-75.8483601232</v>
       </c>
       <c r="Q14">
-        <v>130.1108188368</v>
+        <v>131.8516398768</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08718268706728038</v>
+        <v>0.08719915789005431</v>
       </c>
       <c r="T14">
-        <v>0.9551058124446374</v>
+        <v>0.9561006441121087</v>
       </c>
       <c r="U14">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>-0.2098265540638764</v>
+        <v>-0.218725050843515</v>
       </c>
       <c r="W14">
-        <v>0.2973753669889008</v>
+        <v>0.2873753669889009</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>-0.8132812173018464</v>
+        <v>-0.8477715148973448</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2479,13 +2479,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1144058086578748</v>
+        <v>0.1131203029819159</v>
       </c>
       <c r="C15">
-        <v>1307.61521572321</v>
+        <v>1315.615261118136</v>
       </c>
       <c r="D15">
-        <v>780.2782157232094</v>
+        <v>788.2782611181362</v>
       </c>
       <c r="E15">
         <v>-1159.237</v>
@@ -2512,37 +2512,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M15">
-        <v>62.47326540000002</v>
+        <v>59.93163540000001</v>
       </c>
       <c r="N15">
-        <v>-109.3732654</v>
+        <v>-106.8316354</v>
       </c>
       <c r="O15">
-        <v>-28.2183024732</v>
+        <v>-27.5625619332</v>
       </c>
       <c r="P15">
-        <v>-81.15496292680001</v>
+        <v>-79.26907346680001</v>
       </c>
       <c r="Q15">
-        <v>126.5450370732</v>
+        <v>128.4309265332</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08765835013701923</v>
+        <v>0.08767501027959515</v>
       </c>
       <c r="T15">
-        <v>0.966084040173886</v>
+        <v>0.9670903066881099</v>
       </c>
       <c r="U15">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>-0.1936860499051166</v>
+        <v>-0.2019000469324753</v>
       </c>
       <c r="W15">
-        <v>0.2934080310666777</v>
+        <v>0.2834080310666777</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>-0.750721123663243</v>
+        <v>-0.7825583214437026</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2561,13 +2561,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1164058086578748</v>
+        <v>0.1150203029819159</v>
       </c>
       <c r="C16">
-        <v>1275.75373797654</v>
+        <v>1284.12047549594</v>
       </c>
       <c r="D16">
-        <v>767.9677379765399</v>
+        <v>776.33447549594</v>
       </c>
       <c r="E16">
         <v>-1139.686</v>
@@ -2594,37 +2594,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M16">
-        <v>67.27890120000002</v>
+        <v>64.54176120000001</v>
       </c>
       <c r="N16">
-        <v>-114.1789012</v>
+        <v>-111.4417612</v>
       </c>
       <c r="O16">
-        <v>-29.45815650960001</v>
+        <v>-28.7519743896</v>
       </c>
       <c r="P16">
-        <v>-84.72074469040001</v>
+        <v>-82.68978681040001</v>
       </c>
       <c r="Q16">
-        <v>122.9792553096</v>
+        <v>125.0102131896</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08814507513861247</v>
+        <v>0.08816192900377649</v>
       </c>
       <c r="T16">
-        <v>0.9773175755247453</v>
+        <v>0.9783355428123902</v>
       </c>
       <c r="U16">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>-0.1798513320547512</v>
+        <v>-0.1874786150087271</v>
       </c>
       <c r="W16">
-        <v>0.2900074574190579</v>
+        <v>0.2800074574190579</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>-0.6970981862587255</v>
+        <v>-0.7266612984834384</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2643,13 +2643,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1184058086578748</v>
+        <v>0.1169203029819159</v>
       </c>
       <c r="C17">
-        <v>1244.274672604914</v>
+        <v>1252.982225951624</v>
       </c>
       <c r="D17">
-        <v>756.0396726049139</v>
+        <v>764.7472259516239</v>
       </c>
       <c r="E17">
         <v>-1120.135</v>
@@ -2676,37 +2676,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M17">
-        <v>72.084537</v>
+        <v>69.151887</v>
       </c>
       <c r="N17">
-        <v>-118.984537</v>
+        <v>-116.051887</v>
       </c>
       <c r="O17">
-        <v>-30.698010546</v>
+        <v>-29.941386846</v>
       </c>
       <c r="P17">
-        <v>-88.286526454</v>
+        <v>-86.11050015400001</v>
       </c>
       <c r="Q17">
-        <v>119.413473546</v>
+        <v>121.589499846</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08864325249318439</v>
+        <v>0.08866030463911503</v>
       </c>
       <c r="T17">
-        <v>0.9888154293544481</v>
+        <v>0.9898453727278301</v>
       </c>
       <c r="U17">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>-0.1678612432511012</v>
+        <v>-0.174980040674812</v>
       </c>
       <c r="W17">
-        <v>0.2870602935911207</v>
+        <v>0.2770602935911207</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>-0.6506249738414773</v>
+        <v>-0.6782172119178758</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2725,13 +2725,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1204058086578748</v>
+        <v>0.1188203029819159</v>
       </c>
       <c r="C18">
-        <v>1213.160473265132</v>
+        <v>1222.184782727873</v>
       </c>
       <c r="D18">
-        <v>744.4764732651321</v>
+        <v>753.5007827278733</v>
       </c>
       <c r="E18">
         <v>-1100.584</v>
@@ -2758,37 +2758,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M18">
-        <v>76.89017280000002</v>
+        <v>73.76201280000001</v>
       </c>
       <c r="N18">
-        <v>-123.7901728</v>
+        <v>-120.6620128</v>
       </c>
       <c r="O18">
-        <v>-31.93786458240001</v>
+        <v>-31.1307993024</v>
       </c>
       <c r="P18">
-        <v>-91.85230821760001</v>
+        <v>-89.53121349760001</v>
       </c>
       <c r="Q18">
-        <v>115.8476917824</v>
+        <v>118.1687865024</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08915329121334134</v>
+        <v>0.08917054636100927</v>
       </c>
       <c r="T18">
-        <v>1.000587041608668</v>
+        <v>1.001629246212685</v>
       </c>
       <c r="U18">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>-0.1573699155479073</v>
+        <v>-0.1640437881326362</v>
       </c>
       <c r="W18">
-        <v>0.2844815252416756</v>
+        <v>0.2744815252416756</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>-0.6099609129763848</v>
+        <v>-0.6358286361730086</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2807,13 +2807,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1224058086578748</v>
+        <v>0.1207203029819159</v>
       </c>
       <c r="C19">
-        <v>1182.394650889164</v>
+        <v>1191.713327950187</v>
       </c>
       <c r="D19">
-        <v>733.2616508891643</v>
+        <v>742.580327950187</v>
       </c>
       <c r="E19">
         <v>-1081.033</v>
@@ -2840,37 +2840,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M19">
-        <v>81.69580860000002</v>
+        <v>78.37213860000003</v>
       </c>
       <c r="N19">
-        <v>-128.5958086</v>
+        <v>-125.2721386</v>
       </c>
       <c r="O19">
-        <v>-33.17771861880001</v>
+        <v>-32.32021175880001</v>
       </c>
       <c r="P19">
-        <v>-95.41808998120001</v>
+        <v>-92.95192684120002</v>
       </c>
       <c r="Q19">
-        <v>112.2819100188</v>
+        <v>114.7480731588</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08967562002314064</v>
+        <v>0.08969308306415395</v>
       </c>
       <c r="T19">
-        <v>1.012642307170218</v>
+        <v>1.013697068456211</v>
       </c>
       <c r="U19">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>-0.148112861692148</v>
+        <v>-0.1543941535365988</v>
       </c>
       <c r="W19">
-        <v>0.28220614140393</v>
+        <v>0.27220614140393</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>-0.5740808592718916</v>
+        <v>-0.5984269516922431</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2889,13 +2889,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1244058086578748</v>
+        <v>0.1226203029819159</v>
       </c>
       <c r="C20">
-        <v>1151.961695231789</v>
+        <v>1161.553890491487</v>
       </c>
       <c r="D20">
-        <v>722.3796952317891</v>
+        <v>731.9718904914871</v>
       </c>
       <c r="E20">
         <v>-1061.482</v>
@@ -2922,37 +2922,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M20">
-        <v>86.50144440000001</v>
+        <v>82.98226440000001</v>
       </c>
       <c r="N20">
-        <v>-133.4014444</v>
+        <v>-129.8822644</v>
       </c>
       <c r="O20">
-        <v>-34.4175726552</v>
+        <v>-33.5096242152</v>
       </c>
       <c r="P20">
-        <v>-98.9838717448</v>
+        <v>-96.37264018479999</v>
       </c>
       <c r="Q20">
-        <v>108.7161282552</v>
+        <v>111.3273598152</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09021068856000822</v>
+        <v>0.09022836456493633</v>
       </c>
       <c r="T20">
-        <v>1.024991603599123</v>
+        <v>1.026059227827629</v>
       </c>
       <c r="U20">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>-0.1398843693759176</v>
+        <v>-0.1458167005623433</v>
       </c>
       <c r="W20">
-        <v>0.2801835779926006</v>
+        <v>0.2701835779926005</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>-0.5421874782012308</v>
+        <v>-0.5651810099315631</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2971,13 +2971,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1264058086578748</v>
+        <v>0.1245203029819159</v>
       </c>
       <c r="C21">
-        <v>1121.847003301703</v>
+        <v>1131.693286341205</v>
       </c>
       <c r="D21">
-        <v>711.8160033017033</v>
+        <v>721.662286341205</v>
       </c>
       <c r="E21">
         <v>-1041.931</v>
@@ -3004,37 +3004,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M21">
-        <v>91.30708020000002</v>
+        <v>87.59239020000001</v>
       </c>
       <c r="N21">
-        <v>-138.2070802</v>
+        <v>-134.4923902</v>
       </c>
       <c r="O21">
-        <v>-35.6574266916</v>
+        <v>-34.69903667160001</v>
       </c>
       <c r="P21">
-        <v>-102.5496535084</v>
+        <v>-99.79335352840002</v>
       </c>
       <c r="Q21">
-        <v>105.1503464916</v>
+        <v>107.9066464716</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09075896866568732</v>
+        <v>0.0907768628928985</v>
       </c>
       <c r="T21">
-        <v>1.037645820927507</v>
+        <v>1.038726625702044</v>
       </c>
       <c r="U21">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>-0.1325220341456061</v>
+        <v>-0.1381421373748516</v>
       </c>
       <c r="W21">
-        <v>0.27837391599299</v>
+        <v>0.26837391599299</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>-0.5136512951380081</v>
+        <v>-0.5354346409877966</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3053,13 +3053,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1284058086578748</v>
+        <v>0.1264203029819159</v>
       </c>
       <c r="C22">
-        <v>1092.036813981638</v>
+        <v>1102.119063943675</v>
       </c>
       <c r="D22">
-        <v>701.5568139816376</v>
+        <v>711.6390639436751</v>
       </c>
       <c r="E22">
         <v>-1022.38</v>
@@ -3086,37 +3086,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M22">
-        <v>96.11271600000002</v>
+        <v>92.20251600000002</v>
       </c>
       <c r="N22">
-        <v>-143.012716</v>
+        <v>-139.102516</v>
       </c>
       <c r="O22">
-        <v>-36.89728072800001</v>
+        <v>-35.88844912800001</v>
       </c>
       <c r="P22">
-        <v>-106.115435272</v>
+        <v>-103.214066872</v>
       </c>
       <c r="Q22">
-        <v>101.584564728</v>
+        <v>104.485933128</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09132095577400841</v>
+        <v>0.09133907367905973</v>
       </c>
       <c r="T22">
-        <v>1.050616393689101</v>
+        <v>1.051710708523319</v>
       </c>
       <c r="U22">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>-0.1258959324383258</v>
+        <v>-0.131235030506109</v>
       </c>
       <c r="W22">
-        <v>0.2767452201933405</v>
+        <v>0.2667452201933405</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>-0.4879687303811078</v>
+        <v>-0.5086629089384069</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3135,13 +3135,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1304058086578748</v>
+        <v>0.1283203029819159</v>
       </c>
       <c r="C23">
-        <v>1062.518148221945</v>
+        <v>1072.819454029324</v>
       </c>
       <c r="D23">
-        <v>691.5891482219444</v>
+        <v>701.8904540293242</v>
       </c>
       <c r="E23">
         <v>-1002.829</v>
@@ -3168,37 +3168,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M23">
-        <v>100.9183518</v>
+        <v>96.81264180000001</v>
       </c>
       <c r="N23">
-        <v>-147.8183518</v>
+        <v>-143.7126418</v>
       </c>
       <c r="O23">
-        <v>-38.1371347644</v>
+        <v>-37.07786158440001</v>
       </c>
       <c r="P23">
-        <v>-109.6812170356</v>
+        <v>-106.6347802156</v>
       </c>
       <c r="Q23">
-        <v>98.01878296439997</v>
+        <v>101.0652197844</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09189717040405915</v>
+        <v>0.09191551764968074</v>
       </c>
       <c r="T23">
-        <v>1.063915335381368</v>
+        <v>1.065023502302096</v>
       </c>
       <c r="U23">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>-0.1199008880365008</v>
+        <v>-0.1249857433391514</v>
       </c>
       <c r="W23">
-        <v>0.275271638279372</v>
+        <v>0.2652716382793719</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>-0.4647321241724838</v>
+        <v>-0.4844408656556258</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3217,13 +3217,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1324058086578749</v>
+        <v>0.1302203029819159</v>
       </c>
       <c r="C24">
-        <v>1033.278754261116</v>
+        <v>1043.783323513655</v>
       </c>
       <c r="D24">
-        <v>681.9007542611162</v>
+        <v>692.4053235136547</v>
       </c>
       <c r="E24">
         <v>-983.278</v>
@@ -3250,37 +3250,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M24">
-        <v>105.7239876</v>
+        <v>101.4227676</v>
       </c>
       <c r="N24">
-        <v>-152.6239876</v>
+        <v>-148.3227676</v>
       </c>
       <c r="O24">
-        <v>-39.37698880080001</v>
+        <v>-38.2672740408</v>
       </c>
       <c r="P24">
-        <v>-113.2469987992</v>
+        <v>-110.0554935592</v>
       </c>
       <c r="Q24">
-        <v>94.45300120079997</v>
+        <v>97.64450644079997</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09248815976821376</v>
+        <v>0.09250674223493306</v>
       </c>
       <c r="T24">
-        <v>1.077555275578565</v>
+        <v>1.078677649767507</v>
       </c>
       <c r="U24">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>-0.1144508476712053</v>
+        <v>-0.1193045731873718</v>
       </c>
       <c r="W24">
-        <v>0.2739320183575823</v>
+        <v>0.2639320183575823</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>-0.443607936710098</v>
+        <v>-0.4624208263076426</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3299,13 +3299,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1344058086578748</v>
+        <v>0.1321203029819159</v>
       </c>
       <c r="C25">
-        <v>1004.307057387088</v>
+        <v>1015.000133084359</v>
       </c>
       <c r="D25">
-        <v>672.4800573870878</v>
+        <v>683.1731330843585</v>
       </c>
       <c r="E25">
         <v>-963.7270000000001</v>
@@ -3332,37 +3332,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M25">
-        <v>110.5296234</v>
+        <v>106.0328934</v>
       </c>
       <c r="N25">
-        <v>-157.4296234</v>
+        <v>-152.9328934</v>
       </c>
       <c r="O25">
-        <v>-40.61684283720001</v>
+        <v>-39.4566864972</v>
       </c>
       <c r="P25">
-        <v>-116.8127805628</v>
+        <v>-113.4762069028</v>
       </c>
       <c r="Q25">
-        <v>90.88721943719997</v>
+        <v>94.22379309719997</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09309449950546328</v>
+        <v>0.09311332330291919</v>
       </c>
       <c r="T25">
-        <v>1.091549499936729</v>
+        <v>1.092686450413838</v>
       </c>
       <c r="U25">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>-0.1094747238594138</v>
+        <v>-0.1141174178313991</v>
       </c>
       <c r="W25">
-        <v>0.2727088871246439</v>
+        <v>0.2627088871246439</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>-0.424320635114007</v>
+        <v>-0.4423155729899189</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3381,13 +3381,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1364058086578748</v>
+        <v>0.1340203029819159</v>
       </c>
       <c r="C26">
-        <v>975.5921138061815</v>
+        <v>986.4598981368574</v>
       </c>
       <c r="D26">
-        <v>663.3161138061813</v>
+        <v>674.1838981368574</v>
       </c>
       <c r="E26">
         <v>-944.1760000000002</v>
@@ -3414,37 +3414,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M26">
-        <v>115.3352592</v>
+        <v>110.6430192</v>
       </c>
       <c r="N26">
-        <v>-162.2352592</v>
+        <v>-157.5430192</v>
       </c>
       <c r="O26">
-        <v>-41.85669687360001</v>
+        <v>-40.6460989536</v>
       </c>
       <c r="P26">
-        <v>-120.3785623264</v>
+        <v>-116.8969202464</v>
       </c>
       <c r="Q26">
-        <v>87.32143767359997</v>
+        <v>90.80307975359999</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09371679555158779</v>
+        <v>0.0937358670305892</v>
       </c>
       <c r="T26">
-        <v>1.105911993356949</v>
+        <v>1.107063903708757</v>
       </c>
       <c r="U26">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>-0.1049132770319382</v>
+        <v>-0.1093625254217575</v>
       </c>
       <c r="W26">
-        <v>0.2715876834944504</v>
+        <v>0.2615876834944504</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>-0.4066406086509233</v>
+        <v>-0.4238857574486725</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3463,13 +3463,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1384058086578748</v>
+        <v>0.1359203029819159</v>
       </c>
       <c r="C27">
-        <v>947.1235682331344</v>
+        <v>958.1531527538673</v>
       </c>
       <c r="D27">
-        <v>654.3985682331345</v>
+        <v>665.4281527538674</v>
       </c>
       <c r="E27">
         <v>-924.625</v>
@@ -3496,37 +3496,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M27">
-        <v>120.140895</v>
+        <v>115.253145</v>
       </c>
       <c r="N27">
-        <v>-167.040895</v>
+        <v>-162.153145</v>
       </c>
       <c r="O27">
-        <v>-43.09655091000001</v>
+        <v>-41.83551141000001</v>
       </c>
       <c r="P27">
-        <v>-123.94434409</v>
+        <v>-120.31763359</v>
       </c>
       <c r="Q27">
-        <v>83.75565590999997</v>
+        <v>87.38236640999997</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.0943556861589423</v>
+        <v>0.09437501192433037</v>
       </c>
       <c r="T27">
-        <v>1.120657486601708</v>
+        <v>1.121824755758207</v>
       </c>
       <c r="U27">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>-0.1007167459506607</v>
+        <v>-0.1049880244048872</v>
       </c>
       <c r="W27">
-        <v>0.2705561761546724</v>
+        <v>0.2605561761546724</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>-0.3903749843048865</v>
+        <v>-0.4069303271507254</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3545,13 +3545,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1404058086578748</v>
+        <v>0.1378203029819159</v>
       </c>
       <c r="C28">
-        <v>918.8916148566782</v>
+        <v>930.0709164557993</v>
       </c>
       <c r="D28">
-        <v>645.7176148566782</v>
+        <v>656.8969164557992</v>
       </c>
       <c r="E28">
         <v>-905.0740000000001</v>
@@ -3578,37 +3578,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M28">
-        <v>124.9465308</v>
+        <v>119.8632708</v>
       </c>
       <c r="N28">
-        <v>-171.8465308</v>
+        <v>-166.7632708</v>
       </c>
       <c r="O28">
-        <v>-44.33640494640001</v>
+        <v>-43.02492386640001</v>
       </c>
       <c r="P28">
-        <v>-127.5101258536</v>
+        <v>-123.7383469336</v>
       </c>
       <c r="Q28">
-        <v>80.18987414639996</v>
+        <v>83.96165306639995</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09501184408000909</v>
+        <v>0.09503143100438891</v>
       </c>
       <c r="T28">
-        <v>1.13580150669092</v>
+        <v>1.13698454975494</v>
       </c>
       <c r="U28">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>-0.09684302495255832</v>
+        <v>-0.1009500234662377</v>
       </c>
       <c r="W28">
-        <v>0.2696040155333388</v>
+        <v>0.2596040155333388</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>-0.3753605618316214</v>
+        <v>-0.3912791607218515</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3627,13 +3627,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1424058086578748</v>
+        <v>0.1397203029819159</v>
       </c>
       <c r="C29">
-        <v>890.8869613713158</v>
+        <v>902.2046634764762</v>
       </c>
       <c r="D29">
-        <v>637.263961371316</v>
+        <v>648.5816634764763</v>
       </c>
       <c r="E29">
         <v>-885.523</v>
@@ -3660,37 +3660,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M29">
-        <v>129.7521666</v>
+        <v>124.4733966</v>
       </c>
       <c r="N29">
-        <v>-176.6521666</v>
+        <v>-171.3733966</v>
       </c>
       <c r="O29">
-        <v>-45.57625898280001</v>
+        <v>-44.21433632280001</v>
       </c>
       <c r="P29">
-        <v>-131.0759076172</v>
+        <v>-127.1590602772</v>
       </c>
       <c r="Q29">
-        <v>76.62409238279997</v>
+        <v>80.54093972279996</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09568597893042019</v>
+        <v>0.09570583416883258</v>
       </c>
       <c r="T29">
-        <v>1.151360431440111</v>
+        <v>1.152559680573501</v>
       </c>
       <c r="U29">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>-0.09325624625061173</v>
+        <v>-0.09721113370822887</v>
       </c>
       <c r="W29">
-        <v>0.2687223853284004</v>
+        <v>0.2587223853284004</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>-0.3614583188008207</v>
+        <v>-0.3767873399543755</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3709,13 +3709,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1444058086578748</v>
+        <v>0.1416203029819159</v>
       </c>
       <c r="C30">
-        <v>863.1007957979393</v>
+        <v>874.5462943432015</v>
       </c>
       <c r="D30">
-        <v>629.0287957979394</v>
+        <v>640.4742943432014</v>
       </c>
       <c r="E30">
         <v>-865.972</v>
@@ -3742,37 +3742,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M30">
-        <v>134.5578024</v>
+        <v>129.0835224</v>
       </c>
       <c r="N30">
-        <v>-181.4578024</v>
+        <v>-175.9835224</v>
       </c>
       <c r="O30">
-        <v>-46.81611301920002</v>
+        <v>-45.40374877920001</v>
       </c>
       <c r="P30">
-        <v>-134.6416893808</v>
+        <v>-130.5797736208</v>
       </c>
       <c r="Q30">
-        <v>73.05831061919997</v>
+        <v>77.12022637919998</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09637883974889823</v>
+        <v>0.09639897075451082</v>
       </c>
       <c r="T30">
-        <v>1.167351548543446</v>
+        <v>1.168567453914799</v>
       </c>
       <c r="U30">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>-0.0899256660273756</v>
+        <v>-0.09373930750436354</v>
       </c>
       <c r="W30">
-        <v>0.2679037287095289</v>
+        <v>0.2579037287095289</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>-0.3485490931293627</v>
+        <v>-0.3633306492417192</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3791,13 +3791,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1464058086578748</v>
+        <v>0.1435203029819159</v>
       </c>
       <c r="C31">
-        <v>835.524755844227</v>
+        <v>847.0881095620305</v>
       </c>
       <c r="D31">
-        <v>621.003755844227</v>
+        <v>632.5671095620304</v>
       </c>
       <c r="E31">
         <v>-846.421</v>
@@ -3824,37 +3824,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M31">
-        <v>139.3634382</v>
+        <v>133.6936482</v>
       </c>
       <c r="N31">
-        <v>-186.2634382</v>
+        <v>-180.5936482</v>
       </c>
       <c r="O31">
-        <v>-48.05596705560001</v>
+        <v>-46.59316123560001</v>
       </c>
       <c r="P31">
-        <v>-138.2074711444</v>
+        <v>-134.0004869644</v>
       </c>
       <c r="Q31">
-        <v>69.49252885559997</v>
+        <v>73.69951303559998</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09709121777353061</v>
+        <v>0.09711163231443351</v>
       </c>
       <c r="T31">
-        <v>1.183793119649691</v>
+        <v>1.185026150448811</v>
       </c>
       <c r="U31">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>-0.08682478099194886</v>
+        <v>-0.09050691759041998</v>
       </c>
       <c r="W31">
-        <v>0.2671415311678211</v>
+        <v>0.2571415311678211</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>-0.3365301588835228</v>
+        <v>-0.3508020061644186</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3873,13 +3873,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1484058086578748</v>
+        <v>0.1454203029819159</v>
       </c>
       <c r="C32">
-        <v>808.1509005808641</v>
+        <v>819.8227852285327</v>
       </c>
       <c r="D32">
-        <v>613.180900580864</v>
+        <v>624.8527852285326</v>
       </c>
       <c r="E32">
         <v>-826.8700000000001</v>
@@ -3906,37 +3906,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M32">
-        <v>144.169074</v>
+        <v>138.303774</v>
       </c>
       <c r="N32">
-        <v>-191.069074</v>
+        <v>-185.203774</v>
       </c>
       <c r="O32">
-        <v>-49.295821092</v>
+        <v>-47.78257369200001</v>
       </c>
       <c r="P32">
-        <v>-141.773252908</v>
+        <v>-137.421200308</v>
       </c>
       <c r="Q32">
-        <v>65.926747092</v>
+        <v>70.27879969199998</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09782394945600961</v>
+        <v>0.09784465563321113</v>
       </c>
       <c r="T32">
-        <v>1.200704449930401</v>
+        <v>1.201955095455222</v>
       </c>
       <c r="U32">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>-0.08393062162555058</v>
+        <v>-0.08749002033740599</v>
       </c>
       <c r="W32">
-        <v>0.2664301467955604</v>
+        <v>0.2564301467955604</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>-0.3253124869207387</v>
+        <v>-0.3391086059589379</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3955,13 +3955,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1504058086578748</v>
+        <v>0.1473203029819159</v>
       </c>
       <c r="C33">
-        <v>780.9716842319186</v>
+        <v>792.7433504016548</v>
       </c>
       <c r="D33">
-        <v>605.5526842319188</v>
+        <v>617.3243504016548</v>
       </c>
       <c r="E33">
         <v>-807.3190000000001</v>
@@ -3988,37 +3988,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M33">
-        <v>148.9747098</v>
+        <v>142.9138998</v>
       </c>
       <c r="N33">
-        <v>-195.8747098</v>
+        <v>-189.8138998</v>
       </c>
       <c r="O33">
-        <v>-50.53567512840001</v>
+        <v>-48.9719861484</v>
       </c>
       <c r="P33">
-        <v>-145.3390346716</v>
+        <v>-140.8419136516</v>
       </c>
       <c r="Q33">
-        <v>62.36096532839997</v>
+        <v>66.85808634839998</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09857791973798077</v>
+        <v>0.09859892600470693</v>
       </c>
       <c r="T33">
-        <v>1.218105963697509</v>
+        <v>1.219374734519791</v>
       </c>
       <c r="U33">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>-0.08122318221827474</v>
+        <v>-0.0846677616168445</v>
       </c>
       <c r="W33">
-        <v>0.2657646581892519</v>
+        <v>0.2557646581892519</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>-0.3148185357297471</v>
+        <v>-0.3281696186699399</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4037,13 +4037,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1524058086578748</v>
+        <v>0.1492203029819159</v>
       </c>
       <c r="C34">
-        <v>753.9799318975297</v>
+        <v>765.8431660937522</v>
       </c>
       <c r="D34">
-        <v>598.1119318975296</v>
+        <v>609.9751660937524</v>
       </c>
       <c r="E34">
         <v>-787.768</v>
@@ -4070,37 +4070,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M34">
-        <v>153.7803456</v>
+        <v>147.5240256</v>
       </c>
       <c r="N34">
-        <v>-200.6803456</v>
+        <v>-194.4240256</v>
       </c>
       <c r="O34">
-        <v>-51.77552916480001</v>
+        <v>-50.16139860480001</v>
       </c>
       <c r="P34">
-        <v>-148.9048164352</v>
+        <v>-144.2626269952</v>
       </c>
       <c r="Q34">
-        <v>58.79518356479997</v>
+        <v>63.43737300479998</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.09935406561648048</v>
+        <v>0.0993753807988938</v>
       </c>
       <c r="T34">
-        <v>1.23601928669306</v>
+        <v>1.237306715909788</v>
       </c>
       <c r="U34">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>-0.07868495777395365</v>
+        <v>-0.0820218940663181</v>
       </c>
       <c r="W34">
-        <v>0.2651407626208379</v>
+        <v>0.2551407626208378</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>-0.3049804564881924</v>
+        <v>-0.3179143180865043</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4119,13 +4119,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1544058086578748</v>
+        <v>0.1511203029819159</v>
       </c>
       <c r="C35">
-        <v>727.1688170447154</v>
+        <v>739.1159057436947</v>
       </c>
       <c r="D35">
-        <v>590.8518170447156</v>
+        <v>602.7989057436948</v>
       </c>
       <c r="E35">
         <v>-768.217</v>
@@ -4152,37 +4152,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M35">
-        <v>158.5859814</v>
+        <v>152.1341514</v>
       </c>
       <c r="N35">
-        <v>-205.4859814</v>
+        <v>-199.0341514</v>
       </c>
       <c r="O35">
-        <v>-53.01538320120001</v>
+        <v>-51.35081106120001</v>
       </c>
       <c r="P35">
-        <v>-152.4705981988</v>
+        <v>-147.6833403388</v>
       </c>
       <c r="Q35">
-        <v>55.22940180119997</v>
+        <v>60.01665966119995</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1001533800286668</v>
+        <v>0.100175013348131</v>
       </c>
       <c r="T35">
-        <v>1.254467335748181</v>
+        <v>1.255773980326351</v>
       </c>
       <c r="U35">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>-0.07630056511413687</v>
+        <v>-0.07953638212491453</v>
       </c>
       <c r="W35">
-        <v>0.2645546789050549</v>
+        <v>0.2545546789050548</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>-0.2957386244733988</v>
+        <v>-0.3082805508717616</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4201,13 +4201,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1564058086578748</v>
+        <v>0.1530203029819159</v>
       </c>
       <c r="C36">
-        <v>700.5318406178794</v>
+        <v>712.5555370523296</v>
       </c>
       <c r="D36">
-        <v>583.7658406178796</v>
+        <v>595.7895370523297</v>
       </c>
       <c r="E36">
         <v>-748.6659999999999</v>
@@ -4234,37 +4234,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M36">
-        <v>163.3916172</v>
+        <v>156.7442772000001</v>
       </c>
       <c r="N36">
-        <v>-210.2916172</v>
+        <v>-203.6442772000001</v>
       </c>
       <c r="O36">
-        <v>-54.25523723760001</v>
+        <v>-52.54022351760002</v>
       </c>
       <c r="P36">
-        <v>-156.0363799624</v>
+        <v>-151.1040536824</v>
       </c>
       <c r="Q36">
-        <v>51.66362003759997</v>
+        <v>56.59594631759995</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1009769160897072</v>
+        <v>0.1009988771867391</v>
       </c>
       <c r="T36">
-        <v>1.27347441659285</v>
+        <v>1.274800858816145</v>
       </c>
       <c r="U36">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>-0.07405643084607402</v>
+        <v>-0.07719707676829939</v>
       </c>
       <c r="W36">
-        <v>0.264003070701965</v>
+        <v>0.254003070701965</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>-0.2870404296359459</v>
+        <v>-0.2992134758461216</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4283,13 +4283,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1584058086578748</v>
+        <v>0.1549203029819159</v>
       </c>
       <c r="C37">
-        <v>674.06281163464</v>
+        <v>686.1563050706852</v>
       </c>
       <c r="D37">
-        <v>576.84781163464</v>
+        <v>588.9413050706854</v>
       </c>
       <c r="E37">
         <v>-729.115</v>
@@ -4316,37 +4316,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M37">
-        <v>168.197253</v>
+        <v>161.354403</v>
       </c>
       <c r="N37">
-        <v>-215.0972530000001</v>
+        <v>-208.254403</v>
       </c>
       <c r="O37">
-        <v>-55.49509127400002</v>
+        <v>-53.72963597400001</v>
       </c>
       <c r="P37">
-        <v>-159.602161726</v>
+        <v>-154.524767026</v>
       </c>
       <c r="Q37">
-        <v>48.09783827399997</v>
+        <v>53.17523297399998</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1018257917218565</v>
+        <v>0.1018480906819197</v>
       </c>
       <c r="T37">
-        <v>1.293066330694278</v>
+        <v>1.294413179721009</v>
       </c>
       <c r="U37">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>-0.07194053282190048</v>
+        <v>-0.07499144600349084</v>
       </c>
       <c r="W37">
-        <v>0.2634829829676232</v>
+        <v>0.2534829829676232</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>-0.2788392745034902</v>
+        <v>-0.2906645193933752</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4365,13 +4365,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1604058086578748</v>
+        <v>0.1568203029819159</v>
       </c>
       <c r="C38">
-        <v>647.7558291452222</v>
+        <v>659.9127164412646</v>
       </c>
       <c r="D38">
-        <v>570.0918291452221</v>
+        <v>582.2487164412646</v>
       </c>
       <c r="E38">
         <v>-709.5640000000001</v>
@@ -4398,37 +4398,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M38">
-        <v>173.0028888</v>
+        <v>165.9645288</v>
       </c>
       <c r="N38">
-        <v>-219.9028888</v>
+        <v>-212.8645288</v>
       </c>
       <c r="O38">
-        <v>-56.73494531040001</v>
+        <v>-54.9190484304</v>
       </c>
       <c r="P38">
-        <v>-163.1679434896</v>
+        <v>-157.9454803696</v>
       </c>
       <c r="Q38">
-        <v>44.53205651039997</v>
+        <v>49.75451963039998</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1027011947175105</v>
+        <v>0.1027238420988247</v>
       </c>
       <c r="T38">
-        <v>1.313270492111376</v>
+        <v>1.314638385654149</v>
       </c>
       <c r="U38">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>-0.06994218468795881</v>
+        <v>-0.07290835028117165</v>
       </c>
       <c r="W38">
-        <v>0.2629917889963003</v>
+        <v>0.2529917889963003</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>-0.2710937391006156</v>
+        <v>-0.2825905049657815</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4447,13 +4447,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1624058086578748</v>
+        <v>0.1587203029819159</v>
       </c>
       <c r="C39">
-        <v>621.6052654449105</v>
+        <v>633.819524701733</v>
       </c>
       <c r="D39">
-        <v>563.4922654449106</v>
+        <v>575.7065247017331</v>
       </c>
       <c r="E39">
         <v>-690.013</v>
@@ -4480,37 +4480,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M39">
-        <v>177.8085246</v>
+        <v>170.5746546</v>
       </c>
       <c r="N39">
-        <v>-224.7085246</v>
+        <v>-217.4746546</v>
       </c>
       <c r="O39">
-        <v>-57.97479934680001</v>
+        <v>-56.10846088680001</v>
       </c>
       <c r="P39">
-        <v>-166.7337252532</v>
+        <v>-161.3661937132</v>
       </c>
       <c r="Q39">
-        <v>40.96627474679997</v>
+        <v>46.33380628679996</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1036043882844551</v>
+        <v>0.1036273951480124</v>
       </c>
       <c r="T39">
-        <v>1.334116055478224</v>
+        <v>1.335505661616914</v>
       </c>
       <c r="U39">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>-0.06805185537206802</v>
+        <v>-0.07093785432762648</v>
       </c>
       <c r="W39">
-        <v>0.2625271460504543</v>
+        <v>0.2525271460504543</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>-0.2637668812870855</v>
+        <v>-0.2749529237504902</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4529,13 +4529,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1644058086578748</v>
+        <v>0.1606203029819159</v>
       </c>
       <c r="C40">
-        <v>595.6057504391858</v>
+        <v>607.8717165683752</v>
       </c>
       <c r="D40">
-        <v>557.0437504391859</v>
+        <v>569.3097165683754</v>
       </c>
       <c r="E40">
         <v>-670.462</v>
@@ -4562,37 +4562,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M40">
-        <v>182.6141604</v>
+        <v>175.1847804</v>
       </c>
       <c r="N40">
-        <v>-229.5141604</v>
+        <v>-222.0847804</v>
       </c>
       <c r="O40">
-        <v>-59.21465338320001</v>
+        <v>-57.29787334320001</v>
       </c>
       <c r="P40">
-        <v>-170.2995070168</v>
+        <v>-164.7869070568</v>
       </c>
       <c r="Q40">
-        <v>37.40049298319997</v>
+        <v>42.91309294319996</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1045367171277528</v>
+        <v>0.1045600950697545</v>
       </c>
       <c r="T40">
-        <v>1.355634056373034</v>
+        <v>1.357046075513961</v>
       </c>
       <c r="U40">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>-0.06626101707280307</v>
+        <v>-0.06907106868742578</v>
       </c>
       <c r="W40">
-        <v>0.262086957996495</v>
+        <v>0.2520869579964951</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>-0.2568256475690043</v>
+        <v>-0.2677173204938983</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4611,13 +4611,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1664058086578749</v>
+        <v>0.1625203029819159</v>
       </c>
       <c r="C41">
-        <v>569.7521570702538</v>
+        <v>582.0644991239446</v>
       </c>
       <c r="D41">
-        <v>550.7411570702537</v>
+        <v>563.0534991239447</v>
       </c>
       <c r="E41">
         <v>-650.9110000000001</v>
@@ -4644,37 +4644,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M41">
-        <v>187.4197962</v>
+        <v>179.7949062</v>
       </c>
       <c r="N41">
-        <v>-234.3197962</v>
+        <v>-226.6949062</v>
       </c>
       <c r="O41">
-        <v>-60.45450741960001</v>
+        <v>-58.48728579960001</v>
       </c>
       <c r="P41">
-        <v>-173.8652887804</v>
+        <v>-168.2076204004</v>
       </c>
       <c r="Q41">
-        <v>33.83471121959997</v>
+        <v>39.49237959959999</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1054996141298471</v>
+        <v>0.1055233753167996</v>
       </c>
       <c r="T41">
-        <v>1.377857565493903</v>
+        <v>1.379292732489599</v>
       </c>
       <c r="U41">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>-0.0645620166350389</v>
+        <v>-0.06730001564415845</v>
       </c>
       <c r="W41">
-        <v>0.2616693436888926</v>
+        <v>0.2516693436888926</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>-0.2502403745544144</v>
+        <v>-0.2608527738145676</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4693,13 +4693,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1684058086578749</v>
+        <v>0.1644203029819159</v>
       </c>
       <c r="C42">
-        <v>544.0395877218401</v>
+        <v>556.3932878410984</v>
       </c>
       <c r="D42">
-        <v>544.5795877218401</v>
+        <v>556.9332878410985</v>
       </c>
       <c r="E42">
         <v>-631.36</v>
@@ -4726,37 +4726,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M42">
-        <v>192.225432</v>
+        <v>184.405032</v>
       </c>
       <c r="N42">
-        <v>-239.125432</v>
+        <v>-231.305032</v>
       </c>
       <c r="O42">
-        <v>-61.69436145600002</v>
+        <v>-59.67669825600001</v>
       </c>
       <c r="P42">
-        <v>-177.431070544</v>
+        <v>-171.628333744</v>
       </c>
       <c r="Q42">
-        <v>30.26892945599997</v>
+        <v>36.07166625599996</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1064946076986779</v>
+        <v>0.106518764905413</v>
       </c>
       <c r="T42">
-        <v>1.400821858252135</v>
+        <v>1.402280944697759</v>
       </c>
       <c r="U42">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>-0.06294796621916292</v>
+        <v>-0.06561751525305448</v>
       </c>
       <c r="W42">
-        <v>0.2612726100966703</v>
+        <v>0.2512726100966702</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>-0.243984365190554</v>
+        <v>-0.2543314544692035</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4775,13 +4775,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1704058086578749</v>
+        <v>0.1663203029819159</v>
       </c>
       <c r="C43">
-        <v>518.4633615264918</v>
+        <v>530.853695378524</v>
       </c>
       <c r="D43">
-        <v>538.5543615264918</v>
+        <v>550.9446953785242</v>
       </c>
       <c r="E43">
         <v>-611.809</v>
@@ -4808,37 +4808,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M43">
-        <v>197.0310678</v>
+        <v>189.0151578</v>
       </c>
       <c r="N43">
-        <v>-243.9310678000001</v>
+        <v>-235.9151578</v>
       </c>
       <c r="O43">
-        <v>-62.93421549240001</v>
+        <v>-60.86611071240001</v>
       </c>
       <c r="P43">
-        <v>-180.9968523076</v>
+        <v>-175.0490470876</v>
       </c>
       <c r="Q43">
-        <v>26.70314769239997</v>
+        <v>32.65095291239996</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1075233298630623</v>
+        <v>0.1075478965139793</v>
       </c>
       <c r="T43">
-        <v>1.424564601612341</v>
+        <v>1.426048418336704</v>
       </c>
       <c r="U43">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>-0.06141264996991504</v>
+        <v>-0.06401708805176047</v>
       </c>
       <c r="W43">
-        <v>0.2608952293626051</v>
+        <v>0.2508952293626052</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>-0.2380335270151746</v>
+        <v>-0.2481282482626375</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4857,13 +4857,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1724058086578748</v>
+        <v>0.1682203029819159</v>
       </c>
       <c r="C44">
-        <v>493.0190025062482</v>
+        <v>505.4415210922107</v>
       </c>
       <c r="D44">
-        <v>532.6610025062483</v>
+        <v>545.0835210922107</v>
       </c>
       <c r="E44">
         <v>-592.258</v>
@@ -4890,37 +4890,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M44">
-        <v>201.8367036</v>
+        <v>193.6252836</v>
       </c>
       <c r="N44">
-        <v>-248.7367036</v>
+        <v>-240.5252836</v>
       </c>
       <c r="O44">
-        <v>-64.1740695288</v>
+        <v>-62.05552316880001</v>
       </c>
       <c r="P44">
-        <v>-184.5626340712</v>
+        <v>-178.4697604312</v>
       </c>
       <c r="Q44">
-        <v>23.13736592879997</v>
+        <v>29.23023956879996</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1085875252055288</v>
+        <v>0.1086125154193927</v>
       </c>
       <c r="T44">
-        <v>1.449126060260829</v>
+        <v>1.450635460032165</v>
       </c>
       <c r="U44">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>-0.05995044401825041</v>
+        <v>-0.06249287166957571</v>
       </c>
       <c r="W44">
-        <v>0.2605358191396859</v>
+        <v>0.2505358191396859</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>-0.2323660620862418</v>
+        <v>-0.2422204328278128</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4939,13 +4939,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1744058086578748</v>
+        <v>0.1701203029819159</v>
       </c>
       <c r="C45">
-        <v>467.7022284835376</v>
+        <v>480.1527412091751</v>
       </c>
       <c r="D45">
-        <v>526.8952284835378</v>
+        <v>539.3457412091751</v>
       </c>
       <c r="E45">
         <v>-572.707</v>
@@ -4972,37 +4972,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M45">
-        <v>206.6423394</v>
+        <v>198.2354094</v>
       </c>
       <c r="N45">
-        <v>-253.5423394</v>
+        <v>-245.1354094</v>
       </c>
       <c r="O45">
-        <v>-65.41392356520001</v>
+        <v>-63.24493562520001</v>
       </c>
       <c r="P45">
-        <v>-188.1284158348</v>
+        <v>-181.8904737748</v>
       </c>
       <c r="Q45">
-        <v>19.57158416519997</v>
+        <v>25.80952622519996</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1096890607354504</v>
+        <v>0.1097144893741189</v>
       </c>
       <c r="T45">
-        <v>1.474549324475931</v>
+        <v>1.47608520494501</v>
       </c>
       <c r="U45">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>-0.05855624764573296</v>
+        <v>-0.06103954907260882</v>
       </c>
       <c r="W45">
-        <v>0.2601931256713211</v>
+        <v>0.2501931256713212</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>-0.2269622001772595</v>
+        <v>-0.2365873995062358</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5021,13 +5021,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1764058086578749</v>
+        <v>0.1720203029819159</v>
       </c>
       <c r="C46">
-        <v>442.5089407045658</v>
+        <v>454.9834996153378</v>
       </c>
       <c r="D46">
-        <v>521.252940704566</v>
+        <v>533.7274996153377</v>
       </c>
       <c r="E46">
         <v>-553.1560000000001</v>
@@ -5054,37 +5054,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M46">
-        <v>211.4479752</v>
+        <v>202.8455352</v>
       </c>
       <c r="N46">
-        <v>-258.3479752000001</v>
+        <v>-249.7455352</v>
       </c>
       <c r="O46">
-        <v>-66.65377760160001</v>
+        <v>-64.43434808160001</v>
       </c>
       <c r="P46">
-        <v>-191.6941975984001</v>
+        <v>-185.3111871184</v>
       </c>
       <c r="Q46">
-        <v>16.00580240159994</v>
+        <v>22.38881288159996</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.110829936820012</v>
+        <v>0.1108558195415139</v>
       </c>
       <c r="T46">
-        <v>1.500880562413002</v>
+        <v>1.502443869319028</v>
       </c>
       <c r="U46">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>-0.05722542383560266</v>
+        <v>-0.0596522865936859</v>
       </c>
       <c r="W46">
-        <v>0.2598660091787912</v>
+        <v>0.2498660091787911</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>-0.2218039683550492</v>
+        <v>-0.2312104131538213</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5103,13 +5103,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1784058086578749</v>
+        <v>0.1739203029819159</v>
       </c>
       <c r="C47">
-        <v>417.4352141223494</v>
+        <v>429.9300992132221</v>
       </c>
       <c r="D47">
-        <v>515.7302141223496</v>
+        <v>528.2250992132221</v>
       </c>
       <c r="E47">
         <v>-533.605</v>
@@ -5136,37 +5136,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M47">
-        <v>216.253611</v>
+        <v>207.455661</v>
       </c>
       <c r="N47">
-        <v>-263.1536110000001</v>
+        <v>-254.355661</v>
       </c>
       <c r="O47">
-        <v>-67.89363163800002</v>
+        <v>-65.62376053800001</v>
       </c>
       <c r="P47">
-        <v>-195.2599793620001</v>
+        <v>-188.731900462</v>
       </c>
       <c r="Q47">
-        <v>12.44002063799994</v>
+        <v>18.96809953799999</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1120122993076486</v>
+        <v>0.1120386526240869</v>
       </c>
       <c r="T47">
-        <v>1.52816929991142</v>
+        <v>1.529761030579374</v>
       </c>
       <c r="U47">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>-0.05595374775036704</v>
+        <v>-0.05832668022493732</v>
       </c>
       <c r="W47">
-        <v>0.2595534311970403</v>
+        <v>0.2495534311970402</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>-0.2168749912804926</v>
+        <v>-0.2260724039726252</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5185,13 +5185,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1804058086578748</v>
+        <v>0.1758203029819159</v>
       </c>
       <c r="C48">
-        <v>392.4772882909882</v>
+        <v>404.9889938087844</v>
       </c>
       <c r="D48">
-        <v>510.3232882909882</v>
+        <v>522.8349938087846</v>
       </c>
       <c r="E48">
         <v>-514.054</v>
@@ -5218,37 +5218,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M48">
-        <v>221.0592468</v>
+        <v>212.0657868</v>
       </c>
       <c r="N48">
-        <v>-267.9592468000001</v>
+        <v>-258.9657868</v>
       </c>
       <c r="O48">
-        <v>-69.13348567440002</v>
+        <v>-66.81317299440002</v>
       </c>
       <c r="P48">
-        <v>-198.8257611256001</v>
+        <v>-192.1526138056</v>
       </c>
       <c r="Q48">
-        <v>8.874238874399936</v>
+        <v>15.54738619439996</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.113238452998531</v>
+        <v>0.1132652943393477</v>
       </c>
       <c r="T48">
-        <v>1.556468731391261</v>
+        <v>1.558089938553066</v>
       </c>
       <c r="U48">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>-0.05473736192970689</v>
+        <v>-0.05705870891569955</v>
       </c>
       <c r="W48">
-        <v>0.259254443562322</v>
+        <v>0.249254443562322</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>-0.2121603175570035</v>
+        <v>-0.2211577864949594</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5267,13 +5267,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1824058086578749</v>
+        <v>0.1777203029819159</v>
       </c>
       <c r="C49">
-        <v>367.6315588267803</v>
+        <v>380.156780489953</v>
       </c>
       <c r="D49">
-        <v>505.0285588267804</v>
+        <v>517.5537804899531</v>
       </c>
       <c r="E49">
         <v>-494.5029999999999</v>
@@ -5300,37 +5300,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M49">
-        <v>225.8648826</v>
+        <v>216.6759126000001</v>
       </c>
       <c r="N49">
-        <v>-272.7648826000001</v>
+        <v>-263.5759126</v>
       </c>
       <c r="O49">
-        <v>-70.37333971080002</v>
+        <v>-68.00258545080001</v>
       </c>
       <c r="P49">
-        <v>-202.3915428892001</v>
+        <v>-195.5733271492</v>
       </c>
       <c r="Q49">
-        <v>5.308457110799935</v>
+        <v>12.12667285079996</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1145108766400127</v>
+        <v>0.1145382244212222</v>
       </c>
       <c r="T49">
-        <v>1.585836065945813</v>
+        <v>1.587487861921992</v>
       </c>
       <c r="U49">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>-0.05357273720779823</v>
+        <v>-0.05584469383238679</v>
       </c>
       <c r="W49">
-        <v>0.2589681788056769</v>
+        <v>0.2489681788056768</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>-0.2076462682472802</v>
+        <v>-0.2164523016759177</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5349,13 +5349,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1844058086578748</v>
+        <v>0.1796203029819159</v>
       </c>
       <c r="C50">
-        <v>342.8945693954412</v>
+        <v>355.4301924624593</v>
       </c>
       <c r="D50">
-        <v>499.8425693954412</v>
+        <v>512.3781924624593</v>
       </c>
       <c r="E50">
         <v>-474.9520000000001</v>
@@ -5382,37 +5382,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M50">
-        <v>230.6705184</v>
+        <v>221.2860384</v>
       </c>
       <c r="N50">
-        <v>-277.5705184</v>
+        <v>-268.1860384</v>
       </c>
       <c r="O50">
-        <v>-71.61319374720001</v>
+        <v>-69.1919979072</v>
       </c>
       <c r="P50">
-        <v>-205.9573246528</v>
+        <v>-198.9940404928</v>
       </c>
       <c r="Q50">
-        <v>1.742675347199963</v>
+        <v>8.705959507199964</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1158322396523206</v>
+        <v>0.1158601133523996</v>
       </c>
       <c r="T50">
-        <v>1.616332913367848</v>
+        <v>1.618016474651261</v>
       </c>
       <c r="U50">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>-0.05245663851596911</v>
+        <v>-0.05468126271087874</v>
       </c>
       <c r="W50">
-        <v>0.2586938417472252</v>
+        <v>0.2486938417472252</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>-0.2033203043254617</v>
+        <v>-0.2119428787243363</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5431,13 +5431,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1864058086578748</v>
+        <v>0.1815203029819159</v>
       </c>
       <c r="C51">
-        <v>318.2630041879847</v>
+        <v>330.8060923112687</v>
       </c>
       <c r="D51">
-        <v>494.7620041879848</v>
+        <v>507.3050923112688</v>
       </c>
       <c r="E51">
         <v>-455.4010000000001</v>
@@ -5464,37 +5464,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M51">
-        <v>235.4761542</v>
+        <v>225.8961642</v>
       </c>
       <c r="N51">
-        <v>-282.3761542</v>
+        <v>-272.7961642</v>
       </c>
       <c r="O51">
-        <v>-72.8530477836</v>
+        <v>-70.38141036360001</v>
       </c>
       <c r="P51">
-        <v>-209.5231064164</v>
+        <v>-202.4147538364</v>
       </c>
       <c r="Q51">
-        <v>-1.823106416400037</v>
+        <v>5.285246163599993</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.117205420821974</v>
+        <v>0.1172338410651917</v>
       </c>
       <c r="T51">
-        <v>1.648025715590747</v>
+        <v>1.649742287879717</v>
       </c>
       <c r="U51">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>-0.05138609487278607</v>
+        <v>-0.05356531857392204</v>
       </c>
       <c r="W51">
-        <v>0.2584307021197308</v>
+        <v>0.2484307021197308</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>-0.199170910359636</v>
+        <v>-0.207617513852411</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5513,13 +5513,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1884058086578748</v>
+        <v>0.1834203029819159</v>
       </c>
       <c r="C52">
-        <v>293.7336808508579</v>
+        <v>306.2814656584011</v>
       </c>
       <c r="D52">
-        <v>489.783680850858</v>
+        <v>502.3314656584012</v>
       </c>
       <c r="E52">
         <v>-435.85</v>
@@ -5546,37 +5546,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M52">
-        <v>240.28179</v>
+        <v>230.50629</v>
       </c>
       <c r="N52">
-        <v>-287.18179</v>
+        <v>-277.40629</v>
       </c>
       <c r="O52">
-        <v>-74.09290182000001</v>
+        <v>-71.57082282</v>
       </c>
       <c r="P52">
-        <v>-213.08888818</v>
+        <v>-205.83546718</v>
       </c>
       <c r="Q52">
-        <v>-5.388888180000038</v>
+        <v>1.864532819999965</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1186335292384134</v>
+        <v>0.1186625178864956</v>
       </c>
       <c r="T52">
-        <v>1.680986229902562</v>
+        <v>1.682737133637311</v>
       </c>
       <c r="U52">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>-0.05035837297533034</v>
+        <v>-0.05249401220244359</v>
       </c>
       <c r="W52">
-        <v>0.2581780880773362</v>
+        <v>0.2481780880773362</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>-0.1951874921524432</v>
+        <v>-0.2034651635753626</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5595,13 +5595,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1904058086578749</v>
+        <v>0.1853203029819159</v>
       </c>
       <c r="C53">
-        <v>269.3035438386437</v>
+        <v>281.8534151902013</v>
       </c>
       <c r="D53">
-        <v>484.9045438386439</v>
+        <v>497.4544151902015</v>
       </c>
       <c r="E53">
         <v>-416.299</v>
@@ -5628,37 +5628,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M53">
-        <v>245.0874258</v>
+        <v>235.1164158</v>
       </c>
       <c r="N53">
-        <v>-291.9874258</v>
+        <v>-282.0164158</v>
       </c>
       <c r="O53">
-        <v>-75.33275585640001</v>
+        <v>-72.76023527640001</v>
       </c>
       <c r="P53">
-        <v>-216.6546699436</v>
+        <v>-209.2561805236</v>
       </c>
       <c r="Q53">
-        <v>-8.954669943600038</v>
+        <v>-1.556180523600005</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1201199277942995</v>
+        <v>0.1201495080474445</v>
       </c>
       <c r="T53">
-        <v>1.715292071329145</v>
+        <v>1.717078707793175</v>
       </c>
       <c r="U53">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>-0.04937095389738269</v>
+        <v>-0.05146471784553293</v>
       </c>
       <c r="W53">
-        <v>0.2579353804679767</v>
+        <v>0.2479353804679767</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>-0.1913602864239639</v>
+        <v>-0.1994756505640809</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5677,13 +5677,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1924058086578748</v>
+        <v>0.1872203029819159</v>
       </c>
       <c r="C54">
-        <v>244.9696581601639</v>
+        <v>257.5191550291955</v>
       </c>
       <c r="D54">
-        <v>480.1216581601641</v>
+        <v>492.6711550291957</v>
       </c>
       <c r="E54">
         <v>-396.7479999999999</v>
@@ -5710,37 +5710,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M54">
-        <v>249.8930616000001</v>
+        <v>239.7265416</v>
       </c>
       <c r="N54">
-        <v>-296.7930616000001</v>
+        <v>-286.6265416000001</v>
       </c>
       <c r="O54">
-        <v>-76.57260989280003</v>
+        <v>-73.94964773280002</v>
       </c>
       <c r="P54">
-        <v>-220.2204517072001</v>
+        <v>-212.6768938672</v>
       </c>
       <c r="Q54">
-        <v>-12.5204517072001</v>
+        <v>-4.976893867200033</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1216682596233473</v>
+        <v>0.1216984561317662</v>
       </c>
       <c r="T54">
-        <v>1.751027322815169</v>
+        <v>1.752851180872199</v>
       </c>
       <c r="U54">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>-0.04842151247627916</v>
+        <v>-0.05047501173311883</v>
       </c>
       <c r="W54">
-        <v>0.2577020077666695</v>
+        <v>0.2477020077666694</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>-0.1876802809158109</v>
+        <v>-0.1956395803609257</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5759,13 +5759,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1944058086578748</v>
+        <v>0.1891203029819159</v>
       </c>
       <c r="C55">
-        <v>220.7292034910768</v>
+        <v>233.2760054275552</v>
       </c>
       <c r="D55">
-        <v>475.4322034910771</v>
+        <v>487.9790054275554</v>
       </c>
       <c r="E55">
         <v>-377.1969999999999</v>
@@ -5792,37 +5792,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M55">
-        <v>254.6986974000001</v>
+        <v>244.3366674000001</v>
       </c>
       <c r="N55">
-        <v>-301.5986974000001</v>
+        <v>-291.2366674000001</v>
       </c>
       <c r="O55">
-        <v>-77.81246392920004</v>
+        <v>-75.13906018920002</v>
       </c>
       <c r="P55">
-        <v>-223.7862334708001</v>
+        <v>-216.0976072108001</v>
       </c>
       <c r="Q55">
-        <v>-16.0862334708001</v>
+        <v>-8.397607210800089</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1232824779132058</v>
+        <v>0.1233133169005272</v>
       </c>
       <c r="T55">
-        <v>1.788283223300598</v>
+        <v>1.790145886848204</v>
       </c>
       <c r="U55">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>-0.0475078990333305</v>
+        <v>-0.04952265302117319</v>
       </c>
       <c r="W55">
-        <v>0.2574774415823926</v>
+        <v>0.2474774415823927</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>-0.1841391435400408</v>
+        <v>-0.1919482675239272</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5841,13 +5841,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1964058086578748</v>
+        <v>0.1910203029819159</v>
       </c>
       <c r="C56">
-        <v>196.5794686281638</v>
+        <v>209.1213877609378</v>
       </c>
       <c r="D56">
-        <v>470.8334686281639</v>
+        <v>483.375387760938</v>
       </c>
       <c r="E56">
         <v>-357.646</v>
@@ -5874,37 +5874,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M56">
-        <v>259.5043332000001</v>
+        <v>248.9467932</v>
       </c>
       <c r="N56">
-        <v>-306.4043332000001</v>
+        <v>-295.8467932</v>
       </c>
       <c r="O56">
-        <v>-79.05231796560003</v>
+        <v>-76.32847264560002</v>
       </c>
       <c r="P56">
-        <v>-227.3520152344001</v>
+        <v>-219.5183205544</v>
       </c>
       <c r="Q56">
-        <v>-19.6520152344001</v>
+        <v>-11.81832055440003</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1249668796069711</v>
+        <v>0.1249983890070604</v>
       </c>
       <c r="T56">
-        <v>1.827158945546263</v>
+        <v>1.829062101779686</v>
       </c>
       <c r="U56">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>-0.04662812312530586</v>
+        <v>-0.04860556685411443</v>
       </c>
       <c r="W56">
-        <v>0.2572611926642002</v>
+        <v>0.2472611926642002</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>-0.1807291594004103</v>
+        <v>-0.1883936699771878</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5923,13 +5923,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1984058086578749</v>
+        <v>0.1929203029819159</v>
       </c>
       <c r="C57">
-        <v>172.5178462623821</v>
+        <v>185.0528198030468</v>
       </c>
       <c r="D57">
-        <v>466.3228462623823</v>
+        <v>478.8578198030468</v>
       </c>
       <c r="E57">
         <v>-338.095</v>
@@ -5956,37 +5956,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M57">
-        <v>264.309969</v>
+        <v>253.556919</v>
       </c>
       <c r="N57">
-        <v>-311.209969</v>
+        <v>-300.456919</v>
       </c>
       <c r="O57">
-        <v>-80.292172002</v>
+        <v>-77.51788510200001</v>
       </c>
       <c r="P57">
-        <v>-230.917796998</v>
+        <v>-222.939033898</v>
       </c>
       <c r="Q57">
-        <v>-23.21779699800001</v>
+        <v>-15.23903389800003</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1267261435982372</v>
+        <v>0.1267583532072173</v>
       </c>
       <c r="T57">
-        <v>1.867762477669513</v>
+        <v>1.869707926263679</v>
       </c>
       <c r="U57">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>-0.04578033906848213</v>
+        <v>-0.04772182927494872</v>
       </c>
       <c r="W57">
-        <v>0.2570528073430329</v>
+        <v>0.2470528073430329</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>-0.1774431746840393</v>
+        <v>-0.1849683305230569</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6005,13 +6005,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2004058086578749</v>
+        <v>0.1948203029819159</v>
       </c>
       <c r="C58">
-        <v>148.5418280495169</v>
+        <v>161.0679112627179</v>
       </c>
       <c r="D58">
-        <v>461.897828049517</v>
+        <v>474.423911262718</v>
       </c>
       <c r="E58">
         <v>-318.5439999999999</v>
@@ -6038,37 +6038,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M58">
-        <v>269.1156048000001</v>
+        <v>258.1670448</v>
       </c>
       <c r="N58">
-        <v>-316.0156048000001</v>
+        <v>-305.0670448000001</v>
       </c>
       <c r="O58">
-        <v>-81.53202603840003</v>
+        <v>-78.70729755840001</v>
       </c>
       <c r="P58">
-        <v>-234.4835787616001</v>
+        <v>-226.3597472416001</v>
       </c>
       <c r="Q58">
-        <v>-26.7835787616001</v>
+        <v>-18.65974724160009</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1285653741345608</v>
+        <v>0.1285983157801086</v>
       </c>
       <c r="T58">
-        <v>1.910211624889275</v>
+        <v>1.912201288224217</v>
       </c>
       <c r="U58">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>-0.0449628330136878</v>
+        <v>-0.04686965375218177</v>
       </c>
       <c r="W58">
-        <v>0.2568518643547645</v>
+        <v>0.2468518643547645</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>-0.1742745465646816</v>
+        <v>-0.1816653246208597</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6087,13 +6087,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2024058086578748</v>
+        <v>0.1967203029819159</v>
       </c>
       <c r="C59">
-        <v>124.6489999588462</v>
+        <v>137.1643595666762</v>
       </c>
       <c r="D59">
-        <v>457.5559999588462</v>
+        <v>470.0713595666763</v>
       </c>
       <c r="E59">
         <v>-298.9929999999999</v>
@@ -6120,37 +6120,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M59">
-        <v>273.9212406</v>
+        <v>262.7771706</v>
       </c>
       <c r="N59">
-        <v>-320.8212406</v>
+        <v>-309.6771706000001</v>
       </c>
       <c r="O59">
-        <v>-82.77188007480001</v>
+        <v>-79.89671001480002</v>
       </c>
       <c r="P59">
-        <v>-238.0493605252</v>
+        <v>-229.7804605852</v>
       </c>
       <c r="Q59">
-        <v>-30.34936052520001</v>
+        <v>-22.08046058520006</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.130490150277225</v>
+        <v>0.130523858007553</v>
       </c>
       <c r="T59">
-        <v>1.954635151049491</v>
+        <v>1.956671085624781</v>
       </c>
       <c r="U59">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>-0.04417401138186872</v>
+        <v>-0.04604737912495051</v>
       </c>
       <c r="W59">
-        <v>0.2566579719976633</v>
+        <v>0.2466579719976633</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>-0.171217098379336</v>
+        <v>-0.1784782136625991</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6169,13 +6169,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.2044058086578748</v>
+        <v>0.1986203029819159</v>
       </c>
       <c r="C60">
-        <v>100.8370378816971</v>
+        <v>113.3399458723216</v>
       </c>
       <c r="D60">
-        <v>453.2950378816971</v>
+        <v>465.7979458723217</v>
       </c>
       <c r="E60">
         <v>-279.442</v>
@@ -6202,37 +6202,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M60">
-        <v>278.7268764</v>
+        <v>267.3872964</v>
       </c>
       <c r="N60">
-        <v>-325.6268764</v>
+        <v>-314.2872964000001</v>
       </c>
       <c r="O60">
-        <v>-84.0117341112</v>
+        <v>-81.08612247120001</v>
       </c>
       <c r="P60">
-        <v>-241.6151422888</v>
+        <v>-233.2011739288</v>
       </c>
       <c r="Q60">
-        <v>-33.91514228880004</v>
+        <v>-25.50117392880006</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1325065824266827</v>
+        <v>0.1325410927220185</v>
       </c>
       <c r="T60">
-        <v>2.001174083217335</v>
+        <v>2.00325849242537</v>
       </c>
       <c r="U60">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>-0.04341239049597443</v>
+        <v>-0.04525345879520999</v>
       </c>
       <c r="W60">
-        <v>0.2564707655839105</v>
+        <v>0.2464707655839105</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>-0.1682650794417613</v>
+        <v>-0.1754010030822093</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6251,13 +6251,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.2064058086578748</v>
+        <v>0.2005203029819158</v>
       </c>
       <c r="C61">
-        <v>77.10370348311085</v>
+        <v>89.59253129604554</v>
       </c>
       <c r="D61">
-        <v>449.1127034831109</v>
+        <v>461.6015312960456</v>
       </c>
       <c r="E61">
         <v>-259.8910000000001</v>
@@ -6284,37 +6284,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M61">
-        <v>283.5325122</v>
+        <v>271.9974222</v>
       </c>
       <c r="N61">
-        <v>-330.4325122</v>
+        <v>-318.8974222000001</v>
       </c>
       <c r="O61">
-        <v>-85.2515881476</v>
+        <v>-82.27553492760002</v>
       </c>
       <c r="P61">
-        <v>-245.1809240524</v>
+        <v>-236.6218872724</v>
       </c>
       <c r="Q61">
-        <v>-37.48092405240004</v>
+        <v>-28.92188727240006</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1346213771200164</v>
+        <v>0.1346567291298726</v>
       </c>
       <c r="T61">
-        <v>2.049983207198246</v>
+        <v>2.052118455655257</v>
       </c>
       <c r="U61">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>-0.0426765872672291</v>
+        <v>-0.04448645101901999</v>
       </c>
       <c r="W61">
-        <v>0.2562899051502849</v>
+        <v>0.2462899051502849</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>-0.1654131289427483</v>
+        <v>-0.1724281047248837</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6333,13 +6333,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.2084058086578748</v>
+        <v>0.2024203029819159</v>
       </c>
       <c r="C62">
-        <v>53.44684028105371</v>
+        <v>65.92005334360124</v>
       </c>
       <c r="D62">
-        <v>445.0068402810536</v>
+        <v>457.4800533436012</v>
       </c>
       <c r="E62">
         <v>-240.3400000000001</v>
@@ -6366,37 +6366,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M62">
-        <v>288.338148</v>
+        <v>276.607548</v>
       </c>
       <c r="N62">
-        <v>-335.238148</v>
+        <v>-323.507548</v>
       </c>
       <c r="O62">
-        <v>-86.49144218400001</v>
+        <v>-83.46494738400001</v>
       </c>
       <c r="P62">
-        <v>-248.746705816</v>
+        <v>-240.042600616</v>
       </c>
       <c r="Q62">
-        <v>-41.04670581600004</v>
+        <v>-32.34260061600003</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1368419115480168</v>
+        <v>0.1368781473581195</v>
       </c>
       <c r="T62">
-        <v>2.101232787378202</v>
+        <v>2.103421417046639</v>
       </c>
       <c r="U62">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>-0.04196531081277529</v>
+        <v>-0.043745010168703</v>
       </c>
       <c r="W62">
-        <v>0.2561150733977802</v>
+        <v>0.2461150733977802</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>-0.1626562434603693</v>
+        <v>-0.1695543029794691</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6415,13 +6415,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.2104058086578748</v>
+        <v>0.2043203029819159</v>
       </c>
       <c r="C63">
-        <v>29.86436993874736</v>
+        <v>42.32052253001461</v>
       </c>
       <c r="D63">
-        <v>440.9753699387474</v>
+        <v>453.4315225300147</v>
       </c>
       <c r="E63">
         <v>-220.789</v>
@@ -6448,37 +6448,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M63">
-        <v>293.1437838000001</v>
+        <v>281.2176738000001</v>
       </c>
       <c r="N63">
-        <v>-340.0437838</v>
+        <v>-328.1176738</v>
       </c>
       <c r="O63">
-        <v>-87.73129622040001</v>
+        <v>-84.65435984040001</v>
       </c>
       <c r="P63">
-        <v>-252.3124875796</v>
+        <v>-243.4633139596</v>
       </c>
       <c r="Q63">
-        <v>-44.61248757960004</v>
+        <v>-35.76331395960005</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1391763195364275</v>
+        <v>0.1392134844698661</v>
       </c>
       <c r="T63">
-        <v>2.155110551157131</v>
+        <v>2.157355299535014</v>
       </c>
       <c r="U63">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>-0.04127735489781175</v>
+        <v>-0.04302787885446196</v>
       </c>
       <c r="W63">
-        <v>0.2559459738338822</v>
+        <v>0.2459459738338821</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>-0.1599897476659369</v>
+        <v>-0.1667747242421005</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6497,13 +6497,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.2124058086578748</v>
+        <v>0.2062203029819159</v>
       </c>
       <c r="C64">
-        <v>6.354288756726191</v>
+        <v>18.7920191773967</v>
       </c>
       <c r="D64">
-        <v>437.0162887567263</v>
+        <v>449.4540191773966</v>
       </c>
       <c r="E64">
         <v>-201.2380000000001</v>
@@ -6530,37 +6530,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M64">
-        <v>297.9494196000001</v>
+        <v>285.8277996</v>
       </c>
       <c r="N64">
-        <v>-344.8494196</v>
+        <v>-332.7277996</v>
       </c>
       <c r="O64">
-        <v>-88.97115025680002</v>
+        <v>-85.84377229680001</v>
       </c>
       <c r="P64">
-        <v>-255.8782693432</v>
+        <v>-246.8840273032</v>
       </c>
       <c r="Q64">
-        <v>-48.17826934320004</v>
+        <v>-39.18402730320003</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1416335911031756</v>
+        <v>0.1416717340611784</v>
       </c>
       <c r="T64">
-        <v>2.211823986713897</v>
+        <v>2.214127807417515</v>
       </c>
       <c r="U64">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>-0.04061159110913737</v>
+        <v>-0.04233388080842225</v>
       </c>
       <c r="W64">
-        <v>0.255782329094626</v>
+        <v>0.2457823290946259</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>-0.1574092678648735</v>
+        <v>-0.16408480933497</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6579,13 +6579,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.2144058086578749</v>
+        <v>0.2081203029819159</v>
       </c>
       <c r="C65">
-        <v>-17.08533564782442</v>
+        <v>-4.66730962017391</v>
       </c>
       <c r="D65">
-        <v>433.1276643521757</v>
+        <v>445.5456903798264</v>
       </c>
       <c r="E65">
         <v>-181.6869999999999</v>
@@ -6612,37 +6612,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M65">
-        <v>302.7550554000001</v>
+        <v>290.4379254</v>
       </c>
       <c r="N65">
-        <v>-349.6550554</v>
+        <v>-337.3379254</v>
       </c>
       <c r="O65">
-        <v>-90.21100429320001</v>
+        <v>-87.0331847532</v>
       </c>
       <c r="P65">
-        <v>-259.4440511068</v>
+        <v>-250.3047406468</v>
       </c>
       <c r="Q65">
-        <v>-51.74405110680004</v>
+        <v>-42.60474064680002</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1442236881600182</v>
+        <v>0.1442628620087778</v>
       </c>
       <c r="T65">
-        <v>2.27160301338184</v>
+        <v>2.27396909950988</v>
       </c>
       <c r="U65">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>-0.0399669626788336</v>
+        <v>-0.0416619144463838</v>
       </c>
       <c r="W65">
-        <v>0.2556238794264574</v>
+        <v>0.2456238794264573</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>-0.1549107080574945</v>
+        <v>-0.1614802885518751</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6661,13 +6661,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2164058086578748</v>
+        <v>0.2100203029819159</v>
       </c>
       <c r="C66">
-        <v>-40.45636748600373</v>
+        <v>-28.05925287477544</v>
       </c>
       <c r="D66">
-        <v>429.3076325139963</v>
+        <v>441.7047471252247</v>
       </c>
       <c r="E66">
         <v>-162.136</v>
@@ -6694,37 +6694,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M66">
-        <v>307.5606912000001</v>
+        <v>295.0480512</v>
       </c>
       <c r="N66">
-        <v>-354.4606912</v>
+        <v>-341.9480512</v>
       </c>
       <c r="O66">
-        <v>-91.45085832960001</v>
+        <v>-88.22259720960001</v>
       </c>
       <c r="P66">
-        <v>-263.0098328704</v>
+        <v>-253.7254539904</v>
       </c>
       <c r="Q66">
-        <v>-55.30983287040004</v>
+        <v>-46.02545399040002</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1469576794977965</v>
+        <v>0.1469979415090216</v>
       </c>
       <c r="T66">
-        <v>2.334703097086891</v>
+        <v>2.337134907829599</v>
       </c>
       <c r="U66">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>-0.03934247888697683</v>
+        <v>-0.04101094703315905</v>
       </c>
       <c r="W66">
-        <v>0.2554703813104189</v>
+        <v>0.2454703813104189</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>-0.1524902282440961</v>
+        <v>-0.1589571590432521</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6743,13 +6743,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2184058086578748</v>
+        <v>0.2119203029819159</v>
       </c>
       <c r="C67">
-        <v>-63.76060577716635</v>
+        <v>-51.38553843517388</v>
       </c>
       <c r="D67">
-        <v>425.5543942228337</v>
+        <v>437.9294615648262</v>
       </c>
       <c r="E67">
         <v>-142.585</v>
@@ -6776,37 +6776,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M67">
-        <v>312.366327</v>
+        <v>299.658177</v>
       </c>
       <c r="N67">
-        <v>-359.266327</v>
+        <v>-346.558177</v>
       </c>
       <c r="O67">
-        <v>-92.69071236600001</v>
+        <v>-89.412009666</v>
       </c>
       <c r="P67">
-        <v>-266.575614634</v>
+        <v>-257.146167334</v>
       </c>
       <c r="Q67">
-        <v>-58.87561463400004</v>
+        <v>-49.44616733399999</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1498478989120192</v>
+        <v>0.1498893112664222</v>
       </c>
       <c r="T67">
-        <v>2.401408899860803</v>
+        <v>2.403910190910445</v>
       </c>
       <c r="U67">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>-0.03873720998102334</v>
+        <v>-0.04038000938649507</v>
       </c>
       <c r="W67">
-        <v>0.2553216062133356</v>
+        <v>0.2453216062133355</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>-0.1501442247326488</v>
+        <v>-0.1565116642887405</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6825,13 +6825,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2204058086578748</v>
+        <v>0.2138203029819159</v>
       </c>
       <c r="C68">
-        <v>-86.99978717392992</v>
+        <v>-74.64783557850888</v>
       </c>
       <c r="D68">
-        <v>421.8662128260704</v>
+        <v>434.2181644214914</v>
       </c>
       <c r="E68">
         <v>-123.0339999999999</v>
@@ -6858,37 +6858,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M68">
-        <v>317.1719628000001</v>
+        <v>304.2683028000001</v>
       </c>
       <c r="N68">
-        <v>-364.0719628000001</v>
+        <v>-351.1683028000001</v>
       </c>
       <c r="O68">
-        <v>-93.93056640240002</v>
+        <v>-90.60142212240002</v>
       </c>
       <c r="P68">
-        <v>-270.1413963976</v>
+        <v>-260.5668806776001</v>
       </c>
       <c r="Q68">
-        <v>-62.44139639760004</v>
+        <v>-52.86688067760008</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.152908131232961</v>
+        <v>0.1529507615977876</v>
       </c>
       <c r="T68">
-        <v>2.47203857338612</v>
+        <v>2.474613431819575</v>
       </c>
       <c r="U68">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>-0.03815028255706843</v>
+        <v>-0.03976819106245726</v>
       </c>
       <c r="W68">
-        <v>0.2551773394525275</v>
+        <v>0.2451773394525274</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>-0.1478693122366992</v>
+        <v>-0.1541402754358809</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6907,13 +6907,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2224058086578748</v>
+        <v>0.2157203029819159</v>
       </c>
       <c r="C69">
-        <v>-110.1755886415431</v>
+        <v>-97.84775747130561</v>
       </c>
       <c r="D69">
-        <v>418.2414113584571</v>
+        <v>430.5692425286945</v>
       </c>
       <c r="E69">
         <v>-103.4829999999999</v>
@@ -6940,37 +6940,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M69">
-        <v>321.9775986000001</v>
+        <v>308.8784286000001</v>
       </c>
       <c r="N69">
-        <v>-368.8775986000001</v>
+        <v>-355.7784286000001</v>
       </c>
       <c r="O69">
-        <v>-95.17042043880002</v>
+        <v>-91.79083457880003</v>
       </c>
       <c r="P69">
-        <v>-273.7071781612</v>
+        <v>-263.9875940212</v>
       </c>
       <c r="Q69">
-        <v>-66.00717816120004</v>
+        <v>-56.28759402120005</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1561538321794143</v>
+        <v>0.1561977543734782</v>
       </c>
       <c r="T69">
-        <v>2.5469488331857</v>
+        <v>2.54960171763229</v>
       </c>
       <c r="U69">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>-0.03758087535472413</v>
+        <v>-0.03917463597197282</v>
       </c>
       <c r="W69">
-        <v>0.2550373791621912</v>
+        <v>0.2450373791621912</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>-0.14566230757645</v>
+        <v>-0.1518396743099724</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6989,13 +6989,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2244058086578749</v>
+        <v>0.2176203029819159</v>
       </c>
       <c r="C70">
-        <v>-133.2896300003026</v>
+        <v>-120.9868635074376</v>
       </c>
       <c r="D70">
-        <v>414.6783699996978</v>
+        <v>426.9811364925626</v>
       </c>
       <c r="E70">
         <v>-83.93199999999979</v>
@@ -7022,37 +7022,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M70">
-        <v>326.7832344000001</v>
+        <v>313.4885544000001</v>
       </c>
       <c r="N70">
-        <v>-373.6832344000001</v>
+        <v>-360.3885544000001</v>
       </c>
       <c r="O70">
-        <v>-96.41027447520001</v>
+        <v>-92.98024703520002</v>
       </c>
       <c r="P70">
-        <v>-277.2729599248</v>
+        <v>-267.4083073648001</v>
       </c>
       <c r="Q70">
-        <v>-69.57295992480005</v>
+        <v>-59.70830736480008</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1596023894350211</v>
+        <v>0.1596476841976494</v>
       </c>
       <c r="T70">
-        <v>2.626540984222753</v>
+        <v>2.629276771308299</v>
       </c>
       <c r="U70">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>-0.03702821542303701</v>
+        <v>-0.03859853838414969</v>
       </c>
       <c r="W70">
-        <v>0.2549015353509825</v>
+        <v>0.2449015353509825</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>-0.1435202148179728</v>
+        <v>-0.1496067379230608</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7071,13 +7071,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2264058086578749</v>
+        <v>0.2195203029819159</v>
       </c>
       <c r="C71">
-        <v>-156.3434763391065</v>
+        <v>-144.0666615301543</v>
       </c>
       <c r="D71">
-        <v>411.1755236608938</v>
+        <v>423.452338469846</v>
       </c>
       <c r="E71">
         <v>-64.38099999999986</v>
@@ -7104,37 +7104,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M71">
-        <v>331.5888702000001</v>
+        <v>318.0986802</v>
       </c>
       <c r="N71">
-        <v>-378.4888702000001</v>
+        <v>-364.9986802000001</v>
       </c>
       <c r="O71">
-        <v>-97.65012851160002</v>
+        <v>-94.16965949160003</v>
       </c>
       <c r="P71">
-        <v>-280.8387416884</v>
+        <v>-270.8290207084</v>
       </c>
       <c r="Q71">
-        <v>-73.13874168840005</v>
+        <v>-63.12902070840005</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1632734342555056</v>
+        <v>0.163320190139509</v>
       </c>
       <c r="T71">
-        <v>2.711268112746068</v>
+        <v>2.714092151027922</v>
       </c>
       <c r="U71">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>-0.03649157461980459</v>
+        <v>-0.03803913927713303</v>
       </c>
       <c r="W71">
-        <v>0.254769629041548</v>
+        <v>0.244769629041548</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>-0.1414402117046689</v>
+        <v>-0.1474385243299732</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7153,13 +7153,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2284058086578749</v>
+        <v>0.2214203029819159</v>
       </c>
       <c r="C72">
-        <v>-179.3386403077138</v>
+        <v>-167.088609944828</v>
       </c>
       <c r="D72">
-        <v>407.7313596922864</v>
+        <v>419.9813900551721</v>
       </c>
       <c r="E72">
         <v>-44.82999999999993</v>
@@ -7186,37 +7186,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M72">
-        <v>336.3945060000001</v>
+        <v>322.708806</v>
       </c>
       <c r="N72">
-        <v>-383.2945060000001</v>
+        <v>-369.6088060000001</v>
       </c>
       <c r="O72">
-        <v>-98.88998254800002</v>
+        <v>-95.35907194800002</v>
       </c>
       <c r="P72">
-        <v>-284.404523452</v>
+        <v>-274.2497340520001</v>
       </c>
       <c r="Q72">
-        <v>-76.70452345200005</v>
+        <v>-66.54973405200008</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1671892153973558</v>
+        <v>0.167237529810826</v>
       </c>
       <c r="T72">
-        <v>2.80164371650427</v>
+        <v>2.804561889395519</v>
       </c>
       <c r="U72">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>-0.03597026641095024</v>
+        <v>-0.03749572300174542</v>
       </c>
       <c r="W72">
-        <v>0.2546414914838116</v>
+        <v>0.2446414914838116</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>-0.1394196372517451</v>
+        <v>-0.1453322596966877</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7235,13 +7235,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2304058086578748</v>
+        <v>0.2233203029819159</v>
       </c>
       <c r="C73">
-        <v>-202.2765842947495</v>
+        <v>-190.0541197286402</v>
       </c>
       <c r="D73">
-        <v>404.3444157052507</v>
+        <v>416.5668802713599</v>
       </c>
       <c r="E73">
         <v>-25.279</v>
@@ -7268,37 +7268,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M73">
-        <v>341.2001418</v>
+        <v>327.3189318</v>
       </c>
       <c r="N73">
-        <v>-388.1001418000001</v>
+        <v>-374.2189318000001</v>
       </c>
       <c r="O73">
-        <v>-100.1298365844</v>
+        <v>-96.54848440440001</v>
       </c>
       <c r="P73">
-        <v>-287.9703052156</v>
+        <v>-277.6704473956</v>
       </c>
       <c r="Q73">
-        <v>-80.27030521560005</v>
+        <v>-69.97044739560005</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1713750504110577</v>
+        <v>0.1714250308387855</v>
       </c>
       <c r="T73">
-        <v>2.898252120521658</v>
+        <v>2.901270920064329</v>
       </c>
       <c r="U73">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>-0.03546364294037348</v>
+        <v>-0.03696761422707295</v>
       </c>
       <c r="W73">
-        <v>0.2545169634347438</v>
+        <v>0.2445169634347438</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>-0.1374559803890445</v>
+        <v>-0.1432853264615233</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7317,13 +7317,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2324058086578748</v>
+        <v>0.2252203029819159</v>
       </c>
       <c r="C74">
-        <v>-225.1587224980551</v>
+        <v>-212.9645563430231</v>
       </c>
       <c r="D74">
-        <v>401.0132775019449</v>
+        <v>413.207443656977</v>
       </c>
       <c r="E74">
         <v>-5.728000000000065</v>
@@ -7350,37 +7350,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M74">
-        <v>346.0057776</v>
+        <v>331.9290576</v>
       </c>
       <c r="N74">
-        <v>-392.9057776000001</v>
+        <v>-378.8290576000001</v>
       </c>
       <c r="O74">
-        <v>-101.3696906208</v>
+        <v>-97.73789686080002</v>
       </c>
       <c r="P74">
-        <v>-291.5360869792</v>
+        <v>-281.0911607392001</v>
       </c>
       <c r="Q74">
-        <v>-83.83608697920005</v>
+        <v>-73.39116073920007</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.175859873640024</v>
+        <v>0.1759116390830278</v>
       </c>
       <c r="T74">
-        <v>3.001761124826003</v>
+        <v>3.004887738638055</v>
       </c>
       <c r="U74">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>-0.0349710923439794</v>
+        <v>-0.03645417514058583</v>
       </c>
       <c r="W74">
-        <v>0.2543958944981501</v>
+        <v>0.2443958944981501</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>-0.1355468695503079</v>
+        <v>-0.141295252482891</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7399,13 +7399,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2344058086578749</v>
+        <v>0.2271203029819159</v>
       </c>
       <c r="C75">
-        <v>-247.9864228935348</v>
+        <v>-235.8212415543039</v>
       </c>
       <c r="D75">
-        <v>397.7365771064652</v>
+        <v>409.9017584456961</v>
       </c>
       <c r="E75">
         <v>13.82299999999987</v>
@@ -7432,37 +7432,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M75">
-        <v>350.8114134</v>
+        <v>336.5391834</v>
       </c>
       <c r="N75">
-        <v>-397.7114134</v>
+        <v>-383.4391834</v>
       </c>
       <c r="O75">
-        <v>-102.6095446572</v>
+        <v>-98.92730931720001</v>
       </c>
       <c r="P75">
-        <v>-295.1018687428</v>
+        <v>-284.5118740828</v>
       </c>
       <c r="Q75">
-        <v>-87.40186874279999</v>
+        <v>-76.81187408280005</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.180676905997062</v>
+        <v>0.1807305886786955</v>
       </c>
       <c r="T75">
-        <v>3.112937462782522</v>
+        <v>3.116179877106132</v>
       </c>
       <c r="U75">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>-0.03449203628447284</v>
+        <v>-0.03595480287838602</v>
       </c>
       <c r="W75">
-        <v>0.2542781425187235</v>
+        <v>0.2442781425187234</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>-0.1336900631181117</v>
+        <v>-0.1393597010790157</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2364058086578749</v>
+        <v>0.2290203029819159</v>
       </c>
       <c r="C76">
-        <v>-270.7610091082595</v>
+        <v>-258.6254551676511</v>
       </c>
       <c r="D76">
-        <v>394.5129908917405</v>
+        <v>406.6485448323489</v>
       </c>
       <c r="E76">
         <v>33.37400000000002</v>
@@ -7514,37 +7514,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M76">
-        <v>355.6170492000001</v>
+        <v>341.1493092000001</v>
       </c>
       <c r="N76">
-        <v>-402.5170492000001</v>
+        <v>-388.0493092</v>
       </c>
       <c r="O76">
-        <v>-103.8493986936</v>
+        <v>-100.1167217736</v>
       </c>
       <c r="P76">
-        <v>-298.6676505064</v>
+        <v>-287.9325874264</v>
       </c>
       <c r="Q76">
-        <v>-90.96765050640005</v>
+        <v>-80.23258742640002</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1858644793046413</v>
+        <v>0.1859202267047992</v>
       </c>
       <c r="T76">
-        <v>3.232665826735695</v>
+        <v>3.236032949302521</v>
       </c>
       <c r="U76">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>-0.03402592768603401</v>
+        <v>-0.03546892716381324</v>
       </c>
       <c r="W76">
-        <v>0.2541635730252272</v>
+        <v>0.2441635730252272</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>-0.1318834406435427</v>
+        <v>-0.1374764618752451</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7563,13 +7563,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2384058086578748</v>
+        <v>0.2309203029819158</v>
       </c>
       <c r="C77">
-        <v>-293.4837622032164</v>
+        <v>-281.3784366790999</v>
       </c>
       <c r="D77">
-        <v>391.3412377967836</v>
+        <v>403.4465633209001</v>
       </c>
       <c r="E77">
         <v>52.92499999999995</v>
@@ -7596,37 +7596,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M77">
-        <v>360.4226850000001</v>
+        <v>345.7594350000001</v>
       </c>
       <c r="N77">
-        <v>-407.3226850000001</v>
+        <v>-392.659435</v>
       </c>
       <c r="O77">
-        <v>-105.08925273</v>
+        <v>-101.30613423</v>
       </c>
       <c r="P77">
-        <v>-302.2334322700001</v>
+        <v>-291.35330077</v>
       </c>
       <c r="Q77">
-        <v>-94.53343227000011</v>
+        <v>-83.65330077000004</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1914670584768269</v>
+        <v>0.1915250357729911</v>
       </c>
       <c r="T77">
-        <v>3.361972459805123</v>
+        <v>3.365474267274622</v>
       </c>
       <c r="U77">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>-0.03357224865022022</v>
+        <v>-0.03499600813496239</v>
       </c>
       <c r="W77">
-        <v>0.2540520587182241</v>
+        <v>0.2440520587182241</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>-0.1301249947682954</v>
+        <v>-0.1356434423835751</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7645,13 +7645,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2404058086578749</v>
+        <v>0.2328203029819159</v>
       </c>
       <c r="C78">
-        <v>-316.1559223707482</v>
+        <v>-304.081386850143</v>
       </c>
       <c r="D78">
-        <v>388.220077629252</v>
+        <v>400.2946131498573</v>
       </c>
       <c r="E78">
         <v>72.47600000000011</v>
@@ -7678,37 +7678,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M78">
-        <v>365.2283208000001</v>
+        <v>350.3695608</v>
       </c>
       <c r="N78">
-        <v>-412.1283208000001</v>
+        <v>-397.2695608</v>
       </c>
       <c r="O78">
-        <v>-106.3291067664</v>
+        <v>-102.4955466864</v>
       </c>
       <c r="P78">
-        <v>-305.7992140336</v>
+        <v>-294.7740141136</v>
       </c>
       <c r="Q78">
-        <v>-98.09921403360005</v>
+        <v>-87.07401411360001</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1975365192466947</v>
+        <v>0.1975969122635325</v>
       </c>
       <c r="T78">
-        <v>3.502054645630337</v>
+        <v>3.505702361744399</v>
       </c>
       <c r="U78">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>-0.03313050853640154</v>
+        <v>-0.03453553434371289</v>
       </c>
       <c r="W78">
-        <v>0.2539434789982475</v>
+        <v>0.2439434789982475</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>-0.1284128237845021</v>
+        <v>-0.1338586602469491</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7727,13 +7727,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2424058086578749</v>
+        <v>0.2347203029819159</v>
       </c>
       <c r="C79">
-        <v>-338.7786905514051</v>
+        <v>-326.7354692090755</v>
       </c>
       <c r="D79">
-        <v>385.1483094485951</v>
+        <v>397.1915307909246</v>
       </c>
       <c r="E79">
         <v>92.02700000000004</v>
@@ -7760,37 +7760,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M79">
-        <v>370.0339566000001</v>
+        <v>354.9796866</v>
       </c>
       <c r="N79">
-        <v>-416.9339566000001</v>
+        <v>-401.8796866</v>
       </c>
       <c r="O79">
-        <v>-107.5689608028</v>
+        <v>-103.6849591428</v>
       </c>
       <c r="P79">
-        <v>-309.3649957972001</v>
+        <v>-298.1947274572</v>
       </c>
       <c r="Q79">
-        <v>-101.6649957972001</v>
+        <v>-90.49472745719999</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2041337592139423</v>
+        <v>0.2041967780141208</v>
       </c>
       <c r="T79">
-        <v>3.654317891092526</v>
+        <v>3.658124203559372</v>
       </c>
       <c r="U79">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>-0.03270024219177294</v>
+        <v>-0.03408702091067765</v>
       </c>
       <c r="W79">
-        <v>0.2538377195307378</v>
+        <v>0.2438377195307378</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>-0.1267451247743139</v>
+        <v>-0.1321202360878979</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7809,13 +7809,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2444058086578748</v>
+        <v>0.2366203029819159</v>
       </c>
       <c r="C80">
-        <v>-361.3532299746435</v>
+        <v>-349.341811483057</v>
       </c>
       <c r="D80">
-        <v>382.1247700253567</v>
+        <v>394.1361885169431</v>
       </c>
       <c r="E80">
         <v>111.578</v>
@@ -7842,37 +7842,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M80">
-        <v>374.8395924000001</v>
+        <v>359.5898124</v>
       </c>
       <c r="N80">
-        <v>-421.7395924000001</v>
+        <v>-406.4898124</v>
       </c>
       <c r="O80">
-        <v>-108.8088148392</v>
+        <v>-104.8743715992</v>
       </c>
       <c r="P80">
-        <v>-312.9307775608001</v>
+        <v>-301.6154408008</v>
       </c>
       <c r="Q80">
-        <v>-105.2307775608001</v>
+        <v>-93.91544080080001</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2113307482691215</v>
+        <v>0.2113966315602172</v>
       </c>
       <c r="T80">
-        <v>3.82042324977855</v>
+        <v>3.824402576448435</v>
       </c>
       <c r="U80">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>-0.03228100831751945</v>
+        <v>-0.03365000782207923</v>
       </c>
       <c r="W80">
-        <v>0.2537346718444463</v>
+        <v>0.2437346718444463</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>-0.1251201872772072</v>
+        <v>-0.1304263869072837</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7891,13 +7891,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2464058086578749</v>
+        <v>0.2385203029819158</v>
       </c>
       <c r="C81">
-        <v>-383.8806676275169</v>
+        <v>-371.9015069645743</v>
       </c>
       <c r="D81">
-        <v>379.1483323724834</v>
+        <v>391.1274930354259</v>
       </c>
       <c r="E81">
         <v>131.1290000000001</v>
@@ -7924,37 +7924,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M81">
-        <v>379.6452282000001</v>
+        <v>364.1999382000001</v>
       </c>
       <c r="N81">
-        <v>-426.5452282000001</v>
+        <v>-411.0999382000001</v>
       </c>
       <c r="O81">
-        <v>-110.0486688756</v>
+        <v>-106.0637840556</v>
       </c>
       <c r="P81">
-        <v>-316.4965593244001</v>
+        <v>-305.0361541444001</v>
       </c>
       <c r="Q81">
-        <v>-108.7965593244001</v>
+        <v>-97.3361541444001</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2192131648533654</v>
+        <v>0.2192821854440371</v>
       </c>
       <c r="T81">
-        <v>4.002348166434672</v>
+        <v>4.006516984850741</v>
       </c>
       <c r="U81">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>-0.03187238795906983</v>
+        <v>-0.03322405835597695</v>
       </c>
       <c r="W81">
-        <v>0.2536342329603394</v>
+        <v>0.2436342329603393</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>-0.1235363874382553</v>
+        <v>-0.1287754199844069</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7973,13 +7973,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2484058086578748</v>
+        <v>0.2404203029819159</v>
       </c>
       <c r="C82">
-        <v>-406.3620956552588</v>
+        <v>-394.4156158157955</v>
       </c>
       <c r="D82">
-        <v>376.2179043447414</v>
+        <v>388.1643841842047</v>
       </c>
       <c r="E82">
         <v>150.6800000000001</v>
@@ -8006,37 +8006,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M82">
-        <v>384.4508640000001</v>
+        <v>368.8100640000001</v>
       </c>
       <c r="N82">
-        <v>-431.3508640000001</v>
+        <v>-415.7100640000001</v>
       </c>
       <c r="O82">
-        <v>-111.288522912</v>
+        <v>-107.253196512</v>
       </c>
       <c r="P82">
-        <v>-320.0623410880001</v>
+        <v>-308.4568674880001</v>
       </c>
       <c r="Q82">
-        <v>-112.3623410880001</v>
+        <v>-100.7568674880001</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2278838230960337</v>
+        <v>0.227956294716239</v>
       </c>
       <c r="T82">
-        <v>4.202465574756405</v>
+        <v>4.206842834093279</v>
       </c>
       <c r="U82">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>-0.03147398310958146</v>
+        <v>-0.03280875762652724</v>
       </c>
       <c r="W82">
-        <v>0.2535363050483351</v>
+        <v>0.2435363050483351</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>-0.121992182595277</v>
+        <v>-0.1271657272346018</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8055,13 +8055,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2504058086578748</v>
+        <v>0.2423203029819159</v>
       </c>
       <c r="C83">
-        <v>-428.7985726974148</v>
+        <v>-416.8851663140781</v>
       </c>
       <c r="D83">
-        <v>373.3324273025856</v>
+        <v>385.2458336859221</v>
       </c>
       <c r="E83">
         <v>170.2310000000002</v>
@@ -8088,37 +8088,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M83">
-        <v>389.2564998000001</v>
+        <v>373.4201898000001</v>
       </c>
       <c r="N83">
-        <v>-436.1564998000001</v>
+        <v>-420.3201898000001</v>
       </c>
       <c r="O83">
-        <v>-112.5283769484</v>
+        <v>-108.4426089684</v>
       </c>
       <c r="P83">
-        <v>-323.6281228516001</v>
+        <v>-311.8775808316001</v>
       </c>
       <c r="Q83">
-        <v>-115.9281228516001</v>
+        <v>-104.1775808316001</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2374671822063512</v>
+        <v>0.2375434681223568</v>
       </c>
       <c r="T83">
-        <v>4.423647973427795</v>
+        <v>4.42825561483503</v>
       </c>
       <c r="U83">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>-0.03108541541687058</v>
+        <v>-0.03240371123607629</v>
       </c>
       <c r="W83">
-        <v>0.2534407951094668</v>
+        <v>0.2434407951094668</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>-0.1204861062669402</v>
+        <v>-0.1255957799847918</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8137,13 +8137,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2524058086578748</v>
+        <v>0.2442203029819159</v>
       </c>
       <c r="C84">
-        <v>-451.1911251629531</v>
+        <v>-439.311156041713</v>
       </c>
       <c r="D84">
-        <v>370.4908748370471</v>
+        <v>382.3708439582872</v>
       </c>
       <c r="E84">
         <v>189.7820000000002</v>
@@ -8170,37 +8170,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M84">
-        <v>394.0621356000001</v>
+        <v>378.0303156000001</v>
       </c>
       <c r="N84">
-        <v>-440.9621356000001</v>
+        <v>-424.9303156000001</v>
       </c>
       <c r="O84">
-        <v>-113.7682309848</v>
+        <v>-109.6320214248</v>
       </c>
       <c r="P84">
-        <v>-327.1939046152001</v>
+        <v>-315.2982941752001</v>
       </c>
       <c r="Q84">
-        <v>-119.4939046152001</v>
+        <v>-107.5982941752001</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.248115358995593</v>
+        <v>0.2481958830180433</v>
       </c>
       <c r="T84">
-        <v>4.669406194173784</v>
+        <v>4.674269815659199</v>
       </c>
       <c r="U84">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>-0.03070632498495752</v>
+        <v>-0.03200854402588024</v>
       </c>
       <c r="W84">
-        <v>0.2533476146813026</v>
+        <v>0.2433476146813026</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>-0.1190167635075874</v>
+        <v>-0.1240641241313187</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8219,13 +8219,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2544058086578748</v>
+        <v>0.2461203029819159</v>
       </c>
       <c r="C85">
-        <v>-473.5407484475877</v>
+        <v>-461.6945530227836</v>
       </c>
       <c r="D85">
-        <v>367.6922515524126</v>
+        <v>379.5384469772167</v>
       </c>
       <c r="E85">
         <v>209.3330000000001</v>
@@ -8252,37 +8252,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M85">
-        <v>398.8677714000001</v>
+        <v>382.6404414</v>
       </c>
       <c r="N85">
-        <v>-445.7677714000001</v>
+        <v>-429.5404414000001</v>
       </c>
       <c r="O85">
-        <v>-115.0080850212</v>
+        <v>-110.8214338812</v>
       </c>
       <c r="P85">
-        <v>-330.7596863788001</v>
+        <v>-318.7190075188</v>
       </c>
       <c r="Q85">
-        <v>-123.0596863788001</v>
+        <v>-111.0190075188</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.260016262465922</v>
+        <v>0.2601015231955753</v>
       </c>
       <c r="T85">
-        <v>4.944077146772242</v>
+        <v>4.949226863639153</v>
       </c>
       <c r="U85">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>-0.03033636926224719</v>
+        <v>-0.03162289891713469</v>
       </c>
       <c r="W85">
-        <v>0.2532566795646604</v>
+        <v>0.2432566795646604</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>-0.1175828265978573</v>
+        <v>-0.122569375647809</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8301,13 +8301,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2564058086578748</v>
+        <v>0.2480203029819159</v>
       </c>
       <c r="C86">
-        <v>-495.8484080963378</v>
+        <v>-484.0362968098734</v>
       </c>
       <c r="D86">
-        <v>364.9355919036623</v>
+        <v>376.7477031901266</v>
       </c>
       <c r="E86">
         <v>228.884</v>
@@ -8334,37 +8334,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M86">
-        <v>403.6734072</v>
+        <v>387.2505672</v>
       </c>
       <c r="N86">
-        <v>-450.5734072</v>
+        <v>-434.1505672000001</v>
       </c>
       <c r="O86">
-        <v>-116.2479390576</v>
+        <v>-112.0108463376</v>
       </c>
       <c r="P86">
-        <v>-334.3254681424</v>
+        <v>-322.1397208624001</v>
       </c>
       <c r="Q86">
-        <v>-126.6254681424001</v>
+        <v>-114.4397208624001</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.273404778870042</v>
+        <v>0.2734953683952986</v>
       </c>
       <c r="T86">
-        <v>5.253081968445504</v>
+        <v>5.258553542616597</v>
       </c>
       <c r="U86">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>-0.0299752220091252</v>
+        <v>-0.03124643583478785</v>
       </c>
       <c r="W86">
-        <v>0.253167909569843</v>
+        <v>0.243167909569843</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>-0.1161830310431209</v>
+        <v>-0.1211102164139064</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8383,13 +8383,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2584058086578748</v>
+        <v>0.2499203029819159</v>
       </c>
       <c r="C87">
-        <v>-518.1150409141849</v>
+        <v>-506.3372995231805</v>
       </c>
       <c r="D87">
-        <v>362.2199590858152</v>
+        <v>373.9977004768195</v>
       </c>
       <c r="E87">
         <v>248.4349999999999</v>
@@ -8416,37 +8416,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M87">
-        <v>408.479043</v>
+        <v>391.860693</v>
       </c>
       <c r="N87">
-        <v>-455.379043</v>
+        <v>-438.7606930000001</v>
       </c>
       <c r="O87">
-        <v>-117.487793094</v>
+        <v>-113.200258794</v>
       </c>
       <c r="P87">
-        <v>-337.891249906</v>
+        <v>-325.560434206</v>
       </c>
       <c r="Q87">
-        <v>-130.191249906</v>
+        <v>-117.860434206</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2885784307947115</v>
+        <v>0.2886750596216519</v>
       </c>
       <c r="T87">
-        <v>5.603287433008539</v>
+        <v>5.609123778791036</v>
       </c>
       <c r="U87">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>-0.02962257233842961</v>
+        <v>-0.03087883070731976</v>
       </c>
       <c r="W87">
-        <v>0.253081228280786</v>
+        <v>0.243081228280786</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>-0.1148161718543783</v>
+        <v>-0.1196853903384487</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8465,13 +8465,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2604058086578749</v>
+        <v>0.2518203029819159</v>
       </c>
       <c r="C88">
-        <v>-540.3415560275043</v>
+        <v>-528.5984468444492</v>
       </c>
       <c r="D88">
-        <v>359.5444439724959</v>
+        <v>371.287553155551</v>
       </c>
       <c r="E88">
         <v>267.9860000000001</v>
@@ -8498,37 +8498,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M88">
-        <v>413.2846788000001</v>
+        <v>396.4708188000001</v>
       </c>
       <c r="N88">
-        <v>-460.1846788</v>
+        <v>-443.3708188000001</v>
       </c>
       <c r="O88">
-        <v>-118.7276471304</v>
+        <v>-114.3896712504</v>
       </c>
       <c r="P88">
-        <v>-341.4570316696</v>
+        <v>-328.9811475496001</v>
       </c>
       <c r="Q88">
-        <v>-133.7570316696001</v>
+        <v>-121.2811475496001</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3059197472800481</v>
+        <v>0.3060232781660556</v>
       </c>
       <c r="T88">
-        <v>6.003522249652007</v>
+        <v>6.009775477276111</v>
       </c>
       <c r="U88">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>-0.02927812382286648</v>
+        <v>-0.03051977453630441</v>
       </c>
       <c r="W88">
-        <v>0.2529965628356606</v>
+        <v>0.2429965628356606</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>-0.1134811000886298</v>
+        <v>-0.1182936997531179</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8547,13 +8547,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2624058086578749</v>
+        <v>0.2537203029819159</v>
       </c>
       <c r="C89">
-        <v>-562.5288358988007</v>
+        <v>-550.8205989680021</v>
       </c>
       <c r="D89">
-        <v>356.9081641011995</v>
+        <v>368.616401031998</v>
       </c>
       <c r="E89">
         <v>287.537</v>
@@ -8580,37 +8580,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M89">
-        <v>418.0903146000001</v>
+        <v>401.0809446000001</v>
       </c>
       <c r="N89">
-        <v>-464.9903146</v>
+        <v>-447.9809446</v>
       </c>
       <c r="O89">
-        <v>-119.9675011668</v>
+        <v>-115.5790837068</v>
       </c>
       <c r="P89">
-        <v>-345.0228134332</v>
+        <v>-332.4018608932</v>
       </c>
       <c r="Q89">
-        <v>-137.3228134332001</v>
+        <v>-124.7018608932</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3259289586092825</v>
+        <v>0.3260404534095983</v>
       </c>
       <c r="T89">
-        <v>6.465331653471391</v>
+        <v>6.472065898605042</v>
       </c>
       <c r="U89">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>-0.02894159366398296</v>
+        <v>-0.03016897253013999</v>
       </c>
       <c r="W89">
-        <v>0.2529138437226071</v>
+        <v>0.242913843722607</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>-0.1121767196278409</v>
+        <v>-0.1169340020548062</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8629,13 +8629,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2644058086578748</v>
+        <v>0.2556203029819159</v>
       </c>
       <c r="C90">
-        <v>-584.6777372971287</v>
+        <v>-573.0045915110109</v>
       </c>
       <c r="D90">
-        <v>354.3102627028713</v>
+        <v>365.9834084889893</v>
       </c>
       <c r="E90">
         <v>307.088</v>
@@ -8662,37 +8662,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M90">
-        <v>422.8959504000001</v>
+        <v>405.6910704000001</v>
       </c>
       <c r="N90">
-        <v>-469.7959504</v>
+        <v>-452.5910704</v>
       </c>
       <c r="O90">
-        <v>-121.2073552032</v>
+        <v>-116.7684961632</v>
       </c>
       <c r="P90">
-        <v>-348.5885951968</v>
+        <v>-335.8225742368001</v>
       </c>
       <c r="Q90">
-        <v>-140.8885951968001</v>
+        <v>-128.1225742368001</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3492730384933894</v>
+        <v>0.3493938245270649</v>
       </c>
       <c r="T90">
-        <v>7.004109291260674</v>
+        <v>7.011404723488798</v>
       </c>
       <c r="U90">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>-0.02861271191780133</v>
+        <v>-0.02982614329684295</v>
       </c>
       <c r="W90">
-        <v>0.2528330045893956</v>
+        <v>0.2428330045893956</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>-0.1109019841775245</v>
+        <v>-0.1156052065769106</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8711,13 +8711,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2664058086578749</v>
+        <v>0.2575203029819159</v>
       </c>
       <c r="C91">
-        <v>-606.7890922264371</v>
+        <v>-595.151236385032</v>
       </c>
       <c r="D91">
-        <v>351.7499077735631</v>
+        <v>363.3877636149681</v>
       </c>
       <c r="E91">
         <v>326.6390000000001</v>
@@ -8744,37 +8744,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M91">
-        <v>427.7015862000001</v>
+        <v>410.3011962</v>
       </c>
       <c r="N91">
-        <v>-474.6015862</v>
+        <v>-457.2011962</v>
       </c>
       <c r="O91">
-        <v>-122.4472092396</v>
+        <v>-117.9579086196</v>
       </c>
       <c r="P91">
-        <v>-352.1543769604</v>
+        <v>-339.2432875804</v>
       </c>
       <c r="Q91">
-        <v>-144.4543769604001</v>
+        <v>-131.5432875804</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3768614965382431</v>
+        <v>0.3769932631204345</v>
       </c>
       <c r="T91">
-        <v>7.6408464995571</v>
+        <v>7.64880515289687</v>
       </c>
       <c r="U91">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>-0.02829122077265749</v>
+        <v>-0.02949101809126044</v>
       </c>
       <c r="W91">
-        <v>0.2527539820659193</v>
+        <v>0.2427539820659192</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>-0.1096558944676647</v>
+        <v>-0.1143062716715519</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8793,13 +8793,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2684058086578748</v>
+        <v>0.2594203029819159</v>
       </c>
       <c r="C92">
-        <v>-628.8637088139476</v>
+        <v>-617.2613226307178</v>
       </c>
       <c r="D92">
-        <v>349.2262911860526</v>
+        <v>360.8286773692823</v>
       </c>
       <c r="E92">
         <v>346.1900000000001</v>
@@ -8826,37 +8826,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M92">
-        <v>432.5072220000001</v>
+        <v>414.911322</v>
       </c>
       <c r="N92">
-        <v>-479.407222</v>
+        <v>-461.811322</v>
       </c>
       <c r="O92">
-        <v>-123.687063276</v>
+        <v>-119.147321076</v>
       </c>
       <c r="P92">
-        <v>-355.720158724</v>
+        <v>-342.664000924</v>
       </c>
       <c r="Q92">
-        <v>-148.0201587240001</v>
+        <v>-134.964000924</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4099676461920674</v>
+        <v>0.4101125894324779</v>
       </c>
       <c r="T92">
-        <v>8.404931149512811</v>
+        <v>8.413685668186558</v>
       </c>
       <c r="U92">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>-0.02797687387518352</v>
+        <v>-0.02916334011246866</v>
       </c>
       <c r="W92">
-        <v>0.2526767155985201</v>
+        <v>0.2426767155985201</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>-0.1084374956402461</v>
+        <v>-0.1130362019863125</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8875,13 +8875,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2704058086578748</v>
+        <v>0.2613203029819159</v>
       </c>
       <c r="C93">
-        <v>-650.9023721605704</v>
+        <v>-639.3356172175036</v>
       </c>
       <c r="D93">
-        <v>346.7386278394298</v>
+        <v>358.3053827824964</v>
       </c>
       <c r="E93">
         <v>365.741</v>
@@ -8908,37 +8908,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M93">
-        <v>437.3128578000001</v>
+        <v>419.5214478</v>
       </c>
       <c r="N93">
-        <v>-484.2128578000001</v>
+        <v>-466.4214478</v>
       </c>
       <c r="O93">
-        <v>-124.9269173124</v>
+        <v>-120.3367335324</v>
       </c>
       <c r="P93">
-        <v>-359.2859404876</v>
+        <v>-346.0847142676</v>
       </c>
       <c r="Q93">
-        <v>-151.5859404876001</v>
+        <v>-138.3847142676</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.450430717991186</v>
+        <v>0.4505917660360866</v>
       </c>
       <c r="T93">
-        <v>9.338812388347568</v>
+        <v>9.348539631318397</v>
       </c>
       <c r="U93">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>-0.02766943570073096</v>
+        <v>-0.02884286384749648</v>
       </c>
       <c r="W93">
-        <v>0.2526011472952397</v>
+        <v>0.2426011472952397</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>-0.1072458748090346</v>
+        <v>-0.1117940459205289</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8957,13 +8957,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2724058086578749</v>
+        <v>0.2632203029819159</v>
       </c>
       <c r="C94">
-        <v>-672.9058451552246</v>
+        <v>-661.3748658099751</v>
       </c>
       <c r="D94">
-        <v>344.2861548447756</v>
+        <v>355.8171341900252</v>
       </c>
       <c r="E94">
         <v>385.2920000000001</v>
@@ -8990,37 +8990,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M94">
-        <v>442.1184936000001</v>
+        <v>424.1315736000001</v>
       </c>
       <c r="N94">
-        <v>-489.0184936000001</v>
+        <v>-471.0315736000001</v>
       </c>
       <c r="O94">
-        <v>-126.1667713488</v>
+        <v>-121.5261459888</v>
       </c>
       <c r="P94">
-        <v>-362.8517222512</v>
+        <v>-349.5054276112</v>
       </c>
       <c r="Q94">
-        <v>-155.1517222512001</v>
+        <v>-141.8054276112001</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5010095577400844</v>
+        <v>0.5011907367905974</v>
       </c>
       <c r="T94">
-        <v>10.50616393689102</v>
+        <v>10.5171070852332</v>
       </c>
       <c r="U94">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>-0.02736868096485344</v>
+        <v>-0.02852935445784978</v>
       </c>
       <c r="W94">
-        <v>0.252527221781161</v>
+        <v>0.242527221781161</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>-0.1060801587785016</v>
+        <v>-0.1105788932474798</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9039,13 +9039,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2744058086578748</v>
+        <v>0.2651203029819159</v>
       </c>
       <c r="C95">
-        <v>-694.8748692548459</v>
+        <v>-683.3797935025216</v>
       </c>
       <c r="D95">
-        <v>341.8681307451542</v>
+        <v>353.3632064974786</v>
       </c>
       <c r="E95">
         <v>404.8430000000001</v>
@@ -9072,37 +9072,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M95">
-        <v>446.9241294000001</v>
+        <v>428.7416994000001</v>
       </c>
       <c r="N95">
-        <v>-493.8241294000001</v>
+        <v>-475.6416994000001</v>
       </c>
       <c r="O95">
-        <v>-127.4066253852</v>
+        <v>-122.7155584452</v>
       </c>
       <c r="P95">
-        <v>-366.4175040148</v>
+        <v>-352.9261409548001</v>
       </c>
       <c r="Q95">
-        <v>-158.7175040148001</v>
+        <v>-145.2261409548001</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5660394945600964</v>
+        <v>0.5662465563321115</v>
       </c>
       <c r="T95">
-        <v>12.00704449930402</v>
+        <v>12.01955095455223</v>
       </c>
       <c r="U95">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>-0.02707439407275825</v>
+        <v>-0.02822258720561483</v>
       </c>
       <c r="W95">
-        <v>0.252454886063084</v>
+        <v>0.242454886063084</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>-0.1049395119099157</v>
+        <v>-0.10938987288998</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9121,13 +9121,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2764058086578748</v>
+        <v>0.2670203029819159</v>
       </c>
       <c r="C96">
-        <v>-716.8101652317541</v>
+        <v>-705.3511055238018</v>
       </c>
       <c r="D96">
-        <v>339.4838347682461</v>
+        <v>350.9428944761984</v>
       </c>
       <c r="E96">
         <v>424.3940000000002</v>
@@ -9154,37 +9154,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M96">
-        <v>451.7297652000001</v>
+        <v>433.3518252000001</v>
       </c>
       <c r="N96">
-        <v>-498.6297652000001</v>
+        <v>-480.2518252000001</v>
       </c>
       <c r="O96">
-        <v>-128.6464794216</v>
+        <v>-123.9049709016</v>
       </c>
       <c r="P96">
-        <v>-369.9832857784</v>
+        <v>-356.3468542984001</v>
       </c>
       <c r="Q96">
-        <v>-162.2832857784001</v>
+        <v>-148.6468542984001</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6527460769867793</v>
+        <v>0.6529876490541302</v>
       </c>
       <c r="T96">
-        <v>14.00821858252136</v>
+        <v>14.02280944697761</v>
       </c>
       <c r="U96">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>-0.02678636860389912</v>
+        <v>-0.02792234691619339</v>
       </c>
       <c r="W96">
-        <v>0.2523840894028384</v>
+        <v>0.2423840894028384</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>-0.10382313412364</v>
+        <v>-0.1082261508379587</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9203,13 +9203,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2784058086578748</v>
+        <v>0.2689203029819159</v>
       </c>
       <c r="C97">
-        <v>-738.7124338899609</v>
+        <v>-727.2894879124519</v>
       </c>
       <c r="D97">
-        <v>337.1325661100394</v>
+        <v>348.5555120875484</v>
       </c>
       <c r="E97">
         <v>443.9450000000002</v>
@@ -9236,37 +9236,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M97">
-        <v>456.5354010000001</v>
+        <v>437.9619510000001</v>
       </c>
       <c r="N97">
-        <v>-503.4354010000001</v>
+        <v>-484.8619510000001</v>
       </c>
       <c r="O97">
-        <v>-129.886333458</v>
+        <v>-125.094383358</v>
       </c>
       <c r="P97">
-        <v>-373.549067542</v>
+        <v>-359.7675676420001</v>
       </c>
       <c r="Q97">
-        <v>-165.8490675420001</v>
+        <v>-152.0675676420001</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.7741352923841355</v>
+        <v>0.7744251788649565</v>
       </c>
       <c r="T97">
-        <v>16.80986229902564</v>
+        <v>16.82737133637313</v>
       </c>
       <c r="U97">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>-0.02650440682912123</v>
+        <v>-0.02762842747497031</v>
       </c>
       <c r="W97">
-        <v>0.252314783198598</v>
+        <v>0.242314783198598</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>-0.1027302590276016</v>
+        <v>-0.1070869281975595</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9285,13 +9285,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2804058086578749</v>
+        <v>0.2708203029819159</v>
       </c>
       <c r="C98">
-        <v>-760.5823567519187</v>
+        <v>-749.1956081654012</v>
       </c>
       <c r="D98">
-        <v>334.8136432480813</v>
+        <v>346.2003918345988</v>
       </c>
       <c r="E98">
         <v>463.4959999999999</v>
@@ -9318,37 +9318,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M98">
-        <v>461.3410368</v>
+        <v>442.5720768</v>
       </c>
       <c r="N98">
-        <v>-508.2410368000001</v>
+        <v>-489.4720768</v>
       </c>
       <c r="O98">
-        <v>-131.1261874944</v>
+        <v>-126.2837958144</v>
       </c>
       <c r="P98">
-        <v>-377.1148493056</v>
+        <v>-363.1882809856</v>
       </c>
       <c r="Q98">
-        <v>-169.4148493056001</v>
+        <v>-155.4882809856</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.9562191154801675</v>
+        <v>0.9565814735811937</v>
       </c>
       <c r="T98">
-        <v>21.01232787378201</v>
+        <v>21.03421417046637</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>-0.02622831925798455</v>
+        <v>-0.02734063135543937</v>
       </c>
       <c r="W98">
-        <v>0.2522469208736127</v>
+        <v>0.2422469208736126</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>-0.1016601521627309</v>
+        <v>-0.105971439362168</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9367,13 +9367,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2824058086578748</v>
+        <v>0.2727203029819159</v>
       </c>
       <c r="C99">
-        <v>-782.4205967171188</v>
+        <v>-771.070115860083</v>
       </c>
       <c r="D99">
-        <v>332.5264032828813</v>
+        <v>343.8768841399171</v>
       </c>
       <c r="E99">
         <v>483.047</v>
@@ -9400,37 +9400,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M99">
-        <v>466.1466726</v>
+        <v>447.1822026</v>
       </c>
       <c r="N99">
-        <v>-513.0466726000001</v>
+        <v>-494.0822026000001</v>
       </c>
       <c r="O99">
-        <v>-132.3660415308</v>
+        <v>-127.4732082708</v>
       </c>
       <c r="P99">
-        <v>-380.6806310692</v>
+        <v>-366.6089943292001</v>
       </c>
       <c r="Q99">
-        <v>-172.9806310692001</v>
+        <v>-158.9089943292001</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.259692153973557</v>
+        <v>1.260175298108259</v>
       </c>
       <c r="T99">
-        <v>28.01643716504267</v>
+        <v>28.04561889395517</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>-0.02595792421408781</v>
+        <v>-0.02705876917651731</v>
       </c>
       <c r="W99">
-        <v>0.2521804577718228</v>
+        <v>0.2421804577718228</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>-0.1006121093569294</v>
+        <v>-0.1048789502965788</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9449,13 +9449,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2844058086578748</v>
+        <v>0.2746203029819159</v>
       </c>
       <c r="C100">
-        <v>-804.2277986938773</v>
+        <v>-792.9136432517521</v>
       </c>
       <c r="D100">
-        <v>330.2702013061228</v>
+        <v>341.5843567482479</v>
       </c>
       <c r="E100">
         <v>502.598</v>
@@ -9482,37 +9482,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M100">
-        <v>470.9523084</v>
+        <v>451.7923284</v>
       </c>
       <c r="N100">
-        <v>-517.8523084000001</v>
+        <v>-498.6923284000001</v>
       </c>
       <c r="O100">
-        <v>-133.6058955672</v>
+        <v>-128.6626207272</v>
       </c>
       <c r="P100">
-        <v>-384.2464128328</v>
+        <v>-370.0297076728</v>
       </c>
       <c r="Q100">
-        <v>-176.5464128328001</v>
+        <v>-162.3297076728001</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.866638230960335</v>
+        <v>1.867362947162388</v>
       </c>
       <c r="T100">
-        <v>42.024655747564</v>
+        <v>42.06842834093275</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>-0.02569304743639303</v>
+        <v>-0.02678265928696102</v>
       </c>
       <c r="W100">
-        <v>0.2521153510598654</v>
+        <v>0.2421153510598655</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>-0.09958545517981809</v>
+        <v>-0.1038087569262056</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9531,13 +9531,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2864058086578748</v>
+        <v>0.2765203029819159</v>
       </c>
       <c r="C101">
-        <v>-826.0045902055761</v>
+        <v>-814.7268058470734</v>
       </c>
       <c r="D101">
-        <v>328.0444097944241</v>
+        <v>339.3221941529267</v>
       </c>
       <c r="E101">
         <v>522.1490000000001</v>
@@ -9564,37 +9564,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M101">
-        <v>475.7579442000001</v>
+        <v>456.4024542000001</v>
       </c>
       <c r="N101">
-        <v>-522.6579442000001</v>
+        <v>-503.3024542000001</v>
       </c>
       <c r="O101">
-        <v>-134.8457496036</v>
+        <v>-129.8520331836</v>
       </c>
       <c r="P101">
-        <v>-387.8121945964001</v>
+        <v>-373.4504210164</v>
       </c>
       <c r="Q101">
-        <v>-180.1121945964001</v>
+        <v>-165.7504210164</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.68747646192067</v>
+        <v>3.688925894324775</v>
       </c>
       <c r="T101">
-        <v>84.04931149512802</v>
+        <v>84.13685668186548</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V101">
-        <v>-0.02543352170471229</v>
+        <v>-0.02651212737497151</v>
       </c>
       <c r="W101">
-        <v>0.2520515596350183</v>
+        <v>0.2420515596350183</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>-0.09857954149113279</v>
+        <v>-0.1027601836239205</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/netherlands/netherlands_transportation.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_transportation.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,13 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="B2">
+        <v>0.09032030298191587</v>
+      </c>
+      <c r="C2">
+        <v>1728.708625782469</v>
+      </c>
+      <c r="D2">
+        <v>966.7596257824689</v>
       </c>
       <c r="E2">
-        <v>-1413.4</v>
+        <v>-1393.849</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>19.551</v>
       </c>
       <c r="G2">
         <v>781.5</v>
@@ -1448,43 +1457,45 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.6101258</v>
       </c>
       <c r="N2">
-        <v>-46.90000000000001</v>
+        <v>-51.5101258</v>
       </c>
       <c r="O2">
-        <v>-12.1002</v>
+        <v>-13.2896124564</v>
       </c>
       <c r="P2">
-        <v>-34.7998</v>
+        <v>-38.2205133436</v>
       </c>
       <c r="Q2">
-        <v>172.9002</v>
+        <v>169.4794866564</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S2">
+        <v>0.08259925145782604</v>
+      </c>
+      <c r="T2">
+        <v>0.8498672392107632</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.2358</v>
+      </c>
+      <c r="V2">
+        <v>-2.624700610122179</v>
+      </c>
+      <c r="W2">
+        <v>0.8547044038668099</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>-10.17325817876814</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1492,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09032030298191587</v>
+        <v>0.09222030298191589</v>
       </c>
       <c r="C3">
-        <v>1728.708625782469</v>
+        <v>1691.254348029332</v>
       </c>
       <c r="D3">
-        <v>966.7596257824689</v>
+        <v>948.8563480293321</v>
       </c>
       <c r="E3">
-        <v>-1393.849</v>
+        <v>-1374.298</v>
       </c>
       <c r="F3">
-        <v>19.551</v>
+        <v>39.102</v>
       </c>
       <c r="G3">
         <v>781.5</v>
@@ -1528,37 +1539,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M3">
-        <v>4.6101258</v>
+        <v>9.220251600000001</v>
       </c>
       <c r="N3">
-        <v>-51.5101258</v>
+        <v>-56.1202516</v>
       </c>
       <c r="O3">
-        <v>-13.2896124564</v>
+        <v>-14.4790249128</v>
       </c>
       <c r="P3">
-        <v>-38.2205133436</v>
+        <v>-41.6412266872</v>
       </c>
       <c r="Q3">
-        <v>169.4794866564</v>
+        <v>166.0587733128</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08259925145782604</v>
+        <v>0.08297475402372223</v>
       </c>
       <c r="T3">
-        <v>0.8498672392107632</v>
+        <v>0.8585393538965874</v>
       </c>
       <c r="U3">
         <v>0.2358</v>
       </c>
       <c r="V3">
-        <v>-2.624700610122179</v>
+        <v>-1.31235030506109</v>
       </c>
       <c r="W3">
-        <v>0.8547044038668099</v>
+        <v>0.545252201933405</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1566,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>-10.17325817876814</v>
+        <v>-5.086629089384068</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1574,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09222030298191589</v>
+        <v>0.09412030298191587</v>
       </c>
       <c r="C4">
-        <v>1691.254348029332</v>
+        <v>1654.451110044537</v>
       </c>
       <c r="D4">
-        <v>948.8563480293321</v>
+        <v>931.6041100445368</v>
       </c>
       <c r="E4">
-        <v>-1374.298</v>
+        <v>-1354.747</v>
       </c>
       <c r="F4">
-        <v>39.102</v>
+        <v>58.653</v>
       </c>
       <c r="G4">
         <v>781.5</v>
@@ -1610,37 +1621,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M4">
-        <v>9.220251600000001</v>
+        <v>13.8303774</v>
       </c>
       <c r="N4">
-        <v>-56.1202516</v>
+        <v>-60.73037740000001</v>
       </c>
       <c r="O4">
-        <v>-14.4790249128</v>
+        <v>-15.6684373692</v>
       </c>
       <c r="P4">
-        <v>-41.6412266872</v>
+        <v>-45.0619400308</v>
       </c>
       <c r="Q4">
-        <v>166.0587733128</v>
+        <v>162.6380599692</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08297475402372223</v>
+        <v>0.08335799891056472</v>
       </c>
       <c r="T4">
-        <v>0.8585393538965874</v>
+        <v>0.8673902750707789</v>
       </c>
       <c r="U4">
         <v>0.2358</v>
       </c>
       <c r="V4">
-        <v>-1.31235030506109</v>
+        <v>-0.8749002033740598</v>
       </c>
       <c r="W4">
-        <v>0.545252201933405</v>
+        <v>0.4421014679556033</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1648,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>-5.086629089384068</v>
+        <v>-3.391086059589379</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1656,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09412030298191587</v>
+        <v>0.09602030298191588</v>
       </c>
       <c r="C5">
-        <v>1654.451110044537</v>
+        <v>1618.26403409327</v>
       </c>
       <c r="D5">
-        <v>931.6041100445368</v>
+        <v>914.96803409327</v>
       </c>
       <c r="E5">
-        <v>-1354.747</v>
+        <v>-1335.196</v>
       </c>
       <c r="F5">
-        <v>58.653</v>
+        <v>78.20400000000001</v>
       </c>
       <c r="G5">
         <v>781.5</v>
@@ -1692,37 +1703,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M5">
-        <v>13.8303774</v>
+        <v>18.4405032</v>
       </c>
       <c r="N5">
-        <v>-60.73037740000001</v>
+        <v>-65.3405032</v>
       </c>
       <c r="O5">
-        <v>-15.6684373692</v>
+        <v>-16.8578498256</v>
       </c>
       <c r="P5">
-        <v>-45.0619400308</v>
+        <v>-48.4826533744</v>
       </c>
       <c r="Q5">
-        <v>162.6380599692</v>
+        <v>159.2173466256</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08335799891056472</v>
+        <v>0.08374922806588311</v>
       </c>
       <c r="T5">
-        <v>0.8673902750707789</v>
+        <v>0.8764255904360997</v>
       </c>
       <c r="U5">
         <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>-0.8749002033740598</v>
+        <v>-0.6561751525305448</v>
       </c>
       <c r="W5">
-        <v>0.4421014679556033</v>
+        <v>0.3905261009667025</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1730,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>-3.391086059589379</v>
+        <v>-2.543314544692034</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1738,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09602030298191588</v>
+        <v>0.09792030298191587</v>
       </c>
       <c r="C6">
-        <v>1618.26403409327</v>
+        <v>1582.660690042726</v>
       </c>
       <c r="D6">
-        <v>914.96803409327</v>
+        <v>898.9156900427258</v>
       </c>
       <c r="E6">
-        <v>-1335.196</v>
+        <v>-1315.645</v>
       </c>
       <c r="F6">
-        <v>78.20400000000001</v>
+        <v>97.75500000000001</v>
       </c>
       <c r="G6">
         <v>781.5</v>
@@ -1774,37 +1785,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M6">
-        <v>18.4405032</v>
+        <v>23.050629</v>
       </c>
       <c r="N6">
-        <v>-65.3405032</v>
+        <v>-69.95062900000001</v>
       </c>
       <c r="O6">
-        <v>-16.8578498256</v>
+        <v>-18.047262282</v>
       </c>
       <c r="P6">
-        <v>-48.4826533744</v>
+        <v>-51.903366718</v>
       </c>
       <c r="Q6">
-        <v>159.2173466256</v>
+        <v>155.796633282</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08374922806588311</v>
+        <v>0.08414869362447135</v>
       </c>
       <c r="T6">
-        <v>0.8764255904360997</v>
+        <v>0.8856511229670058</v>
       </c>
       <c r="U6">
         <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>-0.6561751525305448</v>
+        <v>-0.5249401220244359</v>
       </c>
       <c r="W6">
-        <v>0.3905261009667025</v>
+        <v>0.359580880773362</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1812,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>-2.543314544692034</v>
+        <v>-2.034651635753627</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1820,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09792030298191587</v>
+        <v>0.09982030298191587</v>
       </c>
       <c r="C7">
-        <v>1582.660690042726</v>
+        <v>1547.6108843584</v>
       </c>
       <c r="D7">
-        <v>898.9156900427258</v>
+        <v>883.4168843584001</v>
       </c>
       <c r="E7">
-        <v>-1315.645</v>
+        <v>-1296.094</v>
       </c>
       <c r="F7">
-        <v>97.75500000000001</v>
+        <v>117.306</v>
       </c>
       <c r="G7">
         <v>781.5</v>
@@ -1856,37 +1867,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M7">
-        <v>23.050629</v>
+        <v>27.6607548</v>
       </c>
       <c r="N7">
-        <v>-69.95062900000001</v>
+        <v>-74.56075480000001</v>
       </c>
       <c r="O7">
-        <v>-18.047262282</v>
+        <v>-19.2366747384</v>
       </c>
       <c r="P7">
-        <v>-51.903366718</v>
+        <v>-55.32408006160001</v>
       </c>
       <c r="Q7">
-        <v>155.796633282</v>
+        <v>152.3759199384</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08414869362447135</v>
+        <v>0.0845566584502636</v>
       </c>
       <c r="T7">
-        <v>0.8856511229670058</v>
+        <v>0.8950729434241016</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>-0.5249401220244359</v>
+        <v>-0.4374501016870299</v>
       </c>
       <c r="W7">
-        <v>0.359580880773362</v>
+        <v>0.3389507339778016</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1894,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>-2.034651635753627</v>
+        <v>-1.69554302979469</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1902,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09982030298191587</v>
+        <v>0.1017203029819159</v>
       </c>
       <c r="C8">
-        <v>1547.6108843584</v>
+        <v>1513.086470558746</v>
       </c>
       <c r="D8">
-        <v>883.4168843584001</v>
+        <v>868.443470558746</v>
       </c>
       <c r="E8">
-        <v>-1296.094</v>
+        <v>-1276.543</v>
       </c>
       <c r="F8">
-        <v>117.306</v>
+        <v>136.857</v>
       </c>
       <c r="G8">
         <v>781.5</v>
@@ -1938,37 +1949,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M8">
-        <v>27.6607548</v>
+        <v>32.2708806</v>
       </c>
       <c r="N8">
-        <v>-74.56075480000001</v>
+        <v>-79.1708806</v>
       </c>
       <c r="O8">
-        <v>-19.2366747384</v>
+        <v>-20.4260871948</v>
       </c>
       <c r="P8">
-        <v>-55.32408006160001</v>
+        <v>-58.7447934052</v>
       </c>
       <c r="Q8">
-        <v>152.3759199384</v>
+        <v>148.9552065948</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0845566584502636</v>
+        <v>0.08497339671316965</v>
       </c>
       <c r="T8">
-        <v>0.8950729434241016</v>
+        <v>0.9046973836759736</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>-0.4374501016870299</v>
+        <v>-0.3749572300174543</v>
       </c>
       <c r="W8">
-        <v>0.3389507339778017</v>
+        <v>0.3242149148381157</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1976,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>-1.69554302979469</v>
+        <v>-1.453322596966877</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1984,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1017203029819159</v>
+        <v>0.1036203029819159</v>
       </c>
       <c r="C9">
-        <v>1513.086470558746</v>
+        <v>1479.061178624667</v>
       </c>
       <c r="D9">
-        <v>868.4434705587457</v>
+        <v>853.9691786246669</v>
       </c>
       <c r="E9">
-        <v>-1276.543</v>
+        <v>-1256.992</v>
       </c>
       <c r="F9">
-        <v>136.857</v>
+        <v>156.408</v>
       </c>
       <c r="G9">
         <v>781.5</v>
@@ -2020,37 +2031,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M9">
-        <v>32.27088060000001</v>
+        <v>36.8810064</v>
       </c>
       <c r="N9">
-        <v>-79.1708806</v>
+        <v>-83.78100640000001</v>
       </c>
       <c r="O9">
-        <v>-20.4260871948</v>
+        <v>-21.6154996512</v>
       </c>
       <c r="P9">
-        <v>-58.7447934052</v>
+        <v>-62.16550674880001</v>
       </c>
       <c r="Q9">
-        <v>148.9552065948</v>
+        <v>145.5344932512</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08497339671316967</v>
+        <v>0.0853991945035302</v>
       </c>
       <c r="T9">
-        <v>0.9046973836759739</v>
+        <v>0.914531050889843</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>-0.3749572300174542</v>
+        <v>-0.3280875762652724</v>
       </c>
       <c r="W9">
-        <v>0.3242149148381157</v>
+        <v>0.3131630504833512</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2058,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>-1.453322596966876</v>
+        <v>-1.271657272346017</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2066,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1036203029819159</v>
+        <v>0.1055203029819159</v>
       </c>
       <c r="C10">
-        <v>1479.061178624667</v>
+        <v>1445.510461188673</v>
       </c>
       <c r="D10">
-        <v>853.9691786246669</v>
+        <v>839.9694611886736</v>
       </c>
       <c r="E10">
-        <v>-1256.992</v>
+        <v>-1237.441</v>
       </c>
       <c r="F10">
-        <v>156.408</v>
+        <v>175.959</v>
       </c>
       <c r="G10">
         <v>781.5</v>
@@ -2102,37 +2113,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M10">
-        <v>36.8810064</v>
+        <v>41.4911322</v>
       </c>
       <c r="N10">
-        <v>-83.78100640000001</v>
+        <v>-88.39113220000002</v>
       </c>
       <c r="O10">
-        <v>-21.6154996512</v>
+        <v>-22.8049121076</v>
       </c>
       <c r="P10">
-        <v>-62.16550674880001</v>
+        <v>-65.58622009240001</v>
       </c>
       <c r="Q10">
-        <v>145.5344932512</v>
+        <v>142.1137799076</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0853991945035302</v>
+        <v>0.08583435048708549</v>
       </c>
       <c r="T10">
-        <v>0.914531050889843</v>
+        <v>0.9245808426578633</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>-0.3280875762652724</v>
+        <v>-0.2916334011246866</v>
       </c>
       <c r="W10">
-        <v>0.3131630504833512</v>
+        <v>0.3045671559852011</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2140,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>-1.271657272346017</v>
+        <v>-1.130362019863127</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2148,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1055203029819159</v>
+        <v>0.1074203029819159</v>
       </c>
       <c r="C11">
-        <v>1445.510461188673</v>
+        <v>1412.411354609192</v>
       </c>
       <c r="D11">
-        <v>839.9694611886736</v>
+        <v>826.4213546091919</v>
       </c>
       <c r="E11">
-        <v>-1237.441</v>
+        <v>-1217.89</v>
       </c>
       <c r="F11">
-        <v>175.959</v>
+        <v>195.51</v>
       </c>
       <c r="G11">
         <v>781.5</v>
@@ -2184,37 +2195,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M11">
-        <v>41.4911322</v>
+        <v>46.101258</v>
       </c>
       <c r="N11">
-        <v>-88.39113220000002</v>
+        <v>-93.00125800000001</v>
       </c>
       <c r="O11">
-        <v>-22.8049121076</v>
+        <v>-23.994324564</v>
       </c>
       <c r="P11">
-        <v>-65.58622009240001</v>
+        <v>-69.006933436</v>
       </c>
       <c r="Q11">
-        <v>142.1137799076</v>
+        <v>138.693066564</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08583435048708549</v>
+        <v>0.08627917660360865</v>
       </c>
       <c r="T11">
-        <v>0.9245808426578633</v>
+        <v>0.9348539631318395</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>-0.2916334011246866</v>
+        <v>-0.262470061012218</v>
       </c>
       <c r="W11">
-        <v>0.3045671559852011</v>
+        <v>0.297690440386681</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2222,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>-1.130362019863127</v>
+        <v>-1.017325817876814</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2230,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1074203029819159</v>
+        <v>0.1093203029819159</v>
       </c>
       <c r="C12">
-        <v>1412.411354609192</v>
+        <v>1379.742353276094</v>
       </c>
       <c r="D12">
-        <v>826.4213546091918</v>
+        <v>813.3033532760941</v>
       </c>
       <c r="E12">
-        <v>-1217.89</v>
+        <v>-1198.339</v>
       </c>
       <c r="F12">
-        <v>195.51</v>
+        <v>215.061</v>
       </c>
       <c r="G12">
         <v>781.5</v>
@@ -2266,37 +2277,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M12">
-        <v>46.10125800000001</v>
+        <v>50.71138380000001</v>
       </c>
       <c r="N12">
-        <v>-93.00125800000001</v>
+        <v>-97.61138380000001</v>
       </c>
       <c r="O12">
-        <v>-23.994324564</v>
+        <v>-25.1837370204</v>
       </c>
       <c r="P12">
-        <v>-69.006933436</v>
+        <v>-72.42764677960001</v>
       </c>
       <c r="Q12">
-        <v>138.693066564</v>
+        <v>135.2723532204</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08627917660360865</v>
+        <v>0.08673399881263796</v>
       </c>
       <c r="T12">
-        <v>0.9348539631318395</v>
+        <v>0.9453579402456804</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>-0.2624700610122179</v>
+        <v>-0.2386091463747436</v>
       </c>
       <c r="W12">
-        <v>0.297690440386681</v>
+        <v>0.2920640367151645</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2304,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>-1.017325817876813</v>
+        <v>-0.9248416526152852</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2312,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1093203029819159</v>
+        <v>0.1112203029819159</v>
       </c>
       <c r="C13">
-        <v>1379.742353276094</v>
+        <v>1347.483295700265</v>
       </c>
       <c r="D13">
-        <v>813.3033532760941</v>
+        <v>800.5952957002654</v>
       </c>
       <c r="E13">
-        <v>-1198.339</v>
+        <v>-1178.788</v>
       </c>
       <c r="F13">
-        <v>215.061</v>
+        <v>234.612</v>
       </c>
       <c r="G13">
         <v>781.5</v>
@@ -2348,37 +2359,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M13">
-        <v>50.71138380000001</v>
+        <v>55.3215096</v>
       </c>
       <c r="N13">
-        <v>-97.61138380000001</v>
+        <v>-102.2215096</v>
       </c>
       <c r="O13">
-        <v>-25.1837370204</v>
+        <v>-26.3731494768</v>
       </c>
       <c r="P13">
-        <v>-72.42764677960001</v>
+        <v>-75.8483601232</v>
       </c>
       <c r="Q13">
-        <v>135.2723532204</v>
+        <v>131.8516398768</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08673399881263796</v>
+        <v>0.08719915789005431</v>
       </c>
       <c r="T13">
-        <v>0.9453579402456804</v>
+        <v>0.9561006441121087</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>-0.2386091463747436</v>
+        <v>-0.218725050843515</v>
       </c>
       <c r="W13">
-        <v>0.2920640367151645</v>
+        <v>0.2873753669889009</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2386,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>-0.9248416526152852</v>
+        <v>-0.8477715148973448</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2394,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1112203029819159</v>
+        <v>0.1131203029819159</v>
       </c>
       <c r="C14">
-        <v>1347.483295700265</v>
+        <v>1315.615261118136</v>
       </c>
       <c r="D14">
-        <v>800.5952957002654</v>
+        <v>788.2782611181362</v>
       </c>
       <c r="E14">
-        <v>-1178.788</v>
+        <v>-1159.237</v>
       </c>
       <c r="F14">
-        <v>234.612</v>
+        <v>254.163</v>
       </c>
       <c r="G14">
         <v>781.5</v>
@@ -2430,37 +2441,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M14">
-        <v>55.3215096</v>
+        <v>59.93163540000001</v>
       </c>
       <c r="N14">
-        <v>-102.2215096</v>
+        <v>-106.8316354</v>
       </c>
       <c r="O14">
-        <v>-26.3731494768</v>
+        <v>-27.5625619332</v>
       </c>
       <c r="P14">
-        <v>-75.8483601232</v>
+        <v>-79.26907346680001</v>
       </c>
       <c r="Q14">
-        <v>131.8516398768</v>
+        <v>128.4309265332</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08719915789005431</v>
+        <v>0.08767501027959515</v>
       </c>
       <c r="T14">
-        <v>0.9561006441121087</v>
+        <v>0.9670903066881099</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>-0.218725050843515</v>
+        <v>-0.2019000469324753</v>
       </c>
       <c r="W14">
-        <v>0.2873753669889009</v>
+        <v>0.2834080310666777</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2468,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>-0.8477715148973448</v>
+        <v>-0.7825583214437026</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2476,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1131203029819159</v>
+        <v>0.1150203029819159</v>
       </c>
       <c r="C15">
-        <v>1315.615261118136</v>
+        <v>1284.12047549594</v>
       </c>
       <c r="D15">
-        <v>788.2782611181362</v>
+        <v>776.33447549594</v>
       </c>
       <c r="E15">
-        <v>-1159.237</v>
+        <v>-1139.686</v>
       </c>
       <c r="F15">
-        <v>254.163</v>
+        <v>273.7140000000001</v>
       </c>
       <c r="G15">
         <v>781.5</v>
@@ -2512,37 +2523,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M15">
-        <v>59.93163540000001</v>
+        <v>64.54176120000001</v>
       </c>
       <c r="N15">
-        <v>-106.8316354</v>
+        <v>-111.4417612</v>
       </c>
       <c r="O15">
-        <v>-27.5625619332</v>
+        <v>-28.7519743896</v>
       </c>
       <c r="P15">
-        <v>-79.26907346680001</v>
+        <v>-82.68978681040001</v>
       </c>
       <c r="Q15">
-        <v>128.4309265332</v>
+        <v>125.0102131896</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08767501027959515</v>
+        <v>0.08816192900377649</v>
       </c>
       <c r="T15">
-        <v>0.9670903066881099</v>
+        <v>0.9783355428123902</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>-0.2019000469324753</v>
+        <v>-0.1874786150087271</v>
       </c>
       <c r="W15">
-        <v>0.2834080310666777</v>
+        <v>0.2800074574190579</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2550,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>-0.7825583214437026</v>
+        <v>-0.7266612984834384</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2558,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1150203029819159</v>
+        <v>0.1169203029819159</v>
       </c>
       <c r="C16">
-        <v>1284.12047549594</v>
+        <v>1252.982225951624</v>
       </c>
       <c r="D16">
-        <v>776.33447549594</v>
+        <v>764.7472259516239</v>
       </c>
       <c r="E16">
-        <v>-1139.686</v>
+        <v>-1120.135</v>
       </c>
       <c r="F16">
-        <v>273.7140000000001</v>
+        <v>293.265</v>
       </c>
       <c r="G16">
         <v>781.5</v>
@@ -2594,37 +2605,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M16">
-        <v>64.54176120000001</v>
+        <v>69.15188700000002</v>
       </c>
       <c r="N16">
-        <v>-111.4417612</v>
+        <v>-116.051887</v>
       </c>
       <c r="O16">
-        <v>-28.7519743896</v>
+        <v>-29.94138684600001</v>
       </c>
       <c r="P16">
-        <v>-82.68978681040001</v>
+        <v>-86.11050015400002</v>
       </c>
       <c r="Q16">
-        <v>125.0102131896</v>
+        <v>121.589499846</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08816192900377649</v>
+        <v>0.08866030463911503</v>
       </c>
       <c r="T16">
-        <v>0.9783355428123902</v>
+        <v>0.9898453727278301</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>-0.1874786150087271</v>
+        <v>-0.174980040674812</v>
       </c>
       <c r="W16">
-        <v>0.2800074574190579</v>
+        <v>0.2770602935911207</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2632,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>-0.7266612984834384</v>
+        <v>-0.6782172119178758</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2640,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1169203029819159</v>
+        <v>0.1188203029819159</v>
       </c>
       <c r="C17">
-        <v>1252.982225951624</v>
+        <v>1222.184782727873</v>
       </c>
       <c r="D17">
-        <v>764.7472259516239</v>
+        <v>753.5007827278733</v>
       </c>
       <c r="E17">
-        <v>-1120.135</v>
+        <v>-1100.584</v>
       </c>
       <c r="F17">
-        <v>293.265</v>
+        <v>312.816</v>
       </c>
       <c r="G17">
         <v>781.5</v>
@@ -2676,37 +2687,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M17">
-        <v>69.151887</v>
+        <v>73.76201280000001</v>
       </c>
       <c r="N17">
-        <v>-116.051887</v>
+        <v>-120.6620128</v>
       </c>
       <c r="O17">
-        <v>-29.941386846</v>
+        <v>-31.1307993024</v>
       </c>
       <c r="P17">
-        <v>-86.11050015400001</v>
+        <v>-89.53121349760001</v>
       </c>
       <c r="Q17">
-        <v>121.589499846</v>
+        <v>118.1687865024</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08866030463911503</v>
+        <v>0.08917054636100927</v>
       </c>
       <c r="T17">
-        <v>0.9898453727278301</v>
+        <v>1.001629246212685</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>-0.174980040674812</v>
+        <v>-0.1640437881326362</v>
       </c>
       <c r="W17">
-        <v>0.2770602935911207</v>
+        <v>0.2744815252416756</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2714,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>-0.6782172119178758</v>
+        <v>-0.6358286361730086</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2722,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1188203029819159</v>
+        <v>0.1207203029819159</v>
       </c>
       <c r="C18">
-        <v>1222.184782727873</v>
+        <v>1191.713327950187</v>
       </c>
       <c r="D18">
-        <v>753.5007827278733</v>
+        <v>742.580327950187</v>
       </c>
       <c r="E18">
-        <v>-1100.584</v>
+        <v>-1081.033</v>
       </c>
       <c r="F18">
-        <v>312.816</v>
+        <v>332.3670000000001</v>
       </c>
       <c r="G18">
         <v>781.5</v>
@@ -2758,37 +2769,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M18">
-        <v>73.76201280000001</v>
+        <v>78.37213860000003</v>
       </c>
       <c r="N18">
-        <v>-120.6620128</v>
+        <v>-125.2721386</v>
       </c>
       <c r="O18">
-        <v>-31.1307993024</v>
+        <v>-32.32021175880001</v>
       </c>
       <c r="P18">
-        <v>-89.53121349760001</v>
+        <v>-92.95192684120002</v>
       </c>
       <c r="Q18">
-        <v>118.1687865024</v>
+        <v>114.7480731588</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08917054636100927</v>
+        <v>0.08969308306415395</v>
       </c>
       <c r="T18">
-        <v>1.001629246212685</v>
+        <v>1.013697068456211</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>-0.1640437881326362</v>
+        <v>-0.1543941535365988</v>
       </c>
       <c r="W18">
-        <v>0.2744815252416756</v>
+        <v>0.27220614140393</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2796,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>-0.6358286361730086</v>
+        <v>-0.5984269516922431</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2804,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1207203029819159</v>
+        <v>0.1226203029819159</v>
       </c>
       <c r="C19">
-        <v>1191.713327950187</v>
+        <v>1161.553890491487</v>
       </c>
       <c r="D19">
-        <v>742.580327950187</v>
+        <v>731.9718904914871</v>
       </c>
       <c r="E19">
-        <v>-1081.033</v>
+        <v>-1061.482</v>
       </c>
       <c r="F19">
-        <v>332.3670000000001</v>
+        <v>351.9180000000001</v>
       </c>
       <c r="G19">
         <v>781.5</v>
@@ -2840,37 +2851,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M19">
-        <v>78.37213860000003</v>
+        <v>82.98226440000002</v>
       </c>
       <c r="N19">
-        <v>-125.2721386</v>
+        <v>-129.8822644</v>
       </c>
       <c r="O19">
-        <v>-32.32021175880001</v>
+        <v>-33.50962421520001</v>
       </c>
       <c r="P19">
-        <v>-92.95192684120002</v>
+        <v>-96.37264018480002</v>
       </c>
       <c r="Q19">
-        <v>114.7480731588</v>
+        <v>111.3273598152</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08969308306415395</v>
+        <v>0.09022836456493633</v>
       </c>
       <c r="T19">
-        <v>1.013697068456211</v>
+        <v>1.026059227827629</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>-0.1543941535365988</v>
+        <v>-0.1458167005623433</v>
       </c>
       <c r="W19">
-        <v>0.27220614140393</v>
+        <v>0.2701835779926005</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2878,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>-0.5984269516922431</v>
+        <v>-0.5651810099315631</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2886,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1226203029819159</v>
+        <v>0.1245203029819159</v>
       </c>
       <c r="C20">
-        <v>1161.553890491487</v>
+        <v>1131.693286341205</v>
       </c>
       <c r="D20">
-        <v>731.9718904914871</v>
+        <v>721.662286341205</v>
       </c>
       <c r="E20">
-        <v>-1061.482</v>
+        <v>-1041.931</v>
       </c>
       <c r="F20">
-        <v>351.918</v>
+        <v>371.4690000000001</v>
       </c>
       <c r="G20">
         <v>781.5</v>
@@ -2922,37 +2933,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M20">
-        <v>82.98226440000001</v>
+        <v>87.59239020000001</v>
       </c>
       <c r="N20">
-        <v>-129.8822644</v>
+        <v>-134.4923902</v>
       </c>
       <c r="O20">
-        <v>-33.5096242152</v>
+        <v>-34.69903667160001</v>
       </c>
       <c r="P20">
-        <v>-96.37264018479999</v>
+        <v>-99.79335352840002</v>
       </c>
       <c r="Q20">
-        <v>111.3273598152</v>
+        <v>107.9066464716</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09022836456493633</v>
+        <v>0.0907768628928985</v>
       </c>
       <c r="T20">
-        <v>1.026059227827629</v>
+        <v>1.038726625702044</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>-0.1458167005623433</v>
+        <v>-0.1381421373748516</v>
       </c>
       <c r="W20">
-        <v>0.2701835779926005</v>
+        <v>0.26837391599299</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2960,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>-0.5651810099315631</v>
+        <v>-0.5354346409877966</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2968,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1245203029819159</v>
+        <v>0.1264203029819159</v>
       </c>
       <c r="C21">
-        <v>1131.693286341205</v>
+        <v>1102.119063943675</v>
       </c>
       <c r="D21">
-        <v>721.662286341205</v>
+        <v>711.6390639436751</v>
       </c>
       <c r="E21">
-        <v>-1041.931</v>
+        <v>-1022.38</v>
       </c>
       <c r="F21">
-        <v>371.4690000000001</v>
+        <v>391.02</v>
       </c>
       <c r="G21">
         <v>781.5</v>
@@ -3004,37 +3015,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M21">
-        <v>87.59239020000001</v>
+        <v>92.20251600000002</v>
       </c>
       <c r="N21">
-        <v>-134.4923902</v>
+        <v>-139.102516</v>
       </c>
       <c r="O21">
-        <v>-34.69903667160001</v>
+        <v>-35.88844912800001</v>
       </c>
       <c r="P21">
-        <v>-99.79335352840002</v>
+        <v>-103.214066872</v>
       </c>
       <c r="Q21">
-        <v>107.9066464716</v>
+        <v>104.485933128</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0907768628928985</v>
+        <v>0.09133907367905973</v>
       </c>
       <c r="T21">
-        <v>1.038726625702044</v>
+        <v>1.051710708523319</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>-0.1381421373748516</v>
+        <v>-0.131235030506109</v>
       </c>
       <c r="W21">
-        <v>0.26837391599299</v>
+        <v>0.2667452201933405</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3042,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>-0.5354346409877966</v>
+        <v>-0.5086629089384069</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3050,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1264203029819159</v>
+        <v>0.1283203029819159</v>
       </c>
       <c r="C22">
-        <v>1102.119063943675</v>
+        <v>1072.819454029324</v>
       </c>
       <c r="D22">
-        <v>711.6390639436751</v>
+        <v>701.8904540293241</v>
       </c>
       <c r="E22">
-        <v>-1022.38</v>
+        <v>-1002.829</v>
       </c>
       <c r="F22">
-        <v>391.02</v>
+        <v>410.5710000000001</v>
       </c>
       <c r="G22">
         <v>781.5</v>
@@ -3086,37 +3097,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M22">
-        <v>92.20251600000002</v>
+        <v>96.81264180000002</v>
       </c>
       <c r="N22">
-        <v>-139.102516</v>
+        <v>-143.7126418</v>
       </c>
       <c r="O22">
-        <v>-35.88844912800001</v>
+        <v>-37.07786158440001</v>
       </c>
       <c r="P22">
-        <v>-103.214066872</v>
+        <v>-106.6347802156</v>
       </c>
       <c r="Q22">
-        <v>104.485933128</v>
+        <v>101.0652197844</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09133907367905973</v>
+        <v>0.09191551764968074</v>
       </c>
       <c r="T22">
-        <v>1.051710708523319</v>
+        <v>1.065023502302096</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>-0.131235030506109</v>
+        <v>-0.1249857433391514</v>
       </c>
       <c r="W22">
-        <v>0.2667452201933405</v>
+        <v>0.2652716382793719</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3124,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>-0.5086629089384069</v>
+        <v>-0.4844408656556256</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3132,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1283203029819159</v>
+        <v>0.1302203029819159</v>
       </c>
       <c r="C23">
-        <v>1072.819454029324</v>
+        <v>1043.783323513655</v>
       </c>
       <c r="D23">
-        <v>701.8904540293242</v>
+        <v>692.4053235136547</v>
       </c>
       <c r="E23">
-        <v>-1002.829</v>
+        <v>-983.278</v>
       </c>
       <c r="F23">
-        <v>410.571</v>
+        <v>430.122</v>
       </c>
       <c r="G23">
         <v>781.5</v>
@@ -3168,37 +3179,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M23">
-        <v>96.81264180000001</v>
+        <v>101.4227676</v>
       </c>
       <c r="N23">
-        <v>-143.7126418</v>
+        <v>-148.3227676</v>
       </c>
       <c r="O23">
-        <v>-37.07786158440001</v>
+        <v>-38.2672740408</v>
       </c>
       <c r="P23">
-        <v>-106.6347802156</v>
+        <v>-110.0554935592</v>
       </c>
       <c r="Q23">
-        <v>101.0652197844</v>
+        <v>97.64450644079997</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09191551764968074</v>
+        <v>0.09250674223493306</v>
       </c>
       <c r="T23">
-        <v>1.065023502302096</v>
+        <v>1.078677649767507</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>-0.1249857433391514</v>
+        <v>-0.1193045731873718</v>
       </c>
       <c r="W23">
-        <v>0.2652716382793719</v>
+        <v>0.2639320183575823</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3206,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>-0.4844408656556258</v>
+        <v>-0.4624208263076426</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3214,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1302203029819159</v>
+        <v>0.1321203029819159</v>
       </c>
       <c r="C24">
-        <v>1043.783323513655</v>
+        <v>1015.000133084359</v>
       </c>
       <c r="D24">
-        <v>692.4053235136547</v>
+        <v>683.1731330843585</v>
       </c>
       <c r="E24">
-        <v>-983.278</v>
+        <v>-963.7270000000001</v>
       </c>
       <c r="F24">
-        <v>430.122</v>
+        <v>449.6730000000001</v>
       </c>
       <c r="G24">
         <v>781.5</v>
@@ -3250,37 +3261,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M24">
-        <v>101.4227676</v>
+        <v>106.0328934</v>
       </c>
       <c r="N24">
-        <v>-148.3227676</v>
+        <v>-152.9328934</v>
       </c>
       <c r="O24">
-        <v>-38.2672740408</v>
+        <v>-39.4566864972</v>
       </c>
       <c r="P24">
-        <v>-110.0554935592</v>
+        <v>-113.4762069028</v>
       </c>
       <c r="Q24">
-        <v>97.64450644079997</v>
+        <v>94.22379309719997</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09250674223493306</v>
+        <v>0.09311332330291919</v>
       </c>
       <c r="T24">
-        <v>1.078677649767507</v>
+        <v>1.092686450413838</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>-0.1193045731873718</v>
+        <v>-0.1141174178313991</v>
       </c>
       <c r="W24">
-        <v>0.2639320183575823</v>
+        <v>0.2627088871246439</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3288,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>-0.4624208263076426</v>
+        <v>-0.4423155729899189</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3296,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1321203029819159</v>
+        <v>0.1340203029819159</v>
       </c>
       <c r="C25">
-        <v>1015.000133084359</v>
+        <v>986.4598981368573</v>
       </c>
       <c r="D25">
-        <v>683.1731330843585</v>
+        <v>674.1838981368574</v>
       </c>
       <c r="E25">
-        <v>-963.7270000000001</v>
+        <v>-944.176</v>
       </c>
       <c r="F25">
-        <v>449.6730000000001</v>
+        <v>469.224</v>
       </c>
       <c r="G25">
         <v>781.5</v>
@@ -3332,37 +3343,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M25">
-        <v>106.0328934</v>
+        <v>110.6430192</v>
       </c>
       <c r="N25">
-        <v>-152.9328934</v>
+        <v>-157.5430192</v>
       </c>
       <c r="O25">
-        <v>-39.4566864972</v>
+        <v>-40.6460989536</v>
       </c>
       <c r="P25">
-        <v>-113.4762069028</v>
+        <v>-116.8969202464</v>
       </c>
       <c r="Q25">
-        <v>94.22379309719997</v>
+        <v>90.80307975359999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09311332330291919</v>
+        <v>0.0937358670305892</v>
       </c>
       <c r="T25">
-        <v>1.092686450413838</v>
+        <v>1.107063903708757</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>-0.1141174178313991</v>
+        <v>-0.1093625254217575</v>
       </c>
       <c r="W25">
-        <v>0.2627088871246439</v>
+        <v>0.2615876834944504</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3370,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>-0.4423155729899189</v>
+        <v>-0.4238857574486723</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3378,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1340203029819159</v>
+        <v>0.1359203029819159</v>
       </c>
       <c r="C26">
-        <v>986.4598981368574</v>
+        <v>958.1531527538673</v>
       </c>
       <c r="D26">
-        <v>674.1838981368574</v>
+        <v>665.4281527538674</v>
       </c>
       <c r="E26">
-        <v>-944.1760000000002</v>
+        <v>-924.625</v>
       </c>
       <c r="F26">
-        <v>469.224</v>
+        <v>488.775</v>
       </c>
       <c r="G26">
         <v>781.5</v>
@@ -3414,37 +3425,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M26">
-        <v>110.6430192</v>
+        <v>115.253145</v>
       </c>
       <c r="N26">
-        <v>-157.5430192</v>
+        <v>-162.153145</v>
       </c>
       <c r="O26">
-        <v>-40.6460989536</v>
+        <v>-41.83551141000001</v>
       </c>
       <c r="P26">
-        <v>-116.8969202464</v>
+        <v>-120.31763359</v>
       </c>
       <c r="Q26">
-        <v>90.80307975359999</v>
+        <v>87.38236640999997</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0937358670305892</v>
+        <v>0.09437501192433037</v>
       </c>
       <c r="T26">
-        <v>1.107063903708757</v>
+        <v>1.121824755758207</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>-0.1093625254217575</v>
+        <v>-0.1049880244048872</v>
       </c>
       <c r="W26">
-        <v>0.2615876834944504</v>
+        <v>0.2605561761546724</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3452,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>-0.4238857574486725</v>
+        <v>-0.4069303271507254</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3460,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1359203029819159</v>
+        <v>0.1378203029819159</v>
       </c>
       <c r="C27">
-        <v>958.1531527538673</v>
+        <v>930.0709164557993</v>
       </c>
       <c r="D27">
-        <v>665.4281527538674</v>
+        <v>656.8969164557992</v>
       </c>
       <c r="E27">
-        <v>-924.625</v>
+        <v>-905.0740000000001</v>
       </c>
       <c r="F27">
-        <v>488.775</v>
+        <v>508.3260000000001</v>
       </c>
       <c r="G27">
         <v>781.5</v>
@@ -3496,37 +3507,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M27">
-        <v>115.253145</v>
+        <v>119.8632708</v>
       </c>
       <c r="N27">
-        <v>-162.153145</v>
+        <v>-166.7632708</v>
       </c>
       <c r="O27">
-        <v>-41.83551141000001</v>
+        <v>-43.02492386640001</v>
       </c>
       <c r="P27">
-        <v>-120.31763359</v>
+        <v>-123.7383469336</v>
       </c>
       <c r="Q27">
-        <v>87.38236640999997</v>
+        <v>83.96165306639995</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09437501192433037</v>
+        <v>0.09503143100438891</v>
       </c>
       <c r="T27">
-        <v>1.121824755758207</v>
+        <v>1.13698454975494</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>-0.1049880244048872</v>
+        <v>-0.1009500234662377</v>
       </c>
       <c r="W27">
-        <v>0.2605561761546724</v>
+        <v>0.2596040155333388</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3534,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>-0.4069303271507254</v>
+        <v>-0.3912791607218515</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3542,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1378203029819159</v>
+        <v>0.1397203029819159</v>
       </c>
       <c r="C28">
-        <v>930.0709164557993</v>
+        <v>902.2046634764762</v>
       </c>
       <c r="D28">
-        <v>656.8969164557992</v>
+        <v>648.5816634764763</v>
       </c>
       <c r="E28">
-        <v>-905.0740000000001</v>
+        <v>-885.523</v>
       </c>
       <c r="F28">
-        <v>508.3260000000001</v>
+        <v>527.8770000000001</v>
       </c>
       <c r="G28">
         <v>781.5</v>
@@ -3578,37 +3589,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M28">
-        <v>119.8632708</v>
+        <v>124.4733966</v>
       </c>
       <c r="N28">
-        <v>-166.7632708</v>
+        <v>-171.3733966</v>
       </c>
       <c r="O28">
-        <v>-43.02492386640001</v>
+        <v>-44.21433632280001</v>
       </c>
       <c r="P28">
-        <v>-123.7383469336</v>
+        <v>-127.1590602772</v>
       </c>
       <c r="Q28">
-        <v>83.96165306639995</v>
+        <v>80.54093972279996</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09503143100438891</v>
+        <v>0.09570583416883258</v>
       </c>
       <c r="T28">
-        <v>1.13698454975494</v>
+        <v>1.152559680573501</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>-0.1009500234662377</v>
+        <v>-0.09721113370822887</v>
       </c>
       <c r="W28">
-        <v>0.2596040155333388</v>
+        <v>0.2587223853284004</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3616,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>-0.3912791607218515</v>
+        <v>-0.3767873399543755</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3624,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1397203029819159</v>
+        <v>0.1416203029819159</v>
       </c>
       <c r="C29">
-        <v>902.2046634764762</v>
+        <v>874.5462943432015</v>
       </c>
       <c r="D29">
-        <v>648.5816634764763</v>
+        <v>640.4742943432014</v>
       </c>
       <c r="E29">
-        <v>-885.523</v>
+        <v>-865.972</v>
       </c>
       <c r="F29">
-        <v>527.8770000000001</v>
+        <v>547.4280000000001</v>
       </c>
       <c r="G29">
         <v>781.5</v>
@@ -3660,37 +3671,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M29">
-        <v>124.4733966</v>
+        <v>129.0835224</v>
       </c>
       <c r="N29">
-        <v>-171.3733966</v>
+        <v>-175.9835224</v>
       </c>
       <c r="O29">
-        <v>-44.21433632280001</v>
+        <v>-45.40374877920001</v>
       </c>
       <c r="P29">
-        <v>-127.1590602772</v>
+        <v>-130.5797736208</v>
       </c>
       <c r="Q29">
-        <v>80.54093972279996</v>
+        <v>77.12022637919998</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09570583416883258</v>
+        <v>0.09639897075451082</v>
       </c>
       <c r="T29">
-        <v>1.152559680573501</v>
+        <v>1.168567453914799</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>-0.09721113370822887</v>
+        <v>-0.09373930750436354</v>
       </c>
       <c r="W29">
-        <v>0.2587223853284004</v>
+        <v>0.2579037287095289</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3698,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>-0.3767873399543755</v>
+        <v>-0.3633306492417192</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3706,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1416203029819159</v>
+        <v>0.1435203029819159</v>
       </c>
       <c r="C30">
-        <v>874.5462943432015</v>
+        <v>847.0881095620301</v>
       </c>
       <c r="D30">
-        <v>640.4742943432014</v>
+        <v>632.5671095620303</v>
       </c>
       <c r="E30">
-        <v>-865.972</v>
+        <v>-846.4209999999999</v>
       </c>
       <c r="F30">
-        <v>547.4280000000001</v>
+        <v>566.9790000000002</v>
       </c>
       <c r="G30">
         <v>781.5</v>
@@ -3742,37 +3753,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M30">
-        <v>129.0835224</v>
+        <v>133.6936482</v>
       </c>
       <c r="N30">
-        <v>-175.9835224</v>
+        <v>-180.5936482</v>
       </c>
       <c r="O30">
-        <v>-45.40374877920001</v>
+        <v>-46.59316123560001</v>
       </c>
       <c r="P30">
-        <v>-130.5797736208</v>
+        <v>-134.0004869644</v>
       </c>
       <c r="Q30">
-        <v>77.12022637919998</v>
+        <v>73.69951303559995</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09639897075451082</v>
+        <v>0.09711163231443351</v>
       </c>
       <c r="T30">
-        <v>1.168567453914799</v>
+        <v>1.185026150448811</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>-0.09373930750436354</v>
+        <v>-0.09050691759041996</v>
       </c>
       <c r="W30">
-        <v>0.2579037287095289</v>
+        <v>0.2571415311678211</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3780,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>-0.3633306492417192</v>
+        <v>-0.3508020061644184</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3788,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1435203029819159</v>
+        <v>0.1454203029819159</v>
       </c>
       <c r="C31">
-        <v>847.0881095620305</v>
+        <v>819.8227852285327</v>
       </c>
       <c r="D31">
-        <v>632.5671095620304</v>
+        <v>624.8527852285326</v>
       </c>
       <c r="E31">
-        <v>-846.421</v>
+        <v>-826.8700000000001</v>
       </c>
       <c r="F31">
-        <v>566.979</v>
+        <v>586.53</v>
       </c>
       <c r="G31">
         <v>781.5</v>
@@ -3824,37 +3835,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M31">
-        <v>133.6936482</v>
+        <v>138.303774</v>
       </c>
       <c r="N31">
-        <v>-180.5936482</v>
+        <v>-185.203774</v>
       </c>
       <c r="O31">
-        <v>-46.59316123560001</v>
+        <v>-47.78257369200001</v>
       </c>
       <c r="P31">
-        <v>-134.0004869644</v>
+        <v>-137.421200308</v>
       </c>
       <c r="Q31">
-        <v>73.69951303559998</v>
+        <v>70.27879969199998</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09711163231443351</v>
+        <v>0.09784465563321113</v>
       </c>
       <c r="T31">
-        <v>1.185026150448811</v>
+        <v>1.201955095455222</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>-0.09050691759041998</v>
+        <v>-0.08749002033740599</v>
       </c>
       <c r="W31">
-        <v>0.2571415311678211</v>
+        <v>0.2564301467955604</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3862,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>-0.3508020061644186</v>
+        <v>-0.3391086059589379</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3870,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1454203029819159</v>
+        <v>0.1473203029819159</v>
       </c>
       <c r="C32">
-        <v>819.8227852285327</v>
+        <v>792.7433504016548</v>
       </c>
       <c r="D32">
-        <v>624.8527852285326</v>
+        <v>617.3243504016548</v>
       </c>
       <c r="E32">
-        <v>-826.8700000000001</v>
+        <v>-807.3190000000001</v>
       </c>
       <c r="F32">
-        <v>586.53</v>
+        <v>606.081</v>
       </c>
       <c r="G32">
         <v>781.5</v>
@@ -3906,37 +3917,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M32">
-        <v>138.303774</v>
+        <v>142.9138998</v>
       </c>
       <c r="N32">
-        <v>-185.203774</v>
+        <v>-189.8138998</v>
       </c>
       <c r="O32">
-        <v>-47.78257369200001</v>
+        <v>-48.9719861484</v>
       </c>
       <c r="P32">
-        <v>-137.421200308</v>
+        <v>-140.8419136516</v>
       </c>
       <c r="Q32">
-        <v>70.27879969199998</v>
+        <v>66.85808634839998</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09784465563321113</v>
+        <v>0.09859892600470693</v>
       </c>
       <c r="T32">
-        <v>1.201955095455222</v>
+        <v>1.219374734519791</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>-0.08749002033740599</v>
+        <v>-0.0846677616168445</v>
       </c>
       <c r="W32">
-        <v>0.2564301467955604</v>
+        <v>0.2557646581892519</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3944,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>-0.3391086059589379</v>
+        <v>-0.3281696186699399</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3952,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1473203029819159</v>
+        <v>0.1492203029819159</v>
       </c>
       <c r="C33">
-        <v>792.7433504016548</v>
+        <v>765.8431660937522</v>
       </c>
       <c r="D33">
-        <v>617.3243504016548</v>
+        <v>609.9751660937524</v>
       </c>
       <c r="E33">
-        <v>-807.3190000000001</v>
+        <v>-787.768</v>
       </c>
       <c r="F33">
-        <v>606.081</v>
+        <v>625.6320000000001</v>
       </c>
       <c r="G33">
         <v>781.5</v>
@@ -3988,37 +3999,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M33">
-        <v>142.9138998</v>
+        <v>147.5240256</v>
       </c>
       <c r="N33">
-        <v>-189.8138998</v>
+        <v>-194.4240256</v>
       </c>
       <c r="O33">
-        <v>-48.9719861484</v>
+        <v>-50.16139860480001</v>
       </c>
       <c r="P33">
-        <v>-140.8419136516</v>
+        <v>-144.2626269952</v>
       </c>
       <c r="Q33">
-        <v>66.85808634839998</v>
+        <v>63.43737300479998</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09859892600470693</v>
+        <v>0.0993753807988938</v>
       </c>
       <c r="T33">
-        <v>1.219374734519791</v>
+        <v>1.237306715909788</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>-0.0846677616168445</v>
+        <v>-0.0820218940663181</v>
       </c>
       <c r="W33">
-        <v>0.2557646581892519</v>
+        <v>0.2551407626208378</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4026,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>-0.3281696186699399</v>
+        <v>-0.3179143180865043</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4034,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1492203029819159</v>
+        <v>0.1511203029819159</v>
       </c>
       <c r="C34">
-        <v>765.8431660937522</v>
+        <v>739.1159057436947</v>
       </c>
       <c r="D34">
-        <v>609.9751660937524</v>
+        <v>602.7989057436948</v>
       </c>
       <c r="E34">
-        <v>-787.768</v>
+        <v>-768.217</v>
       </c>
       <c r="F34">
-        <v>625.6320000000001</v>
+        <v>645.1830000000001</v>
       </c>
       <c r="G34">
         <v>781.5</v>
@@ -4070,37 +4081,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M34">
-        <v>147.5240256</v>
+        <v>152.1341514</v>
       </c>
       <c r="N34">
-        <v>-194.4240256</v>
+        <v>-199.0341514</v>
       </c>
       <c r="O34">
-        <v>-50.16139860480001</v>
+        <v>-51.35081106120001</v>
       </c>
       <c r="P34">
-        <v>-144.2626269952</v>
+        <v>-147.6833403388</v>
       </c>
       <c r="Q34">
-        <v>63.43737300479998</v>
+        <v>60.01665966119995</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0993753807988938</v>
+        <v>0.100175013348131</v>
       </c>
       <c r="T34">
-        <v>1.237306715909788</v>
+        <v>1.255773980326351</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>-0.0820218940663181</v>
+        <v>-0.07953638212491453</v>
       </c>
       <c r="W34">
-        <v>0.2551407626208378</v>
+        <v>0.2545546789050548</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4108,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>-0.3179143180865043</v>
+        <v>-0.3082805508717616</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4116,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1511203029819159</v>
+        <v>0.1530203029819159</v>
       </c>
       <c r="C35">
-        <v>739.1159057436947</v>
+        <v>712.5555370523296</v>
       </c>
       <c r="D35">
-        <v>602.7989057436948</v>
+        <v>595.7895370523297</v>
       </c>
       <c r="E35">
-        <v>-768.217</v>
+        <v>-748.6659999999999</v>
       </c>
       <c r="F35">
-        <v>645.1830000000001</v>
+        <v>664.7340000000002</v>
       </c>
       <c r="G35">
         <v>781.5</v>
@@ -4152,37 +4163,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M35">
-        <v>152.1341514</v>
+        <v>156.7442772000001</v>
       </c>
       <c r="N35">
-        <v>-199.0341514</v>
+        <v>-203.6442772000001</v>
       </c>
       <c r="O35">
-        <v>-51.35081106120001</v>
+        <v>-52.54022351760002</v>
       </c>
       <c r="P35">
-        <v>-147.6833403388</v>
+        <v>-151.1040536824</v>
       </c>
       <c r="Q35">
-        <v>60.01665966119995</v>
+        <v>56.59594631759995</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.100175013348131</v>
+        <v>0.1009988771867391</v>
       </c>
       <c r="T35">
-        <v>1.255773980326351</v>
+        <v>1.274800858816145</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>-0.07953638212491453</v>
+        <v>-0.07719707676829939</v>
       </c>
       <c r="W35">
-        <v>0.2545546789050548</v>
+        <v>0.254003070701965</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4190,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>-0.3082805508717616</v>
+        <v>-0.2992134758461216</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4198,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1530203029819159</v>
+        <v>0.1549203029819159</v>
       </c>
       <c r="C36">
-        <v>712.5555370523296</v>
+        <v>686.1563050706852</v>
       </c>
       <c r="D36">
-        <v>595.7895370523297</v>
+        <v>588.9413050706854</v>
       </c>
       <c r="E36">
-        <v>-748.6659999999999</v>
+        <v>-729.115</v>
       </c>
       <c r="F36">
-        <v>664.7340000000002</v>
+        <v>684.2850000000001</v>
       </c>
       <c r="G36">
         <v>781.5</v>
@@ -4234,37 +4245,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M36">
-        <v>156.7442772000001</v>
+        <v>161.354403</v>
       </c>
       <c r="N36">
-        <v>-203.6442772000001</v>
+        <v>-208.254403</v>
       </c>
       <c r="O36">
-        <v>-52.54022351760002</v>
+        <v>-53.72963597400001</v>
       </c>
       <c r="P36">
-        <v>-151.1040536824</v>
+        <v>-154.524767026</v>
       </c>
       <c r="Q36">
-        <v>56.59594631759995</v>
+        <v>53.17523297399998</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1009988771867391</v>
+        <v>0.1018480906819197</v>
       </c>
       <c r="T36">
-        <v>1.274800858816145</v>
+        <v>1.294413179721009</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>-0.07719707676829939</v>
+        <v>-0.07499144600349084</v>
       </c>
       <c r="W36">
-        <v>0.254003070701965</v>
+        <v>0.2534829829676232</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4272,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>-0.2992134758461216</v>
+        <v>-0.2906645193933752</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4280,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1549203029819159</v>
+        <v>0.1568203029819159</v>
       </c>
       <c r="C37">
-        <v>686.1563050706852</v>
+        <v>659.9127164412645</v>
       </c>
       <c r="D37">
-        <v>588.9413050706854</v>
+        <v>582.2487164412646</v>
       </c>
       <c r="E37">
-        <v>-729.115</v>
+        <v>-709.564</v>
       </c>
       <c r="F37">
-        <v>684.2850000000001</v>
+        <v>703.8360000000001</v>
       </c>
       <c r="G37">
         <v>781.5</v>
@@ -4316,37 +4327,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M37">
-        <v>161.354403</v>
+        <v>165.9645288</v>
       </c>
       <c r="N37">
-        <v>-208.254403</v>
+        <v>-212.8645288</v>
       </c>
       <c r="O37">
-        <v>-53.72963597400001</v>
+        <v>-54.91904843040001</v>
       </c>
       <c r="P37">
-        <v>-154.524767026</v>
+        <v>-157.9454803696</v>
       </c>
       <c r="Q37">
-        <v>53.17523297399998</v>
+        <v>49.75451963039995</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1018480906819197</v>
+        <v>0.1027238420988247</v>
       </c>
       <c r="T37">
-        <v>1.294413179721009</v>
+        <v>1.314638385654149</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>-0.07499144600349084</v>
+        <v>-0.07290835028117164</v>
       </c>
       <c r="W37">
-        <v>0.2534829829676232</v>
+        <v>0.2529917889963003</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4354,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>-0.2906645193933752</v>
+        <v>-0.2825905049657815</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4362,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1568203029819159</v>
+        <v>0.1587203029819159</v>
       </c>
       <c r="C38">
-        <v>659.9127164412646</v>
+        <v>633.819524701733</v>
       </c>
       <c r="D38">
-        <v>582.2487164412646</v>
+        <v>575.7065247017331</v>
       </c>
       <c r="E38">
-        <v>-709.5640000000001</v>
+        <v>-690.013</v>
       </c>
       <c r="F38">
-        <v>703.836</v>
+        <v>723.3870000000001</v>
       </c>
       <c r="G38">
         <v>781.5</v>
@@ -4398,37 +4409,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M38">
-        <v>165.9645288</v>
+        <v>170.5746546</v>
       </c>
       <c r="N38">
-        <v>-212.8645288</v>
+        <v>-217.4746546</v>
       </c>
       <c r="O38">
-        <v>-54.9190484304</v>
+        <v>-56.10846088680001</v>
       </c>
       <c r="P38">
-        <v>-157.9454803696</v>
+        <v>-161.3661937132</v>
       </c>
       <c r="Q38">
-        <v>49.75451963039998</v>
+        <v>46.33380628679996</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1027238420988247</v>
+        <v>0.1036273951480124</v>
       </c>
       <c r="T38">
-        <v>1.314638385654149</v>
+        <v>1.335505661616914</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>-0.07290835028117165</v>
+        <v>-0.07093785432762648</v>
       </c>
       <c r="W38">
-        <v>0.2529917889963003</v>
+        <v>0.2525271460504543</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4436,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>-0.2825905049657815</v>
+        <v>-0.2749529237504902</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4444,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1587203029819159</v>
+        <v>0.1606203029819159</v>
       </c>
       <c r="C39">
-        <v>633.819524701733</v>
+        <v>607.8717165683752</v>
       </c>
       <c r="D39">
-        <v>575.7065247017331</v>
+        <v>569.3097165683754</v>
       </c>
       <c r="E39">
-        <v>-690.013</v>
+        <v>-670.462</v>
       </c>
       <c r="F39">
-        <v>723.3870000000001</v>
+        <v>742.9380000000001</v>
       </c>
       <c r="G39">
         <v>781.5</v>
@@ -4480,37 +4491,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M39">
-        <v>170.5746546</v>
+        <v>175.1847804</v>
       </c>
       <c r="N39">
-        <v>-217.4746546</v>
+        <v>-222.0847804</v>
       </c>
       <c r="O39">
-        <v>-56.10846088680001</v>
+        <v>-57.29787334320001</v>
       </c>
       <c r="P39">
-        <v>-161.3661937132</v>
+        <v>-164.7869070568</v>
       </c>
       <c r="Q39">
-        <v>46.33380628679996</v>
+        <v>42.91309294319996</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1036273951480124</v>
+        <v>0.1045600950697545</v>
       </c>
       <c r="T39">
-        <v>1.335505661616914</v>
+        <v>1.357046075513961</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>-0.07093785432762648</v>
+        <v>-0.06907106868742578</v>
       </c>
       <c r="W39">
-        <v>0.2525271460504543</v>
+        <v>0.2520869579964951</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4518,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>-0.2749529237504902</v>
+        <v>-0.2677173204938983</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4526,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1606203029819159</v>
+        <v>0.1625203029819159</v>
       </c>
       <c r="C40">
-        <v>607.8717165683752</v>
+        <v>582.0644991239446</v>
       </c>
       <c r="D40">
-        <v>569.3097165683754</v>
+        <v>563.0534991239447</v>
       </c>
       <c r="E40">
-        <v>-670.462</v>
+        <v>-650.9110000000001</v>
       </c>
       <c r="F40">
-        <v>742.9380000000001</v>
+        <v>762.489</v>
       </c>
       <c r="G40">
         <v>781.5</v>
@@ -4562,37 +4573,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M40">
-        <v>175.1847804</v>
+        <v>179.7949062</v>
       </c>
       <c r="N40">
-        <v>-222.0847804</v>
+        <v>-226.6949062</v>
       </c>
       <c r="O40">
-        <v>-57.29787334320001</v>
+        <v>-58.48728579960001</v>
       </c>
       <c r="P40">
-        <v>-164.7869070568</v>
+        <v>-168.2076204004</v>
       </c>
       <c r="Q40">
-        <v>42.91309294319996</v>
+        <v>39.49237959959999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1045600950697545</v>
+        <v>0.1055233753167996</v>
       </c>
       <c r="T40">
-        <v>1.357046075513961</v>
+        <v>1.379292732489599</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>-0.06907106868742578</v>
+        <v>-0.06730001564415845</v>
       </c>
       <c r="W40">
-        <v>0.2520869579964951</v>
+        <v>0.2516693436888926</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4600,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>-0.2677173204938983</v>
+        <v>-0.2608527738145676</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4608,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1625203029819159</v>
+        <v>0.1644203029819159</v>
       </c>
       <c r="C41">
-        <v>582.0644991239446</v>
+        <v>556.3932878410984</v>
       </c>
       <c r="D41">
-        <v>563.0534991239447</v>
+        <v>556.9332878410985</v>
       </c>
       <c r="E41">
-        <v>-650.9110000000001</v>
+        <v>-631.36</v>
       </c>
       <c r="F41">
-        <v>762.489</v>
+        <v>782.0400000000001</v>
       </c>
       <c r="G41">
         <v>781.5</v>
@@ -4644,37 +4655,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M41">
-        <v>179.7949062</v>
+        <v>184.405032</v>
       </c>
       <c r="N41">
-        <v>-226.6949062</v>
+        <v>-231.305032</v>
       </c>
       <c r="O41">
-        <v>-58.48728579960001</v>
+        <v>-59.67669825600001</v>
       </c>
       <c r="P41">
-        <v>-168.2076204004</v>
+        <v>-171.628333744</v>
       </c>
       <c r="Q41">
-        <v>39.49237959959999</v>
+        <v>36.07166625599996</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1055233753167996</v>
+        <v>0.106518764905413</v>
       </c>
       <c r="T41">
-        <v>1.379292732489599</v>
+        <v>1.402280944697759</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>-0.06730001564415845</v>
+        <v>-0.06561751525305448</v>
       </c>
       <c r="W41">
-        <v>0.2516693436888926</v>
+        <v>0.2512726100966702</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4682,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>-0.2608527738145676</v>
+        <v>-0.2543314544692035</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4690,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1644203029819159</v>
+        <v>0.1663203029819159</v>
       </c>
       <c r="C42">
-        <v>556.3932878410984</v>
+        <v>530.853695378524</v>
       </c>
       <c r="D42">
-        <v>556.9332878410985</v>
+        <v>550.9446953785242</v>
       </c>
       <c r="E42">
-        <v>-631.36</v>
+        <v>-611.809</v>
       </c>
       <c r="F42">
-        <v>782.0400000000001</v>
+        <v>801.5910000000001</v>
       </c>
       <c r="G42">
         <v>781.5</v>
@@ -4726,37 +4737,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M42">
-        <v>184.405032</v>
+        <v>189.0151578</v>
       </c>
       <c r="N42">
-        <v>-231.305032</v>
+        <v>-235.9151578</v>
       </c>
       <c r="O42">
-        <v>-59.67669825600001</v>
+        <v>-60.86611071240001</v>
       </c>
       <c r="P42">
-        <v>-171.628333744</v>
+        <v>-175.0490470876</v>
       </c>
       <c r="Q42">
-        <v>36.07166625599996</v>
+        <v>32.65095291239996</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.106518764905413</v>
+        <v>0.1075478965139793</v>
       </c>
       <c r="T42">
-        <v>1.402280944697759</v>
+        <v>1.426048418336704</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>-0.06561751525305448</v>
+        <v>-0.06401708805176047</v>
       </c>
       <c r="W42">
-        <v>0.2512726100966702</v>
+        <v>0.2508952293626052</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4764,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>-0.2543314544692035</v>
+        <v>-0.2481282482626375</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4772,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1663203029819159</v>
+        <v>0.1682203029819159</v>
       </c>
       <c r="C43">
-        <v>530.853695378524</v>
+        <v>505.4415210922106</v>
       </c>
       <c r="D43">
-        <v>550.9446953785242</v>
+        <v>545.0835210922107</v>
       </c>
       <c r="E43">
-        <v>-611.809</v>
+        <v>-592.2579999999999</v>
       </c>
       <c r="F43">
-        <v>801.5910000000001</v>
+        <v>821.1420000000002</v>
       </c>
       <c r="G43">
         <v>781.5</v>
@@ -4808,37 +4819,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M43">
-        <v>189.0151578</v>
+        <v>193.6252836</v>
       </c>
       <c r="N43">
-        <v>-235.9151578</v>
+        <v>-240.5252836000001</v>
       </c>
       <c r="O43">
-        <v>-60.86611071240001</v>
+        <v>-62.05552316880001</v>
       </c>
       <c r="P43">
-        <v>-175.0490470876</v>
+        <v>-178.4697604312</v>
       </c>
       <c r="Q43">
-        <v>32.65095291239996</v>
+        <v>29.23023956879996</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1075478965139793</v>
+        <v>0.1086125154193927</v>
       </c>
       <c r="T43">
-        <v>1.426048418336704</v>
+        <v>1.450635460032165</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>-0.06401708805176047</v>
+        <v>-0.06249287166957569</v>
       </c>
       <c r="W43">
-        <v>0.2508952293626052</v>
+        <v>0.2505358191396859</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4846,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>-0.2481282482626375</v>
+        <v>-0.2422204328278128</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4854,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1682203029819159</v>
+        <v>0.1701203029819159</v>
       </c>
       <c r="C44">
-        <v>505.4415210922107</v>
+        <v>480.1527412091751</v>
       </c>
       <c r="D44">
-        <v>545.0835210922107</v>
+        <v>539.3457412091751</v>
       </c>
       <c r="E44">
-        <v>-592.258</v>
+        <v>-572.707</v>
       </c>
       <c r="F44">
-        <v>821.1420000000001</v>
+        <v>840.6930000000001</v>
       </c>
       <c r="G44">
         <v>781.5</v>
@@ -4890,37 +4901,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M44">
-        <v>193.6252836</v>
+        <v>198.2354094</v>
       </c>
       <c r="N44">
-        <v>-240.5252836</v>
+        <v>-245.1354094</v>
       </c>
       <c r="O44">
-        <v>-62.05552316880001</v>
+        <v>-63.24493562520001</v>
       </c>
       <c r="P44">
-        <v>-178.4697604312</v>
+        <v>-181.8904737748</v>
       </c>
       <c r="Q44">
-        <v>29.23023956879996</v>
+        <v>25.80952622519996</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1086125154193927</v>
+        <v>0.1097144893741189</v>
       </c>
       <c r="T44">
-        <v>1.450635460032165</v>
+        <v>1.47608520494501</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>-0.06249287166957571</v>
+        <v>-0.06103954907260882</v>
       </c>
       <c r="W44">
-        <v>0.2505358191396859</v>
+        <v>0.2501931256713212</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4928,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>-0.2422204328278128</v>
+        <v>-0.2365873995062358</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4936,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1701203029819159</v>
+        <v>0.1720203029819159</v>
       </c>
       <c r="C45">
-        <v>480.1527412091751</v>
+        <v>454.9834996153378</v>
       </c>
       <c r="D45">
-        <v>539.3457412091751</v>
+        <v>533.7274996153377</v>
       </c>
       <c r="E45">
-        <v>-572.707</v>
+        <v>-553.1560000000001</v>
       </c>
       <c r="F45">
-        <v>840.6930000000001</v>
+        <v>860.244</v>
       </c>
       <c r="G45">
         <v>781.5</v>
@@ -4972,37 +4983,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M45">
-        <v>198.2354094</v>
+        <v>202.8455352</v>
       </c>
       <c r="N45">
-        <v>-245.1354094</v>
+        <v>-249.7455352</v>
       </c>
       <c r="O45">
-        <v>-63.24493562520001</v>
+        <v>-64.43434808160001</v>
       </c>
       <c r="P45">
-        <v>-181.8904737748</v>
+        <v>-185.3111871184</v>
       </c>
       <c r="Q45">
-        <v>25.80952622519996</v>
+        <v>22.38881288159996</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1097144893741189</v>
+        <v>0.1108558195415139</v>
       </c>
       <c r="T45">
-        <v>1.47608520494501</v>
+        <v>1.502443869319028</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>-0.06103954907260882</v>
+        <v>-0.0596522865936859</v>
       </c>
       <c r="W45">
-        <v>0.2501931256713212</v>
+        <v>0.2498660091787911</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5010,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>-0.2365873995062358</v>
+        <v>-0.2312104131538213</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5018,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1720203029819159</v>
+        <v>0.1739203029819159</v>
       </c>
       <c r="C46">
-        <v>454.9834996153378</v>
+        <v>429.9300992132221</v>
       </c>
       <c r="D46">
-        <v>533.7274996153377</v>
+        <v>528.2250992132221</v>
       </c>
       <c r="E46">
-        <v>-553.1560000000001</v>
+        <v>-533.605</v>
       </c>
       <c r="F46">
-        <v>860.244</v>
+        <v>879.7950000000001</v>
       </c>
       <c r="G46">
         <v>781.5</v>
@@ -5054,37 +5065,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M46">
-        <v>202.8455352</v>
+        <v>207.455661</v>
       </c>
       <c r="N46">
-        <v>-249.7455352</v>
+        <v>-254.355661</v>
       </c>
       <c r="O46">
-        <v>-64.43434808160001</v>
+        <v>-65.62376053800001</v>
       </c>
       <c r="P46">
-        <v>-185.3111871184</v>
+        <v>-188.731900462</v>
       </c>
       <c r="Q46">
-        <v>22.38881288159996</v>
+        <v>18.96809953799999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1108558195415139</v>
+        <v>0.1120386526240869</v>
       </c>
       <c r="T46">
-        <v>1.502443869319028</v>
+        <v>1.529761030579374</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>-0.0596522865936859</v>
+        <v>-0.05832668022493732</v>
       </c>
       <c r="W46">
-        <v>0.2498660091787911</v>
+        <v>0.2495534311970402</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5092,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>-0.2312104131538213</v>
+        <v>-0.2260724039726252</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5100,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1739203029819159</v>
+        <v>0.1758203029819159</v>
       </c>
       <c r="C47">
-        <v>429.9300992132221</v>
+        <v>404.9889938087844</v>
       </c>
       <c r="D47">
-        <v>528.2250992132221</v>
+        <v>522.8349938087846</v>
       </c>
       <c r="E47">
-        <v>-533.605</v>
+        <v>-514.054</v>
       </c>
       <c r="F47">
-        <v>879.7950000000001</v>
+        <v>899.3460000000001</v>
       </c>
       <c r="G47">
         <v>781.5</v>
@@ -5136,37 +5147,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M47">
-        <v>207.455661</v>
+        <v>212.0657868</v>
       </c>
       <c r="N47">
-        <v>-254.355661</v>
+        <v>-258.9657868</v>
       </c>
       <c r="O47">
-        <v>-65.62376053800001</v>
+        <v>-66.81317299440002</v>
       </c>
       <c r="P47">
-        <v>-188.731900462</v>
+        <v>-192.1526138056</v>
       </c>
       <c r="Q47">
-        <v>18.96809953799999</v>
+        <v>15.54738619439996</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1120386526240869</v>
+        <v>0.1132652943393477</v>
       </c>
       <c r="T47">
-        <v>1.529761030579374</v>
+        <v>1.558089938553066</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>-0.05832668022493732</v>
+        <v>-0.05705870891569955</v>
       </c>
       <c r="W47">
-        <v>0.2495534311970402</v>
+        <v>0.249254443562322</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5174,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>-0.2260724039726252</v>
+        <v>-0.2211577864949594</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5182,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1758203029819159</v>
+        <v>0.1777203029819159</v>
       </c>
       <c r="C48">
-        <v>404.9889938087844</v>
+        <v>380.156780489953</v>
       </c>
       <c r="D48">
-        <v>522.8349938087846</v>
+        <v>517.5537804899531</v>
       </c>
       <c r="E48">
-        <v>-514.054</v>
+        <v>-494.5029999999999</v>
       </c>
       <c r="F48">
-        <v>899.3460000000001</v>
+        <v>918.8970000000002</v>
       </c>
       <c r="G48">
         <v>781.5</v>
@@ -5218,37 +5229,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M48">
-        <v>212.0657868</v>
+        <v>216.6759126000001</v>
       </c>
       <c r="N48">
-        <v>-258.9657868</v>
+        <v>-263.5759126</v>
       </c>
       <c r="O48">
-        <v>-66.81317299440002</v>
+        <v>-68.00258545080001</v>
       </c>
       <c r="P48">
-        <v>-192.1526138056</v>
+        <v>-195.5733271492</v>
       </c>
       <c r="Q48">
-        <v>15.54738619439996</v>
+        <v>12.12667285079996</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1132652943393477</v>
+        <v>0.1145382244212222</v>
       </c>
       <c r="T48">
-        <v>1.558089938553066</v>
+        <v>1.587487861921992</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>-0.05705870891569955</v>
+        <v>-0.05584469383238679</v>
       </c>
       <c r="W48">
-        <v>0.249254443562322</v>
+        <v>0.2489681788056768</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5256,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>-0.2211577864949594</v>
+        <v>-0.2164523016759177</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5264,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1777203029819159</v>
+        <v>0.1796203029819159</v>
       </c>
       <c r="C49">
-        <v>380.156780489953</v>
+        <v>355.430192462459</v>
       </c>
       <c r="D49">
-        <v>517.5537804899531</v>
+        <v>512.3781924624592</v>
       </c>
       <c r="E49">
-        <v>-494.5029999999999</v>
+        <v>-474.952</v>
       </c>
       <c r="F49">
-        <v>918.8970000000002</v>
+        <v>938.4480000000001</v>
       </c>
       <c r="G49">
         <v>781.5</v>
@@ -5300,37 +5311,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M49">
-        <v>216.6759126000001</v>
+        <v>221.2860384</v>
       </c>
       <c r="N49">
-        <v>-263.5759126</v>
+        <v>-268.1860384</v>
       </c>
       <c r="O49">
-        <v>-68.00258545080001</v>
+        <v>-69.1919979072</v>
       </c>
       <c r="P49">
-        <v>-195.5733271492</v>
+        <v>-198.9940404928</v>
       </c>
       <c r="Q49">
-        <v>12.12667285079996</v>
+        <v>8.705959507199964</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1145382244212222</v>
+        <v>0.1158601133523996</v>
       </c>
       <c r="T49">
-        <v>1.587487861921992</v>
+        <v>1.618016474651261</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>-0.05584469383238679</v>
+        <v>-0.05468126271087873</v>
       </c>
       <c r="W49">
-        <v>0.2489681788056768</v>
+        <v>0.2486938417472252</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5338,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>-0.2164523016759177</v>
+        <v>-0.2119428787243363</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5346,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1796203029819159</v>
+        <v>0.1815203029819159</v>
       </c>
       <c r="C50">
-        <v>355.4301924624593</v>
+        <v>330.8060923112687</v>
       </c>
       <c r="D50">
-        <v>512.3781924624593</v>
+        <v>507.3050923112688</v>
       </c>
       <c r="E50">
-        <v>-474.9520000000001</v>
+        <v>-455.4010000000001</v>
       </c>
       <c r="F50">
-        <v>938.448</v>
+        <v>957.999</v>
       </c>
       <c r="G50">
         <v>781.5</v>
@@ -5382,37 +5393,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M50">
-        <v>221.2860384</v>
+        <v>225.8961642</v>
       </c>
       <c r="N50">
-        <v>-268.1860384</v>
+        <v>-272.7961642</v>
       </c>
       <c r="O50">
-        <v>-69.1919979072</v>
+        <v>-70.38141036360001</v>
       </c>
       <c r="P50">
-        <v>-198.9940404928</v>
+        <v>-202.4147538364</v>
       </c>
       <c r="Q50">
-        <v>8.705959507199964</v>
+        <v>5.285246163599993</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1158601133523996</v>
+        <v>0.1172338410651917</v>
       </c>
       <c r="T50">
-        <v>1.618016474651261</v>
+        <v>1.649742287879717</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>-0.05468126271087874</v>
+        <v>-0.05356531857392204</v>
       </c>
       <c r="W50">
-        <v>0.2486938417472252</v>
+        <v>0.2484307021197308</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5420,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>-0.2119428787243363</v>
+        <v>-0.207617513852411</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5428,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1815203029819159</v>
+        <v>0.1834203029819159</v>
       </c>
       <c r="C51">
-        <v>330.8060923112687</v>
+        <v>306.2814656584011</v>
       </c>
       <c r="D51">
-        <v>507.3050923112688</v>
+        <v>502.3314656584012</v>
       </c>
       <c r="E51">
-        <v>-455.4010000000001</v>
+        <v>-435.85</v>
       </c>
       <c r="F51">
-        <v>957.999</v>
+        <v>977.5500000000001</v>
       </c>
       <c r="G51">
         <v>781.5</v>
@@ -5464,37 +5475,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M51">
-        <v>225.8961642</v>
+        <v>230.50629</v>
       </c>
       <c r="N51">
-        <v>-272.7961642</v>
+        <v>-277.40629</v>
       </c>
       <c r="O51">
-        <v>-70.38141036360001</v>
+        <v>-71.57082282</v>
       </c>
       <c r="P51">
-        <v>-202.4147538364</v>
+        <v>-205.83546718</v>
       </c>
       <c r="Q51">
-        <v>5.285246163599993</v>
+        <v>1.864532819999965</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1172338410651917</v>
+        <v>0.1186625178864956</v>
       </c>
       <c r="T51">
-        <v>1.649742287879717</v>
+        <v>1.682737133637311</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>-0.05356531857392204</v>
+        <v>-0.05249401220244359</v>
       </c>
       <c r="W51">
-        <v>0.2484307021197308</v>
+        <v>0.2481780880773362</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5502,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>-0.207617513852411</v>
+        <v>-0.2034651635753626</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5510,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1834203029819159</v>
+        <v>0.1853203029819159</v>
       </c>
       <c r="C52">
-        <v>306.2814656584011</v>
+        <v>281.8534151902013</v>
       </c>
       <c r="D52">
-        <v>502.3314656584012</v>
+        <v>497.4544151902015</v>
       </c>
       <c r="E52">
-        <v>-435.85</v>
+        <v>-416.299</v>
       </c>
       <c r="F52">
-        <v>977.5500000000001</v>
+        <v>997.1010000000001</v>
       </c>
       <c r="G52">
         <v>781.5</v>
@@ -5546,37 +5557,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M52">
-        <v>230.50629</v>
+        <v>235.1164158</v>
       </c>
       <c r="N52">
-        <v>-277.40629</v>
+        <v>-282.0164158</v>
       </c>
       <c r="O52">
-        <v>-71.57082282</v>
+        <v>-72.76023527640001</v>
       </c>
       <c r="P52">
-        <v>-205.83546718</v>
+        <v>-209.2561805236</v>
       </c>
       <c r="Q52">
-        <v>1.864532819999965</v>
+        <v>-1.556180523600005</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1186625178864956</v>
+        <v>0.1201495080474445</v>
       </c>
       <c r="T52">
-        <v>1.682737133637311</v>
+        <v>1.717078707793175</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>-0.05249401220244359</v>
+        <v>-0.05146471784553293</v>
       </c>
       <c r="W52">
-        <v>0.2481780880773362</v>
+        <v>0.2479353804679767</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5584,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>-0.2034651635753626</v>
+        <v>-0.1994756505640809</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5592,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1853203029819159</v>
+        <v>0.1872203029819159</v>
       </c>
       <c r="C53">
-        <v>281.8534151902013</v>
+        <v>257.5191550291955</v>
       </c>
       <c r="D53">
-        <v>497.4544151902015</v>
+        <v>492.6711550291957</v>
       </c>
       <c r="E53">
-        <v>-416.299</v>
+        <v>-396.7479999999999</v>
       </c>
       <c r="F53">
-        <v>997.1010000000001</v>
+        <v>1016.652</v>
       </c>
       <c r="G53">
         <v>781.5</v>
@@ -5628,37 +5639,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M53">
-        <v>235.1164158</v>
+        <v>239.7265416</v>
       </c>
       <c r="N53">
-        <v>-282.0164158</v>
+        <v>-286.6265416000001</v>
       </c>
       <c r="O53">
-        <v>-72.76023527640001</v>
+        <v>-73.94964773280002</v>
       </c>
       <c r="P53">
-        <v>-209.2561805236</v>
+        <v>-212.6768938672</v>
       </c>
       <c r="Q53">
-        <v>-1.556180523600005</v>
+        <v>-4.976893867200033</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1201495080474445</v>
+        <v>0.1216984561317662</v>
       </c>
       <c r="T53">
-        <v>1.717078707793175</v>
+        <v>1.752851180872199</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>-0.05146471784553293</v>
+        <v>-0.05047501173311883</v>
       </c>
       <c r="W53">
-        <v>0.2479353804679767</v>
+        <v>0.2477020077666694</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5666,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>-0.1994756505640809</v>
+        <v>-0.1956395803609257</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5674,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1872203029819159</v>
+        <v>0.1891203029819159</v>
       </c>
       <c r="C54">
-        <v>257.5191550291955</v>
+        <v>233.2760054275552</v>
       </c>
       <c r="D54">
-        <v>492.6711550291957</v>
+        <v>487.9790054275554</v>
       </c>
       <c r="E54">
-        <v>-396.7479999999999</v>
+        <v>-377.1969999999999</v>
       </c>
       <c r="F54">
-        <v>1016.652</v>
+        <v>1036.203</v>
       </c>
       <c r="G54">
         <v>781.5</v>
@@ -5710,37 +5721,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M54">
-        <v>239.7265416</v>
+        <v>244.3366674000001</v>
       </c>
       <c r="N54">
-        <v>-286.6265416000001</v>
+        <v>-291.2366674000001</v>
       </c>
       <c r="O54">
-        <v>-73.94964773280002</v>
+        <v>-75.13906018920002</v>
       </c>
       <c r="P54">
-        <v>-212.6768938672</v>
+        <v>-216.0976072108001</v>
       </c>
       <c r="Q54">
-        <v>-4.976893867200033</v>
+        <v>-8.397607210800089</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1216984561317662</v>
+        <v>0.1233133169005272</v>
       </c>
       <c r="T54">
-        <v>1.752851180872199</v>
+        <v>1.790145886848204</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>-0.05047501173311883</v>
+        <v>-0.04952265302117319</v>
       </c>
       <c r="W54">
-        <v>0.2477020077666694</v>
+        <v>0.2474774415823927</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5748,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>-0.1956395803609257</v>
+        <v>-0.1919482675239272</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5756,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1891203029819159</v>
+        <v>0.1910203029819159</v>
       </c>
       <c r="C55">
-        <v>233.2760054275552</v>
+        <v>209.1213877609378</v>
       </c>
       <c r="D55">
-        <v>487.9790054275554</v>
+        <v>483.375387760938</v>
       </c>
       <c r="E55">
-        <v>-377.1969999999999</v>
+        <v>-357.646</v>
       </c>
       <c r="F55">
-        <v>1036.203</v>
+        <v>1055.754</v>
       </c>
       <c r="G55">
         <v>781.5</v>
@@ -5792,37 +5803,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M55">
-        <v>244.3366674000001</v>
+        <v>248.9467932</v>
       </c>
       <c r="N55">
-        <v>-291.2366674000001</v>
+        <v>-295.8467932</v>
       </c>
       <c r="O55">
-        <v>-75.13906018920002</v>
+        <v>-76.32847264560002</v>
       </c>
       <c r="P55">
-        <v>-216.0976072108001</v>
+        <v>-219.5183205544</v>
       </c>
       <c r="Q55">
-        <v>-8.397607210800089</v>
+        <v>-11.81832055440003</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1233133169005272</v>
+        <v>0.1249983890070604</v>
       </c>
       <c r="T55">
-        <v>1.790145886848204</v>
+        <v>1.829062101779686</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>-0.04952265302117319</v>
+        <v>-0.04860556685411443</v>
       </c>
       <c r="W55">
-        <v>0.2474774415823927</v>
+        <v>0.2472611926642002</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5830,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>-0.1919482675239272</v>
+        <v>-0.1883936699771878</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5838,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1910203029819159</v>
+        <v>0.1929203029819159</v>
       </c>
       <c r="C56">
-        <v>209.1213877609378</v>
+        <v>185.0528198030468</v>
       </c>
       <c r="D56">
-        <v>483.375387760938</v>
+        <v>478.8578198030468</v>
       </c>
       <c r="E56">
-        <v>-357.646</v>
+        <v>-338.095</v>
       </c>
       <c r="F56">
-        <v>1055.754</v>
+        <v>1075.305</v>
       </c>
       <c r="G56">
         <v>781.5</v>
@@ -5874,37 +5885,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M56">
-        <v>248.9467932</v>
+        <v>253.556919</v>
       </c>
       <c r="N56">
-        <v>-295.8467932</v>
+        <v>-300.456919</v>
       </c>
       <c r="O56">
-        <v>-76.32847264560002</v>
+        <v>-77.51788510200001</v>
       </c>
       <c r="P56">
-        <v>-219.5183205544</v>
+        <v>-222.939033898</v>
       </c>
       <c r="Q56">
-        <v>-11.81832055440003</v>
+        <v>-15.23903389800003</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1249983890070604</v>
+        <v>0.1267583532072173</v>
       </c>
       <c r="T56">
-        <v>1.829062101779686</v>
+        <v>1.869707926263679</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>-0.04860556685411443</v>
+        <v>-0.04772182927494872</v>
       </c>
       <c r="W56">
-        <v>0.2472611926642002</v>
+        <v>0.2470528073430329</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5912,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>-0.1883936699771878</v>
+        <v>-0.1849683305230569</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5920,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1929203029819159</v>
+        <v>0.1948203029819159</v>
       </c>
       <c r="C57">
-        <v>185.0528198030468</v>
+        <v>161.0679112627179</v>
       </c>
       <c r="D57">
-        <v>478.8578198030468</v>
+        <v>474.423911262718</v>
       </c>
       <c r="E57">
-        <v>-338.095</v>
+        <v>-318.5439999999999</v>
       </c>
       <c r="F57">
-        <v>1075.305</v>
+        <v>1094.856</v>
       </c>
       <c r="G57">
         <v>781.5</v>
@@ -5956,37 +5967,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M57">
-        <v>253.556919</v>
+        <v>258.1670448</v>
       </c>
       <c r="N57">
-        <v>-300.456919</v>
+        <v>-305.0670448000001</v>
       </c>
       <c r="O57">
-        <v>-77.51788510200001</v>
+        <v>-78.70729755840001</v>
       </c>
       <c r="P57">
-        <v>-222.939033898</v>
+        <v>-226.3597472416001</v>
       </c>
       <c r="Q57">
-        <v>-15.23903389800003</v>
+        <v>-18.65974724160009</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1267583532072173</v>
+        <v>0.1285983157801086</v>
       </c>
       <c r="T57">
-        <v>1.869707926263679</v>
+        <v>1.912201288224217</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>-0.04772182927494872</v>
+        <v>-0.04686965375218177</v>
       </c>
       <c r="W57">
-        <v>0.2470528073430329</v>
+        <v>0.2468518643547645</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5994,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>-0.1849683305230569</v>
+        <v>-0.1816653246208597</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6002,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1948203029819159</v>
+        <v>0.1967203029819159</v>
       </c>
       <c r="C58">
-        <v>161.0679112627179</v>
+        <v>137.1643595666762</v>
       </c>
       <c r="D58">
-        <v>474.423911262718</v>
+        <v>470.0713595666763</v>
       </c>
       <c r="E58">
-        <v>-318.5439999999999</v>
+        <v>-298.9929999999999</v>
       </c>
       <c r="F58">
-        <v>1094.856</v>
+        <v>1114.407</v>
       </c>
       <c r="G58">
         <v>781.5</v>
@@ -6038,37 +6049,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M58">
-        <v>258.1670448</v>
+        <v>262.7771706</v>
       </c>
       <c r="N58">
-        <v>-305.0670448000001</v>
+        <v>-309.6771706000001</v>
       </c>
       <c r="O58">
-        <v>-78.70729755840001</v>
+        <v>-79.89671001480002</v>
       </c>
       <c r="P58">
-        <v>-226.3597472416001</v>
+        <v>-229.7804605852</v>
       </c>
       <c r="Q58">
-        <v>-18.65974724160009</v>
+        <v>-22.08046058520006</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1285983157801086</v>
+        <v>0.130523858007553</v>
       </c>
       <c r="T58">
-        <v>1.912201288224217</v>
+        <v>1.956671085624781</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>-0.04686965375218177</v>
+        <v>-0.04604737912495051</v>
       </c>
       <c r="W58">
-        <v>0.2468518643547645</v>
+        <v>0.2466579719976633</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6076,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>-0.1816653246208597</v>
+        <v>-0.1784782136625991</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6084,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1967203029819159</v>
+        <v>0.1986203029819159</v>
       </c>
       <c r="C59">
-        <v>137.1643595666762</v>
+        <v>113.3399458723216</v>
       </c>
       <c r="D59">
-        <v>470.0713595666763</v>
+        <v>465.7979458723218</v>
       </c>
       <c r="E59">
-        <v>-298.9929999999999</v>
+        <v>-279.4419999999998</v>
       </c>
       <c r="F59">
-        <v>1114.407</v>
+        <v>1133.958</v>
       </c>
       <c r="G59">
         <v>781.5</v>
@@ -6120,37 +6131,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M59">
-        <v>262.7771706</v>
+        <v>267.3872964000001</v>
       </c>
       <c r="N59">
-        <v>-309.6771706000001</v>
+        <v>-314.2872964000001</v>
       </c>
       <c r="O59">
-        <v>-79.89671001480002</v>
+        <v>-81.08612247120001</v>
       </c>
       <c r="P59">
-        <v>-229.7804605852</v>
+        <v>-233.2011739288</v>
       </c>
       <c r="Q59">
-        <v>-22.08046058520006</v>
+        <v>-25.50117392880006</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.130523858007553</v>
+        <v>0.1325410927220186</v>
       </c>
       <c r="T59">
-        <v>1.956671085624781</v>
+        <v>2.003258492425371</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>-0.04604737912495051</v>
+        <v>-0.04525345879520998</v>
       </c>
       <c r="W59">
-        <v>0.2466579719976633</v>
+        <v>0.2464707655839105</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6158,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>-0.1784782136625991</v>
+        <v>-0.1754010030822091</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6166,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1986203029819159</v>
+        <v>0.2005203029819158</v>
       </c>
       <c r="C60">
-        <v>113.3399458723216</v>
+        <v>89.59253129604554</v>
       </c>
       <c r="D60">
-        <v>465.7979458723217</v>
+        <v>461.6015312960456</v>
       </c>
       <c r="E60">
-        <v>-279.442</v>
+        <v>-259.8910000000001</v>
       </c>
       <c r="F60">
-        <v>1133.958</v>
+        <v>1153.509</v>
       </c>
       <c r="G60">
         <v>781.5</v>
@@ -6202,37 +6213,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M60">
-        <v>267.3872964</v>
+        <v>271.9974222</v>
       </c>
       <c r="N60">
-        <v>-314.2872964000001</v>
+        <v>-318.8974222000001</v>
       </c>
       <c r="O60">
-        <v>-81.08612247120001</v>
+        <v>-82.27553492760002</v>
       </c>
       <c r="P60">
-        <v>-233.2011739288</v>
+        <v>-236.6218872724</v>
       </c>
       <c r="Q60">
-        <v>-25.50117392880006</v>
+        <v>-28.92188727240006</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1325410927220185</v>
+        <v>0.1346567291298726</v>
       </c>
       <c r="T60">
-        <v>2.00325849242537</v>
+        <v>2.052118455655257</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>-0.04525345879520999</v>
+        <v>-0.04448645101901999</v>
       </c>
       <c r="W60">
-        <v>0.2464707655839105</v>
+        <v>0.2462899051502849</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6240,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>-0.1754010030822093</v>
+        <v>-0.1724281047248837</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6248,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2005203029819158</v>
+        <v>0.2024203029819159</v>
       </c>
       <c r="C61">
-        <v>89.59253129604554</v>
+        <v>65.92005334360124</v>
       </c>
       <c r="D61">
-        <v>461.6015312960456</v>
+        <v>457.4800533436012</v>
       </c>
       <c r="E61">
-        <v>-259.8910000000001</v>
+        <v>-240.3400000000001</v>
       </c>
       <c r="F61">
-        <v>1153.509</v>
+        <v>1173.06</v>
       </c>
       <c r="G61">
         <v>781.5</v>
@@ -6284,37 +6295,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M61">
-        <v>271.9974222</v>
+        <v>276.607548</v>
       </c>
       <c r="N61">
-        <v>-318.8974222000001</v>
+        <v>-323.507548</v>
       </c>
       <c r="O61">
-        <v>-82.27553492760002</v>
+        <v>-83.46494738400001</v>
       </c>
       <c r="P61">
-        <v>-236.6218872724</v>
+        <v>-240.042600616</v>
       </c>
       <c r="Q61">
-        <v>-28.92188727240006</v>
+        <v>-32.34260061600003</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1346567291298726</v>
+        <v>0.1368781473581195</v>
       </c>
       <c r="T61">
-        <v>2.052118455655257</v>
+        <v>2.103421417046639</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>-0.04448645101901999</v>
+        <v>-0.043745010168703</v>
       </c>
       <c r="W61">
-        <v>0.2462899051502849</v>
+        <v>0.2461150733977802</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6322,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>-0.1724281047248837</v>
+        <v>-0.1695543029794691</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6330,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2024203029819159</v>
+        <v>0.2043203029819159</v>
       </c>
       <c r="C62">
-        <v>65.92005334360124</v>
+        <v>42.32052253001461</v>
       </c>
       <c r="D62">
-        <v>457.4800533436012</v>
+        <v>453.4315225300147</v>
       </c>
       <c r="E62">
-        <v>-240.3400000000001</v>
+        <v>-220.789</v>
       </c>
       <c r="F62">
-        <v>1173.06</v>
+        <v>1192.611</v>
       </c>
       <c r="G62">
         <v>781.5</v>
@@ -6366,37 +6377,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M62">
-        <v>276.607548</v>
+        <v>281.2176738000001</v>
       </c>
       <c r="N62">
-        <v>-323.507548</v>
+        <v>-328.1176738</v>
       </c>
       <c r="O62">
-        <v>-83.46494738400001</v>
+        <v>-84.65435984040001</v>
       </c>
       <c r="P62">
-        <v>-240.042600616</v>
+        <v>-243.4633139596</v>
       </c>
       <c r="Q62">
-        <v>-32.34260061600003</v>
+        <v>-35.76331395960005</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1368781473581195</v>
+        <v>0.1392134844698661</v>
       </c>
       <c r="T62">
-        <v>2.103421417046639</v>
+        <v>2.157355299535014</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>-0.043745010168703</v>
+        <v>-0.04302787885446196</v>
       </c>
       <c r="W62">
-        <v>0.2461150733977802</v>
+        <v>0.2459459738338821</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6404,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>-0.1695543029794691</v>
+        <v>-0.1667747242421005</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6412,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2043203029819159</v>
+        <v>0.2062203029819159</v>
       </c>
       <c r="C63">
-        <v>42.32052253001461</v>
+        <v>18.7920191773967</v>
       </c>
       <c r="D63">
-        <v>453.4315225300147</v>
+        <v>449.4540191773966</v>
       </c>
       <c r="E63">
-        <v>-220.789</v>
+        <v>-201.2380000000001</v>
       </c>
       <c r="F63">
-        <v>1192.611</v>
+        <v>1212.162</v>
       </c>
       <c r="G63">
         <v>781.5</v>
@@ -6448,37 +6459,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M63">
-        <v>281.2176738000001</v>
+        <v>285.8277996</v>
       </c>
       <c r="N63">
-        <v>-328.1176738</v>
+        <v>-332.7277996</v>
       </c>
       <c r="O63">
-        <v>-84.65435984040001</v>
+        <v>-85.84377229680001</v>
       </c>
       <c r="P63">
-        <v>-243.4633139596</v>
+        <v>-246.8840273032</v>
       </c>
       <c r="Q63">
-        <v>-35.76331395960005</v>
+        <v>-39.18402730320003</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1392134844698661</v>
+        <v>0.1416717340611784</v>
       </c>
       <c r="T63">
-        <v>2.157355299535014</v>
+        <v>2.214127807417515</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>-0.04302787885446196</v>
+        <v>-0.04233388080842225</v>
       </c>
       <c r="W63">
-        <v>0.2459459738338821</v>
+        <v>0.2457823290946259</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6486,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>-0.1667747242421005</v>
+        <v>-0.16408480933497</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6494,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2062203029819159</v>
+        <v>0.2081203029819159</v>
       </c>
       <c r="C64">
-        <v>18.7920191773967</v>
+        <v>-4.66730962017391</v>
       </c>
       <c r="D64">
-        <v>449.4540191773966</v>
+        <v>445.5456903798264</v>
       </c>
       <c r="E64">
-        <v>-201.2380000000001</v>
+        <v>-181.6869999999999</v>
       </c>
       <c r="F64">
-        <v>1212.162</v>
+        <v>1231.713</v>
       </c>
       <c r="G64">
         <v>781.5</v>
@@ -6530,37 +6541,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M64">
-        <v>285.8277996</v>
+        <v>290.4379254</v>
       </c>
       <c r="N64">
-        <v>-332.7277996</v>
+        <v>-337.3379254</v>
       </c>
       <c r="O64">
-        <v>-85.84377229680001</v>
+        <v>-87.0331847532</v>
       </c>
       <c r="P64">
-        <v>-246.8840273032</v>
+        <v>-250.3047406468</v>
       </c>
       <c r="Q64">
-        <v>-39.18402730320003</v>
+        <v>-42.60474064680002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1416717340611784</v>
+        <v>0.1442628620087778</v>
       </c>
       <c r="T64">
-        <v>2.214127807417515</v>
+        <v>2.27396909950988</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>-0.04233388080842225</v>
+        <v>-0.0416619144463838</v>
       </c>
       <c r="W64">
-        <v>0.2457823290946259</v>
+        <v>0.2456238794264573</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6568,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>-0.16408480933497</v>
+        <v>-0.1614802885518751</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6576,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2081203029819159</v>
+        <v>0.2100203029819159</v>
       </c>
       <c r="C65">
-        <v>-4.66730962017391</v>
+        <v>-28.05925287477544</v>
       </c>
       <c r="D65">
-        <v>445.5456903798264</v>
+        <v>441.7047471252247</v>
       </c>
       <c r="E65">
-        <v>-181.6869999999999</v>
+        <v>-162.136</v>
       </c>
       <c r="F65">
-        <v>1231.713</v>
+        <v>1251.264</v>
       </c>
       <c r="G65">
         <v>781.5</v>
@@ -6612,37 +6623,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M65">
-        <v>290.4379254</v>
+        <v>295.0480512</v>
       </c>
       <c r="N65">
-        <v>-337.3379254</v>
+        <v>-341.9480512</v>
       </c>
       <c r="O65">
-        <v>-87.0331847532</v>
+        <v>-88.22259720960001</v>
       </c>
       <c r="P65">
-        <v>-250.3047406468</v>
+        <v>-253.7254539904</v>
       </c>
       <c r="Q65">
-        <v>-42.60474064680002</v>
+        <v>-46.02545399040002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1442628620087778</v>
+        <v>0.1469979415090216</v>
       </c>
       <c r="T65">
-        <v>2.27396909950988</v>
+        <v>2.337134907829599</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>-0.0416619144463838</v>
+        <v>-0.04101094703315905</v>
       </c>
       <c r="W65">
-        <v>0.2456238794264573</v>
+        <v>0.2454703813104189</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6650,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>-0.1614802885518751</v>
+        <v>-0.1589571590432521</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6658,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2100203029819159</v>
+        <v>0.2119203029819159</v>
       </c>
       <c r="C66">
-        <v>-28.05925287477544</v>
+        <v>-51.38553843517388</v>
       </c>
       <c r="D66">
-        <v>441.7047471252247</v>
+        <v>437.9294615648262</v>
       </c>
       <c r="E66">
-        <v>-162.136</v>
+        <v>-142.585</v>
       </c>
       <c r="F66">
-        <v>1251.264</v>
+        <v>1270.815</v>
       </c>
       <c r="G66">
         <v>781.5</v>
@@ -6694,37 +6705,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M66">
-        <v>295.0480512</v>
+        <v>299.658177</v>
       </c>
       <c r="N66">
-        <v>-341.9480512</v>
+        <v>-346.558177</v>
       </c>
       <c r="O66">
-        <v>-88.22259720960001</v>
+        <v>-89.412009666</v>
       </c>
       <c r="P66">
-        <v>-253.7254539904</v>
+        <v>-257.146167334</v>
       </c>
       <c r="Q66">
-        <v>-46.02545399040002</v>
+        <v>-49.44616733399999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1469979415090216</v>
+        <v>0.1498893112664222</v>
       </c>
       <c r="T66">
-        <v>2.337134907829599</v>
+        <v>2.403910190910445</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>-0.04101094703315905</v>
+        <v>-0.04038000938649507</v>
       </c>
       <c r="W66">
-        <v>0.2454703813104189</v>
+        <v>0.2453216062133355</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6732,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>-0.1589571590432521</v>
+        <v>-0.1565116642887405</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6740,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2119203029819159</v>
+        <v>0.2138203029819159</v>
       </c>
       <c r="C67">
-        <v>-51.38553843517388</v>
+        <v>-74.64783557850888</v>
       </c>
       <c r="D67">
-        <v>437.9294615648262</v>
+        <v>434.2181644214914</v>
       </c>
       <c r="E67">
-        <v>-142.585</v>
+        <v>-123.0339999999999</v>
       </c>
       <c r="F67">
-        <v>1270.815</v>
+        <v>1290.366</v>
       </c>
       <c r="G67">
         <v>781.5</v>
@@ -6776,37 +6787,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M67">
-        <v>299.658177</v>
+        <v>304.2683028000001</v>
       </c>
       <c r="N67">
-        <v>-346.558177</v>
+        <v>-351.1683028000001</v>
       </c>
       <c r="O67">
-        <v>-89.412009666</v>
+        <v>-90.60142212240002</v>
       </c>
       <c r="P67">
-        <v>-257.146167334</v>
+        <v>-260.5668806776001</v>
       </c>
       <c r="Q67">
-        <v>-49.44616733399999</v>
+        <v>-52.86688067760008</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1498893112664222</v>
+        <v>0.1529507615977876</v>
       </c>
       <c r="T67">
-        <v>2.403910190910445</v>
+        <v>2.474613431819575</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>-0.04038000938649507</v>
+        <v>-0.03976819106245726</v>
       </c>
       <c r="W67">
-        <v>0.2453216062133355</v>
+        <v>0.2451773394525274</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6814,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>-0.1565116642887405</v>
+        <v>-0.1541402754358809</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6822,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2138203029819159</v>
+        <v>0.2157203029819159</v>
       </c>
       <c r="C68">
-        <v>-74.64783557850888</v>
+        <v>-97.84775747130561</v>
       </c>
       <c r="D68">
-        <v>434.2181644214914</v>
+        <v>430.5692425286945</v>
       </c>
       <c r="E68">
-        <v>-123.0339999999999</v>
+        <v>-103.4829999999999</v>
       </c>
       <c r="F68">
-        <v>1290.366</v>
+        <v>1309.917</v>
       </c>
       <c r="G68">
         <v>781.5</v>
@@ -6858,37 +6869,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M68">
-        <v>304.2683028000001</v>
+        <v>308.8784286000001</v>
       </c>
       <c r="N68">
-        <v>-351.1683028000001</v>
+        <v>-355.7784286000001</v>
       </c>
       <c r="O68">
-        <v>-90.60142212240002</v>
+        <v>-91.79083457880003</v>
       </c>
       <c r="P68">
-        <v>-260.5668806776001</v>
+        <v>-263.9875940212</v>
       </c>
       <c r="Q68">
-        <v>-52.86688067760008</v>
+        <v>-56.28759402120005</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1529507615977876</v>
+        <v>0.1561977543734782</v>
       </c>
       <c r="T68">
-        <v>2.474613431819575</v>
+        <v>2.54960171763229</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>-0.03976819106245726</v>
+        <v>-0.03917463597197282</v>
       </c>
       <c r="W68">
-        <v>0.2451773394525274</v>
+        <v>0.2450373791621912</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6896,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>-0.1541402754358809</v>
+        <v>-0.1518396743099724</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6904,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2157203029819159</v>
+        <v>0.2176203029819159</v>
       </c>
       <c r="C69">
-        <v>-97.84775747130561</v>
+        <v>-120.9868635074376</v>
       </c>
       <c r="D69">
-        <v>430.5692425286945</v>
+        <v>426.9811364925626</v>
       </c>
       <c r="E69">
-        <v>-103.4829999999999</v>
+        <v>-83.93199999999979</v>
       </c>
       <c r="F69">
-        <v>1309.917</v>
+        <v>1329.468</v>
       </c>
       <c r="G69">
         <v>781.5</v>
@@ -6940,37 +6951,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M69">
-        <v>308.8784286000001</v>
+        <v>313.4885544000001</v>
       </c>
       <c r="N69">
-        <v>-355.7784286000001</v>
+        <v>-360.3885544000001</v>
       </c>
       <c r="O69">
-        <v>-91.79083457880003</v>
+        <v>-92.98024703520002</v>
       </c>
       <c r="P69">
-        <v>-263.9875940212</v>
+        <v>-267.4083073648001</v>
       </c>
       <c r="Q69">
-        <v>-56.28759402120005</v>
+        <v>-59.70830736480008</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1561977543734782</v>
+        <v>0.1596476841976494</v>
       </c>
       <c r="T69">
-        <v>2.54960171763229</v>
+        <v>2.629276771308299</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>-0.03917463597197282</v>
+        <v>-0.03859853838414969</v>
       </c>
       <c r="W69">
-        <v>0.2450373791621912</v>
+        <v>0.2449015353509825</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6978,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>-0.1518396743099724</v>
+        <v>-0.1496067379230608</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6986,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2176203029819159</v>
+        <v>0.2195203029819159</v>
       </c>
       <c r="C70">
-        <v>-120.9868635074376</v>
+        <v>-144.0666615301543</v>
       </c>
       <c r="D70">
-        <v>426.9811364925626</v>
+        <v>423.452338469846</v>
       </c>
       <c r="E70">
-        <v>-83.93199999999979</v>
+        <v>-64.38099999999986</v>
       </c>
       <c r="F70">
-        <v>1329.468</v>
+        <v>1349.019</v>
       </c>
       <c r="G70">
         <v>781.5</v>
@@ -7022,37 +7033,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M70">
-        <v>313.4885544000001</v>
+        <v>318.0986802</v>
       </c>
       <c r="N70">
-        <v>-360.3885544000001</v>
+        <v>-364.9986802000001</v>
       </c>
       <c r="O70">
-        <v>-92.98024703520002</v>
+        <v>-94.16965949160003</v>
       </c>
       <c r="P70">
-        <v>-267.4083073648001</v>
+        <v>-270.8290207084</v>
       </c>
       <c r="Q70">
-        <v>-59.70830736480008</v>
+        <v>-63.12902070840005</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1596476841976494</v>
+        <v>0.163320190139509</v>
       </c>
       <c r="T70">
-        <v>2.629276771308299</v>
+        <v>2.714092151027922</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>-0.03859853838414969</v>
+        <v>-0.03803913927713303</v>
       </c>
       <c r="W70">
-        <v>0.2449015353509825</v>
+        <v>0.244769629041548</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7060,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>-0.1496067379230608</v>
+        <v>-0.1474385243299732</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7068,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2195203029819159</v>
+        <v>0.2214203029819159</v>
       </c>
       <c r="C71">
-        <v>-144.0666615301543</v>
+        <v>-167.088609944828</v>
       </c>
       <c r="D71">
-        <v>423.452338469846</v>
+        <v>419.9813900551721</v>
       </c>
       <c r="E71">
-        <v>-64.38099999999986</v>
+        <v>-44.82999999999993</v>
       </c>
       <c r="F71">
-        <v>1349.019</v>
+        <v>1368.57</v>
       </c>
       <c r="G71">
         <v>781.5</v>
@@ -7104,37 +7115,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M71">
-        <v>318.0986802</v>
+        <v>322.708806</v>
       </c>
       <c r="N71">
-        <v>-364.9986802000001</v>
+        <v>-369.6088060000001</v>
       </c>
       <c r="O71">
-        <v>-94.16965949160003</v>
+        <v>-95.35907194800002</v>
       </c>
       <c r="P71">
-        <v>-270.8290207084</v>
+        <v>-274.2497340520001</v>
       </c>
       <c r="Q71">
-        <v>-63.12902070840005</v>
+        <v>-66.54973405200008</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.163320190139509</v>
+        <v>0.167237529810826</v>
       </c>
       <c r="T71">
-        <v>2.714092151027922</v>
+        <v>2.804561889395519</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>-0.03803913927713303</v>
+        <v>-0.03749572300174542</v>
       </c>
       <c r="W71">
-        <v>0.244769629041548</v>
+        <v>0.2446414914838116</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7142,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>-0.1474385243299732</v>
+        <v>-0.1453322596966877</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7150,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2214203029819159</v>
+        <v>0.2233203029819159</v>
       </c>
       <c r="C72">
-        <v>-167.088609944828</v>
+        <v>-190.0541197286402</v>
       </c>
       <c r="D72">
-        <v>419.9813900551721</v>
+        <v>416.56688027136</v>
       </c>
       <c r="E72">
-        <v>-44.82999999999993</v>
+        <v>-25.27899999999977</v>
       </c>
       <c r="F72">
-        <v>1368.57</v>
+        <v>1388.121</v>
       </c>
       <c r="G72">
         <v>781.5</v>
@@ -7186,37 +7197,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M72">
-        <v>322.708806</v>
+        <v>327.3189318000001</v>
       </c>
       <c r="N72">
-        <v>-369.6088060000001</v>
+        <v>-374.2189318000001</v>
       </c>
       <c r="O72">
-        <v>-95.35907194800002</v>
+        <v>-96.54848440440001</v>
       </c>
       <c r="P72">
-        <v>-274.2497340520001</v>
+        <v>-277.6704473956</v>
       </c>
       <c r="Q72">
-        <v>-66.54973405200008</v>
+        <v>-69.97044739560005</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.167237529810826</v>
+        <v>0.1714250308387855</v>
       </c>
       <c r="T72">
-        <v>2.804561889395519</v>
+        <v>2.901270920064331</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>-0.03749572300174542</v>
+        <v>-0.03696761422707295</v>
       </c>
       <c r="W72">
-        <v>0.2446414914838116</v>
+        <v>0.2445169634347438</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7224,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>-0.1453322596966877</v>
+        <v>-0.143285326461523</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7232,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2233203029819159</v>
+        <v>0.2252203029819159</v>
       </c>
       <c r="C73">
-        <v>-190.0541197286402</v>
+        <v>-212.9645563430231</v>
       </c>
       <c r="D73">
-        <v>416.5668802713599</v>
+        <v>413.207443656977</v>
       </c>
       <c r="E73">
-        <v>-25.279</v>
+        <v>-5.728000000000065</v>
       </c>
       <c r="F73">
-        <v>1388.121</v>
+        <v>1407.672</v>
       </c>
       <c r="G73">
         <v>781.5</v>
@@ -7268,37 +7279,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M73">
-        <v>327.3189318</v>
+        <v>331.9290576</v>
       </c>
       <c r="N73">
-        <v>-374.2189318000001</v>
+        <v>-378.8290576000001</v>
       </c>
       <c r="O73">
-        <v>-96.54848440440001</v>
+        <v>-97.73789686080002</v>
       </c>
       <c r="P73">
-        <v>-277.6704473956</v>
+        <v>-281.0911607392001</v>
       </c>
       <c r="Q73">
-        <v>-69.97044739560005</v>
+        <v>-73.39116073920007</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1714250308387855</v>
+        <v>0.1759116390830278</v>
       </c>
       <c r="T73">
-        <v>2.901270920064329</v>
+        <v>3.004887738638055</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>-0.03696761422707295</v>
+        <v>-0.03645417514058583</v>
       </c>
       <c r="W73">
-        <v>0.2445169634347438</v>
+        <v>0.2443958944981501</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7306,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>-0.1432853264615233</v>
+        <v>-0.141295252482891</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7314,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2252203029819159</v>
+        <v>0.2271203029819159</v>
       </c>
       <c r="C74">
-        <v>-212.9645563430231</v>
+        <v>-235.8212415543039</v>
       </c>
       <c r="D74">
-        <v>413.207443656977</v>
+        <v>409.9017584456961</v>
       </c>
       <c r="E74">
-        <v>-5.728000000000065</v>
+        <v>13.82299999999987</v>
       </c>
       <c r="F74">
-        <v>1407.672</v>
+        <v>1427.223</v>
       </c>
       <c r="G74">
         <v>781.5</v>
@@ -7350,37 +7361,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M74">
-        <v>331.9290576</v>
+        <v>336.5391834</v>
       </c>
       <c r="N74">
-        <v>-378.8290576000001</v>
+        <v>-383.4391834</v>
       </c>
       <c r="O74">
-        <v>-97.73789686080002</v>
+        <v>-98.92730931720001</v>
       </c>
       <c r="P74">
-        <v>-281.0911607392001</v>
+        <v>-284.5118740828</v>
       </c>
       <c r="Q74">
-        <v>-73.39116073920007</v>
+        <v>-76.81187408280005</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1759116390830278</v>
+        <v>0.1807305886786955</v>
       </c>
       <c r="T74">
-        <v>3.004887738638055</v>
+        <v>3.116179877106132</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>-0.03645417514058583</v>
+        <v>-0.03595480287838602</v>
       </c>
       <c r="W74">
-        <v>0.2443958944981501</v>
+        <v>0.2442781425187234</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7388,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>-0.141295252482891</v>
+        <v>-0.1393597010790157</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7396,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2271203029819159</v>
+        <v>0.2290203029819159</v>
       </c>
       <c r="C75">
-        <v>-235.8212415543039</v>
+        <v>-258.6254551676511</v>
       </c>
       <c r="D75">
-        <v>409.9017584456961</v>
+        <v>406.6485448323489</v>
       </c>
       <c r="E75">
-        <v>13.82299999999987</v>
+        <v>33.37400000000002</v>
       </c>
       <c r="F75">
-        <v>1427.223</v>
+        <v>1446.774</v>
       </c>
       <c r="G75">
         <v>781.5</v>
@@ -7432,37 +7443,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M75">
-        <v>336.5391834</v>
+        <v>341.1493092000001</v>
       </c>
       <c r="N75">
-        <v>-383.4391834</v>
+        <v>-388.0493092</v>
       </c>
       <c r="O75">
-        <v>-98.92730931720001</v>
+        <v>-100.1167217736</v>
       </c>
       <c r="P75">
-        <v>-284.5118740828</v>
+        <v>-287.9325874264</v>
       </c>
       <c r="Q75">
-        <v>-76.81187408280005</v>
+        <v>-80.23258742640002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1807305886786955</v>
+        <v>0.1859202267047992</v>
       </c>
       <c r="T75">
-        <v>3.116179877106132</v>
+        <v>3.236032949302521</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>-0.03595480287838602</v>
+        <v>-0.03546892716381324</v>
       </c>
       <c r="W75">
-        <v>0.2442781425187234</v>
+        <v>0.2441635730252272</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7470,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>-0.1393597010790157</v>
+        <v>-0.1374764618752451</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7478,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2290203029819159</v>
+        <v>0.2309203029819158</v>
       </c>
       <c r="C76">
-        <v>-258.6254551676511</v>
+        <v>-281.3784366790999</v>
       </c>
       <c r="D76">
-        <v>406.6485448323489</v>
+        <v>403.4465633209001</v>
       </c>
       <c r="E76">
-        <v>33.37400000000002</v>
+        <v>52.92499999999995</v>
       </c>
       <c r="F76">
-        <v>1446.774</v>
+        <v>1466.325</v>
       </c>
       <c r="G76">
         <v>781.5</v>
@@ -7514,37 +7525,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M76">
-        <v>341.1493092000001</v>
+        <v>345.7594350000001</v>
       </c>
       <c r="N76">
-        <v>-388.0493092</v>
+        <v>-392.659435</v>
       </c>
       <c r="O76">
-        <v>-100.1167217736</v>
+        <v>-101.30613423</v>
       </c>
       <c r="P76">
-        <v>-287.9325874264</v>
+        <v>-291.35330077</v>
       </c>
       <c r="Q76">
-        <v>-80.23258742640002</v>
+        <v>-83.65330077000004</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1859202267047992</v>
+        <v>0.1915250357729911</v>
       </c>
       <c r="T76">
-        <v>3.236032949302521</v>
+        <v>3.365474267274622</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>-0.03546892716381324</v>
+        <v>-0.03499600813496239</v>
       </c>
       <c r="W76">
-        <v>0.2441635730252272</v>
+        <v>0.2440520587182241</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7552,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>-0.1374764618752451</v>
+        <v>-0.1356434423835751</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7560,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2309203029819158</v>
+        <v>0.2328203029819159</v>
       </c>
       <c r="C77">
-        <v>-281.3784366790999</v>
+        <v>-304.081386850143</v>
       </c>
       <c r="D77">
-        <v>403.4465633209001</v>
+        <v>400.2946131498573</v>
       </c>
       <c r="E77">
-        <v>52.92499999999995</v>
+        <v>72.47600000000011</v>
       </c>
       <c r="F77">
-        <v>1466.325</v>
+        <v>1485.876</v>
       </c>
       <c r="G77">
         <v>781.5</v>
@@ -7596,37 +7607,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M77">
-        <v>345.7594350000001</v>
+        <v>350.3695608</v>
       </c>
       <c r="N77">
-        <v>-392.659435</v>
+        <v>-397.2695608</v>
       </c>
       <c r="O77">
-        <v>-101.30613423</v>
+        <v>-102.4955466864</v>
       </c>
       <c r="P77">
-        <v>-291.35330077</v>
+        <v>-294.7740141136</v>
       </c>
       <c r="Q77">
-        <v>-83.65330077000004</v>
+        <v>-87.07401411360001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1915250357729911</v>
+        <v>0.1975969122635325</v>
       </c>
       <c r="T77">
-        <v>3.365474267274622</v>
+        <v>3.505702361744399</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>-0.03499600813496239</v>
+        <v>-0.03453553434371289</v>
       </c>
       <c r="W77">
-        <v>0.2440520587182241</v>
+        <v>0.2439434789982475</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7634,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>-0.1356434423835751</v>
+        <v>-0.1338586602469491</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7642,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2328203029819159</v>
+        <v>0.2347203029819159</v>
       </c>
       <c r="C78">
-        <v>-304.081386850143</v>
+        <v>-326.7354692090755</v>
       </c>
       <c r="D78">
-        <v>400.2946131498573</v>
+        <v>397.1915307909246</v>
       </c>
       <c r="E78">
-        <v>72.47600000000011</v>
+        <v>92.02700000000004</v>
       </c>
       <c r="F78">
-        <v>1485.876</v>
+        <v>1505.427</v>
       </c>
       <c r="G78">
         <v>781.5</v>
@@ -7678,37 +7689,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M78">
-        <v>350.3695608</v>
+        <v>354.9796866</v>
       </c>
       <c r="N78">
-        <v>-397.2695608</v>
+        <v>-401.8796866</v>
       </c>
       <c r="O78">
-        <v>-102.4955466864</v>
+        <v>-103.6849591428</v>
       </c>
       <c r="P78">
-        <v>-294.7740141136</v>
+        <v>-298.1947274572</v>
       </c>
       <c r="Q78">
-        <v>-87.07401411360001</v>
+        <v>-90.49472745719999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1975969122635325</v>
+        <v>0.2041967780141208</v>
       </c>
       <c r="T78">
-        <v>3.505702361744399</v>
+        <v>3.658124203559372</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>-0.03453553434371289</v>
+        <v>-0.03408702091067765</v>
       </c>
       <c r="W78">
-        <v>0.2439434789982475</v>
+        <v>0.2438377195307378</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7716,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>-0.1338586602469491</v>
+        <v>-0.1321202360878979</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7724,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2347203029819159</v>
+        <v>0.2366203029819159</v>
       </c>
       <c r="C79">
-        <v>-326.7354692090755</v>
+        <v>-349.341811483057</v>
       </c>
       <c r="D79">
-        <v>397.1915307909246</v>
+        <v>394.1361885169431</v>
       </c>
       <c r="E79">
-        <v>92.02700000000004</v>
+        <v>111.578</v>
       </c>
       <c r="F79">
-        <v>1505.427</v>
+        <v>1524.978</v>
       </c>
       <c r="G79">
         <v>781.5</v>
@@ -7760,37 +7771,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M79">
-        <v>354.9796866</v>
+        <v>359.5898124</v>
       </c>
       <c r="N79">
-        <v>-401.8796866</v>
+        <v>-406.4898124</v>
       </c>
       <c r="O79">
-        <v>-103.6849591428</v>
+        <v>-104.8743715992</v>
       </c>
       <c r="P79">
-        <v>-298.1947274572</v>
+        <v>-301.6154408008</v>
       </c>
       <c r="Q79">
-        <v>-90.49472745719999</v>
+        <v>-93.91544080080001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2041967780141208</v>
+        <v>0.2113966315602172</v>
       </c>
       <c r="T79">
-        <v>3.658124203559372</v>
+        <v>3.824402576448435</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>-0.03408702091067765</v>
+        <v>-0.03365000782207923</v>
       </c>
       <c r="W79">
-        <v>0.2438377195307378</v>
+        <v>0.2437346718444463</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7798,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>-0.1321202360878979</v>
+        <v>-0.1304263869072837</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7806,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2366203029819159</v>
+        <v>0.2385203029819158</v>
       </c>
       <c r="C80">
-        <v>-349.341811483057</v>
+        <v>-371.9015069645743</v>
       </c>
       <c r="D80">
-        <v>394.1361885169431</v>
+        <v>391.1274930354259</v>
       </c>
       <c r="E80">
-        <v>111.578</v>
+        <v>131.1290000000001</v>
       </c>
       <c r="F80">
-        <v>1524.978</v>
+        <v>1544.529</v>
       </c>
       <c r="G80">
         <v>781.5</v>
@@ -7842,37 +7853,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M80">
-        <v>359.5898124</v>
+        <v>364.1999382000001</v>
       </c>
       <c r="N80">
-        <v>-406.4898124</v>
+        <v>-411.0999382000001</v>
       </c>
       <c r="O80">
-        <v>-104.8743715992</v>
+        <v>-106.0637840556</v>
       </c>
       <c r="P80">
-        <v>-301.6154408008</v>
+        <v>-305.0361541444001</v>
       </c>
       <c r="Q80">
-        <v>-93.91544080080001</v>
+        <v>-97.3361541444001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2113966315602172</v>
+        <v>0.2192821854440371</v>
       </c>
       <c r="T80">
-        <v>3.824402576448435</v>
+        <v>4.006516984850741</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>-0.03365000782207923</v>
+        <v>-0.03322405835597695</v>
       </c>
       <c r="W80">
-        <v>0.2437346718444463</v>
+        <v>0.2436342329603393</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7880,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>-0.1304263869072837</v>
+        <v>-0.1287754199844069</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7888,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2385203029819158</v>
+        <v>0.2404203029819159</v>
       </c>
       <c r="C81">
-        <v>-371.9015069645743</v>
+        <v>-394.4156158157955</v>
       </c>
       <c r="D81">
-        <v>391.1274930354259</v>
+        <v>388.1643841842047</v>
       </c>
       <c r="E81">
-        <v>131.1290000000001</v>
+        <v>150.6800000000001</v>
       </c>
       <c r="F81">
-        <v>1544.529</v>
+        <v>1564.08</v>
       </c>
       <c r="G81">
         <v>781.5</v>
@@ -7924,37 +7935,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M81">
-        <v>364.1999382000001</v>
+        <v>368.8100640000001</v>
       </c>
       <c r="N81">
-        <v>-411.0999382000001</v>
+        <v>-415.7100640000001</v>
       </c>
       <c r="O81">
-        <v>-106.0637840556</v>
+        <v>-107.253196512</v>
       </c>
       <c r="P81">
-        <v>-305.0361541444001</v>
+        <v>-308.4568674880001</v>
       </c>
       <c r="Q81">
-        <v>-97.3361541444001</v>
+        <v>-100.7568674880001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2192821854440371</v>
+        <v>0.227956294716239</v>
       </c>
       <c r="T81">
-        <v>4.006516984850741</v>
+        <v>4.206842834093279</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>-0.03322405835597695</v>
+        <v>-0.03280875762652724</v>
       </c>
       <c r="W81">
-        <v>0.2436342329603393</v>
+        <v>0.2435363050483351</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7962,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>-0.1287754199844069</v>
+        <v>-0.1271657272346018</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7970,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2404203029819159</v>
+        <v>0.2423203029819159</v>
       </c>
       <c r="C82">
-        <v>-394.4156158157955</v>
+        <v>-416.8851663140781</v>
       </c>
       <c r="D82">
-        <v>388.1643841842047</v>
+        <v>385.2458336859221</v>
       </c>
       <c r="E82">
-        <v>150.6800000000001</v>
+        <v>170.2310000000002</v>
       </c>
       <c r="F82">
-        <v>1564.08</v>
+        <v>1583.631</v>
       </c>
       <c r="G82">
         <v>781.5</v>
@@ -8006,37 +8017,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M82">
-        <v>368.8100640000001</v>
+        <v>373.4201898000001</v>
       </c>
       <c r="N82">
-        <v>-415.7100640000001</v>
+        <v>-420.3201898000001</v>
       </c>
       <c r="O82">
-        <v>-107.253196512</v>
+        <v>-108.4426089684</v>
       </c>
       <c r="P82">
-        <v>-308.4568674880001</v>
+        <v>-311.8775808316001</v>
       </c>
       <c r="Q82">
-        <v>-100.7568674880001</v>
+        <v>-104.1775808316001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.227956294716239</v>
+        <v>0.2375434681223568</v>
       </c>
       <c r="T82">
-        <v>4.206842834093279</v>
+        <v>4.42825561483503</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>-0.03280875762652724</v>
+        <v>-0.03240371123607629</v>
       </c>
       <c r="W82">
-        <v>0.2435363050483351</v>
+        <v>0.2434407951094668</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8044,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>-0.1271657272346018</v>
+        <v>-0.1255957799847918</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8052,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2423203029819159</v>
+        <v>0.2442203029819159</v>
       </c>
       <c r="C83">
-        <v>-416.8851663140781</v>
+        <v>-439.311156041713</v>
       </c>
       <c r="D83">
-        <v>385.2458336859221</v>
+        <v>382.3708439582872</v>
       </c>
       <c r="E83">
-        <v>170.2310000000002</v>
+        <v>189.7820000000002</v>
       </c>
       <c r="F83">
-        <v>1583.631</v>
+        <v>1603.182</v>
       </c>
       <c r="G83">
         <v>781.5</v>
@@ -8088,37 +8099,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M83">
-        <v>373.4201898000001</v>
+        <v>378.0303156000001</v>
       </c>
       <c r="N83">
-        <v>-420.3201898000001</v>
+        <v>-424.9303156000001</v>
       </c>
       <c r="O83">
-        <v>-108.4426089684</v>
+        <v>-109.6320214248</v>
       </c>
       <c r="P83">
-        <v>-311.8775808316001</v>
+        <v>-315.2982941752001</v>
       </c>
       <c r="Q83">
-        <v>-104.1775808316001</v>
+        <v>-107.5982941752001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2375434681223568</v>
+        <v>0.2481958830180433</v>
       </c>
       <c r="T83">
-        <v>4.42825561483503</v>
+        <v>4.674269815659199</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>-0.03240371123607629</v>
+        <v>-0.03200854402588024</v>
       </c>
       <c r="W83">
-        <v>0.2434407951094668</v>
+        <v>0.2433476146813026</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8126,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>-0.1255957799847918</v>
+        <v>-0.1240641241313187</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8134,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2442203029819159</v>
+        <v>0.2461203029819159</v>
       </c>
       <c r="C84">
-        <v>-439.311156041713</v>
+        <v>-461.6945530227836</v>
       </c>
       <c r="D84">
-        <v>382.3708439582872</v>
+        <v>379.5384469772167</v>
       </c>
       <c r="E84">
-        <v>189.7820000000002</v>
+        <v>209.3330000000001</v>
       </c>
       <c r="F84">
-        <v>1603.182</v>
+        <v>1622.733</v>
       </c>
       <c r="G84">
         <v>781.5</v>
@@ -8170,37 +8181,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M84">
-        <v>378.0303156000001</v>
+        <v>382.6404414</v>
       </c>
       <c r="N84">
-        <v>-424.9303156000001</v>
+        <v>-429.5404414000001</v>
       </c>
       <c r="O84">
-        <v>-109.6320214248</v>
+        <v>-110.8214338812</v>
       </c>
       <c r="P84">
-        <v>-315.2982941752001</v>
+        <v>-318.7190075188</v>
       </c>
       <c r="Q84">
-        <v>-107.5982941752001</v>
+        <v>-111.0190075188</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2481958830180433</v>
+        <v>0.2601015231955753</v>
       </c>
       <c r="T84">
-        <v>4.674269815659199</v>
+        <v>4.949226863639153</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>-0.03200854402588024</v>
+        <v>-0.03162289891713469</v>
       </c>
       <c r="W84">
-        <v>0.2433476146813026</v>
+        <v>0.2432566795646604</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8208,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>-0.1240641241313187</v>
+        <v>-0.122569375647809</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8216,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2461203029819159</v>
+        <v>0.2480203029819159</v>
       </c>
       <c r="C85">
-        <v>-461.6945530227836</v>
+        <v>-484.0362968098736</v>
       </c>
       <c r="D85">
-        <v>379.5384469772167</v>
+        <v>376.7477031901266</v>
       </c>
       <c r="E85">
-        <v>209.3330000000001</v>
+        <v>228.8840000000002</v>
       </c>
       <c r="F85">
-        <v>1622.733</v>
+        <v>1642.284</v>
       </c>
       <c r="G85">
         <v>781.5</v>
@@ -8252,37 +8263,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M85">
-        <v>382.6404414</v>
+        <v>387.2505672000001</v>
       </c>
       <c r="N85">
-        <v>-429.5404414000001</v>
+        <v>-434.1505672000001</v>
       </c>
       <c r="O85">
-        <v>-110.8214338812</v>
+        <v>-112.0108463376</v>
       </c>
       <c r="P85">
-        <v>-318.7190075188</v>
+        <v>-322.1397208624001</v>
       </c>
       <c r="Q85">
-        <v>-111.0190075188</v>
+        <v>-114.4397208624001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2601015231955753</v>
+        <v>0.2734953683952988</v>
       </c>
       <c r="T85">
-        <v>4.949226863639153</v>
+        <v>5.258553542616601</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>-0.03162289891713469</v>
+        <v>-0.03124643583478785</v>
       </c>
       <c r="W85">
-        <v>0.2432566795646604</v>
+        <v>0.243167909569843</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8290,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>-0.122569375647809</v>
+        <v>-0.1211102164139064</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8298,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2480203029819159</v>
+        <v>0.2499203029819159</v>
       </c>
       <c r="C86">
-        <v>-484.0362968098734</v>
+        <v>-506.3372995231805</v>
       </c>
       <c r="D86">
-        <v>376.7477031901266</v>
+        <v>373.9977004768195</v>
       </c>
       <c r="E86">
-        <v>228.884</v>
+        <v>248.4349999999999</v>
       </c>
       <c r="F86">
-        <v>1642.284</v>
+        <v>1661.835</v>
       </c>
       <c r="G86">
         <v>781.5</v>
@@ -8334,37 +8345,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M86">
-        <v>387.2505672</v>
+        <v>391.860693</v>
       </c>
       <c r="N86">
-        <v>-434.1505672000001</v>
+        <v>-438.7606930000001</v>
       </c>
       <c r="O86">
-        <v>-112.0108463376</v>
+        <v>-113.200258794</v>
       </c>
       <c r="P86">
-        <v>-322.1397208624001</v>
+        <v>-325.560434206</v>
       </c>
       <c r="Q86">
-        <v>-114.4397208624001</v>
+        <v>-117.860434206</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2734953683952986</v>
+        <v>0.2886750596216519</v>
       </c>
       <c r="T86">
-        <v>5.258553542616597</v>
+        <v>5.609123778791036</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>-0.03124643583478785</v>
+        <v>-0.03087883070731976</v>
       </c>
       <c r="W86">
-        <v>0.243167909569843</v>
+        <v>0.243081228280786</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8372,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>-0.1211102164139064</v>
+        <v>-0.1196853903384487</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8380,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2499203029819159</v>
+        <v>0.2518203029819159</v>
       </c>
       <c r="C87">
-        <v>-506.3372995231805</v>
+        <v>-528.5984468444492</v>
       </c>
       <c r="D87">
-        <v>373.9977004768195</v>
+        <v>371.287553155551</v>
       </c>
       <c r="E87">
-        <v>248.4349999999999</v>
+        <v>267.9860000000001</v>
       </c>
       <c r="F87">
-        <v>1661.835</v>
+        <v>1681.386</v>
       </c>
       <c r="G87">
         <v>781.5</v>
@@ -8416,37 +8427,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M87">
-        <v>391.860693</v>
+        <v>396.4708188000001</v>
       </c>
       <c r="N87">
-        <v>-438.7606930000001</v>
+        <v>-443.3708188000001</v>
       </c>
       <c r="O87">
-        <v>-113.200258794</v>
+        <v>-114.3896712504</v>
       </c>
       <c r="P87">
-        <v>-325.560434206</v>
+        <v>-328.9811475496001</v>
       </c>
       <c r="Q87">
-        <v>-117.860434206</v>
+        <v>-121.2811475496001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2886750596216519</v>
+        <v>0.3060232781660556</v>
       </c>
       <c r="T87">
-        <v>5.609123778791036</v>
+        <v>6.009775477276111</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>-0.03087883070731976</v>
+        <v>-0.03051977453630441</v>
       </c>
       <c r="W87">
-        <v>0.243081228280786</v>
+        <v>0.2429965628356606</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8454,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>-0.1196853903384487</v>
+        <v>-0.1182936997531179</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8462,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2518203029819159</v>
+        <v>0.2537203029819159</v>
       </c>
       <c r="C88">
-        <v>-528.5984468444492</v>
+        <v>-550.8205989680021</v>
       </c>
       <c r="D88">
-        <v>371.287553155551</v>
+        <v>368.616401031998</v>
       </c>
       <c r="E88">
-        <v>267.9860000000001</v>
+        <v>287.537</v>
       </c>
       <c r="F88">
-        <v>1681.386</v>
+        <v>1700.937</v>
       </c>
       <c r="G88">
         <v>781.5</v>
@@ -8498,37 +8509,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M88">
-        <v>396.4708188000001</v>
+        <v>401.0809446000001</v>
       </c>
       <c r="N88">
-        <v>-443.3708188000001</v>
+        <v>-447.9809446</v>
       </c>
       <c r="O88">
-        <v>-114.3896712504</v>
+        <v>-115.5790837068</v>
       </c>
       <c r="P88">
-        <v>-328.9811475496001</v>
+        <v>-332.4018608932</v>
       </c>
       <c r="Q88">
-        <v>-121.2811475496001</v>
+        <v>-124.7018608932</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3060232781660556</v>
+        <v>0.3260404534095983</v>
       </c>
       <c r="T88">
-        <v>6.009775477276111</v>
+        <v>6.472065898605042</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>-0.03051977453630441</v>
+        <v>-0.03016897253013999</v>
       </c>
       <c r="W88">
-        <v>0.2429965628356606</v>
+        <v>0.242913843722607</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8536,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>-0.1182936997531179</v>
+        <v>-0.1169340020548062</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8544,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2537203029819159</v>
+        <v>0.2556203029819159</v>
       </c>
       <c r="C89">
-        <v>-550.8205989680021</v>
+        <v>-573.0045915110109</v>
       </c>
       <c r="D89">
-        <v>368.616401031998</v>
+        <v>365.9834084889893</v>
       </c>
       <c r="E89">
-        <v>287.537</v>
+        <v>307.088</v>
       </c>
       <c r="F89">
-        <v>1700.937</v>
+        <v>1720.488</v>
       </c>
       <c r="G89">
         <v>781.5</v>
@@ -8580,37 +8591,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M89">
-        <v>401.0809446000001</v>
+        <v>405.6910704000001</v>
       </c>
       <c r="N89">
-        <v>-447.9809446</v>
+        <v>-452.5910704</v>
       </c>
       <c r="O89">
-        <v>-115.5790837068</v>
+        <v>-116.7684961632</v>
       </c>
       <c r="P89">
-        <v>-332.4018608932</v>
+        <v>-335.8225742368001</v>
       </c>
       <c r="Q89">
-        <v>-124.7018608932</v>
+        <v>-128.1225742368001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3260404534095983</v>
+        <v>0.3493938245270649</v>
       </c>
       <c r="T89">
-        <v>6.472065898605042</v>
+        <v>7.011404723488798</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>-0.03016897253013999</v>
+        <v>-0.02982614329684295</v>
       </c>
       <c r="W89">
-        <v>0.242913843722607</v>
+        <v>0.2428330045893956</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8618,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>-0.1169340020548062</v>
+        <v>-0.1156052065769106</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8626,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2556203029819159</v>
+        <v>0.2575203029819159</v>
       </c>
       <c r="C90">
-        <v>-573.0045915110109</v>
+        <v>-595.151236385032</v>
       </c>
       <c r="D90">
-        <v>365.9834084889893</v>
+        <v>363.3877636149681</v>
       </c>
       <c r="E90">
-        <v>307.088</v>
+        <v>326.6390000000001</v>
       </c>
       <c r="F90">
-        <v>1720.488</v>
+        <v>1740.039</v>
       </c>
       <c r="G90">
         <v>781.5</v>
@@ -8662,37 +8673,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M90">
-        <v>405.6910704000001</v>
+        <v>410.3011962</v>
       </c>
       <c r="N90">
-        <v>-452.5910704</v>
+        <v>-457.2011962</v>
       </c>
       <c r="O90">
-        <v>-116.7684961632</v>
+        <v>-117.9579086196</v>
       </c>
       <c r="P90">
-        <v>-335.8225742368001</v>
+        <v>-339.2432875804</v>
       </c>
       <c r="Q90">
-        <v>-128.1225742368001</v>
+        <v>-131.5432875804</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3493938245270649</v>
+        <v>0.3769932631204345</v>
       </c>
       <c r="T90">
-        <v>7.011404723488798</v>
+        <v>7.64880515289687</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>-0.02982614329684295</v>
+        <v>-0.02949101809126044</v>
       </c>
       <c r="W90">
-        <v>0.2428330045893956</v>
+        <v>0.2427539820659192</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8700,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>-0.1156052065769106</v>
+        <v>-0.1143062716715519</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8708,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2575203029819159</v>
+        <v>0.2594203029819159</v>
       </c>
       <c r="C91">
-        <v>-595.151236385032</v>
+        <v>-617.2613226307178</v>
       </c>
       <c r="D91">
-        <v>363.3877636149681</v>
+        <v>360.8286773692823</v>
       </c>
       <c r="E91">
-        <v>326.6390000000001</v>
+        <v>346.1900000000001</v>
       </c>
       <c r="F91">
-        <v>1740.039</v>
+        <v>1759.59</v>
       </c>
       <c r="G91">
         <v>781.5</v>
@@ -8744,37 +8755,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M91">
-        <v>410.3011962</v>
+        <v>414.911322</v>
       </c>
       <c r="N91">
-        <v>-457.2011962</v>
+        <v>-461.811322</v>
       </c>
       <c r="O91">
-        <v>-117.9579086196</v>
+        <v>-119.147321076</v>
       </c>
       <c r="P91">
-        <v>-339.2432875804</v>
+        <v>-342.664000924</v>
       </c>
       <c r="Q91">
-        <v>-131.5432875804</v>
+        <v>-134.964000924</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3769932631204345</v>
+        <v>0.4101125894324779</v>
       </c>
       <c r="T91">
-        <v>7.64880515289687</v>
+        <v>8.413685668186558</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>-0.02949101809126044</v>
+        <v>-0.02916334011246866</v>
       </c>
       <c r="W91">
-        <v>0.2427539820659192</v>
+        <v>0.2426767155985201</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8782,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>-0.1143062716715519</v>
+        <v>-0.1130362019863125</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8790,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2594203029819159</v>
+        <v>0.2613203029819159</v>
       </c>
       <c r="C92">
-        <v>-617.2613226307178</v>
+        <v>-639.3356172175036</v>
       </c>
       <c r="D92">
-        <v>360.8286773692823</v>
+        <v>358.3053827824964</v>
       </c>
       <c r="E92">
-        <v>346.1900000000001</v>
+        <v>365.741</v>
       </c>
       <c r="F92">
-        <v>1759.59</v>
+        <v>1779.141</v>
       </c>
       <c r="G92">
         <v>781.5</v>
@@ -8826,37 +8837,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M92">
-        <v>414.911322</v>
+        <v>419.5214478</v>
       </c>
       <c r="N92">
-        <v>-461.811322</v>
+        <v>-466.4214478</v>
       </c>
       <c r="O92">
-        <v>-119.147321076</v>
+        <v>-120.3367335324</v>
       </c>
       <c r="P92">
-        <v>-342.664000924</v>
+        <v>-346.0847142676</v>
       </c>
       <c r="Q92">
-        <v>-134.964000924</v>
+        <v>-138.3847142676</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4101125894324779</v>
+        <v>0.4505917660360866</v>
       </c>
       <c r="T92">
-        <v>8.413685668186558</v>
+        <v>9.348539631318397</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>-0.02916334011246866</v>
+        <v>-0.02884286384749648</v>
       </c>
       <c r="W92">
-        <v>0.2426767155985201</v>
+        <v>0.2426011472952397</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8864,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>-0.1130362019863125</v>
+        <v>-0.1117940459205289</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8872,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2613203029819159</v>
+        <v>0.2632203029819159</v>
       </c>
       <c r="C93">
-        <v>-639.3356172175036</v>
+        <v>-661.3748658099751</v>
       </c>
       <c r="D93">
-        <v>358.3053827824964</v>
+        <v>355.8171341900252</v>
       </c>
       <c r="E93">
-        <v>365.741</v>
+        <v>385.2920000000001</v>
       </c>
       <c r="F93">
-        <v>1779.141</v>
+        <v>1798.692</v>
       </c>
       <c r="G93">
         <v>781.5</v>
@@ -8908,37 +8919,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M93">
-        <v>419.5214478</v>
+        <v>424.1315736000001</v>
       </c>
       <c r="N93">
-        <v>-466.4214478</v>
+        <v>-471.0315736000001</v>
       </c>
       <c r="O93">
-        <v>-120.3367335324</v>
+        <v>-121.5261459888</v>
       </c>
       <c r="P93">
-        <v>-346.0847142676</v>
+        <v>-349.5054276112</v>
       </c>
       <c r="Q93">
-        <v>-138.3847142676</v>
+        <v>-141.8054276112001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4505917660360866</v>
+        <v>0.5011907367905974</v>
       </c>
       <c r="T93">
-        <v>9.348539631318397</v>
+        <v>10.5171070852332</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>-0.02884286384749648</v>
+        <v>-0.02852935445784978</v>
       </c>
       <c r="W93">
-        <v>0.2426011472952397</v>
+        <v>0.242527221781161</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8946,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>-0.1117940459205289</v>
+        <v>-0.1105788932474798</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8954,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2632203029819159</v>
+        <v>0.2651203029819159</v>
       </c>
       <c r="C94">
-        <v>-661.3748658099751</v>
+        <v>-683.3797935025216</v>
       </c>
       <c r="D94">
-        <v>355.8171341900252</v>
+        <v>353.3632064974786</v>
       </c>
       <c r="E94">
-        <v>385.2920000000001</v>
+        <v>404.8430000000001</v>
       </c>
       <c r="F94">
-        <v>1798.692</v>
+        <v>1818.243</v>
       </c>
       <c r="G94">
         <v>781.5</v>
@@ -8990,37 +9001,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M94">
-        <v>424.1315736000001</v>
+        <v>428.7416994000001</v>
       </c>
       <c r="N94">
-        <v>-471.0315736000001</v>
+        <v>-475.6416994000001</v>
       </c>
       <c r="O94">
-        <v>-121.5261459888</v>
+        <v>-122.7155584452</v>
       </c>
       <c r="P94">
-        <v>-349.5054276112</v>
+        <v>-352.9261409548001</v>
       </c>
       <c r="Q94">
-        <v>-141.8054276112001</v>
+        <v>-145.2261409548001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5011907367905974</v>
+        <v>0.5662465563321115</v>
       </c>
       <c r="T94">
-        <v>10.5171070852332</v>
+        <v>12.01955095455223</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>-0.02852935445784978</v>
+        <v>-0.02822258720561483</v>
       </c>
       <c r="W94">
-        <v>0.242527221781161</v>
+        <v>0.242454886063084</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9028,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>-0.1105788932474798</v>
+        <v>-0.10938987288998</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9036,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2651203029819159</v>
+        <v>0.2670203029819159</v>
       </c>
       <c r="C95">
-        <v>-683.3797935025216</v>
+        <v>-705.3511055238018</v>
       </c>
       <c r="D95">
-        <v>353.3632064974786</v>
+        <v>350.9428944761984</v>
       </c>
       <c r="E95">
-        <v>404.8430000000001</v>
+        <v>424.3940000000002</v>
       </c>
       <c r="F95">
-        <v>1818.243</v>
+        <v>1837.794</v>
       </c>
       <c r="G95">
         <v>781.5</v>
@@ -9072,37 +9083,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M95">
-        <v>428.7416994000001</v>
+        <v>433.3518252000001</v>
       </c>
       <c r="N95">
-        <v>-475.6416994000001</v>
+        <v>-480.2518252000001</v>
       </c>
       <c r="O95">
-        <v>-122.7155584452</v>
+        <v>-123.9049709016</v>
       </c>
       <c r="P95">
-        <v>-352.9261409548001</v>
+        <v>-356.3468542984001</v>
       </c>
       <c r="Q95">
-        <v>-145.2261409548001</v>
+        <v>-148.6468542984001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5662465563321115</v>
+        <v>0.6529876490541302</v>
       </c>
       <c r="T95">
-        <v>12.01955095455223</v>
+        <v>14.02280944697761</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>-0.02822258720561483</v>
+        <v>-0.02792234691619339</v>
       </c>
       <c r="W95">
-        <v>0.242454886063084</v>
+        <v>0.2423840894028384</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9110,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>-0.10938987288998</v>
+        <v>-0.1082261508379587</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9118,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2670203029819159</v>
+        <v>0.2689203029819159</v>
       </c>
       <c r="C96">
-        <v>-705.3511055238018</v>
+        <v>-727.2894879124519</v>
       </c>
       <c r="D96">
-        <v>350.9428944761984</v>
+        <v>348.5555120875484</v>
       </c>
       <c r="E96">
-        <v>424.3940000000002</v>
+        <v>443.9450000000002</v>
       </c>
       <c r="F96">
-        <v>1837.794</v>
+        <v>1857.345</v>
       </c>
       <c r="G96">
         <v>781.5</v>
@@ -9154,37 +9165,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M96">
-        <v>433.3518252000001</v>
+        <v>437.9619510000001</v>
       </c>
       <c r="N96">
-        <v>-480.2518252000001</v>
+        <v>-484.8619510000001</v>
       </c>
       <c r="O96">
-        <v>-123.9049709016</v>
+        <v>-125.094383358</v>
       </c>
       <c r="P96">
-        <v>-356.3468542984001</v>
+        <v>-359.7675676420001</v>
       </c>
       <c r="Q96">
-        <v>-148.6468542984001</v>
+        <v>-152.0675676420001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6529876490541302</v>
+        <v>0.7744251788649565</v>
       </c>
       <c r="T96">
-        <v>14.02280944697761</v>
+        <v>16.82737133637313</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>-0.02792234691619339</v>
+        <v>-0.02762842747497031</v>
       </c>
       <c r="W96">
-        <v>0.2423840894028384</v>
+        <v>0.242314783198598</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9192,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>-0.1082261508379587</v>
+        <v>-0.1070869281975595</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9200,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2689203029819159</v>
+        <v>0.270820302981916</v>
       </c>
       <c r="C97">
-        <v>-727.2894879124519</v>
+        <v>-749.1956081654016</v>
       </c>
       <c r="D97">
-        <v>348.5555120875484</v>
+        <v>346.2003918345987</v>
       </c>
       <c r="E97">
-        <v>443.9450000000002</v>
+        <v>463.4960000000001</v>
       </c>
       <c r="F97">
-        <v>1857.345</v>
+        <v>1876.896</v>
       </c>
       <c r="G97">
         <v>781.5</v>
@@ -9236,37 +9247,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M97">
-        <v>437.9619510000001</v>
+        <v>442.5720768</v>
       </c>
       <c r="N97">
-        <v>-484.8619510000001</v>
+        <v>-489.4720768000001</v>
       </c>
       <c r="O97">
-        <v>-125.094383358</v>
+        <v>-126.2837958144</v>
       </c>
       <c r="P97">
-        <v>-359.7675676420001</v>
+        <v>-363.1882809856</v>
       </c>
       <c r="Q97">
-        <v>-152.0675676420001</v>
+        <v>-155.4882809856001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7744251788649565</v>
+        <v>0.9565814735811964</v>
       </c>
       <c r="T97">
-        <v>16.82737133637313</v>
+        <v>21.03421417046643</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>-0.02762842747497031</v>
+        <v>-0.02734063135543937</v>
       </c>
       <c r="W97">
-        <v>0.242314783198598</v>
+        <v>0.2422469208736126</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9274,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>-0.1070869281975595</v>
+        <v>-0.1059714393621682</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9282,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2708203029819159</v>
+        <v>0.2727203029819159</v>
       </c>
       <c r="C98">
-        <v>-749.1956081654012</v>
+        <v>-771.070115860083</v>
       </c>
       <c r="D98">
-        <v>346.2003918345988</v>
+        <v>343.8768841399171</v>
       </c>
       <c r="E98">
-        <v>463.4959999999999</v>
+        <v>483.047</v>
       </c>
       <c r="F98">
-        <v>1876.896</v>
+        <v>1896.447</v>
       </c>
       <c r="G98">
         <v>781.5</v>
@@ -9318,37 +9329,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M98">
-        <v>442.5720768</v>
+        <v>447.1822026</v>
       </c>
       <c r="N98">
-        <v>-489.4720768</v>
+        <v>-494.0822026000001</v>
       </c>
       <c r="O98">
-        <v>-126.2837958144</v>
+        <v>-127.4732082708</v>
       </c>
       <c r="P98">
-        <v>-363.1882809856</v>
+        <v>-366.6089943292001</v>
       </c>
       <c r="Q98">
-        <v>-155.4882809856</v>
+        <v>-158.9089943292001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9565814735811937</v>
+        <v>1.260175298108259</v>
       </c>
       <c r="T98">
-        <v>21.03421417046637</v>
+        <v>28.04561889395517</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>-0.02734063135543937</v>
+        <v>-0.02705876917651731</v>
       </c>
       <c r="W98">
-        <v>0.2422469208736126</v>
+        <v>0.2421804577718228</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9356,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>-0.105971439362168</v>
+        <v>-0.1048789502965788</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9364,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2727203029819159</v>
+        <v>0.2746203029819159</v>
       </c>
       <c r="C99">
-        <v>-771.070115860083</v>
+        <v>-792.9136432517521</v>
       </c>
       <c r="D99">
-        <v>343.8768841399171</v>
+        <v>341.5843567482479</v>
       </c>
       <c r="E99">
-        <v>483.047</v>
+        <v>502.598</v>
       </c>
       <c r="F99">
-        <v>1896.447</v>
+        <v>1915.998</v>
       </c>
       <c r="G99">
         <v>781.5</v>
@@ -9400,37 +9411,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M99">
-        <v>447.1822026</v>
+        <v>451.7923284</v>
       </c>
       <c r="N99">
-        <v>-494.0822026000001</v>
+        <v>-498.6923284000001</v>
       </c>
       <c r="O99">
-        <v>-127.4732082708</v>
+        <v>-128.6626207272</v>
       </c>
       <c r="P99">
-        <v>-366.6089943292001</v>
+        <v>-370.0297076728</v>
       </c>
       <c r="Q99">
-        <v>-158.9089943292001</v>
+        <v>-162.3297076728001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.260175298108259</v>
+        <v>1.867362947162388</v>
       </c>
       <c r="T99">
-        <v>28.04561889395517</v>
+        <v>42.06842834093275</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>-0.02705876917651731</v>
+        <v>-0.02678265928696102</v>
       </c>
       <c r="W99">
-        <v>0.2421804577718228</v>
+        <v>0.2421153510598655</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9438,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>-0.1048789502965788</v>
+        <v>-0.1038087569262056</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9446,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2746203029819159</v>
+        <v>0.2765203029819159</v>
       </c>
       <c r="C100">
-        <v>-792.9136432517521</v>
+        <v>-814.7268058470734</v>
       </c>
       <c r="D100">
-        <v>341.5843567482479</v>
+        <v>339.3221941529267</v>
       </c>
       <c r="E100">
-        <v>502.598</v>
+        <v>522.1490000000001</v>
       </c>
       <c r="F100">
-        <v>1915.998</v>
+        <v>1935.549</v>
       </c>
       <c r="G100">
         <v>781.5</v>
@@ -9482,37 +9493,37 @@
         <v>-46.90000000000001</v>
       </c>
       <c r="M100">
-        <v>451.7923284</v>
+        <v>456.4024542000001</v>
       </c>
       <c r="N100">
-        <v>-498.6923284000001</v>
+        <v>-503.3024542000001</v>
       </c>
       <c r="O100">
-        <v>-128.6626207272</v>
+        <v>-129.8520331836</v>
       </c>
       <c r="P100">
-        <v>-370.0297076728</v>
+        <v>-373.4504210164</v>
       </c>
       <c r="Q100">
-        <v>-162.3297076728001</v>
+        <v>-165.7504210164</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.867362947162388</v>
+        <v>3.688925894324775</v>
       </c>
       <c r="T100">
-        <v>42.06842834093275</v>
+        <v>84.13685668186548</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>-0.02678265928696102</v>
+        <v>-0.02651212737497151</v>
       </c>
       <c r="W100">
-        <v>0.2421153510598655</v>
+        <v>0.2420515596350183</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9520,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>-0.1038087569262056</v>
+        <v>-0.1027601836239205</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2765203029819159</v>
-      </c>
-      <c r="C101">
-        <v>-814.7268058470734</v>
-      </c>
-      <c r="D101">
-        <v>339.3221941529267</v>
-      </c>
-      <c r="E101">
-        <v>522.1490000000001</v>
-      </c>
-      <c r="F101">
-        <v>1935.549</v>
-      </c>
-      <c r="G101">
-        <v>781.5</v>
-      </c>
-      <c r="H101">
-        <v>541.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>160.8</v>
-      </c>
-      <c r="K101">
-        <v>207.7</v>
-      </c>
-      <c r="L101">
-        <v>-46.90000000000001</v>
-      </c>
-      <c r="M101">
-        <v>456.4024542000001</v>
-      </c>
-      <c r="N101">
-        <v>-503.3024542000001</v>
-      </c>
-      <c r="O101">
-        <v>-129.8520331836</v>
-      </c>
-      <c r="P101">
-        <v>-373.4504210164</v>
-      </c>
-      <c r="Q101">
-        <v>-165.7504210164</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.688925894324775</v>
-      </c>
-      <c r="T101">
-        <v>84.13685668186548</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>-0.02651212737497151</v>
-      </c>
-      <c r="W101">
-        <v>0.2420515596350183</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>-0.1027601836239205</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
